--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,10 +107,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -488,11 +488,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,6 +508,16 @@
           <t>Iestyn O'Leary</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Jason Lye-Phillips</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>WIL WILLIAMS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -518,6 +530,8 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -525,11 +539,13 @@
           <t>Tue 04 Aug 2026</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -537,7 +553,9 @@
           <t>Wed 05 Aug 2026</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -545,7 +563,9 @@
           <t>Thu 06 Aug 2026</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -558,6 +578,8 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -566,6 +588,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -574,6 +598,8 @@
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -581,7 +607,9 @@
           <t>Mon 10 Aug 2026</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -589,7 +617,9 @@
           <t>Tue 11 Aug 2026</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -597,7 +627,9 @@
           <t>Wed 12 Aug 2026</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -605,7 +637,9 @@
           <t>Thu 13 Aug 2026</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -618,6 +652,8 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -626,6 +662,8 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -634,6 +672,8 @@
         </is>
       </c>
       <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -641,7 +681,9 @@
           <t>Mon 17 Aug 2026</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -649,7 +691,9 @@
           <t>Tue 18 Aug 2026</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -657,7 +701,9 @@
           <t>Wed 19 Aug 2026</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -665,7 +711,9 @@
           <t>Thu 20 Aug 2026</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -673,7 +721,9 @@
           <t>Fri 21 Aug 2026</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -682,6 +732,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -690,6 +742,8 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -697,7 +751,17 @@
           <t>Mon 24 Aug 2026</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -705,7 +769,17 @@
           <t>Tue 25 Aug 2026</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -713,9 +787,15 @@
           <t>Wed 26 Aug 2026</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Full team meeting</t>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Edit Annibynwyr</t>
         </is>
       </c>
     </row>
@@ -725,9 +805,15 @@
           <t>Thu 27 Aug 2026</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Online Edit - Anifail Perffaith</t>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Edit Annibynwyr</t>
         </is>
       </c>
     </row>
@@ -737,7 +823,17 @@
           <t>Fri 28 Aug 2026</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -746,6 +842,12 @@
         </is>
       </c>
       <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -754,6 +856,12 @@
         </is>
       </c>
       <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -761,7 +869,9 @@
           <t>Mon 31 Aug 2026</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -769,7 +879,9 @@
           <t>Tue 01 Sep 2026</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -777,7 +889,9 @@
           <t>Wed 02 Sep 2026</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -785,7 +899,9 @@
           <t>Thu 03 Sep 2026</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -793,7 +909,9 @@
           <t>Fri 04 Sep 2026</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -802,6 +920,8 @@
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -810,6 +930,8 @@
         </is>
       </c>
       <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -817,7 +939,9 @@
           <t>Mon 07 Sep 2026</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -825,7 +949,9 @@
           <t>Tue 08 Sep 2026</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -833,7 +959,9 @@
           <t>Wed 09 Sep 2026</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -841,7 +969,9 @@
           <t>Thu 10 Sep 2026</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -849,7 +979,9 @@
           <t>Fri 11 Sep 2026</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -858,6 +990,8 @@
         </is>
       </c>
       <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -866,6 +1000,8 @@
         </is>
       </c>
       <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -878,6 +1014,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -890,6 +1028,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -902,6 +1042,8 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -909,7 +1051,9 @@
           <t>Thu 17 Sep 2026</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -917,7 +1061,9 @@
           <t>Fri 18 Sep 2026</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -926,6 +1072,8 @@
         </is>
       </c>
       <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -934,6 +1082,8 @@
         </is>
       </c>
       <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -941,7 +1091,9 @@
           <t>Mon 21 Sep 2026</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -949,7 +1101,9 @@
           <t>Tue 22 Sep 2026</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -957,7 +1111,9 @@
           <t>Wed 23 Sep 2026</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -965,7 +1121,9 @@
           <t>Thu 24 Sep 2026</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -978,6 +1136,8 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -986,6 +1146,8 @@
         </is>
       </c>
       <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -994,6 +1156,8 @@
         </is>
       </c>
       <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1001,7 +1165,9 @@
           <t>Mon 28 Sep 2026</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1009,7 +1175,9 @@
           <t>Tue 29 Sep 2026</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1017,7 +1185,9 @@
           <t>Wed 30 Sep 2026</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1025,7 +1195,9 @@
           <t>Thu 01 Oct 2026</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1033,7 +1205,9 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1042,6 +1216,8 @@
         </is>
       </c>
       <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1050,6 +1226,8 @@
         </is>
       </c>
       <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1057,7 +1235,9 @@
           <t>Mon 05 Oct 2026</t>
         </is>
       </c>
-      <c r="B65" s="6" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1065,7 +1245,9 @@
           <t>Tue 06 Oct 2026</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1078,6 +1260,8 @@
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1085,7 +1269,9 @@
           <t>Thu 08 Oct 2026</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n"/>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1093,7 +1279,9 @@
           <t>Fri 09 Oct 2026</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n"/>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1102,6 +1290,8 @@
         </is>
       </c>
       <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1110,6 +1300,8 @@
         </is>
       </c>
       <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1117,7 +1309,9 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1125,7 +1319,9 @@
           <t>Tue 13 Oct 2026</t>
         </is>
       </c>
-      <c r="B73" s="6" t="n"/>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1133,7 +1329,9 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1141,7 +1339,9 @@
           <t>Thu 15 Oct 2026</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n"/>
+      <c r="B75" s="5" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1149,7 +1349,9 @@
           <t>Fri 16 Oct 2026</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
+      <c r="B76" s="5" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -1158,6 +1360,8 @@
         </is>
       </c>
       <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -1166,6 +1370,8 @@
         </is>
       </c>
       <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1173,7 +1379,9 @@
           <t>Mon 19 Oct 2026</t>
         </is>
       </c>
-      <c r="B79" s="6" t="n"/>
+      <c r="B79" s="5" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -1181,7 +1389,9 @@
           <t>Tue 20 Oct 2026</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n"/>
+      <c r="B80" s="5" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1189,7 +1399,9 @@
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="B81" s="6" t="n"/>
+      <c r="B81" s="5" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -1197,7 +1409,9 @@
           <t>Thu 22 Oct 2026</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n"/>
+      <c r="B82" s="5" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1205,7 +1419,9 @@
           <t>Fri 23 Oct 2026</t>
         </is>
       </c>
-      <c r="B83" s="6" t="n"/>
+      <c r="B83" s="5" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -1214,6 +1430,8 @@
         </is>
       </c>
       <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -1222,6 +1440,8 @@
         </is>
       </c>
       <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -1229,7 +1449,9 @@
           <t>Mon 26 Oct 2026</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1237,7 +1459,9 @@
           <t>Tue 27 Oct 2026</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -1245,7 +1469,9 @@
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="B88" s="6" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1253,7 +1479,9 @@
           <t>Thu 29 Oct 2026</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
+      <c r="B89" s="5" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -1261,7 +1489,9 @@
           <t>Fri 30 Oct 2026</t>
         </is>
       </c>
-      <c r="B90" s="6" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -1270,6 +1500,8 @@
         </is>
       </c>
       <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -1278,6 +1510,8 @@
         </is>
       </c>
       <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1285,7 +1519,9 @@
           <t>Mon 02 Nov 2026</t>
         </is>
       </c>
-      <c r="B93" s="6" t="n"/>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -1293,7 +1529,9 @@
           <t>Tue 03 Nov 2026</t>
         </is>
       </c>
-      <c r="B94" s="6" t="n"/>
+      <c r="B94" s="5" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1301,7 +1539,9 @@
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="B95" s="6" t="n"/>
+      <c r="B95" s="5" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -1309,7 +1549,9 @@
           <t>Thu 05 Nov 2026</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n"/>
+      <c r="B96" s="5" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1317,7 +1559,9 @@
           <t>Fri 06 Nov 2026</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
+      <c r="B97" s="5" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -1326,6 +1570,8 @@
         </is>
       </c>
       <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -1334,6 +1580,8 @@
         </is>
       </c>
       <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -1341,7 +1589,9 @@
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n"/>
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1349,7 +1599,9 @@
           <t>Tue 10 Nov 2026</t>
         </is>
       </c>
-      <c r="B101" s="6" t="n"/>
+      <c r="B101" s="5" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -1357,7 +1609,9 @@
           <t>Wed 11 Nov 2026</t>
         </is>
       </c>
-      <c r="B102" s="6" t="n"/>
+      <c r="B102" s="5" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -1365,7 +1619,9 @@
           <t>Thu 12 Nov 2026</t>
         </is>
       </c>
-      <c r="B103" s="6" t="n"/>
+      <c r="B103" s="5" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -1373,7 +1629,9 @@
           <t>Fri 13 Nov 2026</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n"/>
+      <c r="B104" s="5" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -1382,6 +1640,8 @@
         </is>
       </c>
       <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -1390,6 +1650,8 @@
         </is>
       </c>
       <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -1397,7 +1659,9 @@
           <t>Mon 16 Nov 2026</t>
         </is>
       </c>
-      <c r="B107" s="6" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -1405,7 +1669,9 @@
           <t>Tue 17 Nov 2026</t>
         </is>
       </c>
-      <c r="B108" s="6" t="n"/>
+      <c r="B108" s="5" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -1413,7 +1679,9 @@
           <t>Wed 18 Nov 2026</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -1421,7 +1689,9 @@
           <t>Thu 19 Nov 2026</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -1434,6 +1704,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -1442,6 +1714,8 @@
         </is>
       </c>
       <c r="B112" s="8" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -1450,6 +1724,8 @@
         </is>
       </c>
       <c r="B113" s="8" t="n"/>
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -1457,7 +1733,9 @@
           <t>Mon 23 Nov 2026</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -1465,7 +1743,9 @@
           <t>Tue 24 Nov 2026</t>
         </is>
       </c>
-      <c r="B115" s="6" t="n"/>
+      <c r="B115" s="5" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -1473,7 +1753,9 @@
           <t>Wed 25 Nov 2026</t>
         </is>
       </c>
-      <c r="B116" s="6" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -1481,7 +1763,9 @@
           <t>Thu 26 Nov 2026</t>
         </is>
       </c>
-      <c r="B117" s="6" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -1494,6 +1778,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -1502,6 +1788,8 @@
         </is>
       </c>
       <c r="B119" s="8" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -1510,6 +1798,8 @@
         </is>
       </c>
       <c r="B120" s="8" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -1517,7 +1807,9 @@
           <t>Mon 30 Nov 2026</t>
         </is>
       </c>
-      <c r="B121" s="6" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -1525,7 +1817,9 @@
           <t>Tue 01 Dec 2026</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n"/>
+      <c r="B122" s="5" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -1533,7 +1827,9 @@
           <t>Wed 02 Dec 2026</t>
         </is>
       </c>
-      <c r="B123" s="6" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -1541,7 +1837,9 @@
           <t>Thu 03 Dec 2026</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -1549,7 +1847,9 @@
           <t>Fri 04 Dec 2026</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n"/>
+      <c r="B125" s="5" t="n"/>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -1558,6 +1858,8 @@
         </is>
       </c>
       <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -1566,6 +1868,8 @@
         </is>
       </c>
       <c r="B127" s="8" t="n"/>
+      <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -1573,7 +1877,9 @@
           <t>Mon 07 Dec 2026</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n"/>
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -1581,7 +1887,9 @@
           <t>Tue 08 Dec 2026</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
+      <c r="B129" s="5" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -1589,7 +1897,9 @@
           <t>Wed 09 Dec 2026</t>
         </is>
       </c>
-      <c r="B130" s="6" t="n"/>
+      <c r="B130" s="5" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -1597,7 +1907,9 @@
           <t>Thu 10 Dec 2026</t>
         </is>
       </c>
-      <c r="B131" s="6" t="n"/>
+      <c r="B131" s="5" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -1605,7 +1917,9 @@
           <t>Fri 11 Dec 2026</t>
         </is>
       </c>
-      <c r="B132" s="6" t="n"/>
+      <c r="B132" s="5" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -1614,6 +1928,8 @@
         </is>
       </c>
       <c r="B133" s="8" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -1622,6 +1938,8 @@
         </is>
       </c>
       <c r="B134" s="8" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -1629,7 +1947,9 @@
           <t>Mon 14 Dec 2026</t>
         </is>
       </c>
-      <c r="B135" s="6" t="n"/>
+      <c r="B135" s="5" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -1642,6 +1962,8 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -1654,6 +1976,8 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -1666,6 +1990,8 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -1678,6 +2004,8 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -1686,6 +2014,8 @@
         </is>
       </c>
       <c r="B140" s="8" t="n"/>
+      <c r="C140" s="8" t="n"/>
+      <c r="D140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -1694,6 +2024,8 @@
         </is>
       </c>
       <c r="B141" s="8" t="n"/>
+      <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -1701,7 +2033,9 @@
           <t>Mon 21 Dec 2026</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n"/>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -1709,7 +2043,9 @@
           <t>Tue 22 Dec 2026</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n"/>
+      <c r="B143" s="5" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -1717,7 +2053,9 @@
           <t>Wed 23 Dec 2026</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
+      <c r="B144" s="5" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -1725,7 +2063,9 @@
           <t>Thu 24 Dec 2026</t>
         </is>
       </c>
-      <c r="B145" s="6" t="n"/>
+      <c r="B145" s="5" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -1733,7 +2073,9 @@
           <t>Fri 25 Dec 2026</t>
         </is>
       </c>
-      <c r="B146" s="6" t="n"/>
+      <c r="B146" s="5" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -1742,6 +2084,8 @@
         </is>
       </c>
       <c r="B147" s="8" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -1750,6 +2094,8 @@
         </is>
       </c>
       <c r="B148" s="8" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -1757,7 +2103,9 @@
           <t>Mon 28 Dec 2026</t>
         </is>
       </c>
-      <c r="B149" s="6" t="n"/>
+      <c r="B149" s="5" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -1765,7 +2113,9 @@
           <t>Tue 29 Dec 2026</t>
         </is>
       </c>
-      <c r="B150" s="6" t="n"/>
+      <c r="B150" s="5" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -1773,7 +2123,9 @@
           <t>Wed 30 Dec 2026</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
+      <c r="B151" s="5" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -1781,7 +2133,9 @@
           <t>Thu 31 Dec 2026</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n"/>
+      <c r="B152" s="5" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -1789,7 +2143,9 @@
           <t>Fri 01 Jan 2027</t>
         </is>
       </c>
-      <c r="B153" s="6" t="n"/>
+      <c r="B153" s="5" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -1798,6 +2154,8 @@
         </is>
       </c>
       <c r="B154" s="8" t="n"/>
+      <c r="C154" s="8" t="n"/>
+      <c r="D154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -1806,6 +2164,8 @@
         </is>
       </c>
       <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -1813,7 +2173,9 @@
           <t>Mon 04 Jan 2027</t>
         </is>
       </c>
-      <c r="B156" s="6" t="n"/>
+      <c r="B156" s="5" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -1821,7 +2183,9 @@
           <t>Tue 05 Jan 2027</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n"/>
+      <c r="B157" s="5" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -1834,6 +2198,8 @@
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -1841,7 +2207,9 @@
           <t>Thu 07 Jan 2027</t>
         </is>
       </c>
-      <c r="B159" s="6" t="n"/>
+      <c r="B159" s="5" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -1849,7 +2217,9 @@
           <t>Fri 08 Jan 2027</t>
         </is>
       </c>
-      <c r="B160" s="6" t="n"/>
+      <c r="B160" s="5" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -1858,6 +2228,8 @@
         </is>
       </c>
       <c r="B161" s="8" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -1866,6 +2238,8 @@
         </is>
       </c>
       <c r="B162" s="8" t="n"/>
+      <c r="C162" s="8" t="n"/>
+      <c r="D162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -1873,7 +2247,9 @@
           <t>Mon 11 Jan 2027</t>
         </is>
       </c>
-      <c r="B163" s="6" t="n"/>
+      <c r="B163" s="5" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -1881,7 +2257,9 @@
           <t>Tue 12 Jan 2027</t>
         </is>
       </c>
-      <c r="B164" s="6" t="n"/>
+      <c r="B164" s="5" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -1889,7 +2267,9 @@
           <t>Wed 13 Jan 2027</t>
         </is>
       </c>
-      <c r="B165" s="6" t="n"/>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -1897,7 +2277,9 @@
           <t>Thu 14 Jan 2027</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
+      <c r="B166" s="5" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -1905,7 +2287,9 @@
           <t>Fri 15 Jan 2027</t>
         </is>
       </c>
-      <c r="B167" s="6" t="n"/>
+      <c r="B167" s="5" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -1914,6 +2298,8 @@
         </is>
       </c>
       <c r="B168" s="8" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -1922,6 +2308,8 @@
         </is>
       </c>
       <c r="B169" s="8" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -1929,7 +2317,9 @@
           <t>Mon 18 Jan 2027</t>
         </is>
       </c>
-      <c r="B170" s="6" t="n"/>
+      <c r="B170" s="5" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -1937,7 +2327,9 @@
           <t>Tue 19 Jan 2027</t>
         </is>
       </c>
-      <c r="B171" s="6" t="n"/>
+      <c r="B171" s="5" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -1945,7 +2337,9 @@
           <t>Wed 20 Jan 2027</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -1953,7 +2347,9 @@
           <t>Thu 21 Jan 2027</t>
         </is>
       </c>
-      <c r="B173" s="6" t="n"/>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -1961,7 +2357,9 @@
           <t>Fri 22 Jan 2027</t>
         </is>
       </c>
-      <c r="B174" s="6" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -1970,6 +2368,8 @@
         </is>
       </c>
       <c r="B175" s="8" t="n"/>
+      <c r="C175" s="8" t="n"/>
+      <c r="D175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -1978,6 +2378,8 @@
         </is>
       </c>
       <c r="B176" s="8" t="n"/>
+      <c r="C176" s="8" t="n"/>
+      <c r="D176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -1985,7 +2387,9 @@
           <t>Mon 25 Jan 2027</t>
         </is>
       </c>
-      <c r="B177" s="6" t="n"/>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -1993,7 +2397,9 @@
           <t>Tue 26 Jan 2027</t>
         </is>
       </c>
-      <c r="B178" s="6" t="n"/>
+      <c r="B178" s="5" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -2001,7 +2407,9 @@
           <t>Wed 27 Jan 2027</t>
         </is>
       </c>
-      <c r="B179" s="6" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -2009,7 +2417,9 @@
           <t>Thu 28 Jan 2027</t>
         </is>
       </c>
-      <c r="B180" s="6" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -2017,7 +2427,9 @@
           <t>Fri 29 Jan 2027</t>
         </is>
       </c>
-      <c r="B181" s="6" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -2026,6 +2438,8 @@
         </is>
       </c>
       <c r="B182" s="8" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -2034,6 +2448,8 @@
         </is>
       </c>
       <c r="B183" s="8" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -2041,7 +2457,9 @@
           <t>Mon 01 Feb 2027</t>
         </is>
       </c>
-      <c r="B184" s="6" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -2049,7 +2467,9 @@
           <t>Tue 02 Feb 2027</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
+      <c r="B185" s="5" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -2057,7 +2477,9 @@
           <t>Wed 03 Feb 2027</t>
         </is>
       </c>
-      <c r="B186" s="6" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -2065,7 +2487,9 @@
           <t>Thu 04 Feb 2027</t>
         </is>
       </c>
-      <c r="B187" s="6" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -2073,7 +2497,9 @@
           <t>Fri 05 Feb 2027</t>
         </is>
       </c>
-      <c r="B188" s="6" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -2082,6 +2508,8 @@
         </is>
       </c>
       <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -2090,6 +2518,8 @@
         </is>
       </c>
       <c r="B190" s="8" t="n"/>
+      <c r="C190" s="8" t="n"/>
+      <c r="D190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -2097,7 +2527,9 @@
           <t>Mon 08 Feb 2027</t>
         </is>
       </c>
-      <c r="B191" s="6" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -2105,7 +2537,9 @@
           <t>Tue 09 Feb 2027</t>
         </is>
       </c>
-      <c r="B192" s="6" t="n"/>
+      <c r="B192" s="5" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -2113,7 +2547,9 @@
           <t>Wed 10 Feb 2027</t>
         </is>
       </c>
-      <c r="B193" s="6" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -2121,7 +2557,9 @@
           <t>Thu 11 Feb 2027</t>
         </is>
       </c>
-      <c r="B194" s="6" t="n"/>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -2129,7 +2567,9 @@
           <t>Fri 12 Feb 2027</t>
         </is>
       </c>
-      <c r="B195" s="6" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -2138,6 +2578,8 @@
         </is>
       </c>
       <c r="B196" s="8" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -2146,6 +2588,8 @@
         </is>
       </c>
       <c r="B197" s="8" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -2153,7 +2597,9 @@
           <t>Mon 15 Feb 2027</t>
         </is>
       </c>
-      <c r="B198" s="6" t="n"/>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -2161,7 +2607,9 @@
           <t>Tue 16 Feb 2027</t>
         </is>
       </c>
-      <c r="B199" s="6" t="n"/>
+      <c r="B199" s="5" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -2169,7 +2617,9 @@
           <t>Wed 17 Feb 2027</t>
         </is>
       </c>
-      <c r="B200" s="6" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -2177,7 +2627,9 @@
           <t>Thu 18 Feb 2027</t>
         </is>
       </c>
-      <c r="B201" s="6" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -2185,7 +2637,9 @@
           <t>Fri 19 Feb 2027</t>
         </is>
       </c>
-      <c r="B202" s="6" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -2194,6 +2648,8 @@
         </is>
       </c>
       <c r="B203" s="8" t="n"/>
+      <c r="C203" s="8" t="n"/>
+      <c r="D203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -2202,6 +2658,8 @@
         </is>
       </c>
       <c r="B204" s="8" t="n"/>
+      <c r="C204" s="8" t="n"/>
+      <c r="D204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -2209,7 +2667,9 @@
           <t>Mon 22 Feb 2027</t>
         </is>
       </c>
-      <c r="B205" s="6" t="n"/>
+      <c r="B205" s="5" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -2217,7 +2677,9 @@
           <t>Tue 23 Feb 2027</t>
         </is>
       </c>
-      <c r="B206" s="6" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -2225,7 +2687,9 @@
           <t>Wed 24 Feb 2027</t>
         </is>
       </c>
-      <c r="B207" s="6" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -2233,7 +2697,9 @@
           <t>Thu 25 Feb 2027</t>
         </is>
       </c>
-      <c r="B208" s="6" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -2241,7 +2707,9 @@
           <t>Fri 26 Feb 2027</t>
         </is>
       </c>
-      <c r="B209" s="6" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -2250,6 +2718,8 @@
         </is>
       </c>
       <c r="B210" s="8" t="n"/>
+      <c r="C210" s="8" t="n"/>
+      <c r="D210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -2258,6 +2728,8 @@
         </is>
       </c>
       <c r="B211" s="8" t="n"/>
+      <c r="C211" s="8" t="n"/>
+      <c r="D211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -2265,7 +2737,9 @@
           <t>Mon 01 Mar 2027</t>
         </is>
       </c>
-      <c r="B212" s="6" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -2273,7 +2747,9 @@
           <t>Tue 02 Mar 2027</t>
         </is>
       </c>
-      <c r="B213" s="6" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -2281,7 +2757,9 @@
           <t>Wed 03 Mar 2027</t>
         </is>
       </c>
-      <c r="B214" s="6" t="n"/>
+      <c r="B214" s="5" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -2289,7 +2767,9 @@
           <t>Thu 04 Mar 2027</t>
         </is>
       </c>
-      <c r="B215" s="6" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -2297,7 +2777,9 @@
           <t>Fri 05 Mar 2027</t>
         </is>
       </c>
-      <c r="B216" s="6" t="n"/>
+      <c r="B216" s="5" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -2306,6 +2788,8 @@
         </is>
       </c>
       <c r="B217" s="8" t="n"/>
+      <c r="C217" s="8" t="n"/>
+      <c r="D217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -2314,6 +2798,8 @@
         </is>
       </c>
       <c r="B218" s="8" t="n"/>
+      <c r="C218" s="8" t="n"/>
+      <c r="D218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -2321,7 +2807,9 @@
           <t>Mon 08 Mar 2027</t>
         </is>
       </c>
-      <c r="B219" s="6" t="n"/>
+      <c r="B219" s="5" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -2329,7 +2817,9 @@
           <t>Tue 09 Mar 2027</t>
         </is>
       </c>
-      <c r="B220" s="6" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -2337,7 +2827,9 @@
           <t>Wed 10 Mar 2027</t>
         </is>
       </c>
-      <c r="B221" s="6" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -2345,7 +2837,9 @@
           <t>Thu 11 Mar 2027</t>
         </is>
       </c>
-      <c r="B222" s="6" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -2353,7 +2847,9 @@
           <t>Fri 12 Mar 2027</t>
         </is>
       </c>
-      <c r="B223" s="6" t="n"/>
+      <c r="B223" s="5" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -2362,6 +2858,8 @@
         </is>
       </c>
       <c r="B224" s="8" t="n"/>
+      <c r="C224" s="8" t="n"/>
+      <c r="D224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -2370,6 +2868,8 @@
         </is>
       </c>
       <c r="B225" s="8" t="n"/>
+      <c r="C225" s="8" t="n"/>
+      <c r="D225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -2377,7 +2877,9 @@
           <t>Mon 15 Mar 2027</t>
         </is>
       </c>
-      <c r="B226" s="6" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -2385,7 +2887,9 @@
           <t>Tue 16 Mar 2027</t>
         </is>
       </c>
-      <c r="B227" s="6" t="n"/>
+      <c r="B227" s="5" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -2393,7 +2897,9 @@
           <t>Wed 17 Mar 2027</t>
         </is>
       </c>
-      <c r="B228" s="6" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -2401,7 +2907,9 @@
           <t>Thu 18 Mar 2027</t>
         </is>
       </c>
-      <c r="B229" s="6" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -2409,7 +2917,9 @@
           <t>Fri 19 Mar 2027</t>
         </is>
       </c>
-      <c r="B230" s="6" t="n"/>
+      <c r="B230" s="5" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -2418,6 +2928,8 @@
         </is>
       </c>
       <c r="B231" s="8" t="n"/>
+      <c r="C231" s="8" t="n"/>
+      <c r="D231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -2426,6 +2938,8 @@
         </is>
       </c>
       <c r="B232" s="8" t="n"/>
+      <c r="C232" s="8" t="n"/>
+      <c r="D232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -2433,7 +2947,9 @@
           <t>Mon 22 Mar 2027</t>
         </is>
       </c>
-      <c r="B233" s="6" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -2441,7 +2957,9 @@
           <t>Tue 23 Mar 2027</t>
         </is>
       </c>
-      <c r="B234" s="6" t="n"/>
+      <c r="B234" s="5" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -2449,7 +2967,9 @@
           <t>Wed 24 Mar 2027</t>
         </is>
       </c>
-      <c r="B235" s="6" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -2457,7 +2977,9 @@
           <t>Thu 25 Mar 2027</t>
         </is>
       </c>
-      <c r="B236" s="6" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -2465,7 +2987,9 @@
           <t>Fri 26 Mar 2027</t>
         </is>
       </c>
-      <c r="B237" s="6" t="n"/>
+      <c r="B237" s="5" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -2474,6 +2998,8 @@
         </is>
       </c>
       <c r="B238" s="8" t="n"/>
+      <c r="C238" s="8" t="n"/>
+      <c r="D238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -2482,6 +3008,8 @@
         </is>
       </c>
       <c r="B239" s="8" t="n"/>
+      <c r="C239" s="8" t="n"/>
+      <c r="D239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -2489,7 +3017,9 @@
           <t>Mon 29 Mar 2027</t>
         </is>
       </c>
-      <c r="B240" s="6" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -2497,7 +3027,9 @@
           <t>Tue 30 Mar 2027</t>
         </is>
       </c>
-      <c r="B241" s="6" t="n"/>
+      <c r="B241" s="5" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -2510,6 +3042,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -2522,6 +3056,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -2534,6 +3070,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -2542,6 +3080,8 @@
         </is>
       </c>
       <c r="B245" s="8" t="n"/>
+      <c r="C245" s="8" t="n"/>
+      <c r="D245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -2550,6 +3090,8 @@
         </is>
       </c>
       <c r="B246" s="8" t="n"/>
+      <c r="C246" s="8" t="n"/>
+      <c r="D246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -2562,6 +3104,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -2574,6 +3118,8 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -488,13 +488,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D248"/>
+  <dimension ref="A1:E248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,6 +516,11 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Osh</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>WIL WILLIAMS</t>
         </is>
       </c>
@@ -532,6 +538,7 @@
       </c>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -546,6 +553,7 @@
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -556,6 +564,7 @@
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -566,6 +575,7 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -580,6 +590,7 @@
       </c>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -590,6 +601,7 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -600,6 +612,7 @@
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -610,6 +623,7 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -620,6 +634,7 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -630,6 +645,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -640,6 +656,7 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -654,6 +671,7 @@
       </c>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -664,6 +682,7 @@
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -674,6 +693,7 @@
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -684,6 +704,7 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -694,6 +715,7 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -704,6 +726,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -714,6 +737,7 @@
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -724,6 +748,7 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -734,6 +759,7 @@
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -744,6 +770,7 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -759,6 +786,11 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
+          <t>Edit - Socials</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
           <t>Hansh Socials</t>
         </is>
       </c>
@@ -775,7 +807,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TOIL - Hansh Socials</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -793,7 +830,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -811,7 +853,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -829,7 +876,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -843,7 +895,8 @@
       </c>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -857,7 +910,8 @@
       </c>
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -872,6 +926,7 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -882,6 +937,7 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -892,6 +948,7 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -902,6 +959,7 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -912,6 +970,7 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -922,6 +981,7 @@
       <c r="B35" s="8" t="n"/>
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -932,6 +992,7 @@
       <c r="B36" s="8" t="n"/>
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -942,6 +1003,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -952,6 +1014,7 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -962,6 +1025,7 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -972,6 +1036,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -982,6 +1047,7 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -992,6 +1058,7 @@
       <c r="B42" s="8" t="n"/>
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1002,6 +1069,7 @@
       <c r="B43" s="8" t="n"/>
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1016,6 +1084,7 @@
       </c>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1030,6 +1099,7 @@
       </c>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1044,6 +1114,7 @@
       </c>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1054,6 +1125,7 @@
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1064,6 +1136,7 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1074,6 +1147,7 @@
       <c r="B49" s="8" t="n"/>
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1084,6 +1158,7 @@
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1094,6 +1169,7 @@
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1104,6 +1180,7 @@
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="5" t="n"/>
       <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1114,6 +1191,7 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1124,6 +1202,7 @@
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="5" t="n"/>
       <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1138,6 +1217,7 @@
       </c>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1148,6 +1228,7 @@
       <c r="B56" s="8" t="n"/>
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1158,6 +1239,7 @@
       <c r="B57" s="8" t="n"/>
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1168,6 +1250,7 @@
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
       <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1178,6 +1261,7 @@
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1188,6 +1272,7 @@
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="n"/>
       <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1198,6 +1283,7 @@
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="5" t="n"/>
       <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1208,6 +1294,7 @@
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="5" t="n"/>
       <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1218,6 +1305,7 @@
       <c r="B63" s="8" t="n"/>
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1228,6 +1316,7 @@
       <c r="B64" s="8" t="n"/>
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1238,6 +1327,7 @@
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1248,6 +1338,7 @@
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="5" t="n"/>
       <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1262,6 +1353,7 @@
       </c>
       <c r="C67" s="5" t="n"/>
       <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1272,6 +1364,7 @@
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1282,6 +1375,7 @@
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="5" t="n"/>
+      <c r="E69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1292,6 +1386,7 @@
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1302,6 +1397,7 @@
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1312,6 +1408,7 @@
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="5" t="n"/>
       <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1322,6 +1419,7 @@
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="5" t="n"/>
       <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1332,6 +1430,7 @@
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1342,6 +1441,7 @@
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="5" t="n"/>
       <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1352,6 +1452,7 @@
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="5" t="n"/>
       <c r="D76" s="5" t="n"/>
+      <c r="E76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -1362,6 +1463,7 @@
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -1372,6 +1474,7 @@
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1382,6 +1485,7 @@
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="5" t="n"/>
       <c r="D79" s="5" t="n"/>
+      <c r="E79" s="5" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -1392,6 +1496,7 @@
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="5" t="n"/>
       <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1402,6 +1507,7 @@
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="5" t="n"/>
       <c r="D81" s="5" t="n"/>
+      <c r="E81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -1412,6 +1518,7 @@
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="5" t="n"/>
       <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1422,6 +1529,7 @@
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="5" t="n"/>
       <c r="D83" s="5" t="n"/>
+      <c r="E83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -1432,6 +1540,7 @@
       <c r="B84" s="8" t="n"/>
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -1442,6 +1551,7 @@
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -1452,6 +1562,7 @@
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="5" t="n"/>
       <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1462,6 +1573,7 @@
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="5" t="n"/>
       <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -1472,6 +1584,7 @@
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1482,6 +1595,7 @@
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="5" t="n"/>
       <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -1492,6 +1606,7 @@
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="5" t="n"/>
       <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -1502,6 +1617,7 @@
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -1512,6 +1628,7 @@
       <c r="B92" s="8" t="n"/>
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
+      <c r="E92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1522,6 +1639,7 @@
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="5" t="n"/>
       <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -1532,6 +1650,7 @@
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="5" t="n"/>
       <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1542,6 +1661,7 @@
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -1552,6 +1672,7 @@
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="5" t="n"/>
       <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1562,6 +1683,7 @@
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="5" t="n"/>
       <c r="D97" s="5" t="n"/>
+      <c r="E97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -1572,6 +1694,7 @@
       <c r="B98" s="8" t="n"/>
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -1582,6 +1705,7 @@
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
+      <c r="E99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -1592,6 +1716,7 @@
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1602,6 +1727,7 @@
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="5" t="n"/>
       <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -1612,6 +1738,7 @@
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="5" t="n"/>
       <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -1622,6 +1749,7 @@
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="5" t="n"/>
       <c r="D103" s="5" t="n"/>
+      <c r="E103" s="5" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -1632,6 +1760,7 @@
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="5" t="n"/>
       <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -1642,6 +1771,7 @@
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
       <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -1652,6 +1782,7 @@
       <c r="B106" s="8" t="n"/>
       <c r="C106" s="8" t="n"/>
       <c r="D106" s="8" t="n"/>
+      <c r="E106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -1662,6 +1793,7 @@
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="5" t="n"/>
       <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -1672,6 +1804,7 @@
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="5" t="n"/>
       <c r="D108" s="5" t="n"/>
+      <c r="E108" s="5" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -1682,6 +1815,7 @@
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="5" t="n"/>
       <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -1692,6 +1826,7 @@
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="5" t="n"/>
       <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -1706,6 +1841,7 @@
       </c>
       <c r="C111" s="5" t="n"/>
       <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -1716,6 +1852,7 @@
       <c r="B112" s="8" t="n"/>
       <c r="C112" s="8" t="n"/>
       <c r="D112" s="8" t="n"/>
+      <c r="E112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -1726,6 +1863,7 @@
       <c r="B113" s="8" t="n"/>
       <c r="C113" s="8" t="n"/>
       <c r="D113" s="8" t="n"/>
+      <c r="E113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -1736,6 +1874,7 @@
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="5" t="n"/>
       <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -1746,6 +1885,7 @@
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="5" t="n"/>
       <c r="D115" s="5" t="n"/>
+      <c r="E115" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -1756,6 +1896,7 @@
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="5" t="n"/>
       <c r="D116" s="5" t="n"/>
+      <c r="E116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -1766,6 +1907,7 @@
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="5" t="n"/>
       <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -1780,6 +1922,7 @@
       </c>
       <c r="C118" s="5" t="n"/>
       <c r="D118" s="5" t="n"/>
+      <c r="E118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -1790,6 +1933,7 @@
       <c r="B119" s="8" t="n"/>
       <c r="C119" s="8" t="n"/>
       <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -1800,6 +1944,7 @@
       <c r="B120" s="8" t="n"/>
       <c r="C120" s="8" t="n"/>
       <c r="D120" s="8" t="n"/>
+      <c r="E120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -1810,6 +1955,7 @@
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="5" t="n"/>
       <c r="D121" s="5" t="n"/>
+      <c r="E121" s="5" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -1820,6 +1966,7 @@
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="5" t="n"/>
       <c r="D122" s="5" t="n"/>
+      <c r="E122" s="5" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -1830,6 +1977,7 @@
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="5" t="n"/>
       <c r="D123" s="5" t="n"/>
+      <c r="E123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -1840,6 +1988,7 @@
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="5" t="n"/>
       <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -1850,6 +1999,7 @@
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="5" t="n"/>
       <c r="D125" s="5" t="n"/>
+      <c r="E125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -1860,6 +2010,7 @@
       <c r="B126" s="8" t="n"/>
       <c r="C126" s="8" t="n"/>
       <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -1870,6 +2021,7 @@
       <c r="B127" s="8" t="n"/>
       <c r="C127" s="8" t="n"/>
       <c r="D127" s="8" t="n"/>
+      <c r="E127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -1880,6 +2032,7 @@
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="5" t="n"/>
       <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -1890,6 +2043,7 @@
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="5" t="n"/>
       <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -1900,6 +2054,7 @@
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="5" t="n"/>
       <c r="D130" s="5" t="n"/>
+      <c r="E130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -1910,6 +2065,7 @@
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="5" t="n"/>
       <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -1920,6 +2076,7 @@
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="5" t="n"/>
       <c r="D132" s="5" t="n"/>
+      <c r="E132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -1930,6 +2087,7 @@
       <c r="B133" s="8" t="n"/>
       <c r="C133" s="8" t="n"/>
       <c r="D133" s="8" t="n"/>
+      <c r="E133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -1940,6 +2098,7 @@
       <c r="B134" s="8" t="n"/>
       <c r="C134" s="8" t="n"/>
       <c r="D134" s="8" t="n"/>
+      <c r="E134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -1950,6 +2109,7 @@
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="5" t="n"/>
       <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -1964,6 +2124,7 @@
       </c>
       <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="n"/>
+      <c r="E136" s="5" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -1978,6 +2139,7 @@
       </c>
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5" t="n"/>
+      <c r="E137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -1992,6 +2154,7 @@
       </c>
       <c r="C138" s="5" t="n"/>
       <c r="D138" s="5" t="n"/>
+      <c r="E138" s="5" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -2006,6 +2169,7 @@
       </c>
       <c r="C139" s="5" t="n"/>
       <c r="D139" s="5" t="n"/>
+      <c r="E139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -2016,6 +2180,7 @@
       <c r="B140" s="8" t="n"/>
       <c r="C140" s="8" t="n"/>
       <c r="D140" s="8" t="n"/>
+      <c r="E140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -2026,6 +2191,7 @@
       <c r="B141" s="8" t="n"/>
       <c r="C141" s="8" t="n"/>
       <c r="D141" s="8" t="n"/>
+      <c r="E141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -2036,6 +2202,7 @@
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="5" t="n"/>
       <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -2046,6 +2213,7 @@
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="5" t="n"/>
       <c r="D143" s="5" t="n"/>
+      <c r="E143" s="5" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -2056,6 +2224,7 @@
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="5" t="n"/>
       <c r="D144" s="5" t="n"/>
+      <c r="E144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -2066,6 +2235,7 @@
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="5" t="n"/>
       <c r="D145" s="5" t="n"/>
+      <c r="E145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -2076,6 +2246,7 @@
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="5" t="n"/>
       <c r="D146" s="5" t="n"/>
+      <c r="E146" s="5" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -2086,6 +2257,7 @@
       <c r="B147" s="8" t="n"/>
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="8" t="n"/>
+      <c r="E147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -2096,6 +2268,7 @@
       <c r="B148" s="8" t="n"/>
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="8" t="n"/>
+      <c r="E148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -2106,6 +2279,7 @@
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="5" t="n"/>
       <c r="D149" s="5" t="n"/>
+      <c r="E149" s="5" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -2116,6 +2290,7 @@
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="5" t="n"/>
       <c r="D150" s="5" t="n"/>
+      <c r="E150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -2126,6 +2301,7 @@
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="5" t="n"/>
       <c r="D151" s="5" t="n"/>
+      <c r="E151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -2136,6 +2312,7 @@
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="5" t="n"/>
       <c r="D152" s="5" t="n"/>
+      <c r="E152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -2146,6 +2323,7 @@
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="5" t="n"/>
       <c r="D153" s="5" t="n"/>
+      <c r="E153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -2156,6 +2334,7 @@
       <c r="B154" s="8" t="n"/>
       <c r="C154" s="8" t="n"/>
       <c r="D154" s="8" t="n"/>
+      <c r="E154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -2166,6 +2345,7 @@
       <c r="B155" s="8" t="n"/>
       <c r="C155" s="8" t="n"/>
       <c r="D155" s="8" t="n"/>
+      <c r="E155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -2176,6 +2356,7 @@
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="5" t="n"/>
       <c r="D156" s="5" t="n"/>
+      <c r="E156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -2186,6 +2367,7 @@
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="5" t="n"/>
       <c r="D157" s="5" t="n"/>
+      <c r="E157" s="5" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -2200,6 +2382,7 @@
       </c>
       <c r="C158" s="5" t="n"/>
       <c r="D158" s="5" t="n"/>
+      <c r="E158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -2210,6 +2393,7 @@
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="5" t="n"/>
       <c r="D159" s="5" t="n"/>
+      <c r="E159" s="5" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -2220,6 +2404,7 @@
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="5" t="n"/>
       <c r="D160" s="5" t="n"/>
+      <c r="E160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -2230,6 +2415,7 @@
       <c r="B161" s="8" t="n"/>
       <c r="C161" s="8" t="n"/>
       <c r="D161" s="8" t="n"/>
+      <c r="E161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -2240,6 +2426,7 @@
       <c r="B162" s="8" t="n"/>
       <c r="C162" s="8" t="n"/>
       <c r="D162" s="8" t="n"/>
+      <c r="E162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -2250,6 +2437,7 @@
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="5" t="n"/>
       <c r="D163" s="5" t="n"/>
+      <c r="E163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -2260,6 +2448,7 @@
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="5" t="n"/>
       <c r="D164" s="5" t="n"/>
+      <c r="E164" s="5" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -2270,6 +2459,7 @@
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="5" t="n"/>
       <c r="D165" s="5" t="n"/>
+      <c r="E165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -2280,6 +2470,7 @@
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="5" t="n"/>
       <c r="D166" s="5" t="n"/>
+      <c r="E166" s="5" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -2290,6 +2481,7 @@
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="5" t="n"/>
       <c r="D167" s="5" t="n"/>
+      <c r="E167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -2300,6 +2492,7 @@
       <c r="B168" s="8" t="n"/>
       <c r="C168" s="8" t="n"/>
       <c r="D168" s="8" t="n"/>
+      <c r="E168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -2310,6 +2503,7 @@
       <c r="B169" s="8" t="n"/>
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="8" t="n"/>
+      <c r="E169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -2320,6 +2514,7 @@
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="5" t="n"/>
       <c r="D170" s="5" t="n"/>
+      <c r="E170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -2330,6 +2525,7 @@
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="5" t="n"/>
       <c r="D171" s="5" t="n"/>
+      <c r="E171" s="5" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -2340,6 +2536,7 @@
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="5" t="n"/>
       <c r="D172" s="5" t="n"/>
+      <c r="E172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -2350,6 +2547,7 @@
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="5" t="n"/>
       <c r="D173" s="5" t="n"/>
+      <c r="E173" s="5" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -2360,6 +2558,7 @@
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="5" t="n"/>
       <c r="D174" s="5" t="n"/>
+      <c r="E174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -2370,6 +2569,7 @@
       <c r="B175" s="8" t="n"/>
       <c r="C175" s="8" t="n"/>
       <c r="D175" s="8" t="n"/>
+      <c r="E175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -2380,6 +2580,7 @@
       <c r="B176" s="8" t="n"/>
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="8" t="n"/>
+      <c r="E176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -2390,6 +2591,7 @@
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="5" t="n"/>
       <c r="D177" s="5" t="n"/>
+      <c r="E177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -2400,6 +2602,7 @@
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="5" t="n"/>
       <c r="D178" s="5" t="n"/>
+      <c r="E178" s="5" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -2410,6 +2613,7 @@
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="5" t="n"/>
       <c r="D179" s="5" t="n"/>
+      <c r="E179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -2420,6 +2624,7 @@
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="5" t="n"/>
       <c r="D180" s="5" t="n"/>
+      <c r="E180" s="5" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -2430,6 +2635,7 @@
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="5" t="n"/>
       <c r="D181" s="5" t="n"/>
+      <c r="E181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -2440,6 +2646,7 @@
       <c r="B182" s="8" t="n"/>
       <c r="C182" s="8" t="n"/>
       <c r="D182" s="8" t="n"/>
+      <c r="E182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -2450,6 +2657,7 @@
       <c r="B183" s="8" t="n"/>
       <c r="C183" s="8" t="n"/>
       <c r="D183" s="8" t="n"/>
+      <c r="E183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -2460,6 +2668,7 @@
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="5" t="n"/>
       <c r="D184" s="5" t="n"/>
+      <c r="E184" s="5" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -2470,6 +2679,7 @@
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="5" t="n"/>
       <c r="D185" s="5" t="n"/>
+      <c r="E185" s="5" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -2480,6 +2690,7 @@
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="5" t="n"/>
       <c r="D186" s="5" t="n"/>
+      <c r="E186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -2490,6 +2701,7 @@
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="5" t="n"/>
       <c r="D187" s="5" t="n"/>
+      <c r="E187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -2500,6 +2712,7 @@
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="5" t="n"/>
       <c r="D188" s="5" t="n"/>
+      <c r="E188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -2510,6 +2723,7 @@
       <c r="B189" s="8" t="n"/>
       <c r="C189" s="8" t="n"/>
       <c r="D189" s="8" t="n"/>
+      <c r="E189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -2520,6 +2734,7 @@
       <c r="B190" s="8" t="n"/>
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="8" t="n"/>
+      <c r="E190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -2530,6 +2745,7 @@
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="5" t="n"/>
       <c r="D191" s="5" t="n"/>
+      <c r="E191" s="5" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -2540,6 +2756,7 @@
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="5" t="n"/>
       <c r="D192" s="5" t="n"/>
+      <c r="E192" s="5" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -2550,6 +2767,7 @@
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="5" t="n"/>
       <c r="D193" s="5" t="n"/>
+      <c r="E193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -2560,6 +2778,7 @@
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="5" t="n"/>
       <c r="D194" s="5" t="n"/>
+      <c r="E194" s="5" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -2570,6 +2789,7 @@
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="5" t="n"/>
       <c r="D195" s="5" t="n"/>
+      <c r="E195" s="5" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -2580,6 +2800,7 @@
       <c r="B196" s="8" t="n"/>
       <c r="C196" s="8" t="n"/>
       <c r="D196" s="8" t="n"/>
+      <c r="E196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -2590,6 +2811,7 @@
       <c r="B197" s="8" t="n"/>
       <c r="C197" s="8" t="n"/>
       <c r="D197" s="8" t="n"/>
+      <c r="E197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -2600,6 +2822,7 @@
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="5" t="n"/>
       <c r="D198" s="5" t="n"/>
+      <c r="E198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -2610,6 +2833,7 @@
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="5" t="n"/>
       <c r="D199" s="5" t="n"/>
+      <c r="E199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -2620,6 +2844,7 @@
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="5" t="n"/>
       <c r="D200" s="5" t="n"/>
+      <c r="E200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -2630,6 +2855,7 @@
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="5" t="n"/>
       <c r="D201" s="5" t="n"/>
+      <c r="E201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -2640,6 +2866,7 @@
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="5" t="n"/>
       <c r="D202" s="5" t="n"/>
+      <c r="E202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -2650,6 +2877,7 @@
       <c r="B203" s="8" t="n"/>
       <c r="C203" s="8" t="n"/>
       <c r="D203" s="8" t="n"/>
+      <c r="E203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -2660,6 +2888,7 @@
       <c r="B204" s="8" t="n"/>
       <c r="C204" s="8" t="n"/>
       <c r="D204" s="8" t="n"/>
+      <c r="E204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -2670,6 +2899,7 @@
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="5" t="n"/>
       <c r="D205" s="5" t="n"/>
+      <c r="E205" s="5" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -2680,6 +2910,7 @@
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="5" t="n"/>
       <c r="D206" s="5" t="n"/>
+      <c r="E206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -2690,6 +2921,7 @@
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="5" t="n"/>
       <c r="D207" s="5" t="n"/>
+      <c r="E207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -2700,6 +2932,7 @@
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="5" t="n"/>
       <c r="D208" s="5" t="n"/>
+      <c r="E208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -2710,6 +2943,7 @@
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="5" t="n"/>
       <c r="D209" s="5" t="n"/>
+      <c r="E209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -2720,6 +2954,7 @@
       <c r="B210" s="8" t="n"/>
       <c r="C210" s="8" t="n"/>
       <c r="D210" s="8" t="n"/>
+      <c r="E210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -2730,6 +2965,7 @@
       <c r="B211" s="8" t="n"/>
       <c r="C211" s="8" t="n"/>
       <c r="D211" s="8" t="n"/>
+      <c r="E211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -2740,6 +2976,7 @@
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="5" t="n"/>
       <c r="D212" s="5" t="n"/>
+      <c r="E212" s="5" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -2750,6 +2987,7 @@
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="5" t="n"/>
       <c r="D213" s="5" t="n"/>
+      <c r="E213" s="5" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -2760,6 +2998,7 @@
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="5" t="n"/>
       <c r="D214" s="5" t="n"/>
+      <c r="E214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -2770,6 +3009,7 @@
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="5" t="n"/>
       <c r="D215" s="5" t="n"/>
+      <c r="E215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -2780,6 +3020,7 @@
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="5" t="n"/>
       <c r="D216" s="5" t="n"/>
+      <c r="E216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -2790,6 +3031,7 @@
       <c r="B217" s="8" t="n"/>
       <c r="C217" s="8" t="n"/>
       <c r="D217" s="8" t="n"/>
+      <c r="E217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -2800,6 +3042,7 @@
       <c r="B218" s="8" t="n"/>
       <c r="C218" s="8" t="n"/>
       <c r="D218" s="8" t="n"/>
+      <c r="E218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -2810,6 +3053,7 @@
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="5" t="n"/>
       <c r="D219" s="5" t="n"/>
+      <c r="E219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -2820,6 +3064,7 @@
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="5" t="n"/>
       <c r="D220" s="5" t="n"/>
+      <c r="E220" s="5" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -2830,6 +3075,7 @@
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="5" t="n"/>
       <c r="D221" s="5" t="n"/>
+      <c r="E221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -2840,6 +3086,7 @@
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="5" t="n"/>
       <c r="D222" s="5" t="n"/>
+      <c r="E222" s="5" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -2850,6 +3097,7 @@
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="5" t="n"/>
       <c r="D223" s="5" t="n"/>
+      <c r="E223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -2860,6 +3108,7 @@
       <c r="B224" s="8" t="n"/>
       <c r="C224" s="8" t="n"/>
       <c r="D224" s="8" t="n"/>
+      <c r="E224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -2870,6 +3119,7 @@
       <c r="B225" s="8" t="n"/>
       <c r="C225" s="8" t="n"/>
       <c r="D225" s="8" t="n"/>
+      <c r="E225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -2880,6 +3130,7 @@
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="5" t="n"/>
       <c r="D226" s="5" t="n"/>
+      <c r="E226" s="5" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -2890,6 +3141,7 @@
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="5" t="n"/>
       <c r="D227" s="5" t="n"/>
+      <c r="E227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -2900,6 +3152,7 @@
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="5" t="n"/>
       <c r="D228" s="5" t="n"/>
+      <c r="E228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -2910,6 +3163,7 @@
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="5" t="n"/>
       <c r="D229" s="5" t="n"/>
+      <c r="E229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -2920,6 +3174,7 @@
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="5" t="n"/>
       <c r="D230" s="5" t="n"/>
+      <c r="E230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -2930,6 +3185,7 @@
       <c r="B231" s="8" t="n"/>
       <c r="C231" s="8" t="n"/>
       <c r="D231" s="8" t="n"/>
+      <c r="E231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -2940,6 +3196,7 @@
       <c r="B232" s="8" t="n"/>
       <c r="C232" s="8" t="n"/>
       <c r="D232" s="8" t="n"/>
+      <c r="E232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -2950,6 +3207,7 @@
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="5" t="n"/>
       <c r="D233" s="5" t="n"/>
+      <c r="E233" s="5" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -2960,6 +3218,7 @@
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="5" t="n"/>
       <c r="D234" s="5" t="n"/>
+      <c r="E234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -2970,6 +3229,7 @@
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="5" t="n"/>
       <c r="D235" s="5" t="n"/>
+      <c r="E235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -2980,6 +3240,7 @@
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="5" t="n"/>
       <c r="D236" s="5" t="n"/>
+      <c r="E236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -2990,6 +3251,7 @@
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="5" t="n"/>
       <c r="D237" s="5" t="n"/>
+      <c r="E237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -3000,6 +3262,7 @@
       <c r="B238" s="8" t="n"/>
       <c r="C238" s="8" t="n"/>
       <c r="D238" s="8" t="n"/>
+      <c r="E238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -3010,6 +3273,7 @@
       <c r="B239" s="8" t="n"/>
       <c r="C239" s="8" t="n"/>
       <c r="D239" s="8" t="n"/>
+      <c r="E239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -3020,6 +3284,7 @@
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="5" t="n"/>
       <c r="D240" s="5" t="n"/>
+      <c r="E240" s="5" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -3030,6 +3295,7 @@
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="5" t="n"/>
       <c r="D241" s="5" t="n"/>
+      <c r="E241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -3044,6 +3310,7 @@
       </c>
       <c r="C242" s="5" t="n"/>
       <c r="D242" s="5" t="n"/>
+      <c r="E242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -3058,6 +3325,7 @@
       </c>
       <c r="C243" s="5" t="n"/>
       <c r="D243" s="5" t="n"/>
+      <c r="E243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -3072,6 +3340,7 @@
       </c>
       <c r="C244" s="5" t="n"/>
       <c r="D244" s="5" t="n"/>
+      <c r="E244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -3082,6 +3351,7 @@
       <c r="B245" s="8" t="n"/>
       <c r="C245" s="8" t="n"/>
       <c r="D245" s="8" t="n"/>
+      <c r="E245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -3092,6 +3362,7 @@
       <c r="B246" s="8" t="n"/>
       <c r="C246" s="8" t="n"/>
       <c r="D246" s="8" t="n"/>
+      <c r="E246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -3106,6 +3377,7 @@
       </c>
       <c r="C247" s="5" t="n"/>
       <c r="D247" s="5" t="n"/>
+      <c r="E247" s="5" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -3120,6 +3392,7 @@
       </c>
       <c r="C248" s="5" t="n"/>
       <c r="D248" s="5" t="n"/>
+      <c r="E248" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -104,10 +104,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E248"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,7 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,20 +507,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Bethan Carlam</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Osh</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>WIL WILLIAMS</t>
         </is>
@@ -531,14 +537,15 @@
           <t>Mon 03 Aug 2026</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -546,14 +553,15 @@
           <t>Tue 04 Aug 2026</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -561,10 +569,11 @@
           <t>Wed 05 Aug 2026</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -572,10 +581,11 @@
           <t>Thu 06 Aug 2026</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -583,14 +593,15 @@
           <t>Fri 07 Aug 2026</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -602,6 +613,7 @@
       <c r="C7" s="8" t="n"/>
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -613,6 +625,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -620,10 +633,11 @@
           <t>Mon 10 Aug 2026</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -631,10 +645,11 @@
           <t>Tue 11 Aug 2026</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -642,10 +657,11 @@
           <t>Wed 12 Aug 2026</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -653,10 +669,11 @@
           <t>Thu 13 Aug 2026</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -664,14 +681,15 @@
           <t>Fri 14 Aug 2026</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -683,6 +701,7 @@
       <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -694,6 +713,7 @@
       <c r="C15" s="8" t="n"/>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -701,10 +721,11 @@
           <t>Mon 17 Aug 2026</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -712,10 +733,11 @@
           <t>Tue 18 Aug 2026</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -723,10 +745,11 @@
           <t>Wed 19 Aug 2026</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -734,10 +757,11 @@
           <t>Thu 20 Aug 2026</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -745,10 +769,11 @@
           <t>Fri 21 Aug 2026</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -760,6 +785,7 @@
       <c r="C21" s="8" t="n"/>
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -771,6 +797,7 @@
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -778,18 +805,23 @@
           <t>Mon 24 Aug 2026</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -801,18 +833,23 @@
           <t>Tue 25 Aug 2026</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -824,18 +861,23 @@
           <t>Wed 26 Aug 2026</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="C25" s="4" t="n"/>
       <c r="D25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -847,18 +889,23 @@
           <t>Thu 27 Aug 2026</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="C26" s="4" t="n"/>
       <c r="D26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -870,18 +917,23 @@
           <t>Fri 28 Aug 2026</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -896,7 +948,8 @@
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -911,7 +964,8 @@
       <c r="B29" s="8" t="n"/>
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -923,10 +977,11 @@
           <t>Mon 31 Aug 2026</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -934,10 +989,11 @@
           <t>Tue 01 Sep 2026</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -945,10 +1001,11 @@
           <t>Wed 02 Sep 2026</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -956,10 +1013,11 @@
           <t>Thu 03 Sep 2026</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -967,10 +1025,11 @@
           <t>Fri 04 Sep 2026</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -982,6 +1041,7 @@
       <c r="C35" s="8" t="n"/>
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -993,6 +1053,7 @@
       <c r="C36" s="8" t="n"/>
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1000,10 +1061,11 @@
           <t>Mon 07 Sep 2026</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1011,10 +1073,11 @@
           <t>Tue 08 Sep 2026</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1022,10 +1085,11 @@
           <t>Wed 09 Sep 2026</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1033,10 +1097,11 @@
           <t>Thu 10 Sep 2026</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1044,10 +1109,11 @@
           <t>Fri 11 Sep 2026</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1059,6 +1125,7 @@
       <c r="C42" s="8" t="n"/>
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1070,6 +1137,7 @@
       <c r="C43" s="8" t="n"/>
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1077,14 +1145,15 @@
           <t>Mon 14 Sep 2026</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1092,14 +1161,15 @@
           <t>Tue 15 Sep 2026</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1107,14 +1177,15 @@
           <t>Wed 16 Sep 2026</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1122,10 +1193,11 @@
           <t>Thu 17 Sep 2026</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1133,10 +1205,11 @@
           <t>Fri 18 Sep 2026</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1148,6 +1221,7 @@
       <c r="C49" s="8" t="n"/>
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1159,6 +1233,7 @@
       <c r="C50" s="8" t="n"/>
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1166,10 +1241,11 @@
           <t>Mon 21 Sep 2026</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1177,10 +1253,11 @@
           <t>Tue 22 Sep 2026</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n"/>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1188,10 +1265,11 @@
           <t>Wed 23 Sep 2026</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1199,10 +1277,11 @@
           <t>Thu 24 Sep 2026</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1210,14 +1289,15 @@
           <t>Fri 25 Sep 2026</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1229,6 +1309,7 @@
       <c r="C56" s="8" t="n"/>
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1240,6 +1321,7 @@
       <c r="C57" s="8" t="n"/>
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1247,10 +1329,11 @@
           <t>Mon 28 Sep 2026</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1258,10 +1341,11 @@
           <t>Tue 29 Sep 2026</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1269,10 +1353,11 @@
           <t>Wed 30 Sep 2026</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n"/>
-      <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1280,10 +1365,11 @@
           <t>Thu 01 Oct 2026</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1291,10 +1377,11 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1306,6 +1393,7 @@
       <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1317,6 +1405,7 @@
       <c r="C64" s="8" t="n"/>
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1324,10 +1413,11 @@
           <t>Mon 05 Oct 2026</t>
         </is>
       </c>
-      <c r="B65" s="5" t="n"/>
-      <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1335,10 +1425,11 @@
           <t>Tue 06 Oct 2026</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1346,14 +1437,15 @@
           <t>Wed 07 Oct 2026</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1361,10 +1453,11 @@
           <t>Thu 08 Oct 2026</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n"/>
-      <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1372,10 +1465,11 @@
           <t>Fri 09 Oct 2026</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n"/>
-      <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1387,6 +1481,7 @@
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1398,6 +1493,7 @@
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1405,10 +1501,11 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="B72" s="5" t="n"/>
-      <c r="C72" s="5" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1416,10 +1513,11 @@
           <t>Tue 13 Oct 2026</t>
         </is>
       </c>
-      <c r="B73" s="5" t="n"/>
-      <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1427,10 +1525,11 @@
           <t>Wed 14 Oct 2026</t>
         </is>
       </c>
-      <c r="B74" s="5" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1438,10 +1537,11 @@
           <t>Thu 15 Oct 2026</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1449,10 +1549,11 @@
           <t>Fri 16 Oct 2026</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n"/>
-      <c r="C76" s="5" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -1464,6 +1565,7 @@
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -1475,6 +1577,7 @@
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1482,10 +1585,11 @@
           <t>Mon 19 Oct 2026</t>
         </is>
       </c>
-      <c r="B79" s="5" t="n"/>
-      <c r="C79" s="5" t="n"/>
-      <c r="D79" s="5" t="n"/>
-      <c r="E79" s="5" t="n"/>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -1493,10 +1597,11 @@
           <t>Tue 20 Oct 2026</t>
         </is>
       </c>
-      <c r="B80" s="5" t="n"/>
-      <c r="C80" s="5" t="n"/>
-      <c r="D80" s="5" t="n"/>
-      <c r="E80" s="5" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1504,10 +1609,11 @@
           <t>Wed 21 Oct 2026</t>
         </is>
       </c>
-      <c r="B81" s="5" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
-      <c r="E81" s="5" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -1515,10 +1621,11 @@
           <t>Thu 22 Oct 2026</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n"/>
-      <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1526,10 +1633,11 @@
           <t>Fri 23 Oct 2026</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n"/>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="n"/>
-      <c r="E83" s="5" t="n"/>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -1541,6 +1649,7 @@
       <c r="C84" s="8" t="n"/>
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -1552,6 +1661,7 @@
       <c r="C85" s="8" t="n"/>
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -1559,10 +1669,11 @@
           <t>Mon 26 Oct 2026</t>
         </is>
       </c>
-      <c r="B86" s="5" t="n"/>
-      <c r="C86" s="5" t="n"/>
-      <c r="D86" s="5" t="n"/>
-      <c r="E86" s="5" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1570,10 +1681,11 @@
           <t>Tue 27 Oct 2026</t>
         </is>
       </c>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="5" t="n"/>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -1581,10 +1693,11 @@
           <t>Wed 28 Oct 2026</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1592,10 +1705,11 @@
           <t>Thu 29 Oct 2026</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n"/>
-      <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -1603,10 +1717,11 @@
           <t>Fri 30 Oct 2026</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -1618,6 +1733,7 @@
       <c r="C91" s="8" t="n"/>
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -1629,6 +1745,7 @@
       <c r="C92" s="8" t="n"/>
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1636,10 +1753,11 @@
           <t>Mon 02 Nov 2026</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -1647,10 +1765,11 @@
           <t>Tue 03 Nov 2026</t>
         </is>
       </c>
-      <c r="B94" s="5" t="n"/>
-      <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1658,10 +1777,11 @@
           <t>Wed 04 Nov 2026</t>
         </is>
       </c>
-      <c r="B95" s="5" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -1669,10 +1789,11 @@
           <t>Thu 05 Nov 2026</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n"/>
-      <c r="C96" s="5" t="n"/>
-      <c r="D96" s="5" t="n"/>
-      <c r="E96" s="5" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1680,10 +1801,11 @@
           <t>Fri 06 Nov 2026</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="5" t="n"/>
-      <c r="D97" s="5" t="n"/>
-      <c r="E97" s="5" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -1695,6 +1817,7 @@
       <c r="C98" s="8" t="n"/>
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -1706,6 +1829,7 @@
       <c r="C99" s="8" t="n"/>
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -1713,10 +1837,11 @@
           <t>Mon 09 Nov 2026</t>
         </is>
       </c>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="5" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1724,10 +1849,11 @@
           <t>Tue 10 Nov 2026</t>
         </is>
       </c>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -1735,10 +1861,11 @@
           <t>Wed 11 Nov 2026</t>
         </is>
       </c>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="5" t="n"/>
-      <c r="D102" s="5" t="n"/>
-      <c r="E102" s="5" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -1746,10 +1873,11 @@
           <t>Thu 12 Nov 2026</t>
         </is>
       </c>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -1757,10 +1885,11 @@
           <t>Fri 13 Nov 2026</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -1772,6 +1901,7 @@
       <c r="C105" s="8" t="n"/>
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -1783,6 +1913,7 @@
       <c r="C106" s="8" t="n"/>
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -1790,10 +1921,11 @@
           <t>Mon 16 Nov 2026</t>
         </is>
       </c>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="5" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -1801,10 +1933,11 @@
           <t>Tue 17 Nov 2026</t>
         </is>
       </c>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="5" t="n"/>
-      <c r="D108" s="5" t="n"/>
-      <c r="E108" s="5" t="n"/>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -1812,10 +1945,11 @@
           <t>Wed 18 Nov 2026</t>
         </is>
       </c>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -1823,10 +1957,11 @@
           <t>Thu 19 Nov 2026</t>
         </is>
       </c>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="5" t="n"/>
-      <c r="D110" s="5" t="n"/>
-      <c r="E110" s="5" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -1834,14 +1969,15 @@
           <t>Fri 20 Nov 2026</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -1853,6 +1989,7 @@
       <c r="C112" s="8" t="n"/>
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
+      <c r="F112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -1864,6 +2001,7 @@
       <c r="C113" s="8" t="n"/>
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
+      <c r="F113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -1871,10 +2009,11 @@
           <t>Mon 23 Nov 2026</t>
         </is>
       </c>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="5" t="n"/>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -1882,10 +2021,11 @@
           <t>Tue 24 Nov 2026</t>
         </is>
       </c>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -1893,10 +2033,11 @@
           <t>Wed 25 Nov 2026</t>
         </is>
       </c>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="5" t="n"/>
-      <c r="D116" s="5" t="n"/>
-      <c r="E116" s="5" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -1904,10 +2045,11 @@
           <t>Thu 26 Nov 2026</t>
         </is>
       </c>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="5" t="n"/>
-      <c r="D117" s="5" t="n"/>
-      <c r="E117" s="5" t="n"/>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -1915,14 +2057,15 @@
           <t>Fri 27 Nov 2026</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="5" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -1934,6 +2077,7 @@
       <c r="C119" s="8" t="n"/>
       <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -1945,6 +2089,7 @@
       <c r="C120" s="8" t="n"/>
       <c r="D120" s="8" t="n"/>
       <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -1952,10 +2097,11 @@
           <t>Mon 30 Nov 2026</t>
         </is>
       </c>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="5" t="n"/>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -1963,10 +2109,11 @@
           <t>Tue 01 Dec 2026</t>
         </is>
       </c>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="5" t="n"/>
-      <c r="E122" s="5" t="n"/>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -1974,10 +2121,11 @@
           <t>Wed 02 Dec 2026</t>
         </is>
       </c>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="5" t="n"/>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -1985,10 +2133,11 @@
           <t>Thu 03 Dec 2026</t>
         </is>
       </c>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="5" t="n"/>
-      <c r="D124" s="5" t="n"/>
-      <c r="E124" s="5" t="n"/>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -1996,10 +2145,11 @@
           <t>Fri 04 Dec 2026</t>
         </is>
       </c>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="5" t="n"/>
-      <c r="D125" s="5" t="n"/>
-      <c r="E125" s="5" t="n"/>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -2011,6 +2161,7 @@
       <c r="C126" s="8" t="n"/>
       <c r="D126" s="8" t="n"/>
       <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -2022,6 +2173,7 @@
       <c r="C127" s="8" t="n"/>
       <c r="D127" s="8" t="n"/>
       <c r="E127" s="8" t="n"/>
+      <c r="F127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -2029,10 +2181,11 @@
           <t>Mon 07 Dec 2026</t>
         </is>
       </c>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="5" t="n"/>
-      <c r="E128" s="5" t="n"/>
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -2040,10 +2193,11 @@
           <t>Tue 08 Dec 2026</t>
         </is>
       </c>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="5" t="n"/>
-      <c r="D129" s="5" t="n"/>
-      <c r="E129" s="5" t="n"/>
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="n"/>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -2051,10 +2205,11 @@
           <t>Wed 09 Dec 2026</t>
         </is>
       </c>
-      <c r="B130" s="5" t="n"/>
-      <c r="C130" s="5" t="n"/>
-      <c r="D130" s="5" t="n"/>
-      <c r="E130" s="5" t="n"/>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="4" t="n"/>
+      <c r="D130" s="4" t="n"/>
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -2062,10 +2217,11 @@
           <t>Thu 10 Dec 2026</t>
         </is>
       </c>
-      <c r="B131" s="5" t="n"/>
-      <c r="C131" s="5" t="n"/>
-      <c r="D131" s="5" t="n"/>
-      <c r="E131" s="5" t="n"/>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -2073,10 +2229,11 @@
           <t>Fri 11 Dec 2026</t>
         </is>
       </c>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="5" t="n"/>
-      <c r="D132" s="5" t="n"/>
-      <c r="E132" s="5" t="n"/>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -2088,6 +2245,7 @@
       <c r="C133" s="8" t="n"/>
       <c r="D133" s="8" t="n"/>
       <c r="E133" s="8" t="n"/>
+      <c r="F133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -2099,6 +2257,7 @@
       <c r="C134" s="8" t="n"/>
       <c r="D134" s="8" t="n"/>
       <c r="E134" s="8" t="n"/>
+      <c r="F134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -2106,10 +2265,11 @@
           <t>Mon 14 Dec 2026</t>
         </is>
       </c>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="5" t="n"/>
-      <c r="E135" s="5" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -2117,14 +2277,15 @@
           <t>Tue 15 Dec 2026</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="5" t="n"/>
-      <c r="E136" s="5" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -2132,14 +2293,15 @@
           <t>Wed 16 Dec 2026</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="5" t="n"/>
-      <c r="E137" s="5" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -2147,14 +2309,15 @@
           <t>Thu 17 Dec 2026</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="n"/>
-      <c r="E138" s="5" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -2162,14 +2325,15 @@
           <t>Fri 18 Dec 2026</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n"/>
-      <c r="D139" s="5" t="n"/>
-      <c r="E139" s="5" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -2181,6 +2345,7 @@
       <c r="C140" s="8" t="n"/>
       <c r="D140" s="8" t="n"/>
       <c r="E140" s="8" t="n"/>
+      <c r="F140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -2192,6 +2357,7 @@
       <c r="C141" s="8" t="n"/>
       <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
+      <c r="F141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -2199,10 +2365,11 @@
           <t>Mon 21 Dec 2026</t>
         </is>
       </c>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="5" t="n"/>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -2210,10 +2377,11 @@
           <t>Tue 22 Dec 2026</t>
         </is>
       </c>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="5" t="n"/>
-      <c r="D143" s="5" t="n"/>
-      <c r="E143" s="5" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -2221,10 +2389,11 @@
           <t>Wed 23 Dec 2026</t>
         </is>
       </c>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="n"/>
-      <c r="E144" s="5" t="n"/>
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -2232,10 +2401,11 @@
           <t>Thu 24 Dec 2026</t>
         </is>
       </c>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="5" t="n"/>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -2243,10 +2413,11 @@
           <t>Fri 25 Dec 2026</t>
         </is>
       </c>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="5" t="n"/>
-      <c r="D146" s="5" t="n"/>
-      <c r="E146" s="5" t="n"/>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -2258,6 +2429,7 @@
       <c r="C147" s="8" t="n"/>
       <c r="D147" s="8" t="n"/>
       <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -2269,6 +2441,7 @@
       <c r="C148" s="8" t="n"/>
       <c r="D148" s="8" t="n"/>
       <c r="E148" s="8" t="n"/>
+      <c r="F148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -2276,10 +2449,11 @@
           <t>Mon 28 Dec 2026</t>
         </is>
       </c>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="5" t="n"/>
-      <c r="E149" s="5" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -2287,10 +2461,11 @@
           <t>Tue 29 Dec 2026</t>
         </is>
       </c>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
-      <c r="E150" s="5" t="n"/>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -2298,10 +2473,11 @@
           <t>Wed 30 Dec 2026</t>
         </is>
       </c>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="5" t="n"/>
-      <c r="E151" s="5" t="n"/>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -2309,10 +2485,11 @@
           <t>Thu 31 Dec 2026</t>
         </is>
       </c>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="5" t="n"/>
-      <c r="E152" s="5" t="n"/>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
+      <c r="E152" s="4" t="n"/>
+      <c r="F152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -2320,10 +2497,11 @@
           <t>Fri 01 Jan 2027</t>
         </is>
       </c>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
-      <c r="E153" s="5" t="n"/>
+      <c r="B153" s="4" t="n"/>
+      <c r="C153" s="4" t="n"/>
+      <c r="D153" s="4" t="n"/>
+      <c r="E153" s="4" t="n"/>
+      <c r="F153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -2335,6 +2513,7 @@
       <c r="C154" s="8" t="n"/>
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
+      <c r="F154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -2346,6 +2525,7 @@
       <c r="C155" s="8" t="n"/>
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -2353,10 +2533,11 @@
           <t>Mon 04 Jan 2027</t>
         </is>
       </c>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="5" t="n"/>
-      <c r="D156" s="5" t="n"/>
-      <c r="E156" s="5" t="n"/>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -2364,10 +2545,11 @@
           <t>Tue 05 Jan 2027</t>
         </is>
       </c>
-      <c r="B157" s="5" t="n"/>
-      <c r="C157" s="5" t="n"/>
-      <c r="D157" s="5" t="n"/>
-      <c r="E157" s="5" t="n"/>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -2375,14 +2557,15 @@
           <t>Wed 06 Jan 2027</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="5" t="n"/>
-      <c r="E158" s="5" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -2390,10 +2573,11 @@
           <t>Thu 07 Jan 2027</t>
         </is>
       </c>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="5" t="n"/>
-      <c r="D159" s="5" t="n"/>
-      <c r="E159" s="5" t="n"/>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="4" t="n"/>
+      <c r="F159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -2401,10 +2585,11 @@
           <t>Fri 08 Jan 2027</t>
         </is>
       </c>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
-      <c r="E160" s="5" t="n"/>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="4" t="n"/>
+      <c r="D160" s="4" t="n"/>
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -2416,6 +2601,7 @@
       <c r="C161" s="8" t="n"/>
       <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
+      <c r="F161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -2427,6 +2613,7 @@
       <c r="C162" s="8" t="n"/>
       <c r="D162" s="8" t="n"/>
       <c r="E162" s="8" t="n"/>
+      <c r="F162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -2434,10 +2621,11 @@
           <t>Mon 11 Jan 2027</t>
         </is>
       </c>
-      <c r="B163" s="5" t="n"/>
-      <c r="C163" s="5" t="n"/>
-      <c r="D163" s="5" t="n"/>
-      <c r="E163" s="5" t="n"/>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -2445,10 +2633,11 @@
           <t>Tue 12 Jan 2027</t>
         </is>
       </c>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="5" t="n"/>
-      <c r="E164" s="5" t="n"/>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="n"/>
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -2456,10 +2645,11 @@
           <t>Wed 13 Jan 2027</t>
         </is>
       </c>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="5" t="n"/>
-      <c r="D165" s="5" t="n"/>
-      <c r="E165" s="5" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -2467,10 +2657,11 @@
           <t>Thu 14 Jan 2027</t>
         </is>
       </c>
-      <c r="B166" s="5" t="n"/>
-      <c r="C166" s="5" t="n"/>
-      <c r="D166" s="5" t="n"/>
-      <c r="E166" s="5" t="n"/>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
+      <c r="E166" s="4" t="n"/>
+      <c r="F166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -2478,10 +2669,11 @@
           <t>Fri 15 Jan 2027</t>
         </is>
       </c>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
-      <c r="E167" s="5" t="n"/>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
+      <c r="E167" s="4" t="n"/>
+      <c r="F167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -2493,6 +2685,7 @@
       <c r="C168" s="8" t="n"/>
       <c r="D168" s="8" t="n"/>
       <c r="E168" s="8" t="n"/>
+      <c r="F168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -2504,6 +2697,7 @@
       <c r="C169" s="8" t="n"/>
       <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
+      <c r="F169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -2511,10 +2705,11 @@
           <t>Mon 18 Jan 2027</t>
         </is>
       </c>
-      <c r="B170" s="5" t="n"/>
-      <c r="C170" s="5" t="n"/>
-      <c r="D170" s="5" t="n"/>
-      <c r="E170" s="5" t="n"/>
+      <c r="B170" s="4" t="n"/>
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="n"/>
+      <c r="E170" s="4" t="n"/>
+      <c r="F170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -2522,10 +2717,11 @@
           <t>Tue 19 Jan 2027</t>
         </is>
       </c>
-      <c r="B171" s="5" t="n"/>
-      <c r="C171" s="5" t="n"/>
-      <c r="D171" s="5" t="n"/>
-      <c r="E171" s="5" t="n"/>
+      <c r="B171" s="4" t="n"/>
+      <c r="C171" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
+      <c r="E171" s="4" t="n"/>
+      <c r="F171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -2533,10 +2729,11 @@
           <t>Wed 20 Jan 2027</t>
         </is>
       </c>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="5" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="4" t="n"/>
+      <c r="F172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -2544,10 +2741,11 @@
           <t>Thu 21 Jan 2027</t>
         </is>
       </c>
-      <c r="B173" s="5" t="n"/>
-      <c r="C173" s="5" t="n"/>
-      <c r="D173" s="5" t="n"/>
-      <c r="E173" s="5" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -2555,10 +2753,11 @@
           <t>Fri 22 Jan 2027</t>
         </is>
       </c>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="5" t="n"/>
-      <c r="E174" s="5" t="n"/>
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -2570,6 +2769,7 @@
       <c r="C175" s="8" t="n"/>
       <c r="D175" s="8" t="n"/>
       <c r="E175" s="8" t="n"/>
+      <c r="F175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -2581,6 +2781,7 @@
       <c r="C176" s="8" t="n"/>
       <c r="D176" s="8" t="n"/>
       <c r="E176" s="8" t="n"/>
+      <c r="F176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -2588,10 +2789,11 @@
           <t>Mon 25 Jan 2027</t>
         </is>
       </c>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="5" t="n"/>
-      <c r="D177" s="5" t="n"/>
-      <c r="E177" s="5" t="n"/>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -2599,10 +2801,11 @@
           <t>Tue 26 Jan 2027</t>
         </is>
       </c>
-      <c r="B178" s="5" t="n"/>
-      <c r="C178" s="5" t="n"/>
-      <c r="D178" s="5" t="n"/>
-      <c r="E178" s="5" t="n"/>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -2610,10 +2813,11 @@
           <t>Wed 27 Jan 2027</t>
         </is>
       </c>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="5" t="n"/>
-      <c r="E179" s="5" t="n"/>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="4" t="n"/>
+      <c r="F179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -2621,10 +2825,11 @@
           <t>Thu 28 Jan 2027</t>
         </is>
       </c>
-      <c r="B180" s="5" t="n"/>
-      <c r="C180" s="5" t="n"/>
-      <c r="D180" s="5" t="n"/>
-      <c r="E180" s="5" t="n"/>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="4" t="n"/>
+      <c r="F180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -2632,10 +2837,11 @@
           <t>Fri 29 Jan 2027</t>
         </is>
       </c>
-      <c r="B181" s="5" t="n"/>
-      <c r="C181" s="5" t="n"/>
-      <c r="D181" s="5" t="n"/>
-      <c r="E181" s="5" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -2647,6 +2853,7 @@
       <c r="C182" s="8" t="n"/>
       <c r="D182" s="8" t="n"/>
       <c r="E182" s="8" t="n"/>
+      <c r="F182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -2658,6 +2865,7 @@
       <c r="C183" s="8" t="n"/>
       <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
+      <c r="F183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -2665,10 +2873,11 @@
           <t>Mon 01 Feb 2027</t>
         </is>
       </c>
-      <c r="B184" s="5" t="n"/>
-      <c r="C184" s="5" t="n"/>
-      <c r="D184" s="5" t="n"/>
-      <c r="E184" s="5" t="n"/>
+      <c r="B184" s="4" t="n"/>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
+      <c r="E184" s="4" t="n"/>
+      <c r="F184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -2676,10 +2885,11 @@
           <t>Tue 02 Feb 2027</t>
         </is>
       </c>
-      <c r="B185" s="5" t="n"/>
-      <c r="C185" s="5" t="n"/>
-      <c r="D185" s="5" t="n"/>
-      <c r="E185" s="5" t="n"/>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="4" t="n"/>
+      <c r="F185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -2687,10 +2897,11 @@
           <t>Wed 03 Feb 2027</t>
         </is>
       </c>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="5" t="n"/>
-      <c r="D186" s="5" t="n"/>
-      <c r="E186" s="5" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -2698,10 +2909,11 @@
           <t>Thu 04 Feb 2027</t>
         </is>
       </c>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="5" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="4" t="n"/>
+      <c r="F187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -2709,10 +2921,11 @@
           <t>Fri 05 Feb 2027</t>
         </is>
       </c>
-      <c r="B188" s="5" t="n"/>
-      <c r="C188" s="5" t="n"/>
-      <c r="D188" s="5" t="n"/>
-      <c r="E188" s="5" t="n"/>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="4" t="n"/>
+      <c r="F188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -2724,6 +2937,7 @@
       <c r="C189" s="8" t="n"/>
       <c r="D189" s="8" t="n"/>
       <c r="E189" s="8" t="n"/>
+      <c r="F189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -2735,6 +2949,7 @@
       <c r="C190" s="8" t="n"/>
       <c r="D190" s="8" t="n"/>
       <c r="E190" s="8" t="n"/>
+      <c r="F190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -2742,10 +2957,11 @@
           <t>Mon 08 Feb 2027</t>
         </is>
       </c>
-      <c r="B191" s="5" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="5" t="n"/>
-      <c r="E191" s="5" t="n"/>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="n"/>
+      <c r="E191" s="4" t="n"/>
+      <c r="F191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -2753,10 +2969,11 @@
           <t>Tue 09 Feb 2027</t>
         </is>
       </c>
-      <c r="B192" s="5" t="n"/>
-      <c r="C192" s="5" t="n"/>
-      <c r="D192" s="5" t="n"/>
-      <c r="E192" s="5" t="n"/>
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="4" t="n"/>
+      <c r="F192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -2764,10 +2981,11 @@
           <t>Wed 10 Feb 2027</t>
         </is>
       </c>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="5" t="n"/>
-      <c r="E193" s="5" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="4" t="n"/>
+      <c r="F193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -2775,10 +2993,11 @@
           <t>Thu 11 Feb 2027</t>
         </is>
       </c>
-      <c r="B194" s="5" t="n"/>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="5" t="n"/>
-      <c r="E194" s="5" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="n"/>
+      <c r="E194" s="4" t="n"/>
+      <c r="F194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -2786,10 +3005,11 @@
           <t>Fri 12 Feb 2027</t>
         </is>
       </c>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="5" t="n"/>
-      <c r="D195" s="5" t="n"/>
-      <c r="E195" s="5" t="n"/>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -2801,6 +3021,7 @@
       <c r="C196" s="8" t="n"/>
       <c r="D196" s="8" t="n"/>
       <c r="E196" s="8" t="n"/>
+      <c r="F196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -2812,6 +3033,7 @@
       <c r="C197" s="8" t="n"/>
       <c r="D197" s="8" t="n"/>
       <c r="E197" s="8" t="n"/>
+      <c r="F197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -2819,10 +3041,11 @@
           <t>Mon 15 Feb 2027</t>
         </is>
       </c>
-      <c r="B198" s="5" t="n"/>
-      <c r="C198" s="5" t="n"/>
-      <c r="D198" s="5" t="n"/>
-      <c r="E198" s="5" t="n"/>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="4" t="n"/>
+      <c r="D198" s="4" t="n"/>
+      <c r="E198" s="4" t="n"/>
+      <c r="F198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -2830,10 +3053,11 @@
           <t>Tue 16 Feb 2027</t>
         </is>
       </c>
-      <c r="B199" s="5" t="n"/>
-      <c r="C199" s="5" t="n"/>
-      <c r="D199" s="5" t="n"/>
-      <c r="E199" s="5" t="n"/>
+      <c r="B199" s="4" t="n"/>
+      <c r="C199" s="4" t="n"/>
+      <c r="D199" s="4" t="n"/>
+      <c r="E199" s="4" t="n"/>
+      <c r="F199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -2841,10 +3065,11 @@
           <t>Wed 17 Feb 2027</t>
         </is>
       </c>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
-      <c r="E200" s="5" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="4" t="n"/>
+      <c r="D200" s="4" t="n"/>
+      <c r="E200" s="4" t="n"/>
+      <c r="F200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -2852,10 +3077,11 @@
           <t>Thu 18 Feb 2027</t>
         </is>
       </c>
-      <c r="B201" s="5" t="n"/>
-      <c r="C201" s="5" t="n"/>
-      <c r="D201" s="5" t="n"/>
-      <c r="E201" s="5" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="4" t="n"/>
+      <c r="F201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -2863,10 +3089,11 @@
           <t>Fri 19 Feb 2027</t>
         </is>
       </c>
-      <c r="B202" s="5" t="n"/>
-      <c r="C202" s="5" t="n"/>
-      <c r="D202" s="5" t="n"/>
-      <c r="E202" s="5" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="4" t="n"/>
+      <c r="D202" s="4" t="n"/>
+      <c r="E202" s="4" t="n"/>
+      <c r="F202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -2878,6 +3105,7 @@
       <c r="C203" s="8" t="n"/>
       <c r="D203" s="8" t="n"/>
       <c r="E203" s="8" t="n"/>
+      <c r="F203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -2889,6 +3117,7 @@
       <c r="C204" s="8" t="n"/>
       <c r="D204" s="8" t="n"/>
       <c r="E204" s="8" t="n"/>
+      <c r="F204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -2896,10 +3125,11 @@
           <t>Mon 22 Feb 2027</t>
         </is>
       </c>
-      <c r="B205" s="5" t="n"/>
-      <c r="C205" s="5" t="n"/>
-      <c r="D205" s="5" t="n"/>
-      <c r="E205" s="5" t="n"/>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
+      <c r="E205" s="4" t="n"/>
+      <c r="F205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -2907,10 +3137,11 @@
           <t>Tue 23 Feb 2027</t>
         </is>
       </c>
-      <c r="B206" s="5" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="5" t="n"/>
-      <c r="E206" s="5" t="n"/>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="4" t="n"/>
+      <c r="D206" s="4" t="n"/>
+      <c r="E206" s="4" t="n"/>
+      <c r="F206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -2918,10 +3149,11 @@
           <t>Wed 24 Feb 2027</t>
         </is>
       </c>
-      <c r="B207" s="5" t="n"/>
-      <c r="C207" s="5" t="n"/>
-      <c r="D207" s="5" t="n"/>
-      <c r="E207" s="5" t="n"/>
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="4" t="n"/>
+      <c r="E207" s="4" t="n"/>
+      <c r="F207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -2929,10 +3161,11 @@
           <t>Thu 25 Feb 2027</t>
         </is>
       </c>
-      <c r="B208" s="5" t="n"/>
-      <c r="C208" s="5" t="n"/>
-      <c r="D208" s="5" t="n"/>
-      <c r="E208" s="5" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="4" t="n"/>
+      <c r="D208" s="4" t="n"/>
+      <c r="E208" s="4" t="n"/>
+      <c r="F208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -2940,10 +3173,11 @@
           <t>Fri 26 Feb 2027</t>
         </is>
       </c>
-      <c r="B209" s="5" t="n"/>
-      <c r="C209" s="5" t="n"/>
-      <c r="D209" s="5" t="n"/>
-      <c r="E209" s="5" t="n"/>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="n"/>
+      <c r="D209" s="4" t="n"/>
+      <c r="E209" s="4" t="n"/>
+      <c r="F209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -2955,6 +3189,7 @@
       <c r="C210" s="8" t="n"/>
       <c r="D210" s="8" t="n"/>
       <c r="E210" s="8" t="n"/>
+      <c r="F210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -2966,6 +3201,7 @@
       <c r="C211" s="8" t="n"/>
       <c r="D211" s="8" t="n"/>
       <c r="E211" s="8" t="n"/>
+      <c r="F211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -2973,10 +3209,11 @@
           <t>Mon 01 Mar 2027</t>
         </is>
       </c>
-      <c r="B212" s="5" t="n"/>
-      <c r="C212" s="5" t="n"/>
-      <c r="D212" s="5" t="n"/>
-      <c r="E212" s="5" t="n"/>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="4" t="n"/>
+      <c r="F212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -2984,10 +3221,11 @@
           <t>Tue 02 Mar 2027</t>
         </is>
       </c>
-      <c r="B213" s="5" t="n"/>
-      <c r="C213" s="5" t="n"/>
-      <c r="D213" s="5" t="n"/>
-      <c r="E213" s="5" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -2995,10 +3233,11 @@
           <t>Wed 03 Mar 2027</t>
         </is>
       </c>
-      <c r="B214" s="5" t="n"/>
-      <c r="C214" s="5" t="n"/>
-      <c r="D214" s="5" t="n"/>
-      <c r="E214" s="5" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -3006,10 +3245,11 @@
           <t>Thu 04 Mar 2027</t>
         </is>
       </c>
-      <c r="B215" s="5" t="n"/>
-      <c r="C215" s="5" t="n"/>
-      <c r="D215" s="5" t="n"/>
-      <c r="E215" s="5" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
+      <c r="E215" s="4" t="n"/>
+      <c r="F215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -3017,10 +3257,11 @@
           <t>Fri 05 Mar 2027</t>
         </is>
       </c>
-      <c r="B216" s="5" t="n"/>
-      <c r="C216" s="5" t="n"/>
-      <c r="D216" s="5" t="n"/>
-      <c r="E216" s="5" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="4" t="n"/>
+      <c r="F216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -3032,6 +3273,7 @@
       <c r="C217" s="8" t="n"/>
       <c r="D217" s="8" t="n"/>
       <c r="E217" s="8" t="n"/>
+      <c r="F217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -3043,6 +3285,7 @@
       <c r="C218" s="8" t="n"/>
       <c r="D218" s="8" t="n"/>
       <c r="E218" s="8" t="n"/>
+      <c r="F218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -3050,10 +3293,11 @@
           <t>Mon 08 Mar 2027</t>
         </is>
       </c>
-      <c r="B219" s="5" t="n"/>
-      <c r="C219" s="5" t="n"/>
-      <c r="D219" s="5" t="n"/>
-      <c r="E219" s="5" t="n"/>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="4" t="n"/>
+      <c r="D219" s="4" t="n"/>
+      <c r="E219" s="4" t="n"/>
+      <c r="F219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -3061,10 +3305,11 @@
           <t>Tue 09 Mar 2027</t>
         </is>
       </c>
-      <c r="B220" s="5" t="n"/>
-      <c r="C220" s="5" t="n"/>
-      <c r="D220" s="5" t="n"/>
-      <c r="E220" s="5" t="n"/>
+      <c r="B220" s="4" t="n"/>
+      <c r="C220" s="4" t="n"/>
+      <c r="D220" s="4" t="n"/>
+      <c r="E220" s="4" t="n"/>
+      <c r="F220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -3072,10 +3317,11 @@
           <t>Wed 10 Mar 2027</t>
         </is>
       </c>
-      <c r="B221" s="5" t="n"/>
-      <c r="C221" s="5" t="n"/>
-      <c r="D221" s="5" t="n"/>
-      <c r="E221" s="5" t="n"/>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="4" t="n"/>
+      <c r="E221" s="4" t="n"/>
+      <c r="F221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -3083,10 +3329,11 @@
           <t>Thu 11 Mar 2027</t>
         </is>
       </c>
-      <c r="B222" s="5" t="n"/>
-      <c r="C222" s="5" t="n"/>
-      <c r="D222" s="5" t="n"/>
-      <c r="E222" s="5" t="n"/>
+      <c r="B222" s="4" t="n"/>
+      <c r="C222" s="4" t="n"/>
+      <c r="D222" s="4" t="n"/>
+      <c r="E222" s="4" t="n"/>
+      <c r="F222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -3094,10 +3341,11 @@
           <t>Fri 12 Mar 2027</t>
         </is>
       </c>
-      <c r="B223" s="5" t="n"/>
-      <c r="C223" s="5" t="n"/>
-      <c r="D223" s="5" t="n"/>
-      <c r="E223" s="5" t="n"/>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="4" t="n"/>
+      <c r="D223" s="4" t="n"/>
+      <c r="E223" s="4" t="n"/>
+      <c r="F223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -3109,6 +3357,7 @@
       <c r="C224" s="8" t="n"/>
       <c r="D224" s="8" t="n"/>
       <c r="E224" s="8" t="n"/>
+      <c r="F224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -3120,6 +3369,7 @@
       <c r="C225" s="8" t="n"/>
       <c r="D225" s="8" t="n"/>
       <c r="E225" s="8" t="n"/>
+      <c r="F225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -3127,10 +3377,11 @@
           <t>Mon 15 Mar 2027</t>
         </is>
       </c>
-      <c r="B226" s="5" t="n"/>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="5" t="n"/>
-      <c r="E226" s="5" t="n"/>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="4" t="n"/>
+      <c r="D226" s="4" t="n"/>
+      <c r="E226" s="4" t="n"/>
+      <c r="F226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -3138,10 +3389,11 @@
           <t>Tue 16 Mar 2027</t>
         </is>
       </c>
-      <c r="B227" s="5" t="n"/>
-      <c r="C227" s="5" t="n"/>
-      <c r="D227" s="5" t="n"/>
-      <c r="E227" s="5" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="4" t="n"/>
+      <c r="F227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -3149,10 +3401,11 @@
           <t>Wed 17 Mar 2027</t>
         </is>
       </c>
-      <c r="B228" s="5" t="n"/>
-      <c r="C228" s="5" t="n"/>
-      <c r="D228" s="5" t="n"/>
-      <c r="E228" s="5" t="n"/>
+      <c r="B228" s="4" t="n"/>
+      <c r="C228" s="4" t="n"/>
+      <c r="D228" s="4" t="n"/>
+      <c r="E228" s="4" t="n"/>
+      <c r="F228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -3160,10 +3413,11 @@
           <t>Thu 18 Mar 2027</t>
         </is>
       </c>
-      <c r="B229" s="5" t="n"/>
-      <c r="C229" s="5" t="n"/>
-      <c r="D229" s="5" t="n"/>
-      <c r="E229" s="5" t="n"/>
+      <c r="B229" s="4" t="n"/>
+      <c r="C229" s="4" t="n"/>
+      <c r="D229" s="4" t="n"/>
+      <c r="E229" s="4" t="n"/>
+      <c r="F229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -3171,10 +3425,11 @@
           <t>Fri 19 Mar 2027</t>
         </is>
       </c>
-      <c r="B230" s="5" t="n"/>
-      <c r="C230" s="5" t="n"/>
-      <c r="D230" s="5" t="n"/>
-      <c r="E230" s="5" t="n"/>
+      <c r="B230" s="4" t="n"/>
+      <c r="C230" s="4" t="n"/>
+      <c r="D230" s="4" t="n"/>
+      <c r="E230" s="4" t="n"/>
+      <c r="F230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -3186,6 +3441,7 @@
       <c r="C231" s="8" t="n"/>
       <c r="D231" s="8" t="n"/>
       <c r="E231" s="8" t="n"/>
+      <c r="F231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -3197,6 +3453,7 @@
       <c r="C232" s="8" t="n"/>
       <c r="D232" s="8" t="n"/>
       <c r="E232" s="8" t="n"/>
+      <c r="F232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -3204,10 +3461,11 @@
           <t>Mon 22 Mar 2027</t>
         </is>
       </c>
-      <c r="B233" s="5" t="n"/>
-      <c r="C233" s="5" t="n"/>
-      <c r="D233" s="5" t="n"/>
-      <c r="E233" s="5" t="n"/>
+      <c r="B233" s="4" t="n"/>
+      <c r="C233" s="4" t="n"/>
+      <c r="D233" s="4" t="n"/>
+      <c r="E233" s="4" t="n"/>
+      <c r="F233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -3215,10 +3473,11 @@
           <t>Tue 23 Mar 2027</t>
         </is>
       </c>
-      <c r="B234" s="5" t="n"/>
-      <c r="C234" s="5" t="n"/>
-      <c r="D234" s="5" t="n"/>
-      <c r="E234" s="5" t="n"/>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="4" t="n"/>
+      <c r="D234" s="4" t="n"/>
+      <c r="E234" s="4" t="n"/>
+      <c r="F234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -3226,10 +3485,11 @@
           <t>Wed 24 Mar 2027</t>
         </is>
       </c>
-      <c r="B235" s="5" t="n"/>
-      <c r="C235" s="5" t="n"/>
-      <c r="D235" s="5" t="n"/>
-      <c r="E235" s="5" t="n"/>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="4" t="n"/>
+      <c r="D235" s="4" t="n"/>
+      <c r="E235" s="4" t="n"/>
+      <c r="F235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -3237,10 +3497,11 @@
           <t>Thu 25 Mar 2027</t>
         </is>
       </c>
-      <c r="B236" s="5" t="n"/>
-      <c r="C236" s="5" t="n"/>
-      <c r="D236" s="5" t="n"/>
-      <c r="E236" s="5" t="n"/>
+      <c r="B236" s="4" t="n"/>
+      <c r="C236" s="4" t="n"/>
+      <c r="D236" s="4" t="n"/>
+      <c r="E236" s="4" t="n"/>
+      <c r="F236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -3248,10 +3509,11 @@
           <t>Fri 26 Mar 2027</t>
         </is>
       </c>
-      <c r="B237" s="5" t="n"/>
-      <c r="C237" s="5" t="n"/>
-      <c r="D237" s="5" t="n"/>
-      <c r="E237" s="5" t="n"/>
+      <c r="B237" s="4" t="n"/>
+      <c r="C237" s="4" t="n"/>
+      <c r="D237" s="4" t="n"/>
+      <c r="E237" s="4" t="n"/>
+      <c r="F237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -3263,6 +3525,7 @@
       <c r="C238" s="8" t="n"/>
       <c r="D238" s="8" t="n"/>
       <c r="E238" s="8" t="n"/>
+      <c r="F238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -3274,6 +3537,7 @@
       <c r="C239" s="8" t="n"/>
       <c r="D239" s="8" t="n"/>
       <c r="E239" s="8" t="n"/>
+      <c r="F239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -3281,10 +3545,11 @@
           <t>Mon 29 Mar 2027</t>
         </is>
       </c>
-      <c r="B240" s="5" t="n"/>
-      <c r="C240" s="5" t="n"/>
-      <c r="D240" s="5" t="n"/>
-      <c r="E240" s="5" t="n"/>
+      <c r="B240" s="4" t="n"/>
+      <c r="C240" s="4" t="n"/>
+      <c r="D240" s="4" t="n"/>
+      <c r="E240" s="4" t="n"/>
+      <c r="F240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -3292,10 +3557,11 @@
           <t>Tue 30 Mar 2027</t>
         </is>
       </c>
-      <c r="B241" s="5" t="n"/>
-      <c r="C241" s="5" t="n"/>
-      <c r="D241" s="5" t="n"/>
-      <c r="E241" s="5" t="n"/>
+      <c r="B241" s="4" t="n"/>
+      <c r="C241" s="4" t="n"/>
+      <c r="D241" s="4" t="n"/>
+      <c r="E241" s="4" t="n"/>
+      <c r="F241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -3303,14 +3569,15 @@
           <t>Wed 31 Mar 2027</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B242" s="4" t="n"/>
+      <c r="C242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C242" s="5" t="n"/>
-      <c r="D242" s="5" t="n"/>
-      <c r="E242" s="5" t="n"/>
+      <c r="D242" s="4" t="n"/>
+      <c r="E242" s="4" t="n"/>
+      <c r="F242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -3318,14 +3585,15 @@
           <t>Thu 01 Apr 2027</t>
         </is>
       </c>
-      <c r="B243" s="4" t="inlineStr">
+      <c r="B243" s="4" t="n"/>
+      <c r="C243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C243" s="5" t="n"/>
-      <c r="D243" s="5" t="n"/>
-      <c r="E243" s="5" t="n"/>
+      <c r="D243" s="4" t="n"/>
+      <c r="E243" s="4" t="n"/>
+      <c r="F243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -3333,14 +3601,15 @@
           <t>Fri 02 Apr 2027</t>
         </is>
       </c>
-      <c r="B244" s="4" t="inlineStr">
+      <c r="B244" s="4" t="n"/>
+      <c r="C244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C244" s="5" t="n"/>
-      <c r="D244" s="5" t="n"/>
-      <c r="E244" s="5" t="n"/>
+      <c r="D244" s="4" t="n"/>
+      <c r="E244" s="4" t="n"/>
+      <c r="F244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -3352,6 +3621,7 @@
       <c r="C245" s="8" t="n"/>
       <c r="D245" s="8" t="n"/>
       <c r="E245" s="8" t="n"/>
+      <c r="F245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -3363,6 +3633,7 @@
       <c r="C246" s="8" t="n"/>
       <c r="D246" s="8" t="n"/>
       <c r="E246" s="8" t="n"/>
+      <c r="F246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -3370,14 +3641,15 @@
           <t>Mon 05 Apr 2027</t>
         </is>
       </c>
-      <c r="B247" s="4" t="inlineStr">
+      <c r="B247" s="4" t="n"/>
+      <c r="C247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C247" s="5" t="n"/>
-      <c r="D247" s="5" t="n"/>
-      <c r="E247" s="5" t="n"/>
+      <c r="D247" s="4" t="n"/>
+      <c r="E247" s="4" t="n"/>
+      <c r="F247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -3385,14 +3657,15 @@
           <t>Tue 06 Apr 2027</t>
         </is>
       </c>
-      <c r="B248" s="4" t="inlineStr">
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="C248" s="5" t="n"/>
-      <c r="D248" s="5" t="n"/>
-      <c r="E248" s="5" t="n"/>
+      <c r="D248" s="4" t="n"/>
+      <c r="E248" s="4" t="n"/>
+      <c r="F248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,6 +497,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +528,11 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>WIL WILLIAMS</t>
         </is>
       </c>
@@ -546,6 +552,7 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -562,6 +569,7 @@
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -574,6 +582,7 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -586,6 +595,7 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -602,6 +612,7 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -614,6 +625,7 @@
       <c r="D7" s="8" t="n"/>
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -626,6 +638,7 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -638,6 +651,7 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -650,6 +664,7 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -662,6 +677,7 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -674,6 +690,7 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -690,6 +707,7 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -702,6 +720,7 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -714,6 +733,7 @@
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -726,6 +746,7 @@
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -738,6 +759,7 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -750,6 +772,7 @@
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -762,6 +785,7 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -774,6 +798,7 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -786,6 +811,7 @@
       <c r="D21" s="8" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -798,6 +824,7 @@
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -823,6 +850,12 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
+          <t>Sŵ Ni
+Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
           <t>Hansh Socials</t>
         </is>
       </c>
@@ -851,6 +884,12 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
+          <t>Sŵ Ni
+Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
           <t>Hansh Socials</t>
         </is>
       </c>
@@ -879,6 +918,12 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
+          <t>Sŵ Ni
+Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
           <t>Edit Annibynwyr</t>
         </is>
       </c>
@@ -907,6 +952,12 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
+          <t>Anifail Perffaith
+Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
           <t>Edit Annibynwyr</t>
         </is>
       </c>
@@ -934,6 +985,12 @@
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni
+TOIL - Darts</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -949,7 +1006,8 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -965,7 +1023,8 @@
       <c r="C29" s="8" t="n"/>
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -982,6 +1041,7 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -994,6 +1054,7 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1006,6 +1067,7 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1018,6 +1080,7 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1030,6 +1093,7 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1042,6 +1106,7 @@
       <c r="D35" s="8" t="n"/>
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1054,6 +1119,7 @@
       <c r="D36" s="8" t="n"/>
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1066,6 +1132,7 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1078,6 +1145,7 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1090,6 +1158,7 @@
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1102,6 +1171,7 @@
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1114,6 +1184,7 @@
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1126,6 +1197,7 @@
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1138,6 +1210,7 @@
       <c r="D43" s="8" t="n"/>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1154,6 +1227,7 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1170,6 +1244,7 @@
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1186,6 +1261,7 @@
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1198,6 +1274,7 @@
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1210,6 +1287,7 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1222,6 +1300,7 @@
       <c r="D49" s="8" t="n"/>
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
+      <c r="G49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1234,6 +1313,7 @@
       <c r="D50" s="8" t="n"/>
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
+      <c r="G50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1246,6 +1326,7 @@
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1258,6 +1339,7 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1270,6 +1352,7 @@
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1282,6 +1365,7 @@
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1298,6 +1382,7 @@
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1310,6 +1395,7 @@
       <c r="D56" s="8" t="n"/>
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1322,6 +1408,7 @@
       <c r="D57" s="8" t="n"/>
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1334,6 +1421,7 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1346,6 +1434,7 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1358,6 +1447,7 @@
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1370,6 +1460,7 @@
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1382,6 +1473,7 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1394,6 +1486,7 @@
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1406,6 +1499,7 @@
       <c r="D64" s="8" t="n"/>
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1418,6 +1512,7 @@
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1430,6 +1525,7 @@
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1446,6 +1542,7 @@
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1458,6 +1555,7 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1470,6 +1568,7 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1482,6 +1581,7 @@
       <c r="D70" s="8" t="n"/>
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
+      <c r="G70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1494,6 +1594,7 @@
       <c r="D71" s="8" t="n"/>
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1506,6 +1607,7 @@
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1518,6 +1620,7 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1530,6 +1633,7 @@
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1542,6 +1646,7 @@
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1554,6 +1659,7 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -1566,6 +1672,7 @@
       <c r="D77" s="8" t="n"/>
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -1578,6 +1685,7 @@
       <c r="D78" s="8" t="n"/>
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
+      <c r="G78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1590,6 +1698,7 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -1602,6 +1711,7 @@
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1614,6 +1724,7 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -1626,6 +1737,7 @@
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1638,6 +1750,7 @@
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -1650,6 +1763,7 @@
       <c r="D84" s="8" t="n"/>
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -1662,6 +1776,7 @@
       <c r="D85" s="8" t="n"/>
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -1674,6 +1789,7 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1686,6 +1802,7 @@
       <c r="D87" s="4" t="n"/>
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -1698,6 +1815,7 @@
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1710,6 +1828,7 @@
       <c r="D89" s="4" t="n"/>
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -1722,6 +1841,7 @@
       <c r="D90" s="4" t="n"/>
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -1734,6 +1854,7 @@
       <c r="D91" s="8" t="n"/>
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -1746,6 +1867,7 @@
       <c r="D92" s="8" t="n"/>
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1758,6 +1880,7 @@
       <c r="D93" s="4" t="n"/>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -1770,6 +1893,7 @@
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1782,6 +1906,7 @@
       <c r="D95" s="4" t="n"/>
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -1794,6 +1919,7 @@
       <c r="D96" s="4" t="n"/>
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1806,6 +1932,7 @@
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -1818,6 +1945,7 @@
       <c r="D98" s="8" t="n"/>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
+      <c r="G98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -1830,6 +1958,7 @@
       <c r="D99" s="8" t="n"/>
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
+      <c r="G99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -1842,6 +1971,7 @@
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1854,6 +1984,7 @@
       <c r="D101" s="4" t="n"/>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -1866,6 +1997,7 @@
       <c r="D102" s="4" t="n"/>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -1878,6 +2010,7 @@
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -1890,6 +2023,7 @@
       <c r="D104" s="4" t="n"/>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -1902,6 +2036,7 @@
       <c r="D105" s="8" t="n"/>
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
+      <c r="G105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -1914,6 +2049,7 @@
       <c r="D106" s="8" t="n"/>
       <c r="E106" s="8" t="n"/>
       <c r="F106" s="8" t="n"/>
+      <c r="G106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -1926,6 +2062,7 @@
       <c r="D107" s="4" t="n"/>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -1938,6 +2075,7 @@
       <c r="D108" s="4" t="n"/>
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -1950,6 +2088,7 @@
       <c r="D109" s="4" t="n"/>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -1962,6 +2101,7 @@
       <c r="D110" s="4" t="n"/>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
+      <c r="G110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -1978,6 +2118,7 @@
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -1990,6 +2131,7 @@
       <c r="D112" s="8" t="n"/>
       <c r="E112" s="8" t="n"/>
       <c r="F112" s="8" t="n"/>
+      <c r="G112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -2002,6 +2144,7 @@
       <c r="D113" s="8" t="n"/>
       <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
+      <c r="G113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2014,6 +2157,7 @@
       <c r="D114" s="4" t="n"/>
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2026,6 +2170,7 @@
       <c r="D115" s="4" t="n"/>
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -2038,6 +2183,7 @@
       <c r="D116" s="4" t="n"/>
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -2050,6 +2196,7 @@
       <c r="D117" s="4" t="n"/>
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2066,6 +2213,7 @@
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -2078,6 +2226,7 @@
       <c r="D119" s="8" t="n"/>
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
+      <c r="G119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -2090,6 +2239,7 @@
       <c r="D120" s="8" t="n"/>
       <c r="E120" s="8" t="n"/>
       <c r="F120" s="8" t="n"/>
+      <c r="G120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -2102,6 +2252,7 @@
       <c r="D121" s="4" t="n"/>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -2114,6 +2265,7 @@
       <c r="D122" s="4" t="n"/>
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -2126,6 +2278,7 @@
       <c r="D123" s="4" t="n"/>
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -2138,6 +2291,7 @@
       <c r="D124" s="4" t="n"/>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -2150,6 +2304,7 @@
       <c r="D125" s="4" t="n"/>
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -2162,6 +2317,7 @@
       <c r="D126" s="8" t="n"/>
       <c r="E126" s="8" t="n"/>
       <c r="F126" s="8" t="n"/>
+      <c r="G126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -2174,6 +2330,7 @@
       <c r="D127" s="8" t="n"/>
       <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n"/>
+      <c r="G127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -2186,6 +2343,7 @@
       <c r="D128" s="4" t="n"/>
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -2198,6 +2356,7 @@
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -2210,6 +2369,7 @@
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -2222,6 +2382,7 @@
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -2234,6 +2395,7 @@
       <c r="D132" s="4" t="n"/>
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -2246,6 +2408,7 @@
       <c r="D133" s="8" t="n"/>
       <c r="E133" s="8" t="n"/>
       <c r="F133" s="8" t="n"/>
+      <c r="G133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -2258,6 +2421,7 @@
       <c r="D134" s="8" t="n"/>
       <c r="E134" s="8" t="n"/>
       <c r="F134" s="8" t="n"/>
+      <c r="G134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -2270,6 +2434,7 @@
       <c r="D135" s="4" t="n"/>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -2286,6 +2451,7 @@
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -2302,6 +2468,7 @@
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -2318,6 +2485,7 @@
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -2334,6 +2502,7 @@
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -2346,6 +2515,7 @@
       <c r="D140" s="8" t="n"/>
       <c r="E140" s="8" t="n"/>
       <c r="F140" s="8" t="n"/>
+      <c r="G140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -2358,6 +2528,7 @@
       <c r="D141" s="8" t="n"/>
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="8" t="n"/>
+      <c r="G141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -2370,6 +2541,7 @@
       <c r="D142" s="4" t="n"/>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -2382,6 +2554,7 @@
       <c r="D143" s="4" t="n"/>
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -2394,6 +2567,7 @@
       <c r="D144" s="4" t="n"/>
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -2406,6 +2580,7 @@
       <c r="D145" s="4" t="n"/>
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -2418,6 +2593,7 @@
       <c r="D146" s="4" t="n"/>
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -2430,6 +2606,7 @@
       <c r="D147" s="8" t="n"/>
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n"/>
+      <c r="G147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -2442,6 +2619,7 @@
       <c r="D148" s="8" t="n"/>
       <c r="E148" s="8" t="n"/>
       <c r="F148" s="8" t="n"/>
+      <c r="G148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -2454,6 +2632,7 @@
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -2466,6 +2645,7 @@
       <c r="D150" s="4" t="n"/>
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -2478,6 +2658,7 @@
       <c r="D151" s="4" t="n"/>
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -2490,6 +2671,7 @@
       <c r="D152" s="4" t="n"/>
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -2502,6 +2684,7 @@
       <c r="D153" s="4" t="n"/>
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
+      <c r="G153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -2514,6 +2697,7 @@
       <c r="D154" s="8" t="n"/>
       <c r="E154" s="8" t="n"/>
       <c r="F154" s="8" t="n"/>
+      <c r="G154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -2526,6 +2710,7 @@
       <c r="D155" s="8" t="n"/>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
+      <c r="G155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -2538,6 +2723,7 @@
       <c r="D156" s="4" t="n"/>
       <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -2550,6 +2736,7 @@
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="4" t="n"/>
       <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -2566,6 +2753,7 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -2578,6 +2766,7 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="n"/>
+      <c r="G159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -2590,6 +2779,7 @@
       <c r="D160" s="4" t="n"/>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
+      <c r="G160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -2602,6 +2792,7 @@
       <c r="D161" s="8" t="n"/>
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
+      <c r="G161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -2614,6 +2805,7 @@
       <c r="D162" s="8" t="n"/>
       <c r="E162" s="8" t="n"/>
       <c r="F162" s="8" t="n"/>
+      <c r="G162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -2626,6 +2818,7 @@
       <c r="D163" s="4" t="n"/>
       <c r="E163" s="4" t="n"/>
       <c r="F163" s="4" t="n"/>
+      <c r="G163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -2638,6 +2831,7 @@
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="4" t="n"/>
+      <c r="G164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -2650,6 +2844,7 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="4" t="n"/>
+      <c r="G165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -2662,6 +2857,7 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="n"/>
+      <c r="G166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -2674,6 +2870,7 @@
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
+      <c r="G167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -2686,6 +2883,7 @@
       <c r="D168" s="8" t="n"/>
       <c r="E168" s="8" t="n"/>
       <c r="F168" s="8" t="n"/>
+      <c r="G168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -2698,6 +2896,7 @@
       <c r="D169" s="8" t="n"/>
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
+      <c r="G169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -2710,6 +2909,7 @@
       <c r="D170" s="4" t="n"/>
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="4" t="n"/>
+      <c r="G170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -2722,6 +2922,7 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="n"/>
+      <c r="G171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -2734,6 +2935,7 @@
       <c r="D172" s="4" t="n"/>
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
+      <c r="G172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -2746,6 +2948,7 @@
       <c r="D173" s="4" t="n"/>
       <c r="E173" s="4" t="n"/>
       <c r="F173" s="4" t="n"/>
+      <c r="G173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -2758,6 +2961,7 @@
       <c r="D174" s="4" t="n"/>
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="n"/>
+      <c r="G174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -2770,6 +2974,7 @@
       <c r="D175" s="8" t="n"/>
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
+      <c r="G175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -2782,6 +2987,7 @@
       <c r="D176" s="8" t="n"/>
       <c r="E176" s="8" t="n"/>
       <c r="F176" s="8" t="n"/>
+      <c r="G176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -2794,6 +3000,7 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="4" t="n"/>
       <c r="F177" s="4" t="n"/>
+      <c r="G177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -2806,6 +3013,7 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="4" t="n"/>
+      <c r="G178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -2818,6 +3026,7 @@
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="4" t="n"/>
       <c r="F179" s="4" t="n"/>
+      <c r="G179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -2830,6 +3039,7 @@
       <c r="D180" s="4" t="n"/>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="n"/>
+      <c r="G180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -2842,6 +3052,7 @@
       <c r="D181" s="4" t="n"/>
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="n"/>
+      <c r="G181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -2854,6 +3065,7 @@
       <c r="D182" s="8" t="n"/>
       <c r="E182" s="8" t="n"/>
       <c r="F182" s="8" t="n"/>
+      <c r="G182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -2866,6 +3078,7 @@
       <c r="D183" s="8" t="n"/>
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
+      <c r="G183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -2878,6 +3091,7 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="4" t="n"/>
       <c r="F184" s="4" t="n"/>
+      <c r="G184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -2890,6 +3104,7 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="4" t="n"/>
       <c r="F185" s="4" t="n"/>
+      <c r="G185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -2902,6 +3117,7 @@
       <c r="D186" s="4" t="n"/>
       <c r="E186" s="4" t="n"/>
       <c r="F186" s="4" t="n"/>
+      <c r="G186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -2914,6 +3130,7 @@
       <c r="D187" s="4" t="n"/>
       <c r="E187" s="4" t="n"/>
       <c r="F187" s="4" t="n"/>
+      <c r="G187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -2926,6 +3143,7 @@
       <c r="D188" s="4" t="n"/>
       <c r="E188" s="4" t="n"/>
       <c r="F188" s="4" t="n"/>
+      <c r="G188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -2938,6 +3156,7 @@
       <c r="D189" s="8" t="n"/>
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
+      <c r="G189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -2950,6 +3169,7 @@
       <c r="D190" s="8" t="n"/>
       <c r="E190" s="8" t="n"/>
       <c r="F190" s="8" t="n"/>
+      <c r="G190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -2962,6 +3182,7 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="4" t="n"/>
       <c r="F191" s="4" t="n"/>
+      <c r="G191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -2974,6 +3195,7 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="4" t="n"/>
       <c r="F192" s="4" t="n"/>
+      <c r="G192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -2986,6 +3208,7 @@
       <c r="D193" s="4" t="n"/>
       <c r="E193" s="4" t="n"/>
       <c r="F193" s="4" t="n"/>
+      <c r="G193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -2998,6 +3221,7 @@
       <c r="D194" s="4" t="n"/>
       <c r="E194" s="4" t="n"/>
       <c r="F194" s="4" t="n"/>
+      <c r="G194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -3010,6 +3234,7 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="4" t="n"/>
       <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -3022,6 +3247,7 @@
       <c r="D196" s="8" t="n"/>
       <c r="E196" s="8" t="n"/>
       <c r="F196" s="8" t="n"/>
+      <c r="G196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -3034,6 +3260,7 @@
       <c r="D197" s="8" t="n"/>
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
+      <c r="G197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -3046,6 +3273,7 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="4" t="n"/>
+      <c r="G198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -3058,6 +3286,7 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="4" t="n"/>
       <c r="F199" s="4" t="n"/>
+      <c r="G199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -3070,6 +3299,7 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="4" t="n"/>
       <c r="F200" s="4" t="n"/>
+      <c r="G200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -3082,6 +3312,7 @@
       <c r="D201" s="4" t="n"/>
       <c r="E201" s="4" t="n"/>
       <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -3094,6 +3325,7 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="4" t="n"/>
       <c r="F202" s="4" t="n"/>
+      <c r="G202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -3106,6 +3338,7 @@
       <c r="D203" s="8" t="n"/>
       <c r="E203" s="8" t="n"/>
       <c r="F203" s="8" t="n"/>
+      <c r="G203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -3118,6 +3351,7 @@
       <c r="D204" s="8" t="n"/>
       <c r="E204" s="8" t="n"/>
       <c r="F204" s="8" t="n"/>
+      <c r="G204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -3130,6 +3364,7 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="4" t="n"/>
       <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -3142,6 +3377,7 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="4" t="n"/>
       <c r="F206" s="4" t="n"/>
+      <c r="G206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -3154,6 +3390,7 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="4" t="n"/>
       <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -3166,6 +3403,7 @@
       <c r="D208" s="4" t="n"/>
       <c r="E208" s="4" t="n"/>
       <c r="F208" s="4" t="n"/>
+      <c r="G208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -3178,6 +3416,7 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="4" t="n"/>
       <c r="F209" s="4" t="n"/>
+      <c r="G209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -3190,6 +3429,7 @@
       <c r="D210" s="8" t="n"/>
       <c r="E210" s="8" t="n"/>
       <c r="F210" s="8" t="n"/>
+      <c r="G210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -3202,6 +3442,7 @@
       <c r="D211" s="8" t="n"/>
       <c r="E211" s="8" t="n"/>
       <c r="F211" s="8" t="n"/>
+      <c r="G211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -3214,6 +3455,7 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="4" t="n"/>
       <c r="F212" s="4" t="n"/>
+      <c r="G212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -3226,6 +3468,7 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="4" t="n"/>
       <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -3238,6 +3481,7 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="4" t="n"/>
       <c r="F214" s="4" t="n"/>
+      <c r="G214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -3250,6 +3494,7 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="4" t="n"/>
       <c r="F215" s="4" t="n"/>
+      <c r="G215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -3262,6 +3507,7 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="4" t="n"/>
       <c r="F216" s="4" t="n"/>
+      <c r="G216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -3274,6 +3520,7 @@
       <c r="D217" s="8" t="n"/>
       <c r="E217" s="8" t="n"/>
       <c r="F217" s="8" t="n"/>
+      <c r="G217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -3286,6 +3533,7 @@
       <c r="D218" s="8" t="n"/>
       <c r="E218" s="8" t="n"/>
       <c r="F218" s="8" t="n"/>
+      <c r="G218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -3298,6 +3546,7 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="4" t="n"/>
       <c r="F219" s="4" t="n"/>
+      <c r="G219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -3310,6 +3559,7 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="4" t="n"/>
       <c r="F220" s="4" t="n"/>
+      <c r="G220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -3322,6 +3572,7 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="4" t="n"/>
       <c r="F221" s="4" t="n"/>
+      <c r="G221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -3334,6 +3585,7 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="4" t="n"/>
       <c r="F222" s="4" t="n"/>
+      <c r="G222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -3346,6 +3598,7 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="4" t="n"/>
       <c r="F223" s="4" t="n"/>
+      <c r="G223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -3358,6 +3611,7 @@
       <c r="D224" s="8" t="n"/>
       <c r="E224" s="8" t="n"/>
       <c r="F224" s="8" t="n"/>
+      <c r="G224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -3370,6 +3624,7 @@
       <c r="D225" s="8" t="n"/>
       <c r="E225" s="8" t="n"/>
       <c r="F225" s="8" t="n"/>
+      <c r="G225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -3382,6 +3637,7 @@
       <c r="D226" s="4" t="n"/>
       <c r="E226" s="4" t="n"/>
       <c r="F226" s="4" t="n"/>
+      <c r="G226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -3394,6 +3650,7 @@
       <c r="D227" s="4" t="n"/>
       <c r="E227" s="4" t="n"/>
       <c r="F227" s="4" t="n"/>
+      <c r="G227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -3406,6 +3663,7 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="4" t="n"/>
       <c r="F228" s="4" t="n"/>
+      <c r="G228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -3418,6 +3676,7 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="4" t="n"/>
       <c r="F229" s="4" t="n"/>
+      <c r="G229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -3430,6 +3689,7 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="4" t="n"/>
       <c r="F230" s="4" t="n"/>
+      <c r="G230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -3442,6 +3702,7 @@
       <c r="D231" s="8" t="n"/>
       <c r="E231" s="8" t="n"/>
       <c r="F231" s="8" t="n"/>
+      <c r="G231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -3454,6 +3715,7 @@
       <c r="D232" s="8" t="n"/>
       <c r="E232" s="8" t="n"/>
       <c r="F232" s="8" t="n"/>
+      <c r="G232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -3466,6 +3728,7 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="4" t="n"/>
       <c r="F233" s="4" t="n"/>
+      <c r="G233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -3478,6 +3741,7 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="4" t="n"/>
       <c r="F234" s="4" t="n"/>
+      <c r="G234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -3490,6 +3754,7 @@
       <c r="D235" s="4" t="n"/>
       <c r="E235" s="4" t="n"/>
       <c r="F235" s="4" t="n"/>
+      <c r="G235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -3502,6 +3767,7 @@
       <c r="D236" s="4" t="n"/>
       <c r="E236" s="4" t="n"/>
       <c r="F236" s="4" t="n"/>
+      <c r="G236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -3514,6 +3780,7 @@
       <c r="D237" s="4" t="n"/>
       <c r="E237" s="4" t="n"/>
       <c r="F237" s="4" t="n"/>
+      <c r="G237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -3526,6 +3793,7 @@
       <c r="D238" s="8" t="n"/>
       <c r="E238" s="8" t="n"/>
       <c r="F238" s="8" t="n"/>
+      <c r="G238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -3538,6 +3806,7 @@
       <c r="D239" s="8" t="n"/>
       <c r="E239" s="8" t="n"/>
       <c r="F239" s="8" t="n"/>
+      <c r="G239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -3550,6 +3819,7 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="4" t="n"/>
       <c r="F240" s="4" t="n"/>
+      <c r="G240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -3562,6 +3832,7 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="4" t="n"/>
       <c r="F241" s="4" t="n"/>
+      <c r="G241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -3578,6 +3849,7 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="4" t="n"/>
+      <c r="G242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -3594,6 +3866,7 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="4" t="n"/>
       <c r="F243" s="4" t="n"/>
+      <c r="G243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -3610,6 +3883,7 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="4" t="n"/>
+      <c r="G244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -3622,6 +3896,7 @@
       <c r="D245" s="8" t="n"/>
       <c r="E245" s="8" t="n"/>
       <c r="F245" s="8" t="n"/>
+      <c r="G245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -3634,6 +3909,7 @@
       <c r="D246" s="8" t="n"/>
       <c r="E246" s="8" t="n"/>
       <c r="F246" s="8" t="n"/>
+      <c r="G246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -3650,6 +3926,7 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="4" t="n"/>
       <c r="F247" s="4" t="n"/>
+      <c r="G247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -3666,6 +3943,7 @@
       <c r="D248" s="4" t="n"/>
       <c r="E248" s="4" t="n"/>
       <c r="F248" s="4" t="n"/>
+      <c r="G248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:K248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -498,6 +498,10 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,32 +512,52 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Bethan Carlam</t>
+          <t>Bethan Evans</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Ceri Siggins</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cerys Pinkman</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Osh</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>WIL WILLIAMS</t>
+          <t>Lara Hughes</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Osian Lewis</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Owain Jones</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Rhodri Lewis</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Wil Williams</t>
         </is>
       </c>
     </row>
@@ -544,15 +568,19 @@
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -561,15 +589,19 @@
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -583,6 +615,10 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -596,6 +632,10 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -604,15 +644,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -626,6 +670,10 @@
       <c r="E7" s="8" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -639,6 +687,10 @@
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -652,6 +704,10 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -665,6 +721,10 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -678,6 +738,10 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -691,6 +755,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -699,15 +767,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -721,6 +793,10 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -734,6 +810,10 @@
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -747,6 +827,10 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -760,6 +844,10 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -773,6 +861,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -786,6 +878,10 @@
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -799,6 +895,10 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -812,6 +912,10 @@
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -825,6 +929,10 @@
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -838,23 +946,34 @@
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Mabli</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Sŵ Ni
-Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -871,24 +990,39 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Short</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Datblygu</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Sŵ Ni
-Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -905,24 +1039,43 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Short</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Sŵ Ni
-Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Black History 2026</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -939,24 +1092,39 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Short</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Anifail Perffaith</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Anifail Perffaith
-Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Black History 2026</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -974,23 +1142,34 @@
         </is>
       </c>
       <c r="C27" s="4" t="n"/>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>Sŵ Ni
-TOIL - Darts</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Black History 2026</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>TOIL - Darts</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1007,7 +1186,11 @@
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1024,7 +1207,11 @@
       <c r="D29" s="8" t="n"/>
       <c r="E29" s="8" t="n"/>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1042,6 +1229,10 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1055,6 +1246,10 @@
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1068,6 +1263,10 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1081,6 +1280,10 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1094,6 +1297,10 @@
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1107,6 +1314,10 @@
       <c r="E35" s="8" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1120,6 +1331,10 @@
       <c r="E36" s="8" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1133,6 +1348,10 @@
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1146,6 +1365,10 @@
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1159,6 +1382,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1172,6 +1399,10 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1185,6 +1416,10 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1198,6 +1433,10 @@
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1211,6 +1450,10 @@
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1219,15 +1462,19 @@
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1236,15 +1483,19 @@
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1253,15 +1504,19 @@
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1275,6 +1530,10 @@
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1288,6 +1547,10 @@
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1301,6 +1564,10 @@
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1314,6 +1581,10 @@
       <c r="E50" s="8" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1327,6 +1598,10 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1340,6 +1615,10 @@
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1353,6 +1632,10 @@
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1366,6 +1649,10 @@
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1374,15 +1661,19 @@
         </is>
       </c>
       <c r="B55" s="4" t="n"/>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1396,6 +1687,10 @@
       <c r="E56" s="8" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="8" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1409,6 +1704,10 @@
       <c r="E57" s="8" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="8" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1422,6 +1721,10 @@
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1435,6 +1738,10 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1448,6 +1755,10 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1461,6 +1772,10 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1474,6 +1789,10 @@
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1487,6 +1806,10 @@
       <c r="E63" s="8" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1500,6 +1823,10 @@
       <c r="E64" s="8" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1513,6 +1840,10 @@
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1526,6 +1857,10 @@
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
       <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1534,15 +1869,19 @@
         </is>
       </c>
       <c r="B67" s="4" t="n"/>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1556,6 +1895,10 @@
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1569,6 +1912,10 @@
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1582,6 +1929,10 @@
       <c r="E70" s="8" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1595,6 +1946,10 @@
       <c r="E71" s="8" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1608,6 +1963,10 @@
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1621,6 +1980,10 @@
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -1634,6 +1997,10 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1647,6 +2014,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -1660,6 +2031,10 @@
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -1673,6 +2048,10 @@
       <c r="E77" s="8" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -1686,6 +2065,10 @@
       <c r="E78" s="8" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -1699,6 +2082,10 @@
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -1712,6 +2099,10 @@
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="n"/>
+      <c r="J80" s="4" t="n"/>
+      <c r="K80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -1725,6 +2116,10 @@
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -1738,6 +2133,10 @@
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -1751,6 +2150,10 @@
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -1764,6 +2167,10 @@
       <c r="E84" s="8" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="8" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -1777,6 +2184,10 @@
       <c r="E85" s="8" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -1790,6 +2201,10 @@
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="n"/>
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -1803,6 +2218,10 @@
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -1816,6 +2235,10 @@
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
       <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
+      <c r="K88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -1829,6 +2252,10 @@
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
       <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -1842,6 +2269,10 @@
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
       <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -1855,6 +2286,10 @@
       <c r="E91" s="8" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -1868,6 +2303,10 @@
       <c r="E92" s="8" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="8" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -1881,6 +2320,10 @@
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
       <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -1894,6 +2337,10 @@
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -1907,6 +2354,10 @@
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
       <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -1920,6 +2371,10 @@
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
       <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -1933,6 +2388,10 @@
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
       <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -1946,6 +2405,10 @@
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -1959,6 +2422,10 @@
       <c r="E99" s="8" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -1972,6 +2439,10 @@
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -1985,6 +2456,10 @@
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -1998,6 +2473,10 @@
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+      <c r="I102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2011,6 +2490,10 @@
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2024,6 +2507,10 @@
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -2037,6 +2524,10 @@
       <c r="E105" s="8" t="n"/>
       <c r="F105" s="8" t="n"/>
       <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -2050,6 +2541,10 @@
       <c r="E106" s="8" t="n"/>
       <c r="F106" s="8" t="n"/>
       <c r="G106" s="8" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -2063,6 +2558,10 @@
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
       <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2076,6 +2575,10 @@
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
       <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="n"/>
+      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2089,6 +2592,10 @@
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2102,6 +2609,10 @@
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="4" t="n"/>
+      <c r="J110" s="4" t="n"/>
+      <c r="K110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2110,15 +2621,19 @@
         </is>
       </c>
       <c r="B111" s="4" t="n"/>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
+      <c r="K111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -2132,6 +2647,10 @@
       <c r="E112" s="8" t="n"/>
       <c r="F112" s="8" t="n"/>
       <c r="G112" s="8" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="8" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -2145,6 +2664,10 @@
       <c r="E113" s="8" t="n"/>
       <c r="F113" s="8" t="n"/>
       <c r="G113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2158,6 +2681,10 @@
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
       <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="n"/>
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2171,6 +2698,10 @@
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="n"/>
       <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -2184,6 +2715,10 @@
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="4" t="n"/>
+      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -2197,6 +2732,10 @@
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
       <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2205,15 +2744,19 @@
         </is>
       </c>
       <c r="B118" s="4" t="n"/>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
       <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -2227,6 +2770,10 @@
       <c r="E119" s="8" t="n"/>
       <c r="F119" s="8" t="n"/>
       <c r="G119" s="8" t="n"/>
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="8" t="n"/>
+      <c r="J119" s="8" t="n"/>
+      <c r="K119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -2240,6 +2787,10 @@
       <c r="E120" s="8" t="n"/>
       <c r="F120" s="8" t="n"/>
       <c r="G120" s="8" t="n"/>
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="8" t="n"/>
+      <c r="J120" s="8" t="n"/>
+      <c r="K120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -2253,6 +2804,10 @@
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -2266,6 +2821,10 @@
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -2279,6 +2838,10 @@
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
+      <c r="K123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -2292,6 +2855,10 @@
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="4" t="n"/>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
+      <c r="K124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -2305,6 +2872,10 @@
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -2318,6 +2889,10 @@
       <c r="E126" s="8" t="n"/>
       <c r="F126" s="8" t="n"/>
       <c r="G126" s="8" t="n"/>
+      <c r="H126" s="8" t="n"/>
+      <c r="I126" s="8" t="n"/>
+      <c r="J126" s="8" t="n"/>
+      <c r="K126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -2331,6 +2906,10 @@
       <c r="E127" s="8" t="n"/>
       <c r="F127" s="8" t="n"/>
       <c r="G127" s="8" t="n"/>
+      <c r="H127" s="8" t="n"/>
+      <c r="I127" s="8" t="n"/>
+      <c r="J127" s="8" t="n"/>
+      <c r="K127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -2344,6 +2923,10 @@
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="n"/>
       <c r="G128" s="4" t="n"/>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="n"/>
+      <c r="J128" s="4" t="n"/>
+      <c r="K128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -2357,6 +2940,10 @@
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="4" t="n"/>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="n"/>
+      <c r="J129" s="4" t="n"/>
+      <c r="K129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -2370,6 +2957,10 @@
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="4" t="n"/>
+      <c r="J130" s="4" t="n"/>
+      <c r="K130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -2383,6 +2974,10 @@
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
+      <c r="K131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -2396,6 +2991,10 @@
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="4" t="n"/>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
+      <c r="K132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -2409,6 +3008,10 @@
       <c r="E133" s="8" t="n"/>
       <c r="F133" s="8" t="n"/>
       <c r="G133" s="8" t="n"/>
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="8" t="n"/>
+      <c r="J133" s="8" t="n"/>
+      <c r="K133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -2422,6 +3025,10 @@
       <c r="E134" s="8" t="n"/>
       <c r="F134" s="8" t="n"/>
       <c r="G134" s="8" t="n"/>
+      <c r="H134" s="8" t="n"/>
+      <c r="I134" s="8" t="n"/>
+      <c r="J134" s="8" t="n"/>
+      <c r="K134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -2435,6 +3042,10 @@
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -2443,15 +3054,19 @@
         </is>
       </c>
       <c r="B136" s="4" t="n"/>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
       <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -2460,15 +3075,19 @@
         </is>
       </c>
       <c r="B137" s="4" t="n"/>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
       <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -2477,15 +3096,19 @@
         </is>
       </c>
       <c r="B138" s="4" t="n"/>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="D138" s="4" t="n"/>
-      <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
       <c r="G138" s="4" t="n"/>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="4" t="n"/>
+      <c r="J138" s="4" t="n"/>
+      <c r="K138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -2494,15 +3117,19 @@
         </is>
       </c>
       <c r="B139" s="4" t="n"/>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="D139" s="4" t="n"/>
-      <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
       <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -2516,6 +3143,10 @@
       <c r="E140" s="8" t="n"/>
       <c r="F140" s="8" t="n"/>
       <c r="G140" s="8" t="n"/>
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="8" t="n"/>
+      <c r="J140" s="8" t="n"/>
+      <c r="K140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -2529,6 +3160,10 @@
       <c r="E141" s="8" t="n"/>
       <c r="F141" s="8" t="n"/>
       <c r="G141" s="8" t="n"/>
+      <c r="H141" s="8" t="n"/>
+      <c r="I141" s="8" t="n"/>
+      <c r="J141" s="8" t="n"/>
+      <c r="K141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -2542,6 +3177,10 @@
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
       <c r="G142" s="4" t="n"/>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -2555,6 +3194,10 @@
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
       <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -2568,6 +3211,10 @@
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
       <c r="G144" s="4" t="n"/>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="4" t="n"/>
+      <c r="J144" s="4" t="n"/>
+      <c r="K144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -2581,6 +3228,10 @@
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
       <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -2594,6 +3245,10 @@
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
       <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -2607,6 +3262,10 @@
       <c r="E147" s="8" t="n"/>
       <c r="F147" s="8" t="n"/>
       <c r="G147" s="8" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="8" t="n"/>
+      <c r="J147" s="8" t="n"/>
+      <c r="K147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -2620,6 +3279,10 @@
       <c r="E148" s="8" t="n"/>
       <c r="F148" s="8" t="n"/>
       <c r="G148" s="8" t="n"/>
+      <c r="H148" s="8" t="n"/>
+      <c r="I148" s="8" t="n"/>
+      <c r="J148" s="8" t="n"/>
+      <c r="K148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -2633,6 +3296,10 @@
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
       <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="K149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -2646,6 +3313,10 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
       <c r="G150" s="4" t="n"/>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
+      <c r="K150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -2659,6 +3330,10 @@
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="n"/>
       <c r="G151" s="4" t="n"/>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
+      <c r="K151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -2672,6 +3347,10 @@
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="n"/>
       <c r="G152" s="4" t="n"/>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="4" t="n"/>
+      <c r="J152" s="4" t="n"/>
+      <c r="K152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -2685,6 +3364,10 @@
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
       <c r="G153" s="4" t="n"/>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="n"/>
+      <c r="J153" s="4" t="n"/>
+      <c r="K153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -2698,6 +3381,10 @@
       <c r="E154" s="8" t="n"/>
       <c r="F154" s="8" t="n"/>
       <c r="G154" s="8" t="n"/>
+      <c r="H154" s="8" t="n"/>
+      <c r="I154" s="8" t="n"/>
+      <c r="J154" s="8" t="n"/>
+      <c r="K154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -2711,6 +3398,10 @@
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
       <c r="G155" s="8" t="n"/>
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="8" t="n"/>
+      <c r="J155" s="8" t="n"/>
+      <c r="K155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -2724,6 +3415,10 @@
       <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="n"/>
       <c r="G156" s="4" t="n"/>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="4" t="n"/>
+      <c r="J156" s="4" t="n"/>
+      <c r="K156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -2737,6 +3432,10 @@
       <c r="E157" s="4" t="n"/>
       <c r="F157" s="4" t="n"/>
       <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
+      <c r="K157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -2745,15 +3444,19 @@
         </is>
       </c>
       <c r="B158" s="4" t="n"/>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="C158" s="4" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
-      <c r="D158" s="4" t="n"/>
-      <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="4" t="n"/>
+      <c r="J158" s="4" t="n"/>
+      <c r="K158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -2767,6 +3470,10 @@
       <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="n"/>
       <c r="G159" s="4" t="n"/>
+      <c r="H159" s="4" t="n"/>
+      <c r="I159" s="4" t="n"/>
+      <c r="J159" s="4" t="n"/>
+      <c r="K159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -2780,6 +3487,10 @@
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
+      <c r="H160" s="4" t="n"/>
+      <c r="I160" s="4" t="n"/>
+      <c r="J160" s="4" t="n"/>
+      <c r="K160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -2793,6 +3504,10 @@
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
       <c r="G161" s="8" t="n"/>
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="8" t="n"/>
+      <c r="J161" s="8" t="n"/>
+      <c r="K161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -2806,6 +3521,10 @@
       <c r="E162" s="8" t="n"/>
       <c r="F162" s="8" t="n"/>
       <c r="G162" s="8" t="n"/>
+      <c r="H162" s="8" t="n"/>
+      <c r="I162" s="8" t="n"/>
+      <c r="J162" s="8" t="n"/>
+      <c r="K162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -2819,6 +3538,10 @@
       <c r="E163" s="4" t="n"/>
       <c r="F163" s="4" t="n"/>
       <c r="G163" s="4" t="n"/>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
+      <c r="K163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -2832,6 +3555,10 @@
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="4" t="n"/>
       <c r="G164" s="4" t="n"/>
+      <c r="H164" s="4" t="n"/>
+      <c r="I164" s="4" t="n"/>
+      <c r="J164" s="4" t="n"/>
+      <c r="K164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -2845,6 +3572,10 @@
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="4" t="n"/>
       <c r="G165" s="4" t="n"/>
+      <c r="H165" s="4" t="n"/>
+      <c r="I165" s="4" t="n"/>
+      <c r="J165" s="4" t="n"/>
+      <c r="K165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -2858,6 +3589,10 @@
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="n"/>
       <c r="G166" s="4" t="n"/>
+      <c r="H166" s="4" t="n"/>
+      <c r="I166" s="4" t="n"/>
+      <c r="J166" s="4" t="n"/>
+      <c r="K166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -2871,6 +3606,10 @@
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
       <c r="G167" s="4" t="n"/>
+      <c r="H167" s="4" t="n"/>
+      <c r="I167" s="4" t="n"/>
+      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -2884,6 +3623,10 @@
       <c r="E168" s="8" t="n"/>
       <c r="F168" s="8" t="n"/>
       <c r="G168" s="8" t="n"/>
+      <c r="H168" s="8" t="n"/>
+      <c r="I168" s="8" t="n"/>
+      <c r="J168" s="8" t="n"/>
+      <c r="K168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -2897,6 +3640,10 @@
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
       <c r="G169" s="8" t="n"/>
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+      <c r="K169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -2910,6 +3657,10 @@
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="4" t="n"/>
       <c r="G170" s="4" t="n"/>
+      <c r="H170" s="4" t="n"/>
+      <c r="I170" s="4" t="n"/>
+      <c r="J170" s="4" t="n"/>
+      <c r="K170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -2923,6 +3674,10 @@
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="n"/>
       <c r="G171" s="4" t="n"/>
+      <c r="H171" s="4" t="n"/>
+      <c r="I171" s="4" t="n"/>
+      <c r="J171" s="4" t="n"/>
+      <c r="K171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -2936,6 +3691,10 @@
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
       <c r="G172" s="4" t="n"/>
+      <c r="H172" s="4" t="n"/>
+      <c r="I172" s="4" t="n"/>
+      <c r="J172" s="4" t="n"/>
+      <c r="K172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -2949,6 +3708,10 @@
       <c r="E173" s="4" t="n"/>
       <c r="F173" s="4" t="n"/>
       <c r="G173" s="4" t="n"/>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
+      <c r="K173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -2962,6 +3725,10 @@
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="n"/>
       <c r="G174" s="4" t="n"/>
+      <c r="H174" s="4" t="n"/>
+      <c r="I174" s="4" t="n"/>
+      <c r="J174" s="4" t="n"/>
+      <c r="K174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -2975,6 +3742,10 @@
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
       <c r="G175" s="8" t="n"/>
+      <c r="H175" s="8" t="n"/>
+      <c r="I175" s="8" t="n"/>
+      <c r="J175" s="8" t="n"/>
+      <c r="K175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -2988,6 +3759,10 @@
       <c r="E176" s="8" t="n"/>
       <c r="F176" s="8" t="n"/>
       <c r="G176" s="8" t="n"/>
+      <c r="H176" s="8" t="n"/>
+      <c r="I176" s="8" t="n"/>
+      <c r="J176" s="8" t="n"/>
+      <c r="K176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -3001,6 +3776,10 @@
       <c r="E177" s="4" t="n"/>
       <c r="F177" s="4" t="n"/>
       <c r="G177" s="4" t="n"/>
+      <c r="H177" s="4" t="n"/>
+      <c r="I177" s="4" t="n"/>
+      <c r="J177" s="4" t="n"/>
+      <c r="K177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -3014,6 +3793,10 @@
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="4" t="n"/>
       <c r="G178" s="4" t="n"/>
+      <c r="H178" s="4" t="n"/>
+      <c r="I178" s="4" t="n"/>
+      <c r="J178" s="4" t="n"/>
+      <c r="K178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -3027,6 +3810,10 @@
       <c r="E179" s="4" t="n"/>
       <c r="F179" s="4" t="n"/>
       <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
+      <c r="K179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -3040,6 +3827,10 @@
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="n"/>
       <c r="G180" s="4" t="n"/>
+      <c r="H180" s="4" t="n"/>
+      <c r="I180" s="4" t="n"/>
+      <c r="J180" s="4" t="n"/>
+      <c r="K180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -3053,6 +3844,10 @@
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="n"/>
       <c r="G181" s="4" t="n"/>
+      <c r="H181" s="4" t="n"/>
+      <c r="I181" s="4" t="n"/>
+      <c r="J181" s="4" t="n"/>
+      <c r="K181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -3066,6 +3861,10 @@
       <c r="E182" s="8" t="n"/>
       <c r="F182" s="8" t="n"/>
       <c r="G182" s="8" t="n"/>
+      <c r="H182" s="8" t="n"/>
+      <c r="I182" s="8" t="n"/>
+      <c r="J182" s="8" t="n"/>
+      <c r="K182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -3079,6 +3878,10 @@
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
       <c r="G183" s="8" t="n"/>
+      <c r="H183" s="8" t="n"/>
+      <c r="I183" s="8" t="n"/>
+      <c r="J183" s="8" t="n"/>
+      <c r="K183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -3092,6 +3895,10 @@
       <c r="E184" s="4" t="n"/>
       <c r="F184" s="4" t="n"/>
       <c r="G184" s="4" t="n"/>
+      <c r="H184" s="4" t="n"/>
+      <c r="I184" s="4" t="n"/>
+      <c r="J184" s="4" t="n"/>
+      <c r="K184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -3105,6 +3912,10 @@
       <c r="E185" s="4" t="n"/>
       <c r="F185" s="4" t="n"/>
       <c r="G185" s="4" t="n"/>
+      <c r="H185" s="4" t="n"/>
+      <c r="I185" s="4" t="n"/>
+      <c r="J185" s="4" t="n"/>
+      <c r="K185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -3118,6 +3929,10 @@
       <c r="E186" s="4" t="n"/>
       <c r="F186" s="4" t="n"/>
       <c r="G186" s="4" t="n"/>
+      <c r="H186" s="4" t="n"/>
+      <c r="I186" s="4" t="n"/>
+      <c r="J186" s="4" t="n"/>
+      <c r="K186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -3131,6 +3946,10 @@
       <c r="E187" s="4" t="n"/>
       <c r="F187" s="4" t="n"/>
       <c r="G187" s="4" t="n"/>
+      <c r="H187" s="4" t="n"/>
+      <c r="I187" s="4" t="n"/>
+      <c r="J187" s="4" t="n"/>
+      <c r="K187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -3144,6 +3963,10 @@
       <c r="E188" s="4" t="n"/>
       <c r="F188" s="4" t="n"/>
       <c r="G188" s="4" t="n"/>
+      <c r="H188" s="4" t="n"/>
+      <c r="I188" s="4" t="n"/>
+      <c r="J188" s="4" t="n"/>
+      <c r="K188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -3157,6 +3980,10 @@
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
       <c r="G189" s="8" t="n"/>
+      <c r="H189" s="8" t="n"/>
+      <c r="I189" s="8" t="n"/>
+      <c r="J189" s="8" t="n"/>
+      <c r="K189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -3170,6 +3997,10 @@
       <c r="E190" s="8" t="n"/>
       <c r="F190" s="8" t="n"/>
       <c r="G190" s="8" t="n"/>
+      <c r="H190" s="8" t="n"/>
+      <c r="I190" s="8" t="n"/>
+      <c r="J190" s="8" t="n"/>
+      <c r="K190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -3183,6 +4014,10 @@
       <c r="E191" s="4" t="n"/>
       <c r="F191" s="4" t="n"/>
       <c r="G191" s="4" t="n"/>
+      <c r="H191" s="4" t="n"/>
+      <c r="I191" s="4" t="n"/>
+      <c r="J191" s="4" t="n"/>
+      <c r="K191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -3196,6 +4031,10 @@
       <c r="E192" s="4" t="n"/>
       <c r="F192" s="4" t="n"/>
       <c r="G192" s="4" t="n"/>
+      <c r="H192" s="4" t="n"/>
+      <c r="I192" s="4" t="n"/>
+      <c r="J192" s="4" t="n"/>
+      <c r="K192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -3209,6 +4048,10 @@
       <c r="E193" s="4" t="n"/>
       <c r="F193" s="4" t="n"/>
       <c r="G193" s="4" t="n"/>
+      <c r="H193" s="4" t="n"/>
+      <c r="I193" s="4" t="n"/>
+      <c r="J193" s="4" t="n"/>
+      <c r="K193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -3222,6 +4065,10 @@
       <c r="E194" s="4" t="n"/>
       <c r="F194" s="4" t="n"/>
       <c r="G194" s="4" t="n"/>
+      <c r="H194" s="4" t="n"/>
+      <c r="I194" s="4" t="n"/>
+      <c r="J194" s="4" t="n"/>
+      <c r="K194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -3235,6 +4082,10 @@
       <c r="E195" s="4" t="n"/>
       <c r="F195" s="4" t="n"/>
       <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -3248,6 +4099,10 @@
       <c r="E196" s="8" t="n"/>
       <c r="F196" s="8" t="n"/>
       <c r="G196" s="8" t="n"/>
+      <c r="H196" s="8" t="n"/>
+      <c r="I196" s="8" t="n"/>
+      <c r="J196" s="8" t="n"/>
+      <c r="K196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -3261,6 +4116,10 @@
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
       <c r="G197" s="8" t="n"/>
+      <c r="H197" s="8" t="n"/>
+      <c r="I197" s="8" t="n"/>
+      <c r="J197" s="8" t="n"/>
+      <c r="K197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -3274,6 +4133,10 @@
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="4" t="n"/>
       <c r="G198" s="4" t="n"/>
+      <c r="H198" s="4" t="n"/>
+      <c r="I198" s="4" t="n"/>
+      <c r="J198" s="4" t="n"/>
+      <c r="K198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -3287,6 +4150,10 @@
       <c r="E199" s="4" t="n"/>
       <c r="F199" s="4" t="n"/>
       <c r="G199" s="4" t="n"/>
+      <c r="H199" s="4" t="n"/>
+      <c r="I199" s="4" t="n"/>
+      <c r="J199" s="4" t="n"/>
+      <c r="K199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -3300,6 +4167,10 @@
       <c r="E200" s="4" t="n"/>
       <c r="F200" s="4" t="n"/>
       <c r="G200" s="4" t="n"/>
+      <c r="H200" s="4" t="n"/>
+      <c r="I200" s="4" t="n"/>
+      <c r="J200" s="4" t="n"/>
+      <c r="K200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -3313,6 +4184,10 @@
       <c r="E201" s="4" t="n"/>
       <c r="F201" s="4" t="n"/>
       <c r="G201" s="4" t="n"/>
+      <c r="H201" s="4" t="n"/>
+      <c r="I201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
+      <c r="K201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -3326,6 +4201,10 @@
       <c r="E202" s="4" t="n"/>
       <c r="F202" s="4" t="n"/>
       <c r="G202" s="4" t="n"/>
+      <c r="H202" s="4" t="n"/>
+      <c r="I202" s="4" t="n"/>
+      <c r="J202" s="4" t="n"/>
+      <c r="K202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -3339,6 +4218,10 @@
       <c r="E203" s="8" t="n"/>
       <c r="F203" s="8" t="n"/>
       <c r="G203" s="8" t="n"/>
+      <c r="H203" s="8" t="n"/>
+      <c r="I203" s="8" t="n"/>
+      <c r="J203" s="8" t="n"/>
+      <c r="K203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -3352,6 +4235,10 @@
       <c r="E204" s="8" t="n"/>
       <c r="F204" s="8" t="n"/>
       <c r="G204" s="8" t="n"/>
+      <c r="H204" s="8" t="n"/>
+      <c r="I204" s="8" t="n"/>
+      <c r="J204" s="8" t="n"/>
+      <c r="K204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -3365,6 +4252,10 @@
       <c r="E205" s="4" t="n"/>
       <c r="F205" s="4" t="n"/>
       <c r="G205" s="4" t="n"/>
+      <c r="H205" s="4" t="n"/>
+      <c r="I205" s="4" t="n"/>
+      <c r="J205" s="4" t="n"/>
+      <c r="K205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -3378,6 +4269,10 @@
       <c r="E206" s="4" t="n"/>
       <c r="F206" s="4" t="n"/>
       <c r="G206" s="4" t="n"/>
+      <c r="H206" s="4" t="n"/>
+      <c r="I206" s="4" t="n"/>
+      <c r="J206" s="4" t="n"/>
+      <c r="K206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -3391,6 +4286,10 @@
       <c r="E207" s="4" t="n"/>
       <c r="F207" s="4" t="n"/>
       <c r="G207" s="4" t="n"/>
+      <c r="H207" s="4" t="n"/>
+      <c r="I207" s="4" t="n"/>
+      <c r="J207" s="4" t="n"/>
+      <c r="K207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -3404,6 +4303,10 @@
       <c r="E208" s="4" t="n"/>
       <c r="F208" s="4" t="n"/>
       <c r="G208" s="4" t="n"/>
+      <c r="H208" s="4" t="n"/>
+      <c r="I208" s="4" t="n"/>
+      <c r="J208" s="4" t="n"/>
+      <c r="K208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -3417,6 +4320,10 @@
       <c r="E209" s="4" t="n"/>
       <c r="F209" s="4" t="n"/>
       <c r="G209" s="4" t="n"/>
+      <c r="H209" s="4" t="n"/>
+      <c r="I209" s="4" t="n"/>
+      <c r="J209" s="4" t="n"/>
+      <c r="K209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -3430,6 +4337,10 @@
       <c r="E210" s="8" t="n"/>
       <c r="F210" s="8" t="n"/>
       <c r="G210" s="8" t="n"/>
+      <c r="H210" s="8" t="n"/>
+      <c r="I210" s="8" t="n"/>
+      <c r="J210" s="8" t="n"/>
+      <c r="K210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -3443,6 +4354,10 @@
       <c r="E211" s="8" t="n"/>
       <c r="F211" s="8" t="n"/>
       <c r="G211" s="8" t="n"/>
+      <c r="H211" s="8" t="n"/>
+      <c r="I211" s="8" t="n"/>
+      <c r="J211" s="8" t="n"/>
+      <c r="K211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -3456,6 +4371,10 @@
       <c r="E212" s="4" t="n"/>
       <c r="F212" s="4" t="n"/>
       <c r="G212" s="4" t="n"/>
+      <c r="H212" s="4" t="n"/>
+      <c r="I212" s="4" t="n"/>
+      <c r="J212" s="4" t="n"/>
+      <c r="K212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -3469,6 +4388,10 @@
       <c r="E213" s="4" t="n"/>
       <c r="F213" s="4" t="n"/>
       <c r="G213" s="4" t="n"/>
+      <c r="H213" s="4" t="n"/>
+      <c r="I213" s="4" t="n"/>
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -3482,6 +4405,10 @@
       <c r="E214" s="4" t="n"/>
       <c r="F214" s="4" t="n"/>
       <c r="G214" s="4" t="n"/>
+      <c r="H214" s="4" t="n"/>
+      <c r="I214" s="4" t="n"/>
+      <c r="J214" s="4" t="n"/>
+      <c r="K214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -3495,6 +4422,10 @@
       <c r="E215" s="4" t="n"/>
       <c r="F215" s="4" t="n"/>
       <c r="G215" s="4" t="n"/>
+      <c r="H215" s="4" t="n"/>
+      <c r="I215" s="4" t="n"/>
+      <c r="J215" s="4" t="n"/>
+      <c r="K215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -3508,6 +4439,10 @@
       <c r="E216" s="4" t="n"/>
       <c r="F216" s="4" t="n"/>
       <c r="G216" s="4" t="n"/>
+      <c r="H216" s="4" t="n"/>
+      <c r="I216" s="4" t="n"/>
+      <c r="J216" s="4" t="n"/>
+      <c r="K216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -3521,6 +4456,10 @@
       <c r="E217" s="8" t="n"/>
       <c r="F217" s="8" t="n"/>
       <c r="G217" s="8" t="n"/>
+      <c r="H217" s="8" t="n"/>
+      <c r="I217" s="8" t="n"/>
+      <c r="J217" s="8" t="n"/>
+      <c r="K217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -3534,6 +4473,10 @@
       <c r="E218" s="8" t="n"/>
       <c r="F218" s="8" t="n"/>
       <c r="G218" s="8" t="n"/>
+      <c r="H218" s="8" t="n"/>
+      <c r="I218" s="8" t="n"/>
+      <c r="J218" s="8" t="n"/>
+      <c r="K218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -3547,6 +4490,10 @@
       <c r="E219" s="4" t="n"/>
       <c r="F219" s="4" t="n"/>
       <c r="G219" s="4" t="n"/>
+      <c r="H219" s="4" t="n"/>
+      <c r="I219" s="4" t="n"/>
+      <c r="J219" s="4" t="n"/>
+      <c r="K219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -3560,6 +4507,10 @@
       <c r="E220" s="4" t="n"/>
       <c r="F220" s="4" t="n"/>
       <c r="G220" s="4" t="n"/>
+      <c r="H220" s="4" t="n"/>
+      <c r="I220" s="4" t="n"/>
+      <c r="J220" s="4" t="n"/>
+      <c r="K220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -3573,6 +4524,10 @@
       <c r="E221" s="4" t="n"/>
       <c r="F221" s="4" t="n"/>
       <c r="G221" s="4" t="n"/>
+      <c r="H221" s="4" t="n"/>
+      <c r="I221" s="4" t="n"/>
+      <c r="J221" s="4" t="n"/>
+      <c r="K221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -3586,6 +4541,10 @@
       <c r="E222" s="4" t="n"/>
       <c r="F222" s="4" t="n"/>
       <c r="G222" s="4" t="n"/>
+      <c r="H222" s="4" t="n"/>
+      <c r="I222" s="4" t="n"/>
+      <c r="J222" s="4" t="n"/>
+      <c r="K222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -3599,6 +4558,10 @@
       <c r="E223" s="4" t="n"/>
       <c r="F223" s="4" t="n"/>
       <c r="G223" s="4" t="n"/>
+      <c r="H223" s="4" t="n"/>
+      <c r="I223" s="4" t="n"/>
+      <c r="J223" s="4" t="n"/>
+      <c r="K223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -3612,6 +4575,10 @@
       <c r="E224" s="8" t="n"/>
       <c r="F224" s="8" t="n"/>
       <c r="G224" s="8" t="n"/>
+      <c r="H224" s="8" t="n"/>
+      <c r="I224" s="8" t="n"/>
+      <c r="J224" s="8" t="n"/>
+      <c r="K224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -3625,6 +4592,10 @@
       <c r="E225" s="8" t="n"/>
       <c r="F225" s="8" t="n"/>
       <c r="G225" s="8" t="n"/>
+      <c r="H225" s="8" t="n"/>
+      <c r="I225" s="8" t="n"/>
+      <c r="J225" s="8" t="n"/>
+      <c r="K225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -3638,6 +4609,10 @@
       <c r="E226" s="4" t="n"/>
       <c r="F226" s="4" t="n"/>
       <c r="G226" s="4" t="n"/>
+      <c r="H226" s="4" t="n"/>
+      <c r="I226" s="4" t="n"/>
+      <c r="J226" s="4" t="n"/>
+      <c r="K226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -3651,6 +4626,10 @@
       <c r="E227" s="4" t="n"/>
       <c r="F227" s="4" t="n"/>
       <c r="G227" s="4" t="n"/>
+      <c r="H227" s="4" t="n"/>
+      <c r="I227" s="4" t="n"/>
+      <c r="J227" s="4" t="n"/>
+      <c r="K227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -3664,6 +4643,10 @@
       <c r="E228" s="4" t="n"/>
       <c r="F228" s="4" t="n"/>
       <c r="G228" s="4" t="n"/>
+      <c r="H228" s="4" t="n"/>
+      <c r="I228" s="4" t="n"/>
+      <c r="J228" s="4" t="n"/>
+      <c r="K228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -3677,6 +4660,10 @@
       <c r="E229" s="4" t="n"/>
       <c r="F229" s="4" t="n"/>
       <c r="G229" s="4" t="n"/>
+      <c r="H229" s="4" t="n"/>
+      <c r="I229" s="4" t="n"/>
+      <c r="J229" s="4" t="n"/>
+      <c r="K229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -3690,6 +4677,10 @@
       <c r="E230" s="4" t="n"/>
       <c r="F230" s="4" t="n"/>
       <c r="G230" s="4" t="n"/>
+      <c r="H230" s="4" t="n"/>
+      <c r="I230" s="4" t="n"/>
+      <c r="J230" s="4" t="n"/>
+      <c r="K230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -3703,6 +4694,10 @@
       <c r="E231" s="8" t="n"/>
       <c r="F231" s="8" t="n"/>
       <c r="G231" s="8" t="n"/>
+      <c r="H231" s="8" t="n"/>
+      <c r="I231" s="8" t="n"/>
+      <c r="J231" s="8" t="n"/>
+      <c r="K231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -3716,6 +4711,10 @@
       <c r="E232" s="8" t="n"/>
       <c r="F232" s="8" t="n"/>
       <c r="G232" s="8" t="n"/>
+      <c r="H232" s="8" t="n"/>
+      <c r="I232" s="8" t="n"/>
+      <c r="J232" s="8" t="n"/>
+      <c r="K232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -3729,6 +4728,10 @@
       <c r="E233" s="4" t="n"/>
       <c r="F233" s="4" t="n"/>
       <c r="G233" s="4" t="n"/>
+      <c r="H233" s="4" t="n"/>
+      <c r="I233" s="4" t="n"/>
+      <c r="J233" s="4" t="n"/>
+      <c r="K233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -3742,6 +4745,10 @@
       <c r="E234" s="4" t="n"/>
       <c r="F234" s="4" t="n"/>
       <c r="G234" s="4" t="n"/>
+      <c r="H234" s="4" t="n"/>
+      <c r="I234" s="4" t="n"/>
+      <c r="J234" s="4" t="n"/>
+      <c r="K234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -3755,6 +4762,10 @@
       <c r="E235" s="4" t="n"/>
       <c r="F235" s="4" t="n"/>
       <c r="G235" s="4" t="n"/>
+      <c r="H235" s="4" t="n"/>
+      <c r="I235" s="4" t="n"/>
+      <c r="J235" s="4" t="n"/>
+      <c r="K235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -3768,6 +4779,10 @@
       <c r="E236" s="4" t="n"/>
       <c r="F236" s="4" t="n"/>
       <c r="G236" s="4" t="n"/>
+      <c r="H236" s="4" t="n"/>
+      <c r="I236" s="4" t="n"/>
+      <c r="J236" s="4" t="n"/>
+      <c r="K236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -3781,6 +4796,10 @@
       <c r="E237" s="4" t="n"/>
       <c r="F237" s="4" t="n"/>
       <c r="G237" s="4" t="n"/>
+      <c r="H237" s="4" t="n"/>
+      <c r="I237" s="4" t="n"/>
+      <c r="J237" s="4" t="n"/>
+      <c r="K237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -3794,6 +4813,10 @@
       <c r="E238" s="8" t="n"/>
       <c r="F238" s="8" t="n"/>
       <c r="G238" s="8" t="n"/>
+      <c r="H238" s="8" t="n"/>
+      <c r="I238" s="8" t="n"/>
+      <c r="J238" s="8" t="n"/>
+      <c r="K238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -3807,6 +4830,10 @@
       <c r="E239" s="8" t="n"/>
       <c r="F239" s="8" t="n"/>
       <c r="G239" s="8" t="n"/>
+      <c r="H239" s="8" t="n"/>
+      <c r="I239" s="8" t="n"/>
+      <c r="J239" s="8" t="n"/>
+      <c r="K239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -3820,6 +4847,10 @@
       <c r="E240" s="4" t="n"/>
       <c r="F240" s="4" t="n"/>
       <c r="G240" s="4" t="n"/>
+      <c r="H240" s="4" t="n"/>
+      <c r="I240" s="4" t="n"/>
+      <c r="J240" s="4" t="n"/>
+      <c r="K240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -3833,6 +4864,10 @@
       <c r="E241" s="4" t="n"/>
       <c r="F241" s="4" t="n"/>
       <c r="G241" s="4" t="n"/>
+      <c r="H241" s="4" t="n"/>
+      <c r="I241" s="4" t="n"/>
+      <c r="J241" s="4" t="n"/>
+      <c r="K241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -3841,15 +4876,19 @@
         </is>
       </c>
       <c r="B242" s="4" t="n"/>
-      <c r="C242" s="5" t="inlineStr">
+      <c r="C242" s="4" t="n"/>
+      <c r="D242" s="4" t="n"/>
+      <c r="E242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D242" s="4" t="n"/>
-      <c r="E242" s="4" t="n"/>
       <c r="F242" s="4" t="n"/>
       <c r="G242" s="4" t="n"/>
+      <c r="H242" s="4" t="n"/>
+      <c r="I242" s="4" t="n"/>
+      <c r="J242" s="4" t="n"/>
+      <c r="K242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -3858,15 +4897,19 @@
         </is>
       </c>
       <c r="B243" s="4" t="n"/>
-      <c r="C243" s="5" t="inlineStr">
+      <c r="C243" s="4" t="n"/>
+      <c r="D243" s="4" t="n"/>
+      <c r="E243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D243" s="4" t="n"/>
-      <c r="E243" s="4" t="n"/>
       <c r="F243" s="4" t="n"/>
       <c r="G243" s="4" t="n"/>
+      <c r="H243" s="4" t="n"/>
+      <c r="I243" s="4" t="n"/>
+      <c r="J243" s="4" t="n"/>
+      <c r="K243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -3875,15 +4918,19 @@
         </is>
       </c>
       <c r="B244" s="4" t="n"/>
-      <c r="C244" s="5" t="inlineStr">
+      <c r="C244" s="4" t="n"/>
+      <c r="D244" s="4" t="n"/>
+      <c r="E244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D244" s="4" t="n"/>
-      <c r="E244" s="4" t="n"/>
       <c r="F244" s="4" t="n"/>
       <c r="G244" s="4" t="n"/>
+      <c r="H244" s="4" t="n"/>
+      <c r="I244" s="4" t="n"/>
+      <c r="J244" s="4" t="n"/>
+      <c r="K244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -3897,6 +4944,10 @@
       <c r="E245" s="8" t="n"/>
       <c r="F245" s="8" t="n"/>
       <c r="G245" s="8" t="n"/>
+      <c r="H245" s="8" t="n"/>
+      <c r="I245" s="8" t="n"/>
+      <c r="J245" s="8" t="n"/>
+      <c r="K245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -3910,6 +4961,10 @@
       <c r="E246" s="8" t="n"/>
       <c r="F246" s="8" t="n"/>
       <c r="G246" s="8" t="n"/>
+      <c r="H246" s="8" t="n"/>
+      <c r="I246" s="8" t="n"/>
+      <c r="J246" s="8" t="n"/>
+      <c r="K246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -3918,15 +4973,19 @@
         </is>
       </c>
       <c r="B247" s="4" t="n"/>
-      <c r="C247" s="5" t="inlineStr">
+      <c r="C247" s="4" t="n"/>
+      <c r="D247" s="4" t="n"/>
+      <c r="E247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D247" s="4" t="n"/>
-      <c r="E247" s="4" t="n"/>
       <c r="F247" s="4" t="n"/>
       <c r="G247" s="4" t="n"/>
+      <c r="H247" s="4" t="n"/>
+      <c r="I247" s="4" t="n"/>
+      <c r="J247" s="4" t="n"/>
+      <c r="K247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -3935,15 +4994,19 @@
         </is>
       </c>
       <c r="B248" s="4" t="n"/>
-      <c r="C248" s="5" t="inlineStr">
+      <c r="C248" s="4" t="n"/>
+      <c r="D248" s="4" t="n"/>
+      <c r="E248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="D248" s="4" t="n"/>
-      <c r="E248" s="4" t="n"/>
       <c r="F248" s="4" t="n"/>
       <c r="G248" s="4" t="n"/>
+      <c r="H248" s="4" t="n"/>
+      <c r="I248" s="4" t="n"/>
+      <c r="J248" s="4" t="n"/>
+      <c r="K248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K248"/>
+  <dimension ref="A1:L248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,7 @@
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,35 +528,40 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Elin Jones</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Lara Hughes</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Osian Lewis</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Owain Jones</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Rhodri Lewis</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -570,17 +576,18 @@
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -591,17 +598,18 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -619,6 +627,7 @@
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -636,6 +645,7 @@
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -646,17 +656,18 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -674,6 +685,7 @@
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -691,6 +703,7 @@
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -708,6 +721,7 @@
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -725,6 +739,7 @@
       <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -742,6 +757,7 @@
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -759,6 +775,7 @@
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -769,17 +786,18 @@
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -797,6 +815,7 @@
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -814,6 +833,7 @@
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -831,6 +851,7 @@
       <c r="I16" s="4" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -848,6 +869,7 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -865,6 +887,7 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -882,6 +905,7 @@
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -899,6 +923,7 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -916,6 +941,7 @@
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -933,6 +959,7 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -952,28 +979,29 @@
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1001,28 +1029,29 @@
         </is>
       </c>
       <c r="E24" s="4" t="n"/>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1050,32 +1079,33 @@
         </is>
       </c>
       <c r="E25" s="4" t="n"/>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Black History 2026</t>
-        </is>
-      </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1102,29 +1132,38 @@
           <t>Anifail Perffaith</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>A/L - 1/2 Day Annual Leave</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Datblygu</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Black History 2026</t>
-        </is>
-      </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1147,29 +1186,38 @@
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Datblygu</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1190,7 +1238,8 @@
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
-      <c r="K28" s="10" t="inlineStr">
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1211,7 +1260,8 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
-      <c r="K29" s="10" t="inlineStr">
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1233,6 +1283,7 @@
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1250,6 +1301,7 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1267,6 +1319,7 @@
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1284,6 +1337,7 @@
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1301,6 +1355,7 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -1318,6 +1373,7 @@
       <c r="I35" s="8" t="n"/>
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1335,6 +1391,7 @@
       <c r="I36" s="8" t="n"/>
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1352,6 +1409,7 @@
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1369,6 +1427,7 @@
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1386,6 +1445,7 @@
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1403,6 +1463,7 @@
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1420,6 +1481,7 @@
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1437,6 +1499,7 @@
       <c r="I42" s="8" t="n"/>
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1454,6 +1517,7 @@
       <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1464,17 +1528,18 @@
       <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1485,17 +1550,18 @@
       <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1506,17 +1572,18 @@
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1534,6 +1601,7 @@
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1551,6 +1619,7 @@
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1568,6 +1637,7 @@
       <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1585,6 +1655,7 @@
       <c r="I50" s="8" t="n"/>
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1602,6 +1673,7 @@
       <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1619,6 +1691,7 @@
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1636,6 +1709,7 @@
       <c r="I53" s="4" t="n"/>
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1653,6 +1727,7 @@
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1663,17 +1738,18 @@
       <c r="B55" s="4" t="n"/>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1691,6 +1767,7 @@
       <c r="I56" s="8" t="n"/>
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1708,6 +1785,7 @@
       <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1725,6 +1803,7 @@
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1742,6 +1821,7 @@
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1759,6 +1839,7 @@
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1776,6 +1857,7 @@
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1793,6 +1875,7 @@
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1810,6 +1893,7 @@
       <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -1827,6 +1911,7 @@
       <c r="I64" s="8" t="n"/>
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1844,6 +1929,7 @@
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1861,6 +1947,7 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1871,17 +1958,18 @@
       <c r="B67" s="4" t="n"/>
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1899,6 +1987,7 @@
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1916,6 +2005,7 @@
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -1933,6 +2023,7 @@
       <c r="I70" s="8" t="n"/>
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
+      <c r="L70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -1950,6 +2041,7 @@
       <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1967,6 +2059,7 @@
       <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1984,6 +2077,7 @@
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2001,6 +2095,7 @@
       <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2018,6 +2113,7 @@
       <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2035,6 +2131,7 @@
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -2052,6 +2149,7 @@
       <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -2069,6 +2167,7 @@
       <c r="I78" s="8" t="n"/>
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
+      <c r="L78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2086,6 +2185,7 @@
       <c r="I79" s="4" t="n"/>
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2103,6 +2203,7 @@
       <c r="I80" s="4" t="n"/>
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2120,6 +2221,7 @@
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2137,6 +2239,7 @@
       <c r="I82" s="4" t="n"/>
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2154,6 +2257,7 @@
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -2171,6 +2275,7 @@
       <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
+      <c r="L84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -2188,6 +2293,7 @@
       <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2205,6 +2311,7 @@
       <c r="I86" s="4" t="n"/>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2222,6 +2329,7 @@
       <c r="I87" s="4" t="n"/>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
+      <c r="L87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2239,6 +2347,7 @@
       <c r="I88" s="4" t="n"/>
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2256,6 +2365,7 @@
       <c r="I89" s="4" t="n"/>
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2273,6 +2383,7 @@
       <c r="I90" s="4" t="n"/>
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -2290,6 +2401,7 @@
       <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -2307,6 +2419,7 @@
       <c r="I92" s="8" t="n"/>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2324,6 +2437,7 @@
       <c r="I93" s="4" t="n"/>
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2341,6 +2455,7 @@
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2358,6 +2473,7 @@
       <c r="I95" s="4" t="n"/>
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2375,6 +2491,7 @@
       <c r="I96" s="4" t="n"/>
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2392,6 +2509,7 @@
       <c r="I97" s="4" t="n"/>
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -2409,6 +2527,7 @@
       <c r="I98" s="8" t="n"/>
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -2426,6 +2545,7 @@
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2443,6 +2563,7 @@
       <c r="I100" s="4" t="n"/>
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -2460,6 +2581,7 @@
       <c r="I101" s="4" t="n"/>
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
+      <c r="L101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2477,6 +2599,7 @@
       <c r="I102" s="4" t="n"/>
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2494,6 +2617,7 @@
       <c r="I103" s="4" t="n"/>
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2511,6 +2635,7 @@
       <c r="I104" s="4" t="n"/>
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -2528,6 +2653,7 @@
       <c r="I105" s="8" t="n"/>
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
+      <c r="L105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -2545,6 +2671,7 @@
       <c r="I106" s="8" t="n"/>
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
+      <c r="L106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -2562,6 +2689,7 @@
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
+      <c r="L107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2579,6 +2707,7 @@
       <c r="I108" s="4" t="n"/>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
+      <c r="L108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2596,6 +2725,7 @@
       <c r="I109" s="4" t="n"/>
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2613,6 +2743,7 @@
       <c r="I110" s="4" t="n"/>
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
+      <c r="L110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2623,17 +2754,18 @@
       <c r="B111" s="4" t="n"/>
       <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="n"/>
-      <c r="E111" s="5" t="inlineStr">
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F111" s="4" t="n"/>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="4" t="n"/>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
+      <c r="L111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -2651,6 +2783,7 @@
       <c r="I112" s="8" t="n"/>
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
+      <c r="L112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -2668,6 +2801,7 @@
       <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2685,6 +2819,7 @@
       <c r="I114" s="4" t="n"/>
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2702,6 +2837,7 @@
       <c r="I115" s="4" t="n"/>
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -2719,6 +2855,7 @@
       <c r="I116" s="4" t="n"/>
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
+      <c r="L116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -2736,6 +2873,7 @@
       <c r="I117" s="4" t="n"/>
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2746,17 +2884,18 @@
       <c r="B118" s="4" t="n"/>
       <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="n"/>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F118" s="4" t="n"/>
       <c r="G118" s="4" t="n"/>
       <c r="H118" s="4" t="n"/>
       <c r="I118" s="4" t="n"/>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -2774,6 +2913,7 @@
       <c r="I119" s="8" t="n"/>
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
+      <c r="L119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -2791,6 +2931,7 @@
       <c r="I120" s="8" t="n"/>
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
+      <c r="L120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -2808,6 +2949,7 @@
       <c r="I121" s="4" t="n"/>
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -2825,6 +2967,7 @@
       <c r="I122" s="4" t="n"/>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -2842,6 +2985,7 @@
       <c r="I123" s="4" t="n"/>
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
+      <c r="L123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -2859,6 +3003,7 @@
       <c r="I124" s="4" t="n"/>
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
+      <c r="L124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -2876,6 +3021,7 @@
       <c r="I125" s="4" t="n"/>
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -2893,6 +3039,7 @@
       <c r="I126" s="8" t="n"/>
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
+      <c r="L126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -2910,6 +3057,7 @@
       <c r="I127" s="8" t="n"/>
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="8" t="n"/>
+      <c r="L127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -2927,6 +3075,7 @@
       <c r="I128" s="4" t="n"/>
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
+      <c r="L128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -2944,6 +3093,7 @@
       <c r="I129" s="4" t="n"/>
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -2961,6 +3111,7 @@
       <c r="I130" s="4" t="n"/>
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
+      <c r="L130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -2978,6 +3129,7 @@
       <c r="I131" s="4" t="n"/>
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -2995,6 +3147,7 @@
       <c r="I132" s="4" t="n"/>
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
+      <c r="L132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -3012,6 +3165,7 @@
       <c r="I133" s="8" t="n"/>
       <c r="J133" s="8" t="n"/>
       <c r="K133" s="8" t="n"/>
+      <c r="L133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -3029,6 +3183,7 @@
       <c r="I134" s="8" t="n"/>
       <c r="J134" s="8" t="n"/>
       <c r="K134" s="8" t="n"/>
+      <c r="L134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3046,6 +3201,7 @@
       <c r="I135" s="4" t="n"/>
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3056,17 +3212,18 @@
       <c r="B136" s="4" t="n"/>
       <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F136" s="4" t="n"/>
       <c r="G136" s="4" t="n"/>
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="4" t="n"/>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3077,17 +3234,18 @@
       <c r="B137" s="4" t="n"/>
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
-      <c r="E137" s="5" t="inlineStr">
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F137" s="4" t="n"/>
       <c r="G137" s="4" t="n"/>
       <c r="H137" s="4" t="n"/>
       <c r="I137" s="4" t="n"/>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3098,17 +3256,18 @@
       <c r="B138" s="4" t="n"/>
       <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
-      <c r="E138" s="5" t="inlineStr">
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F138" s="4" t="n"/>
       <c r="G138" s="4" t="n"/>
       <c r="H138" s="4" t="n"/>
       <c r="I138" s="4" t="n"/>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
+      <c r="L138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3119,17 +3278,18 @@
       <c r="B139" s="4" t="n"/>
       <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F139" s="4" t="n"/>
       <c r="G139" s="4" t="n"/>
       <c r="H139" s="4" t="n"/>
       <c r="I139" s="4" t="n"/>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -3147,6 +3307,7 @@
       <c r="I140" s="8" t="n"/>
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
+      <c r="L140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -3164,6 +3325,7 @@
       <c r="I141" s="8" t="n"/>
       <c r="J141" s="8" t="n"/>
       <c r="K141" s="8" t="n"/>
+      <c r="L141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3181,6 +3343,7 @@
       <c r="I142" s="4" t="n"/>
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3198,6 +3361,7 @@
       <c r="I143" s="4" t="n"/>
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
+      <c r="L143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -3215,6 +3379,7 @@
       <c r="I144" s="4" t="n"/>
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
+      <c r="L144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -3232,6 +3397,7 @@
       <c r="I145" s="4" t="n"/>
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -3249,6 +3415,7 @@
       <c r="I146" s="4" t="n"/>
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -3266,6 +3433,7 @@
       <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
+      <c r="L147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -3283,6 +3451,7 @@
       <c r="I148" s="8" t="n"/>
       <c r="J148" s="8" t="n"/>
       <c r="K148" s="8" t="n"/>
+      <c r="L148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -3300,6 +3469,7 @@
       <c r="I149" s="4" t="n"/>
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -3317,6 +3487,7 @@
       <c r="I150" s="4" t="n"/>
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
+      <c r="L150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -3334,6 +3505,7 @@
       <c r="I151" s="4" t="n"/>
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
+      <c r="L151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -3351,6 +3523,7 @@
       <c r="I152" s="4" t="n"/>
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
+      <c r="L152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -3368,6 +3541,7 @@
       <c r="I153" s="4" t="n"/>
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -3385,6 +3559,7 @@
       <c r="I154" s="8" t="n"/>
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
+      <c r="L154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -3402,6 +3577,7 @@
       <c r="I155" s="8" t="n"/>
       <c r="J155" s="8" t="n"/>
       <c r="K155" s="8" t="n"/>
+      <c r="L155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -3419,6 +3595,7 @@
       <c r="I156" s="4" t="n"/>
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
+      <c r="L156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -3436,6 +3613,7 @@
       <c r="I157" s="4" t="n"/>
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -3446,17 +3624,18 @@
       <c r="B158" s="4" t="n"/>
       <c r="C158" s="4" t="n"/>
       <c r="D158" s="4" t="n"/>
-      <c r="E158" s="5" t="inlineStr">
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
-      <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
       <c r="H158" s="4" t="n"/>
       <c r="I158" s="4" t="n"/>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
+      <c r="L158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -3474,6 +3653,7 @@
       <c r="I159" s="4" t="n"/>
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
+      <c r="L159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -3491,6 +3671,7 @@
       <c r="I160" s="4" t="n"/>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
+      <c r="L160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -3508,6 +3689,7 @@
       <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n"/>
       <c r="K161" s="8" t="n"/>
+      <c r="L161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -3525,6 +3707,7 @@
       <c r="I162" s="8" t="n"/>
       <c r="J162" s="8" t="n"/>
       <c r="K162" s="8" t="n"/>
+      <c r="L162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -3542,6 +3725,7 @@
       <c r="I163" s="4" t="n"/>
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
+      <c r="L163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -3559,6 +3743,7 @@
       <c r="I164" s="4" t="n"/>
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
+      <c r="L164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -3576,6 +3761,7 @@
       <c r="I165" s="4" t="n"/>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -3593,6 +3779,7 @@
       <c r="I166" s="4" t="n"/>
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
+      <c r="L166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -3610,6 +3797,7 @@
       <c r="I167" s="4" t="n"/>
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
+      <c r="L167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -3627,6 +3815,7 @@
       <c r="I168" s="8" t="n"/>
       <c r="J168" s="8" t="n"/>
       <c r="K168" s="8" t="n"/>
+      <c r="L168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -3644,6 +3833,7 @@
       <c r="I169" s="8" t="n"/>
       <c r="J169" s="8" t="n"/>
       <c r="K169" s="8" t="n"/>
+      <c r="L169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -3661,6 +3851,7 @@
       <c r="I170" s="4" t="n"/>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
+      <c r="L170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -3678,6 +3869,7 @@
       <c r="I171" s="4" t="n"/>
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
+      <c r="L171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -3695,6 +3887,7 @@
       <c r="I172" s="4" t="n"/>
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
+      <c r="L172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -3712,6 +3905,7 @@
       <c r="I173" s="4" t="n"/>
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -3729,6 +3923,7 @@
       <c r="I174" s="4" t="n"/>
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
+      <c r="L174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -3746,6 +3941,7 @@
       <c r="I175" s="8" t="n"/>
       <c r="J175" s="8" t="n"/>
       <c r="K175" s="8" t="n"/>
+      <c r="L175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -3763,6 +3959,7 @@
       <c r="I176" s="8" t="n"/>
       <c r="J176" s="8" t="n"/>
       <c r="K176" s="8" t="n"/>
+      <c r="L176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -3780,6 +3977,7 @@
       <c r="I177" s="4" t="n"/>
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
+      <c r="L177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -3797,6 +3995,7 @@
       <c r="I178" s="4" t="n"/>
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
+      <c r="L178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -3814,6 +4013,7 @@
       <c r="I179" s="4" t="n"/>
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -3831,6 +4031,7 @@
       <c r="I180" s="4" t="n"/>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
+      <c r="L180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -3848,6 +4049,7 @@
       <c r="I181" s="4" t="n"/>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -3865,6 +4067,7 @@
       <c r="I182" s="8" t="n"/>
       <c r="J182" s="8" t="n"/>
       <c r="K182" s="8" t="n"/>
+      <c r="L182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -3882,6 +4085,7 @@
       <c r="I183" s="8" t="n"/>
       <c r="J183" s="8" t="n"/>
       <c r="K183" s="8" t="n"/>
+      <c r="L183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -3899,6 +4103,7 @@
       <c r="I184" s="4" t="n"/>
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
+      <c r="L184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -3916,6 +4121,7 @@
       <c r="I185" s="4" t="n"/>
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -3933,6 +4139,7 @@
       <c r="I186" s="4" t="n"/>
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
+      <c r="L186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -3950,6 +4157,7 @@
       <c r="I187" s="4" t="n"/>
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -3967,6 +4175,7 @@
       <c r="I188" s="4" t="n"/>
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
+      <c r="L188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -3984,6 +4193,7 @@
       <c r="I189" s="8" t="n"/>
       <c r="J189" s="8" t="n"/>
       <c r="K189" s="8" t="n"/>
+      <c r="L189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -4001,6 +4211,7 @@
       <c r="I190" s="8" t="n"/>
       <c r="J190" s="8" t="n"/>
       <c r="K190" s="8" t="n"/>
+      <c r="L190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4018,6 +4229,7 @@
       <c r="I191" s="4" t="n"/>
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4035,6 +4247,7 @@
       <c r="I192" s="4" t="n"/>
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
+      <c r="L192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4052,6 +4265,7 @@
       <c r="I193" s="4" t="n"/>
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4069,6 +4283,7 @@
       <c r="I194" s="4" t="n"/>
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
+      <c r="L194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4086,6 +4301,7 @@
       <c r="I195" s="4" t="n"/>
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -4103,6 +4319,7 @@
       <c r="I196" s="8" t="n"/>
       <c r="J196" s="8" t="n"/>
       <c r="K196" s="8" t="n"/>
+      <c r="L196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -4120,6 +4337,7 @@
       <c r="I197" s="8" t="n"/>
       <c r="J197" s="8" t="n"/>
       <c r="K197" s="8" t="n"/>
+      <c r="L197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -4137,6 +4355,7 @@
       <c r="I198" s="4" t="n"/>
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
+      <c r="L198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -4154,6 +4373,7 @@
       <c r="I199" s="4" t="n"/>
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
+      <c r="L199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -4171,6 +4391,7 @@
       <c r="I200" s="4" t="n"/>
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
+      <c r="L200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -4188,6 +4409,7 @@
       <c r="I201" s="4" t="n"/>
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -4205,6 +4427,7 @@
       <c r="I202" s="4" t="n"/>
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
+      <c r="L202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -4222,6 +4445,7 @@
       <c r="I203" s="8" t="n"/>
       <c r="J203" s="8" t="n"/>
       <c r="K203" s="8" t="n"/>
+      <c r="L203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -4239,6 +4463,7 @@
       <c r="I204" s="8" t="n"/>
       <c r="J204" s="8" t="n"/>
       <c r="K204" s="8" t="n"/>
+      <c r="L204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -4256,6 +4481,7 @@
       <c r="I205" s="4" t="n"/>
       <c r="J205" s="4" t="n"/>
       <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -4273,6 +4499,7 @@
       <c r="I206" s="4" t="n"/>
       <c r="J206" s="4" t="n"/>
       <c r="K206" s="4" t="n"/>
+      <c r="L206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -4290,6 +4517,7 @@
       <c r="I207" s="4" t="n"/>
       <c r="J207" s="4" t="n"/>
       <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -4307,6 +4535,7 @@
       <c r="I208" s="4" t="n"/>
       <c r="J208" s="4" t="n"/>
       <c r="K208" s="4" t="n"/>
+      <c r="L208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -4324,6 +4553,7 @@
       <c r="I209" s="4" t="n"/>
       <c r="J209" s="4" t="n"/>
       <c r="K209" s="4" t="n"/>
+      <c r="L209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -4341,6 +4571,7 @@
       <c r="I210" s="8" t="n"/>
       <c r="J210" s="8" t="n"/>
       <c r="K210" s="8" t="n"/>
+      <c r="L210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -4358,6 +4589,7 @@
       <c r="I211" s="8" t="n"/>
       <c r="J211" s="8" t="n"/>
       <c r="K211" s="8" t="n"/>
+      <c r="L211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -4375,6 +4607,7 @@
       <c r="I212" s="4" t="n"/>
       <c r="J212" s="4" t="n"/>
       <c r="K212" s="4" t="n"/>
+      <c r="L212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -4392,6 +4625,7 @@
       <c r="I213" s="4" t="n"/>
       <c r="J213" s="4" t="n"/>
       <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -4409,6 +4643,7 @@
       <c r="I214" s="4" t="n"/>
       <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n"/>
+      <c r="L214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -4426,6 +4661,7 @@
       <c r="I215" s="4" t="n"/>
       <c r="J215" s="4" t="n"/>
       <c r="K215" s="4" t="n"/>
+      <c r="L215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -4443,6 +4679,7 @@
       <c r="I216" s="4" t="n"/>
       <c r="J216" s="4" t="n"/>
       <c r="K216" s="4" t="n"/>
+      <c r="L216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -4460,6 +4697,7 @@
       <c r="I217" s="8" t="n"/>
       <c r="J217" s="8" t="n"/>
       <c r="K217" s="8" t="n"/>
+      <c r="L217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -4477,6 +4715,7 @@
       <c r="I218" s="8" t="n"/>
       <c r="J218" s="8" t="n"/>
       <c r="K218" s="8" t="n"/>
+      <c r="L218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -4494,6 +4733,7 @@
       <c r="I219" s="4" t="n"/>
       <c r="J219" s="4" t="n"/>
       <c r="K219" s="4" t="n"/>
+      <c r="L219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -4511,6 +4751,7 @@
       <c r="I220" s="4" t="n"/>
       <c r="J220" s="4" t="n"/>
       <c r="K220" s="4" t="n"/>
+      <c r="L220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -4528,6 +4769,7 @@
       <c r="I221" s="4" t="n"/>
       <c r="J221" s="4" t="n"/>
       <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -4545,6 +4787,7 @@
       <c r="I222" s="4" t="n"/>
       <c r="J222" s="4" t="n"/>
       <c r="K222" s="4" t="n"/>
+      <c r="L222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -4562,6 +4805,7 @@
       <c r="I223" s="4" t="n"/>
       <c r="J223" s="4" t="n"/>
       <c r="K223" s="4" t="n"/>
+      <c r="L223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -4579,6 +4823,7 @@
       <c r="I224" s="8" t="n"/>
       <c r="J224" s="8" t="n"/>
       <c r="K224" s="8" t="n"/>
+      <c r="L224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -4596,6 +4841,7 @@
       <c r="I225" s="8" t="n"/>
       <c r="J225" s="8" t="n"/>
       <c r="K225" s="8" t="n"/>
+      <c r="L225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -4613,6 +4859,7 @@
       <c r="I226" s="4" t="n"/>
       <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
+      <c r="L226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -4630,6 +4877,7 @@
       <c r="I227" s="4" t="n"/>
       <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
+      <c r="L227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -4647,6 +4895,7 @@
       <c r="I228" s="4" t="n"/>
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
+      <c r="L228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -4664,6 +4913,7 @@
       <c r="I229" s="4" t="n"/>
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
+      <c r="L229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -4681,6 +4931,7 @@
       <c r="I230" s="4" t="n"/>
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
+      <c r="L230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -4698,6 +4949,7 @@
       <c r="I231" s="8" t="n"/>
       <c r="J231" s="8" t="n"/>
       <c r="K231" s="8" t="n"/>
+      <c r="L231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -4715,6 +4967,7 @@
       <c r="I232" s="8" t="n"/>
       <c r="J232" s="8" t="n"/>
       <c r="K232" s="8" t="n"/>
+      <c r="L232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -4732,6 +4985,7 @@
       <c r="I233" s="4" t="n"/>
       <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
+      <c r="L233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -4749,6 +5003,7 @@
       <c r="I234" s="4" t="n"/>
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
+      <c r="L234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -4766,6 +5021,7 @@
       <c r="I235" s="4" t="n"/>
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
+      <c r="L235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -4783,6 +5039,7 @@
       <c r="I236" s="4" t="n"/>
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
+      <c r="L236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -4800,6 +5057,7 @@
       <c r="I237" s="4" t="n"/>
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
+      <c r="L237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -4817,6 +5075,7 @@
       <c r="I238" s="8" t="n"/>
       <c r="J238" s="8" t="n"/>
       <c r="K238" s="8" t="n"/>
+      <c r="L238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -4834,6 +5093,7 @@
       <c r="I239" s="8" t="n"/>
       <c r="J239" s="8" t="n"/>
       <c r="K239" s="8" t="n"/>
+      <c r="L239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -4851,6 +5111,7 @@
       <c r="I240" s="4" t="n"/>
       <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
+      <c r="L240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -4868,6 +5129,7 @@
       <c r="I241" s="4" t="n"/>
       <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
+      <c r="L241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -4878,17 +5140,18 @@
       <c r="B242" s="4" t="n"/>
       <c r="C242" s="4" t="n"/>
       <c r="D242" s="4" t="n"/>
-      <c r="E242" s="5" t="inlineStr">
+      <c r="E242" s="4" t="n"/>
+      <c r="F242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F242" s="4" t="n"/>
       <c r="G242" s="4" t="n"/>
       <c r="H242" s="4" t="n"/>
       <c r="I242" s="4" t="n"/>
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
+      <c r="L242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -4899,17 +5162,18 @@
       <c r="B243" s="4" t="n"/>
       <c r="C243" s="4" t="n"/>
       <c r="D243" s="4" t="n"/>
-      <c r="E243" s="5" t="inlineStr">
+      <c r="E243" s="4" t="n"/>
+      <c r="F243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F243" s="4" t="n"/>
       <c r="G243" s="4" t="n"/>
       <c r="H243" s="4" t="n"/>
       <c r="I243" s="4" t="n"/>
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
+      <c r="L243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -4920,17 +5184,18 @@
       <c r="B244" s="4" t="n"/>
       <c r="C244" s="4" t="n"/>
       <c r="D244" s="4" t="n"/>
-      <c r="E244" s="5" t="inlineStr">
+      <c r="E244" s="4" t="n"/>
+      <c r="F244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F244" s="4" t="n"/>
       <c r="G244" s="4" t="n"/>
       <c r="H244" s="4" t="n"/>
       <c r="I244" s="4" t="n"/>
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
+      <c r="L244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -4948,6 +5213,7 @@
       <c r="I245" s="8" t="n"/>
       <c r="J245" s="8" t="n"/>
       <c r="K245" s="8" t="n"/>
+      <c r="L245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -4965,6 +5231,7 @@
       <c r="I246" s="8" t="n"/>
       <c r="J246" s="8" t="n"/>
       <c r="K246" s="8" t="n"/>
+      <c r="L246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -4975,17 +5242,18 @@
       <c r="B247" s="4" t="n"/>
       <c r="C247" s="4" t="n"/>
       <c r="D247" s="4" t="n"/>
-      <c r="E247" s="5" t="inlineStr">
+      <c r="E247" s="4" t="n"/>
+      <c r="F247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F247" s="4" t="n"/>
       <c r="G247" s="4" t="n"/>
       <c r="H247" s="4" t="n"/>
       <c r="I247" s="4" t="n"/>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
+      <c r="L247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -4996,17 +5264,18 @@
       <c r="B248" s="4" t="n"/>
       <c r="C248" s="4" t="n"/>
       <c r="D248" s="4" t="n"/>
-      <c r="E248" s="5" t="inlineStr">
+      <c r="E248" s="4" t="n"/>
+      <c r="F248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F248" s="4" t="n"/>
       <c r="G248" s="4" t="n"/>
       <c r="H248" s="4" t="n"/>
       <c r="I248" s="4" t="n"/>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
+      <c r="L248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +70,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -97,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -121,6 +126,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1278,7 +1286,11 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1308,7 +1308,11 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
@@ -1326,7 +1330,11 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
@@ -1344,7 +1352,11 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
@@ -1362,7 +1374,11 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1295,7 +1295,11 @@
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>External - Darts 6 G</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1317,7 +1321,11 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>Fresh From Wales</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1339,7 +1347,11 @@
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>Fresh From Wales</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1354,14 +1366,18 @@
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Sŵ Ni</t>
+          <t>Record VO &amp; Title Song</t>
         </is>
       </c>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1281,7 +1281,11 @@
           <t>Mon 31 Aug 2026</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
@@ -1292,9 +1296,17 @@
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>TOIL - Darts 6 G</t>
+        </is>
+      </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
@@ -1318,9 +1330,17 @@
         </is>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
@@ -1344,9 +1364,17 @@
         </is>
       </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
@@ -1359,7 +1387,11 @@
           <t>Thu 03 Sep 2026</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Linda Wilson</t>
+        </is>
+      </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
@@ -1370,9 +1402,17 @@
         </is>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
@@ -1385,7 +1425,11 @@
           <t>Fri 04 Sep 2026</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Linda Wilson</t>
+        </is>
+      </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
@@ -1396,10 +1440,22 @@
         </is>
       </c>
       <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L248"/>
+  <dimension ref="A1:M248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -511,6 +511,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,35 +542,40 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>Euros Llyr Morgan</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Lara Hughes</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Osian Lewis</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Owain Jones</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rhodri Lewis</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -585,17 +591,18 @@
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -607,17 +614,18 @@
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -636,6 +644,7 @@
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -654,6 +663,7 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -665,17 +675,18 @@
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -694,6 +705,7 @@
       <c r="J7" s="8" t="n"/>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -712,6 +724,7 @@
       <c r="J8" s="8" t="n"/>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -730,6 +743,7 @@
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -748,6 +762,7 @@
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -766,6 +781,7 @@
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -784,6 +800,7 @@
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -795,17 +812,18 @@
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -824,6 +842,7 @@
       <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -842,6 +861,7 @@
       <c r="J15" s="8" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -860,6 +880,7 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -878,6 +899,7 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -896,6 +918,7 @@
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -914,6 +937,7 @@
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -932,6 +956,7 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -950,6 +975,7 @@
       <c r="J21" s="8" t="n"/>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -968,6 +994,7 @@
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -988,28 +1015,29 @@
       </c>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1038,28 +1066,29 @@
       </c>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1088,32 +1117,33 @@
       </c>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1146,32 +1176,33 @@
         </is>
       </c>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1200,32 +1231,33 @@
         </is>
       </c>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1241,13 +1273,18 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Film - Linda Wilson</t>
+        </is>
+      </c>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1269,7 +1306,8 @@
       <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="10" t="inlineStr">
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1286,28 +1324,45 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C30" s="4" t="n"/>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Film - Hansh Socials</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>Film - Hansh Socials</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="L30" s="10" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -1321,27 +1376,36 @@
       </c>
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Cardi Con</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L31" s="10" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
         </is>
@@ -1358,24 +1422,29 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Cardi Con</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
         </is>
@@ -1395,25 +1464,34 @@
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Film - Linda Wilson</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1434,24 +1512,29 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1474,6 +1557,7 @@
       <c r="J35" s="8" t="n"/>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1492,6 +1576,7 @@
       <c r="J36" s="8" t="n"/>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1510,6 +1595,7 @@
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1528,6 +1614,7 @@
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1546,6 +1633,7 @@
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
       <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1564,6 +1652,7 @@
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1582,6 +1671,7 @@
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1600,6 +1690,7 @@
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="8" t="n"/>
+      <c r="M42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1618,6 +1709,7 @@
       <c r="J43" s="8" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1629,17 +1721,18 @@
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1651,17 +1744,18 @@
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1673,17 +1767,18 @@
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1702,6 +1797,7 @@
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1720,6 +1816,7 @@
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -1738,6 +1835,7 @@
       <c r="J49" s="8" t="n"/>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -1756,6 +1854,7 @@
       <c r="J50" s="8" t="n"/>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1774,6 +1873,7 @@
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1792,6 +1892,7 @@
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1810,6 +1911,7 @@
       <c r="J53" s="4" t="n"/>
       <c r="K53" s="4" t="n"/>
       <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1828,6 +1930,7 @@
       <c r="J54" s="4" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1839,17 +1942,18 @@
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -1868,6 +1972,7 @@
       <c r="J56" s="8" t="n"/>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
+      <c r="M56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -1886,6 +1991,7 @@
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1904,6 +2010,7 @@
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1922,6 +2029,7 @@
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1940,6 +2048,7 @@
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1958,6 +2067,7 @@
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1976,6 +2086,7 @@
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -1994,6 +2105,7 @@
       <c r="J63" s="8" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -2012,6 +2124,7 @@
       <c r="J64" s="8" t="n"/>
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2030,6 +2143,7 @@
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2048,6 +2162,7 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2059,17 +2174,18 @@
       <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2088,6 +2204,7 @@
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2106,6 +2223,7 @@
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2124,6 +2242,7 @@
       <c r="J70" s="8" t="n"/>
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
+      <c r="M70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -2142,6 +2261,7 @@
       <c r="J71" s="8" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2160,6 +2280,7 @@
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2178,6 +2299,7 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2196,6 +2318,7 @@
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2214,6 +2337,7 @@
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2232,6 +2356,7 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -2250,6 +2375,7 @@
       <c r="J77" s="8" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -2268,6 +2394,7 @@
       <c r="J78" s="8" t="n"/>
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
+      <c r="M78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2286,6 +2413,7 @@
       <c r="J79" s="4" t="n"/>
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2304,6 +2432,7 @@
       <c r="J80" s="4" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2322,6 +2451,7 @@
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2340,6 +2470,7 @@
       <c r="J82" s="4" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2358,6 +2489,7 @@
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -2376,6 +2508,7 @@
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
+      <c r="M84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -2394,6 +2527,7 @@
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2412,6 +2546,7 @@
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2430,6 +2565,7 @@
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2448,6 +2584,7 @@
       <c r="J88" s="4" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2466,6 +2603,7 @@
       <c r="J89" s="4" t="n"/>
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2484,6 +2622,7 @@
       <c r="J90" s="4" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -2502,6 +2641,7 @@
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -2520,6 +2660,7 @@
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2538,6 +2679,7 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2556,6 +2698,7 @@
       <c r="J94" s="4" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2574,6 +2717,7 @@
       <c r="J95" s="4" t="n"/>
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2592,6 +2736,7 @@
       <c r="J96" s="4" t="n"/>
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2610,6 +2755,7 @@
       <c r="J97" s="4" t="n"/>
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -2628,6 +2774,7 @@
       <c r="J98" s="8" t="n"/>
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -2646,6 +2793,7 @@
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2664,6 +2812,7 @@
       <c r="J100" s="4" t="n"/>
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -2682,6 +2831,7 @@
       <c r="J101" s="4" t="n"/>
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="4" t="n"/>
+      <c r="M101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2700,6 +2850,7 @@
       <c r="J102" s="4" t="n"/>
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2718,6 +2869,7 @@
       <c r="J103" s="4" t="n"/>
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2736,6 +2888,7 @@
       <c r="J104" s="4" t="n"/>
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -2754,6 +2907,7 @@
       <c r="J105" s="8" t="n"/>
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
+      <c r="M105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -2772,6 +2926,7 @@
       <c r="J106" s="8" t="n"/>
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
+      <c r="M106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -2790,6 +2945,7 @@
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2808,6 +2964,7 @@
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="4" t="n"/>
+      <c r="M108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2826,6 +2983,7 @@
       <c r="J109" s="4" t="n"/>
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2844,6 +3002,7 @@
       <c r="J110" s="4" t="n"/>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
+      <c r="M110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2855,17 +3014,18 @@
       <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
-      <c r="F111" s="5" t="inlineStr">
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="4" t="n"/>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -2884,6 +3044,7 @@
       <c r="J112" s="8" t="n"/>
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
+      <c r="M112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -2902,6 +3063,7 @@
       <c r="J113" s="8" t="n"/>
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
+      <c r="M113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2920,6 +3082,7 @@
       <c r="J114" s="4" t="n"/>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2938,6 +3101,7 @@
       <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -2956,6 +3120,7 @@
       <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
+      <c r="M116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -2974,6 +3139,7 @@
       <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2985,17 +3151,18 @@
       <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n"/>
       <c r="H118" s="4" t="n"/>
       <c r="I118" s="4" t="n"/>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -3014,6 +3181,7 @@
       <c r="J119" s="8" t="n"/>
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
+      <c r="M119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -3032,6 +3200,7 @@
       <c r="J120" s="8" t="n"/>
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
+      <c r="M120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3050,6 +3219,7 @@
       <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3068,6 +3238,7 @@
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3086,6 +3257,7 @@
       <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3104,6 +3276,7 @@
       <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3122,6 +3295,7 @@
       <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -3140,6 +3314,7 @@
       <c r="J126" s="8" t="n"/>
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
+      <c r="M126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -3158,6 +3333,7 @@
       <c r="J127" s="8" t="n"/>
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
+      <c r="M127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3176,6 +3352,7 @@
       <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
+      <c r="M128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3194,6 +3371,7 @@
       <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3212,6 +3390,7 @@
       <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3230,6 +3409,7 @@
       <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3248,6 +3428,7 @@
       <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -3266,6 +3447,7 @@
       <c r="J133" s="8" t="n"/>
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="8" t="n"/>
+      <c r="M133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -3284,6 +3466,7 @@
       <c r="J134" s="8" t="n"/>
       <c r="K134" s="8" t="n"/>
       <c r="L134" s="8" t="n"/>
+      <c r="M134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3302,6 +3485,7 @@
       <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3313,17 +3497,18 @@
       <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n"/>
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="4" t="n"/>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3335,17 +3520,18 @@
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="4" t="n"/>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n"/>
       <c r="H137" s="4" t="n"/>
       <c r="I137" s="4" t="n"/>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3357,17 +3543,18 @@
       <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="4" t="n"/>
-      <c r="F138" s="5" t="inlineStr">
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n"/>
       <c r="H138" s="4" t="n"/>
       <c r="I138" s="4" t="n"/>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3379,17 +3566,18 @@
       <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="4" t="n"/>
-      <c r="F139" s="5" t="inlineStr">
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n"/>
       <c r="H139" s="4" t="n"/>
       <c r="I139" s="4" t="n"/>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -3408,6 +3596,7 @@
       <c r="J140" s="8" t="n"/>
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
+      <c r="M140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -3426,6 +3615,7 @@
       <c r="J141" s="8" t="n"/>
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
+      <c r="M141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3444,6 +3634,7 @@
       <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3462,6 +3653,7 @@
       <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
+      <c r="M143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -3480,6 +3672,7 @@
       <c r="J144" s="4" t="n"/>
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -3498,6 +3691,7 @@
       <c r="J145" s="4" t="n"/>
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -3516,6 +3710,7 @@
       <c r="J146" s="4" t="n"/>
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -3534,6 +3729,7 @@
       <c r="J147" s="8" t="n"/>
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
+      <c r="M147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -3552,6 +3748,7 @@
       <c r="J148" s="8" t="n"/>
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
+      <c r="M148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -3570,6 +3767,7 @@
       <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -3588,6 +3786,7 @@
       <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -3606,6 +3805,7 @@
       <c r="J151" s="4" t="n"/>
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="4" t="n"/>
+      <c r="M151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -3624,6 +3824,7 @@
       <c r="J152" s="4" t="n"/>
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -3642,6 +3843,7 @@
       <c r="J153" s="4" t="n"/>
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -3660,6 +3862,7 @@
       <c r="J154" s="8" t="n"/>
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
+      <c r="M154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -3678,6 +3881,7 @@
       <c r="J155" s="8" t="n"/>
       <c r="K155" s="8" t="n"/>
       <c r="L155" s="8" t="n"/>
+      <c r="M155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -3696,6 +3900,7 @@
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
+      <c r="M156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -3714,6 +3919,7 @@
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -3725,17 +3931,18 @@
       <c r="C158" s="4" t="n"/>
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="4" t="n"/>
-      <c r="F158" s="5" t="inlineStr">
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n"/>
       <c r="H158" s="4" t="n"/>
       <c r="I158" s="4" t="n"/>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
+      <c r="M158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -3754,6 +3961,7 @@
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
+      <c r="M159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -3772,6 +3980,7 @@
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -3790,6 +3999,7 @@
       <c r="J161" s="8" t="n"/>
       <c r="K161" s="8" t="n"/>
       <c r="L161" s="8" t="n"/>
+      <c r="M161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -3808,6 +4018,7 @@
       <c r="J162" s="8" t="n"/>
       <c r="K162" s="8" t="n"/>
       <c r="L162" s="8" t="n"/>
+      <c r="M162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -3826,6 +4037,7 @@
       <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
+      <c r="M163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -3844,6 +4056,7 @@
       <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -3862,6 +4075,7 @@
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -3880,6 +4094,7 @@
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
+      <c r="M166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -3898,6 +4113,7 @@
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
+      <c r="M167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -3916,6 +4132,7 @@
       <c r="J168" s="8" t="n"/>
       <c r="K168" s="8" t="n"/>
       <c r="L168" s="8" t="n"/>
+      <c r="M168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -3934,6 +4151,7 @@
       <c r="J169" s="8" t="n"/>
       <c r="K169" s="8" t="n"/>
       <c r="L169" s="8" t="n"/>
+      <c r="M169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -3952,6 +4170,7 @@
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
+      <c r="M170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -3970,6 +4189,7 @@
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
+      <c r="M171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -3988,6 +4208,7 @@
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
+      <c r="M172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4006,6 +4227,7 @@
       <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
+      <c r="M173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4024,6 +4246,7 @@
       <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -4042,6 +4265,7 @@
       <c r="J175" s="8" t="n"/>
       <c r="K175" s="8" t="n"/>
       <c r="L175" s="8" t="n"/>
+      <c r="M175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -4060,6 +4284,7 @@
       <c r="J176" s="8" t="n"/>
       <c r="K176" s="8" t="n"/>
       <c r="L176" s="8" t="n"/>
+      <c r="M176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4078,6 +4303,7 @@
       <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
+      <c r="M177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4096,6 +4322,7 @@
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
+      <c r="M178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4114,6 +4341,7 @@
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -4132,6 +4360,7 @@
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
+      <c r="M180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4150,6 +4379,7 @@
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -4168,6 +4398,7 @@
       <c r="J182" s="8" t="n"/>
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
+      <c r="M182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -4186,6 +4417,7 @@
       <c r="J183" s="8" t="n"/>
       <c r="K183" s="8" t="n"/>
       <c r="L183" s="8" t="n"/>
+      <c r="M183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -4204,6 +4436,7 @@
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
+      <c r="M184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4222,6 +4455,7 @@
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4240,6 +4474,7 @@
       <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
+      <c r="M186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4258,6 +4493,7 @@
       <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -4276,6 +4512,7 @@
       <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
+      <c r="M188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -4294,6 +4531,7 @@
       <c r="J189" s="8" t="n"/>
       <c r="K189" s="8" t="n"/>
       <c r="L189" s="8" t="n"/>
+      <c r="M189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -4312,6 +4550,7 @@
       <c r="J190" s="8" t="n"/>
       <c r="K190" s="8" t="n"/>
       <c r="L190" s="8" t="n"/>
+      <c r="M190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4330,6 +4569,7 @@
       <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4348,6 +4588,7 @@
       <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
+      <c r="M192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4366,6 +4607,7 @@
       <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4384,6 +4626,7 @@
       <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
+      <c r="M194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4402,6 +4645,7 @@
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -4420,6 +4664,7 @@
       <c r="J196" s="8" t="n"/>
       <c r="K196" s="8" t="n"/>
       <c r="L196" s="8" t="n"/>
+      <c r="M196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -4438,6 +4683,7 @@
       <c r="J197" s="8" t="n"/>
       <c r="K197" s="8" t="n"/>
       <c r="L197" s="8" t="n"/>
+      <c r="M197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -4456,6 +4702,7 @@
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -4474,6 +4721,7 @@
       <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
+      <c r="M199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -4492,6 +4740,7 @@
       <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
+      <c r="M200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -4510,6 +4759,7 @@
       <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -4528,6 +4778,7 @@
       <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
+      <c r="M202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -4546,6 +4797,7 @@
       <c r="J203" s="8" t="n"/>
       <c r="K203" s="8" t="n"/>
       <c r="L203" s="8" t="n"/>
+      <c r="M203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -4564,6 +4816,7 @@
       <c r="J204" s="8" t="n"/>
       <c r="K204" s="8" t="n"/>
       <c r="L204" s="8" t="n"/>
+      <c r="M204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -4582,6 +4835,7 @@
       <c r="J205" s="4" t="n"/>
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -4600,6 +4854,7 @@
       <c r="J206" s="4" t="n"/>
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
+      <c r="M206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -4618,6 +4873,7 @@
       <c r="J207" s="4" t="n"/>
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -4636,6 +4892,7 @@
       <c r="J208" s="4" t="n"/>
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
+      <c r="M208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -4654,6 +4911,7 @@
       <c r="J209" s="4" t="n"/>
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
+      <c r="M209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -4672,6 +4930,7 @@
       <c r="J210" s="8" t="n"/>
       <c r="K210" s="8" t="n"/>
       <c r="L210" s="8" t="n"/>
+      <c r="M210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -4690,6 +4949,7 @@
       <c r="J211" s="8" t="n"/>
       <c r="K211" s="8" t="n"/>
       <c r="L211" s="8" t="n"/>
+      <c r="M211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -4708,6 +4968,7 @@
       <c r="J212" s="4" t="n"/>
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
+      <c r="M212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -4726,6 +4987,7 @@
       <c r="J213" s="4" t="n"/>
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -4744,6 +5006,7 @@
       <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
+      <c r="M214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -4762,6 +5025,7 @@
       <c r="J215" s="4" t="n"/>
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
+      <c r="M215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -4780,6 +5044,7 @@
       <c r="J216" s="4" t="n"/>
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
+      <c r="M216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -4798,6 +5063,7 @@
       <c r="J217" s="8" t="n"/>
       <c r="K217" s="8" t="n"/>
       <c r="L217" s="8" t="n"/>
+      <c r="M217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -4816,6 +5082,7 @@
       <c r="J218" s="8" t="n"/>
       <c r="K218" s="8" t="n"/>
       <c r="L218" s="8" t="n"/>
+      <c r="M218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -4834,6 +5101,7 @@
       <c r="J219" s="4" t="n"/>
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
+      <c r="M219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -4852,6 +5120,7 @@
       <c r="J220" s="4" t="n"/>
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
+      <c r="M220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -4870,6 +5139,7 @@
       <c r="J221" s="4" t="n"/>
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
+      <c r="M221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -4888,6 +5158,7 @@
       <c r="J222" s="4" t="n"/>
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
+      <c r="M222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -4906,6 +5177,7 @@
       <c r="J223" s="4" t="n"/>
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
+      <c r="M223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -4924,6 +5196,7 @@
       <c r="J224" s="8" t="n"/>
       <c r="K224" s="8" t="n"/>
       <c r="L224" s="8" t="n"/>
+      <c r="M224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -4942,6 +5215,7 @@
       <c r="J225" s="8" t="n"/>
       <c r="K225" s="8" t="n"/>
       <c r="L225" s="8" t="n"/>
+      <c r="M225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -4960,6 +5234,7 @@
       <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
+      <c r="M226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -4978,6 +5253,7 @@
       <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
+      <c r="M227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -4996,6 +5272,7 @@
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
+      <c r="M228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -5014,6 +5291,7 @@
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
+      <c r="M229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -5032,6 +5310,7 @@
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
+      <c r="M230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -5050,6 +5329,7 @@
       <c r="J231" s="8" t="n"/>
       <c r="K231" s="8" t="n"/>
       <c r="L231" s="8" t="n"/>
+      <c r="M231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -5068,6 +5348,7 @@
       <c r="J232" s="8" t="n"/>
       <c r="K232" s="8" t="n"/>
       <c r="L232" s="8" t="n"/>
+      <c r="M232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -5086,6 +5367,7 @@
       <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
+      <c r="M233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -5104,6 +5386,7 @@
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
+      <c r="M234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -5122,6 +5405,7 @@
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
+      <c r="M235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -5140,6 +5424,7 @@
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
+      <c r="M236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -5158,6 +5443,7 @@
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
+      <c r="M237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -5176,6 +5462,7 @@
       <c r="J238" s="8" t="n"/>
       <c r="K238" s="8" t="n"/>
       <c r="L238" s="8" t="n"/>
+      <c r="M238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -5194,6 +5481,7 @@
       <c r="J239" s="8" t="n"/>
       <c r="K239" s="8" t="n"/>
       <c r="L239" s="8" t="n"/>
+      <c r="M239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -5212,6 +5500,7 @@
       <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -5230,6 +5519,7 @@
       <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
+      <c r="M241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -5241,17 +5531,18 @@
       <c r="C242" s="4" t="n"/>
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="4" t="n"/>
-      <c r="F242" s="5" t="inlineStr">
+      <c r="F242" s="4" t="n"/>
+      <c r="G242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n"/>
       <c r="H242" s="4" t="n"/>
       <c r="I242" s="4" t="n"/>
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -5263,17 +5554,18 @@
       <c r="C243" s="4" t="n"/>
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="4" t="n"/>
-      <c r="F243" s="5" t="inlineStr">
+      <c r="F243" s="4" t="n"/>
+      <c r="G243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n"/>
       <c r="H243" s="4" t="n"/>
       <c r="I243" s="4" t="n"/>
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
+      <c r="M243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -5285,17 +5577,18 @@
       <c r="C244" s="4" t="n"/>
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="4" t="n"/>
-      <c r="F244" s="5" t="inlineStr">
+      <c r="F244" s="4" t="n"/>
+      <c r="G244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n"/>
       <c r="H244" s="4" t="n"/>
       <c r="I244" s="4" t="n"/>
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
+      <c r="M244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -5314,6 +5607,7 @@
       <c r="J245" s="8" t="n"/>
       <c r="K245" s="8" t="n"/>
       <c r="L245" s="8" t="n"/>
+      <c r="M245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -5332,6 +5626,7 @@
       <c r="J246" s="8" t="n"/>
       <c r="K246" s="8" t="n"/>
       <c r="L246" s="8" t="n"/>
+      <c r="M246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -5343,17 +5638,18 @@
       <c r="C247" s="4" t="n"/>
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="4" t="n"/>
-      <c r="F247" s="5" t="inlineStr">
+      <c r="F247" s="4" t="n"/>
+      <c r="G247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n"/>
       <c r="H247" s="4" t="n"/>
       <c r="I247" s="4" t="n"/>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
+      <c r="M247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -5365,17 +5661,18 @@
       <c r="C248" s="4" t="n"/>
       <c r="D248" s="4" t="n"/>
       <c r="E248" s="4" t="n"/>
-      <c r="F248" s="5" t="inlineStr">
+      <c r="F248" s="4" t="n"/>
+      <c r="G248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n"/>
       <c r="H248" s="4" t="n"/>
       <c r="I248" s="4" t="n"/>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
+      <c r="M248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1590,12 +1590,20 @@
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>Black History 2026</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1609,7 +1617,11 @@
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n"/>
@@ -1628,7 +1640,11 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n"/>
@@ -1647,7 +1663,11 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Sw Ni - Cont/ Prep</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
@@ -1666,7 +1686,11 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Sw Ni - Cont/ Prep</t>
+        </is>
+      </c>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1596,12 +1596,24 @@
         </is>
       </c>
       <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Black History 2026</t>
+          <t>Film - Black History 2026</t>
         </is>
       </c>
     </row>
@@ -1624,9 +1636,21 @@
       </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1647,9 +1671,21 @@
       </c>
       <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="4" t="n"/>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1670,9 +1706,21 @@
       </c>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1693,9 +1741,21 @@
       </c>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>Film - Black History 2026</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -1751,7 +1811,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n"/>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Sw Ni - Prep</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -1774,7 +1838,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n"/>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Sw Ni - Prep</t>
+        </is>
+      </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
@@ -1797,7 +1865,11 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n"/>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -1816,7 +1888,11 @@
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
@@ -1835,7 +1911,11 @@
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1820,7 +1820,11 @@
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>TOIL - Darts 6 G</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1801,7 +1801,11 @@
           <t>Mon 14 Sep 2026</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Development - Our Lives</t>
+        </is>
+      </c>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
@@ -1817,7 +1821,11 @@
         </is>
       </c>
       <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="6" t="inlineStr">
@@ -1832,7 +1840,11 @@
           <t>Tue 15 Sep 2026</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Development - Our Lives</t>
+        </is>
+      </c>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
@@ -1848,7 +1860,11 @@
         </is>
       </c>
       <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
@@ -1859,10 +1875,22 @@
           <t>Wed 16 Sep 2026</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Development - Our Lives</t>
+        </is>
+      </c>
       <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -1875,10 +1903,18 @@
         </is>
       </c>
       <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1886,10 +1922,22 @@
           <t>Thu 17 Sep 2026</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Development - Our Lives</t>
+        </is>
+      </c>
       <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="10" t="inlineStr">
@@ -1898,10 +1946,18 @@
         </is>
       </c>
       <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1909,10 +1965,22 @@
           <t>Fri 18 Sep 2026</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n"/>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Development - Our Lives</t>
+        </is>
+      </c>
       <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="10" t="inlineStr">
@@ -1921,10 +1989,18 @@
         </is>
       </c>
       <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2052,12 +2052,24 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2071,12 +2083,28 @@
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2090,12 +2118,28 @@
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2109,12 +2153,28 @@
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="4" t="n"/>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2132,12 +2192,28 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n"/>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+        </is>
+      </c>
       <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2048,8 +2048,16 @@
       </c>
       <c r="B51" s="4" t="n"/>
       <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="10" t="inlineStr">
@@ -2079,8 +2087,16 @@
       </c>
       <c r="B52" s="4" t="n"/>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="10" t="inlineStr">
@@ -2114,8 +2130,16 @@
       </c>
       <c r="B53" s="4" t="n"/>
       <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="10" t="inlineStr">
@@ -2149,8 +2173,16 @@
       </c>
       <c r="B54" s="4" t="n"/>
       <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="10" t="inlineStr">
@@ -2184,8 +2216,16 @@
       </c>
       <c r="B55" s="4" t="n"/>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -2265,7 +2305,11 @@
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
@@ -2284,7 +2328,11 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
@@ -2303,7 +2351,11 @@
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="n"/>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
@@ -2322,7 +2374,11 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
@@ -2341,7 +2397,11 @@
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
       <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2304,7 +2304,11 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Black History 2026</t>
+        </is>
+      </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -2314,7 +2318,11 @@
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2337,7 +2345,11 @@
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2360,7 +2372,11 @@
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2383,7 +2399,11 @@
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
+      <c r="M61" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -2406,7 +2426,11 @@
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M248"/>
+  <dimension ref="A1:O248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,8 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,45 +539,55 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Derwena Burt</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Elin Jones</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Euros Llyr Morgan</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Hannah Holton</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Iestyn O'Leary</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Jason Lye-Phillips</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Lara Hughes</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Osian Lewis</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Owain Jones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Rhodri Lewis</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -592,17 +604,19 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -615,17 +629,19 @@
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -645,6 +661,8 @@
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -664,6 +682,8 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -676,17 +696,19 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -706,6 +728,8 @@
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -725,6 +749,8 @@
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -744,6 +770,8 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -763,6 +791,8 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -782,6 +812,8 @@
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -801,6 +833,8 @@
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -813,17 +847,19 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -843,6 +879,8 @@
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -862,6 +900,8 @@
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -881,6 +921,8 @@
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -900,6 +942,8 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -919,6 +963,8 @@
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -938,6 +984,8 @@
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -957,6 +1005,8 @@
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -976,6 +1026,8 @@
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -995,6 +1047,8 @@
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1016,28 +1070,30 @@
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1067,28 +1123,30 @@
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="O24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1118,32 +1176,34 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="O25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1170,39 +1230,41 @@
           <t>Anifail Perffaith</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>A/L - 1/2 Day Annual Leave</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1225,39 +1287,41 @@
           <t>Sŵ Ni</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="O27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1273,18 +1337,20 @@
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="E28" s="8" t="n"/>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1307,7 +1373,9 @@
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1330,39 +1398,41 @@
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="N30" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="O30" s="10" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -1384,28 +1454,30 @@
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr">
+      <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Edit - Cardi Con</t>
         </is>
       </c>
-      <c r="L31" s="9" t="inlineStr">
+      <c r="N31" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="O31" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
         </is>
@@ -1423,28 +1495,30 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="10" t="inlineStr">
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="10" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="K32" s="10" t="inlineStr">
+      <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Edit - Cardi Con</t>
         </is>
       </c>
-      <c r="L32" s="9" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M32" s="10" t="inlineStr">
+      <c r="O32" s="10" t="inlineStr">
         <is>
           <t>Fresh From Wales</t>
         </is>
@@ -1464,34 +1538,36 @@
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Record VO &amp; Title Song</t>
-        </is>
-      </c>
+      <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="10" t="inlineStr">
         <is>
+          <t>Record VO &amp; Title Song</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="N33" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M33" s="10" t="inlineStr">
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1513,28 +1589,30 @@
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="O34" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1558,6 +1636,8 @@
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1577,6 +1657,8 @@
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1590,28 +1672,30 @@
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="N37" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="O37" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1629,24 +1713,26 @@
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M38" s="10" t="inlineStr">
+      <c r="O38" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1664,24 +1750,26 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="10" t="inlineStr">
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M39" s="10" t="inlineStr">
+      <c r="O39" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1699,24 +1787,26 @@
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="10" t="inlineStr">
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="N40" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M40" s="10" t="inlineStr">
+      <c r="O40" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1734,24 +1824,26 @@
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="10" t="inlineStr">
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="O41" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1775,6 +1867,8 @@
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1794,6 +1888,8 @@
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1810,25 +1906,27 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
       </c>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="6" t="inlineStr">
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
@@ -1849,25 +1947,27 @@
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
       </c>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1886,31 +1986,33 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -1933,27 +2035,29 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="10" t="inlineStr">
         <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="10" t="inlineStr">
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -1976,27 +2080,29 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="10" t="inlineStr">
         <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="10" t="inlineStr">
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n"/>
+      <c r="O48" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2020,6 +2126,8 @@
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -2039,6 +2147,8 @@
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2053,27 +2163,29 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E51" s="10" t="inlineStr">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n"/>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Film - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
       <c r="J51" s="10" t="inlineStr">
         <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="10" t="inlineStr">
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2092,31 +2204,33 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr">
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>Film - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="10" t="inlineStr">
         <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="9" t="inlineStr">
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M52" s="10" t="inlineStr">
+      <c r="O52" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2135,31 +2249,33 @@
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="E53" s="10" t="inlineStr">
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>Film - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
+      <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
       <c r="J53" s="10" t="inlineStr">
         <is>
+          <t>Film - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="9" t="inlineStr">
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M53" s="10" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2178,31 +2294,33 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F54" s="4" t="n"/>
       <c r="G54" s="4" t="n"/>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
-        </is>
-      </c>
+      <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
       <c r="J54" s="10" t="inlineStr">
         <is>
+          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M54" s="10" t="inlineStr">
+      <c r="O54" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -2221,35 +2339,37 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="10" t="inlineStr">
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="9" t="inlineStr">
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M55" s="10" t="inlineStr">
+      <c r="O55" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -2273,6 +2393,8 @@
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -2292,6 +2414,8 @@
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2301,24 +2425,34 @@
       </c>
       <c r="B58" s="4" t="n"/>
       <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O58" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2332,20 +2466,30 @@
       </c>
       <c r="B59" s="4" t="n"/>
       <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="10" t="inlineStr">
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="O59" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2359,20 +2503,26 @@
       </c>
       <c r="B60" s="4" t="n"/>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
-      <c r="M60" s="10" t="inlineStr">
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="n"/>
+      <c r="O60" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2386,20 +2536,26 @@
       </c>
       <c r="B61" s="4" t="n"/>
       <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2411,24 +2567,77 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni
+Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon
+Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni</t>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon</t>
+        </is>
+      </c>
+      <c r="O62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathly S4C Athrawon
+Film - Sŵ Ni</t>
         </is>
       </c>
     </row>
@@ -2450,6 +2659,8 @@
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -2469,6 +2680,8 @@
       <c r="K64" s="8" t="n"/>
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
+      <c r="N64" s="8" t="n"/>
+      <c r="O64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2488,6 +2701,8 @@
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
       <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2507,6 +2722,8 @@
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2519,17 +2736,19 @@
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>Delivery - Deep Watch</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2549,6 +2768,8 @@
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2568,6 +2789,8 @@
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2587,6 +2810,8 @@
       <c r="K70" s="8" t="n"/>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
+      <c r="N70" s="8" t="n"/>
+      <c r="O70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -2606,6 +2831,8 @@
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
+      <c r="N71" s="8" t="n"/>
+      <c r="O71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2625,6 +2852,8 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2644,6 +2873,8 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2663,6 +2894,8 @@
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2682,6 +2915,8 @@
       <c r="K75" s="4" t="n"/>
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2701,6 +2936,8 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -2720,6 +2957,8 @@
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -2739,6 +2978,8 @@
       <c r="K78" s="8" t="n"/>
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
+      <c r="N78" s="8" t="n"/>
+      <c r="O78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2758,6 +2999,8 @@
       <c r="K79" s="4" t="n"/>
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2777,6 +3020,8 @@
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2796,6 +3041,8 @@
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2815,6 +3062,8 @@
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2834,6 +3083,8 @@
       <c r="K83" s="4" t="n"/>
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -2853,6 +3104,8 @@
       <c r="K84" s="8" t="n"/>
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
+      <c r="N84" s="8" t="n"/>
+      <c r="O84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -2872,6 +3125,8 @@
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2891,6 +3146,8 @@
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2910,6 +3167,8 @@
       <c r="K87" s="4" t="n"/>
       <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2929,6 +3188,8 @@
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2948,6 +3209,8 @@
       <c r="K89" s="4" t="n"/>
       <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2967,6 +3230,8 @@
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -2986,6 +3251,8 @@
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -3005,6 +3272,8 @@
       <c r="K92" s="8" t="n"/>
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
+      <c r="N92" s="8" t="n"/>
+      <c r="O92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3024,6 +3293,8 @@
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -3043,6 +3314,8 @@
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3062,6 +3335,8 @@
       <c r="K95" s="4" t="n"/>
       <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -3081,6 +3356,8 @@
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4" t="n"/>
+      <c r="O96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3100,6 +3377,8 @@
       <c r="K97" s="4" t="n"/>
       <c r="L97" s="4" t="n"/>
       <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -3119,6 +3398,8 @@
       <c r="K98" s="8" t="n"/>
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
+      <c r="N98" s="8" t="n"/>
+      <c r="O98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -3138,6 +3419,8 @@
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
+      <c r="N99" s="8" t="n"/>
+      <c r="O99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -3157,6 +3440,8 @@
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3176,6 +3461,8 @@
       <c r="K101" s="4" t="n"/>
       <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
+      <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -3195,6 +3482,8 @@
       <c r="K102" s="4" t="n"/>
       <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
+      <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3214,6 +3503,8 @@
       <c r="K103" s="4" t="n"/>
       <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -3233,6 +3524,8 @@
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
+      <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -3252,6 +3545,8 @@
       <c r="K105" s="8" t="n"/>
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
+      <c r="N105" s="8" t="n"/>
+      <c r="O105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -3271,6 +3566,8 @@
       <c r="K106" s="8" t="n"/>
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
+      <c r="N106" s="8" t="n"/>
+      <c r="O106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3290,6 +3587,8 @@
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -3309,6 +3608,8 @@
       <c r="K108" s="4" t="n"/>
       <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
+      <c r="N108" s="4" t="n"/>
+      <c r="O108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3328,6 +3629,8 @@
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -3347,6 +3650,8 @@
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
+      <c r="N110" s="4" t="n"/>
+      <c r="O110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3359,17 +3664,19 @@
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H111" s="4" t="n"/>
-      <c r="I111" s="4" t="n"/>
       <c r="J111" s="4" t="n"/>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -3389,6 +3696,8 @@
       <c r="K112" s="8" t="n"/>
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
+      <c r="N112" s="8" t="n"/>
+      <c r="O112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -3408,6 +3717,8 @@
       <c r="K113" s="8" t="n"/>
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
+      <c r="N113" s="8" t="n"/>
+      <c r="O113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -3427,6 +3738,8 @@
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3446,6 +3759,8 @@
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -3465,6 +3780,8 @@
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3484,6 +3801,8 @@
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -3496,17 +3815,19 @@
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
       <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
+      <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -3526,6 +3847,8 @@
       <c r="K119" s="8" t="n"/>
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
+      <c r="N119" s="8" t="n"/>
+      <c r="O119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -3545,6 +3868,8 @@
       <c r="K120" s="8" t="n"/>
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
+      <c r="N120" s="8" t="n"/>
+      <c r="O120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3564,6 +3889,8 @@
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
+      <c r="O121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3583,6 +3910,8 @@
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
+      <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3602,6 +3931,8 @@
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3621,6 +3952,8 @@
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
+      <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3640,6 +3973,8 @@
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -3659,6 +3994,8 @@
       <c r="K126" s="8" t="n"/>
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
+      <c r="N126" s="8" t="n"/>
+      <c r="O126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -3678,6 +4015,8 @@
       <c r="K127" s="8" t="n"/>
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
+      <c r="N127" s="8" t="n"/>
+      <c r="O127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3697,6 +4036,8 @@
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
+      <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3716,6 +4057,8 @@
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3735,6 +4078,8 @@
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
+      <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3754,6 +4099,8 @@
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3773,6 +4120,8 @@
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
+      <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -3792,6 +4141,8 @@
       <c r="K133" s="8" t="n"/>
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
+      <c r="N133" s="8" t="n"/>
+      <c r="O133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -3811,6 +4162,8 @@
       <c r="K134" s="8" t="n"/>
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
+      <c r="N134" s="8" t="n"/>
+      <c r="O134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3830,6 +4183,8 @@
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3842,17 +4197,19 @@
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G136" s="4" t="n"/>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="4" t="n"/>
       <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
+      <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3865,17 +4222,19 @@
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
-      <c r="G137" s="5" t="inlineStr">
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="4" t="n"/>
       <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3888,17 +4247,19 @@
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G138" s="4" t="n"/>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="H138" s="4" t="n"/>
-      <c r="I138" s="4" t="n"/>
       <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
+      <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3911,17 +4272,19 @@
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
-      <c r="G139" s="5" t="inlineStr">
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="H139" s="4" t="n"/>
-      <c r="I139" s="4" t="n"/>
       <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -3941,6 +4304,8 @@
       <c r="K140" s="8" t="n"/>
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
+      <c r="N140" s="8" t="n"/>
+      <c r="O140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -3960,6 +4325,8 @@
       <c r="K141" s="8" t="n"/>
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
+      <c r="N141" s="8" t="n"/>
+      <c r="O141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3979,6 +4346,8 @@
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3998,6 +4367,8 @@
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
+      <c r="N143" s="4" t="n"/>
+      <c r="O143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -4017,6 +4388,8 @@
       <c r="K144" s="4" t="n"/>
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
+      <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4036,6 +4409,8 @@
       <c r="K145" s="4" t="n"/>
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -4055,6 +4430,8 @@
       <c r="K146" s="4" t="n"/>
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -4074,6 +4451,8 @@
       <c r="K147" s="8" t="n"/>
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
+      <c r="N147" s="8" t="n"/>
+      <c r="O147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -4093,6 +4472,8 @@
       <c r="K148" s="8" t="n"/>
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
+      <c r="N148" s="8" t="n"/>
+      <c r="O148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -4112,6 +4493,8 @@
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -4131,6 +4514,8 @@
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
+      <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -4150,6 +4535,8 @@
       <c r="K151" s="4" t="n"/>
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
+      <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -4169,6 +4556,8 @@
       <c r="K152" s="4" t="n"/>
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
+      <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -4188,6 +4577,8 @@
       <c r="K153" s="4" t="n"/>
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
+      <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -4207,6 +4598,8 @@
       <c r="K154" s="8" t="n"/>
       <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
+      <c r="N154" s="8" t="n"/>
+      <c r="O154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -4226,6 +4619,8 @@
       <c r="K155" s="8" t="n"/>
       <c r="L155" s="8" t="n"/>
       <c r="M155" s="8" t="n"/>
+      <c r="N155" s="8" t="n"/>
+      <c r="O155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -4245,6 +4640,8 @@
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
+      <c r="N156" s="4" t="n"/>
+      <c r="O156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -4264,6 +4661,8 @@
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
+      <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -4276,17 +4675,19 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
-      <c r="G158" s="5" t="inlineStr">
+      <c r="G158" s="4" t="n"/>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sioe Gerdd</t>
         </is>
       </c>
-      <c r="H158" s="4" t="n"/>
-      <c r="I158" s="4" t="n"/>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
+      <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -4306,6 +4707,8 @@
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
+      <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -4325,6 +4728,8 @@
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
+      <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -4344,6 +4749,8 @@
       <c r="K161" s="8" t="n"/>
       <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
+      <c r="N161" s="8" t="n"/>
+      <c r="O161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -4363,6 +4770,8 @@
       <c r="K162" s="8" t="n"/>
       <c r="L162" s="8" t="n"/>
       <c r="M162" s="8" t="n"/>
+      <c r="N162" s="8" t="n"/>
+      <c r="O162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -4382,6 +4791,8 @@
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -4401,6 +4812,8 @@
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
+      <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4420,6 +4833,8 @@
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -4439,6 +4854,8 @@
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
+      <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -4458,6 +4875,8 @@
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -4477,6 +4896,8 @@
       <c r="K168" s="8" t="n"/>
       <c r="L168" s="8" t="n"/>
       <c r="M168" s="8" t="n"/>
+      <c r="N168" s="8" t="n"/>
+      <c r="O168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -4496,6 +4917,8 @@
       <c r="K169" s="8" t="n"/>
       <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
+      <c r="N169" s="8" t="n"/>
+      <c r="O169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4515,6 +4938,8 @@
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
+      <c r="N170" s="4" t="n"/>
+      <c r="O170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -4534,6 +4959,8 @@
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
+      <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4553,6 +4980,8 @@
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
+      <c r="N172" s="4" t="n"/>
+      <c r="O172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4572,6 +5001,8 @@
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
+      <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4591,6 +5022,8 @@
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
+      <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -4610,6 +5043,8 @@
       <c r="K175" s="8" t="n"/>
       <c r="L175" s="8" t="n"/>
       <c r="M175" s="8" t="n"/>
+      <c r="N175" s="8" t="n"/>
+      <c r="O175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -4629,6 +5064,8 @@
       <c r="K176" s="8" t="n"/>
       <c r="L176" s="8" t="n"/>
       <c r="M176" s="8" t="n"/>
+      <c r="N176" s="8" t="n"/>
+      <c r="O176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4648,6 +5085,8 @@
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
+      <c r="N177" s="4" t="n"/>
+      <c r="O177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4667,6 +5106,8 @@
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
+      <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4686,6 +5127,8 @@
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -4705,6 +5148,8 @@
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
+      <c r="N180" s="4" t="n"/>
+      <c r="O180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4724,6 +5169,8 @@
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -4743,6 +5190,8 @@
       <c r="K182" s="8" t="n"/>
       <c r="L182" s="8" t="n"/>
       <c r="M182" s="8" t="n"/>
+      <c r="N182" s="8" t="n"/>
+      <c r="O182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -4762,6 +5211,8 @@
       <c r="K183" s="8" t="n"/>
       <c r="L183" s="8" t="n"/>
       <c r="M183" s="8" t="n"/>
+      <c r="N183" s="8" t="n"/>
+      <c r="O183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -4781,6 +5232,8 @@
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
+      <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4800,6 +5253,8 @@
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4819,6 +5274,8 @@
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
+      <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4838,6 +5295,8 @@
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -4857,6 +5316,8 @@
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
+      <c r="N188" s="4" t="n"/>
+      <c r="O188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -4876,6 +5337,8 @@
       <c r="K189" s="8" t="n"/>
       <c r="L189" s="8" t="n"/>
       <c r="M189" s="8" t="n"/>
+      <c r="N189" s="8" t="n"/>
+      <c r="O189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -4895,6 +5358,8 @@
       <c r="K190" s="8" t="n"/>
       <c r="L190" s="8" t="n"/>
       <c r="M190" s="8" t="n"/>
+      <c r="N190" s="8" t="n"/>
+      <c r="O190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4914,6 +5379,8 @@
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4933,6 +5400,8 @@
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
+      <c r="N192" s="4" t="n"/>
+      <c r="O192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4952,6 +5421,8 @@
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
+      <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4971,6 +5442,8 @@
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
+      <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4990,6 +5463,8 @@
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -5009,6 +5484,8 @@
       <c r="K196" s="8" t="n"/>
       <c r="L196" s="8" t="n"/>
       <c r="M196" s="8" t="n"/>
+      <c r="N196" s="8" t="n"/>
+      <c r="O196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -5028,6 +5505,8 @@
       <c r="K197" s="8" t="n"/>
       <c r="L197" s="8" t="n"/>
       <c r="M197" s="8" t="n"/>
+      <c r="N197" s="8" t="n"/>
+      <c r="O197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -5047,6 +5526,8 @@
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
+      <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -5066,6 +5547,8 @@
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
+      <c r="N199" s="4" t="n"/>
+      <c r="O199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -5085,6 +5568,8 @@
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
+      <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -5104,6 +5589,8 @@
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
+      <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -5123,6 +5610,8 @@
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
+      <c r="N202" s="4" t="n"/>
+      <c r="O202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -5142,6 +5631,8 @@
       <c r="K203" s="8" t="n"/>
       <c r="L203" s="8" t="n"/>
       <c r="M203" s="8" t="n"/>
+      <c r="N203" s="8" t="n"/>
+      <c r="O203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -5161,6 +5652,8 @@
       <c r="K204" s="8" t="n"/>
       <c r="L204" s="8" t="n"/>
       <c r="M204" s="8" t="n"/>
+      <c r="N204" s="8" t="n"/>
+      <c r="O204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -5180,6 +5673,8 @@
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
       <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -5199,6 +5694,8 @@
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
+      <c r="N206" s="4" t="n"/>
+      <c r="O206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -5218,6 +5715,8 @@
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -5237,6 +5736,8 @@
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
+      <c r="N208" s="4" t="n"/>
+      <c r="O208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -5256,6 +5757,8 @@
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
+      <c r="N209" s="4" t="n"/>
+      <c r="O209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -5275,6 +5778,8 @@
       <c r="K210" s="8" t="n"/>
       <c r="L210" s="8" t="n"/>
       <c r="M210" s="8" t="n"/>
+      <c r="N210" s="8" t="n"/>
+      <c r="O210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -5294,6 +5799,8 @@
       <c r="K211" s="8" t="n"/>
       <c r="L211" s="8" t="n"/>
       <c r="M211" s="8" t="n"/>
+      <c r="N211" s="8" t="n"/>
+      <c r="O211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -5313,6 +5820,8 @@
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
+      <c r="N212" s="4" t="n"/>
+      <c r="O212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -5332,6 +5841,8 @@
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
+      <c r="N213" s="4" t="n"/>
+      <c r="O213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -5351,6 +5862,8 @@
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
+      <c r="N214" s="4" t="n"/>
+      <c r="O214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -5370,6 +5883,8 @@
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
       <c r="M215" s="4" t="n"/>
+      <c r="N215" s="4" t="n"/>
+      <c r="O215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -5389,6 +5904,8 @@
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
       <c r="M216" s="4" t="n"/>
+      <c r="N216" s="4" t="n"/>
+      <c r="O216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -5408,6 +5925,8 @@
       <c r="K217" s="8" t="n"/>
       <c r="L217" s="8" t="n"/>
       <c r="M217" s="8" t="n"/>
+      <c r="N217" s="8" t="n"/>
+      <c r="O217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -5427,6 +5946,8 @@
       <c r="K218" s="8" t="n"/>
       <c r="L218" s="8" t="n"/>
       <c r="M218" s="8" t="n"/>
+      <c r="N218" s="8" t="n"/>
+      <c r="O218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -5446,6 +5967,8 @@
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
       <c r="M219" s="4" t="n"/>
+      <c r="N219" s="4" t="n"/>
+      <c r="O219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -5465,6 +5988,8 @@
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
       <c r="M220" s="4" t="n"/>
+      <c r="N220" s="4" t="n"/>
+      <c r="O220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -5484,6 +6009,8 @@
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
       <c r="M221" s="4" t="n"/>
+      <c r="N221" s="4" t="n"/>
+      <c r="O221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -5503,6 +6030,8 @@
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
       <c r="M222" s="4" t="n"/>
+      <c r="N222" s="4" t="n"/>
+      <c r="O222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -5522,6 +6051,8 @@
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
       <c r="M223" s="4" t="n"/>
+      <c r="N223" s="4" t="n"/>
+      <c r="O223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -5541,6 +6072,8 @@
       <c r="K224" s="8" t="n"/>
       <c r="L224" s="8" t="n"/>
       <c r="M224" s="8" t="n"/>
+      <c r="N224" s="8" t="n"/>
+      <c r="O224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -5560,6 +6093,8 @@
       <c r="K225" s="8" t="n"/>
       <c r="L225" s="8" t="n"/>
       <c r="M225" s="8" t="n"/>
+      <c r="N225" s="8" t="n"/>
+      <c r="O225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -5579,6 +6114,8 @@
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
       <c r="M226" s="4" t="n"/>
+      <c r="N226" s="4" t="n"/>
+      <c r="O226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -5598,6 +6135,8 @@
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
       <c r="M227" s="4" t="n"/>
+      <c r="N227" s="4" t="n"/>
+      <c r="O227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -5617,6 +6156,8 @@
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
       <c r="M228" s="4" t="n"/>
+      <c r="N228" s="4" t="n"/>
+      <c r="O228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -5636,6 +6177,8 @@
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
       <c r="M229" s="4" t="n"/>
+      <c r="N229" s="4" t="n"/>
+      <c r="O229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -5655,6 +6198,8 @@
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
       <c r="M230" s="4" t="n"/>
+      <c r="N230" s="4" t="n"/>
+      <c r="O230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -5674,6 +6219,8 @@
       <c r="K231" s="8" t="n"/>
       <c r="L231" s="8" t="n"/>
       <c r="M231" s="8" t="n"/>
+      <c r="N231" s="8" t="n"/>
+      <c r="O231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -5693,6 +6240,8 @@
       <c r="K232" s="8" t="n"/>
       <c r="L232" s="8" t="n"/>
       <c r="M232" s="8" t="n"/>
+      <c r="N232" s="8" t="n"/>
+      <c r="O232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -5712,6 +6261,8 @@
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
       <c r="M233" s="4" t="n"/>
+      <c r="N233" s="4" t="n"/>
+      <c r="O233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -5731,6 +6282,8 @@
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
       <c r="M234" s="4" t="n"/>
+      <c r="N234" s="4" t="n"/>
+      <c r="O234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -5750,6 +6303,8 @@
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
       <c r="M235" s="4" t="n"/>
+      <c r="N235" s="4" t="n"/>
+      <c r="O235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -5769,6 +6324,8 @@
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
       <c r="M236" s="4" t="n"/>
+      <c r="N236" s="4" t="n"/>
+      <c r="O236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -5788,6 +6345,8 @@
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
       <c r="M237" s="4" t="n"/>
+      <c r="N237" s="4" t="n"/>
+      <c r="O237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -5807,6 +6366,8 @@
       <c r="K238" s="8" t="n"/>
       <c r="L238" s="8" t="n"/>
       <c r="M238" s="8" t="n"/>
+      <c r="N238" s="8" t="n"/>
+      <c r="O238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -5826,6 +6387,8 @@
       <c r="K239" s="8" t="n"/>
       <c r="L239" s="8" t="n"/>
       <c r="M239" s="8" t="n"/>
+      <c r="N239" s="8" t="n"/>
+      <c r="O239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -5845,6 +6408,8 @@
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
       <c r="M240" s="4" t="n"/>
+      <c r="N240" s="4" t="n"/>
+      <c r="O240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -5864,6 +6429,8 @@
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
       <c r="M241" s="4" t="n"/>
+      <c r="N241" s="4" t="n"/>
+      <c r="O241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -5876,17 +6443,19 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="4" t="n"/>
-      <c r="G242" s="5" t="inlineStr">
+      <c r="G242" s="4" t="n"/>
+      <c r="H242" s="4" t="n"/>
+      <c r="I242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H242" s="4" t="n"/>
-      <c r="I242" s="4" t="n"/>
       <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
       <c r="M242" s="4" t="n"/>
+      <c r="N242" s="4" t="n"/>
+      <c r="O242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -5899,17 +6468,19 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="4" t="n"/>
       <c r="F243" s="4" t="n"/>
-      <c r="G243" s="5" t="inlineStr">
+      <c r="G243" s="4" t="n"/>
+      <c r="H243" s="4" t="n"/>
+      <c r="I243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H243" s="4" t="n"/>
-      <c r="I243" s="4" t="n"/>
       <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
+      <c r="N243" s="4" t="n"/>
+      <c r="O243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -5922,17 +6493,19 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="4" t="n"/>
-      <c r="G244" s="5" t="inlineStr">
+      <c r="G244" s="4" t="n"/>
+      <c r="H244" s="4" t="n"/>
+      <c r="I244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H244" s="4" t="n"/>
-      <c r="I244" s="4" t="n"/>
       <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>
+      <c r="N244" s="4" t="n"/>
+      <c r="O244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -5952,6 +6525,8 @@
       <c r="K245" s="8" t="n"/>
       <c r="L245" s="8" t="n"/>
       <c r="M245" s="8" t="n"/>
+      <c r="N245" s="8" t="n"/>
+      <c r="O245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -5971,6 +6546,8 @@
       <c r="K246" s="8" t="n"/>
       <c r="L246" s="8" t="n"/>
       <c r="M246" s="8" t="n"/>
+      <c r="N246" s="8" t="n"/>
+      <c r="O246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -5983,17 +6560,19 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="4" t="n"/>
       <c r="F247" s="4" t="n"/>
-      <c r="G247" s="5" t="inlineStr">
+      <c r="G247" s="4" t="n"/>
+      <c r="H247" s="4" t="n"/>
+      <c r="I247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H247" s="4" t="n"/>
-      <c r="I247" s="4" t="n"/>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
       <c r="M247" s="4" t="n"/>
+      <c r="N247" s="4" t="n"/>
+      <c r="O247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -6006,17 +6585,19 @@
       <c r="D248" s="4" t="n"/>
       <c r="E248" s="4" t="n"/>
       <c r="F248" s="4" t="n"/>
-      <c r="G248" s="5" t="inlineStr">
+      <c r="G248" s="4" t="n"/>
+      <c r="H248" s="4" t="n"/>
+      <c r="I248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="H248" s="4" t="n"/>
-      <c r="I248" s="4" t="n"/>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
       <c r="M248" s="4" t="n"/>
+      <c r="N248" s="4" t="n"/>
+      <c r="O248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2431,7 +2431,11 @@
         </is>
       </c>
       <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="5" t="inlineStr">
@@ -2472,7 +2476,11 @@
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
@@ -2509,7 +2517,11 @@
         </is>
       </c>
       <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="n"/>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
@@ -2520,7 +2532,11 @@
       </c>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="10" t="inlineStr">
         <is>
@@ -2542,7 +2558,11 @@
         </is>
       </c>
       <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
@@ -2553,7 +2573,11 @@
       </c>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="10" t="inlineStr">
         <is>
@@ -2590,7 +2614,8 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Film - Sŵ Ni
+Parti Dathly S4C Athrawon</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
@@ -2624,9 +2649,10 @@
           <t>Parti Dathly S4C Athrawon</t>
         </is>
       </c>
-      <c r="M62" s="10" t="inlineStr">
-        <is>
-          <t>Parti Dathly S4C Athrawon</t>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave
+Parti Dathly S4C Athrawon</t>
         </is>
       </c>
       <c r="N62" s="10" t="inlineStr">
@@ -2738,11 +2764,7 @@
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Delivery - Deep Watch</t>
-        </is>
-      </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2593,76 +2593,76 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
-Parti Dathly S4C Athrawon</t>
+Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
-Parti Dathly S4C Athrawon</t>
+Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon
+          <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave
-Parti Dathly S4C Athrawon</t>
+Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon</t>
+          <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathly S4C Athrawon
+          <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
         </is>
       </c>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2726,7 +2726,11 @@
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
     </row>
@@ -2747,7 +2751,11 @@
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="n"/>
-      <c r="M66" s="4" t="n"/>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="n"/>
     </row>
@@ -2765,10 +2773,18 @@
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
     </row>
@@ -2786,7 +2802,11 @@
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
@@ -2807,7 +2827,11 @@
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
@@ -2870,8 +2894,16 @@
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
+      <c r="J72" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
@@ -2891,8 +2923,16 @@
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
@@ -2912,9 +2952,21 @@
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
+      <c r="J74" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
@@ -2933,9 +2985,21 @@
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
+      <c r="J75" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
@@ -2954,9 +3018,21 @@
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="n"/>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n"/>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2847,7 +2847,11 @@
       <c r="B70" s="8" t="n"/>
       <c r="C70" s="8" t="n"/>
       <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
@@ -2868,7 +2872,11 @@
       <c r="B71" s="8" t="n"/>
       <c r="C71" s="8" t="n"/>
       <c r="D71" s="8" t="n"/>
-      <c r="E71" s="8" t="n"/>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
@@ -2889,7 +2897,11 @@
       <c r="B72" s="4" t="n"/>
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
@@ -2918,7 +2930,11 @@
       <c r="B73" s="4" t="n"/>
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
@@ -2947,7 +2963,11 @@
       <c r="B74" s="4" t="n"/>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
@@ -2980,7 +3000,11 @@
       <c r="B75" s="4" t="n"/>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
@@ -3013,7 +3037,11 @@
       <c r="B76" s="4" t="n"/>
       <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
@@ -3046,7 +3074,11 @@
       <c r="B77" s="8" t="n"/>
       <c r="C77" s="8" t="n"/>
       <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
@@ -3067,7 +3099,11 @@
       <c r="B78" s="8" t="n"/>
       <c r="C78" s="8" t="n"/>
       <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
@@ -3088,14 +3124,30 @@
       <c r="B79" s="4" t="n"/>
       <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="n"/>
-      <c r="L79" s="4" t="n"/>
+      <c r="J79" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
       <c r="O79" s="4" t="n"/>
@@ -3114,9 +3166,21 @@
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
+      <c r="J80" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
@@ -3135,9 +3199,21 @@
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
+      <c r="J81" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
       <c r="O81" s="4" t="n"/>
@@ -3156,9 +3232,21 @@
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
+      <c r="J82" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
@@ -3177,9 +3265,21 @@
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n"/>
-      <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
+      <c r="J83" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
       <c r="O83" s="4" t="n"/>
@@ -3240,7 +3340,11 @@
       <c r="G86" s="4" t="n"/>
       <c r="H86" s="4" t="n"/>
       <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="n"/>
+      <c r="J86" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -3346,7 +3346,11 @@
         </is>
       </c>
       <c r="K86" s="4" t="n"/>
-      <c r="L86" s="4" t="n"/>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="n"/>
       <c r="O86" s="4" t="n"/>
@@ -3365,9 +3369,17 @@
       <c r="G87" s="4" t="n"/>
       <c r="H87" s="4" t="n"/>
       <c r="I87" s="4" t="n"/>
-      <c r="J87" s="4" t="n"/>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="n"/>
-      <c r="L87" s="4" t="n"/>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
       <c r="O87" s="4" t="n"/>
@@ -3386,9 +3398,17 @@
       <c r="G88" s="4" t="n"/>
       <c r="H88" s="4" t="n"/>
       <c r="I88" s="4" t="n"/>
-      <c r="J88" s="4" t="n"/>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
       <c r="O88" s="4" t="n"/>
@@ -3407,9 +3427,17 @@
       <c r="G89" s="4" t="n"/>
       <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
       <c r="O89" s="4" t="n"/>
@@ -3428,9 +3456,17 @@
       <c r="G90" s="4" t="n"/>
       <c r="H90" s="4" t="n"/>
       <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M90" s="4" t="n"/>
       <c r="N90" s="4" t="n"/>
       <c r="O90" s="4" t="n"/>
@@ -3491,9 +3527,17 @@
       <c r="G93" s="4" t="n"/>
       <c r="H93" s="4" t="n"/>
       <c r="I93" s="4" t="n"/>
-      <c r="J93" s="4" t="n"/>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K93" s="4" t="n"/>
-      <c r="L93" s="4" t="n"/>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
       <c r="O93" s="4" t="n"/>
@@ -3512,9 +3556,17 @@
       <c r="G94" s="4" t="n"/>
       <c r="H94" s="4" t="n"/>
       <c r="I94" s="4" t="n"/>
-      <c r="J94" s="4" t="n"/>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
       <c r="O94" s="4" t="n"/>
@@ -3533,9 +3585,17 @@
       <c r="G95" s="4" t="n"/>
       <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="n"/>
-      <c r="L95" s="4" t="n"/>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
       <c r="O95" s="4" t="n"/>
@@ -3554,9 +3614,17 @@
       <c r="G96" s="4" t="n"/>
       <c r="H96" s="4" t="n"/>
       <c r="I96" s="4" t="n"/>
-      <c r="J96" s="4" t="n"/>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
       <c r="O96" s="4" t="n"/>
@@ -3575,11 +3643,23 @@
       <c r="G97" s="4" t="n"/>
       <c r="H97" s="4" t="n"/>
       <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M97" s="4" t="n"/>
-      <c r="N97" s="4" t="n"/>
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="O97" s="4" t="n"/>
     </row>
     <row r="98">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -3718,9 +3718,17 @@
       <c r="G100" s="4" t="n"/>
       <c r="H100" s="4" t="n"/>
       <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K100" s="4" t="n"/>
-      <c r="L100" s="4" t="n"/>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
       <c r="O100" s="4" t="n"/>
@@ -3739,9 +3747,17 @@
       <c r="G101" s="4" t="n"/>
       <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="n"/>
-      <c r="J101" s="4" t="n"/>
+      <c r="J101" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="n"/>
-      <c r="L101" s="4" t="n"/>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
       <c r="O101" s="4" t="n"/>
@@ -3760,9 +3776,17 @@
       <c r="G102" s="4" t="n"/>
       <c r="H102" s="4" t="n"/>
       <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
+      <c r="J102" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
       <c r="O102" s="4" t="n"/>
@@ -3781,9 +3805,17 @@
       <c r="G103" s="4" t="n"/>
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="n"/>
-      <c r="J103" s="4" t="n"/>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="n"/>
-      <c r="L103" s="4" t="n"/>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
       <c r="O103" s="4" t="n"/>
@@ -3802,9 +3834,17 @@
       <c r="G104" s="4" t="n"/>
       <c r="H104" s="4" t="n"/>
       <c r="I104" s="4" t="n"/>
-      <c r="J104" s="4" t="n"/>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="n"/>
-      <c r="L104" s="4" t="n"/>
+      <c r="L104" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
       <c r="O104" s="4" t="n"/>
@@ -3907,7 +3947,12 @@
       <c r="G109" s="4" t="n"/>
       <c r="H109" s="4" t="n"/>
       <c r="I109" s="4" t="n"/>
-      <c r="J109" s="4" t="n"/>
+      <c r="J109" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
@@ -3928,7 +3973,12 @@
       <c r="G110" s="4" t="n"/>
       <c r="H110" s="4" t="n"/>
       <c r="I110" s="4" t="n"/>
-      <c r="J110" s="4" t="n"/>
+      <c r="J110" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K110" s="4" t="n"/>
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
@@ -3953,7 +4003,12 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J111" s="4" t="n"/>
+      <c r="J111" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="n"/>
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
@@ -4016,7 +4071,12 @@
       <c r="G114" s="4" t="n"/>
       <c r="H114" s="4" t="n"/>
       <c r="I114" s="4" t="n"/>
-      <c r="J114" s="4" t="n"/>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Mabli a Ceff Ceff
+Dub - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K114" s="4" t="n"/>
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
@@ -4037,7 +4097,12 @@
       <c r="G115" s="4" t="n"/>
       <c r="H115" s="4" t="n"/>
       <c r="I115" s="4" t="n"/>
-      <c r="J115" s="4" t="n"/>
+      <c r="J115" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Mabli a Ceff Ceff
+Online Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -3907,7 +3907,11 @@
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
       <c r="K107" s="4" t="n"/>
-      <c r="L107" s="4" t="n"/>
+      <c r="L107" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
       <c r="O107" s="4" t="n"/>
@@ -3928,7 +3932,11 @@
       <c r="I108" s="4" t="n"/>
       <c r="J108" s="4" t="n"/>
       <c r="K108" s="4" t="n"/>
-      <c r="L108" s="4" t="n"/>
+      <c r="L108" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
       <c r="O108" s="4" t="n"/>
@@ -3954,7 +3962,11 @@
         </is>
       </c>
       <c r="K109" s="4" t="n"/>
-      <c r="L109" s="4" t="n"/>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
       <c r="O109" s="4" t="n"/>
@@ -3980,7 +3992,11 @@
         </is>
       </c>
       <c r="K110" s="4" t="n"/>
-      <c r="L110" s="4" t="n"/>
+      <c r="L110" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
       <c r="O110" s="4" t="n"/>
@@ -3995,7 +4011,11 @@
       <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="n"/>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="4" t="n"/>
       <c r="I111" s="5" t="inlineStr">
@@ -4010,7 +4030,11 @@
         </is>
       </c>
       <c r="K111" s="4" t="n"/>
-      <c r="L111" s="4" t="n"/>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
       <c r="O111" s="4" t="n"/>
@@ -4078,7 +4102,11 @@
         </is>
       </c>
       <c r="K114" s="4" t="n"/>
-      <c r="L114" s="4" t="n"/>
+      <c r="L114" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
       <c r="O114" s="4" t="n"/>
@@ -4123,7 +4151,11 @@
       <c r="G116" s="4" t="n"/>
       <c r="H116" s="4" t="n"/>
       <c r="I116" s="4" t="n"/>
-      <c r="J116" s="4" t="n"/>
+      <c r="J116" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
@@ -4144,7 +4176,11 @@
       <c r="G117" s="4" t="n"/>
       <c r="H117" s="4" t="n"/>
       <c r="I117" s="4" t="n"/>
-      <c r="J117" s="4" t="n"/>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
@@ -4161,7 +4197,11 @@
       <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="n"/>
       <c r="H118" s="4" t="n"/>
       <c r="I118" s="5" t="inlineStr">
@@ -4169,7 +4209,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J118" s="4" t="n"/>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
@@ -4232,7 +4276,11 @@
       <c r="G121" s="4" t="n"/>
       <c r="H121" s="4" t="n"/>
       <c r="I121" s="4" t="n"/>
-      <c r="J121" s="4" t="n"/>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
@@ -4253,7 +4301,11 @@
       <c r="G122" s="4" t="n"/>
       <c r="H122" s="4" t="n"/>
       <c r="I122" s="4" t="n"/>
-      <c r="J122" s="4" t="n"/>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
@@ -4274,7 +4326,11 @@
       <c r="G123" s="4" t="n"/>
       <c r="H123" s="4" t="n"/>
       <c r="I123" s="4" t="n"/>
-      <c r="J123" s="4" t="n"/>
+      <c r="J123" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - External</t>
+        </is>
+      </c>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
@@ -4295,7 +4351,11 @@
       <c r="G124" s="4" t="n"/>
       <c r="H124" s="4" t="n"/>
       <c r="I124" s="4" t="n"/>
-      <c r="J124" s="4" t="n"/>
+      <c r="J124" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - External</t>
+        </is>
+      </c>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
@@ -4316,7 +4376,11 @@
       <c r="G125" s="4" t="n"/>
       <c r="H125" s="4" t="n"/>
       <c r="I125" s="4" t="n"/>
-      <c r="J125" s="4" t="n"/>
+      <c r="J125" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - External</t>
+        </is>
+      </c>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
@@ -4379,7 +4443,11 @@
       <c r="G128" s="4" t="n"/>
       <c r="H128" s="4" t="n"/>
       <c r="I128" s="4" t="n"/>
-      <c r="J128" s="4" t="n"/>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
@@ -4400,7 +4468,11 @@
       <c r="G129" s="4" t="n"/>
       <c r="H129" s="4" t="n"/>
       <c r="I129" s="4" t="n"/>
-      <c r="J129" s="4" t="n"/>
+      <c r="J129" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
@@ -4421,7 +4493,11 @@
       <c r="G130" s="4" t="n"/>
       <c r="H130" s="4" t="n"/>
       <c r="I130" s="4" t="n"/>
-      <c r="J130" s="4" t="n"/>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
@@ -4442,7 +4518,11 @@
       <c r="G131" s="4" t="n"/>
       <c r="H131" s="4" t="n"/>
       <c r="I131" s="4" t="n"/>
-      <c r="J131" s="4" t="n"/>
+      <c r="J131" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
@@ -4463,7 +4543,11 @@
       <c r="G132" s="4" t="n"/>
       <c r="H132" s="4" t="n"/>
       <c r="I132" s="4" t="n"/>
-      <c r="J132" s="4" t="n"/>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
@@ -4526,7 +4610,11 @@
       <c r="G135" s="4" t="n"/>
       <c r="H135" s="4" t="n"/>
       <c r="I135" s="4" t="n"/>
-      <c r="J135" s="4" t="n"/>
+      <c r="J135" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
@@ -4548,10 +4636,15 @@
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Delivery - Mabli a Ceff Ceff</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="n"/>
+          <t>Delivery - Mabli a Ceff Ceff
+Delivery - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
@@ -4576,7 +4669,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J137" s="4" t="n"/>
+      <c r="J137" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
@@ -4601,7 +4698,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J138" s="4" t="n"/>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
@@ -4626,7 +4727,11 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J139" s="4" t="n"/>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -4631,13 +4631,16 @@
       <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
-      <c r="F136" s="4" t="n"/>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="n"/>
       <c r="H136" s="4" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Delivery - Mabli a Ceff Ceff
-Delivery - Mabli a Ceff Ceff</t>
+          <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J136" s="10" t="inlineStr">
@@ -4661,7 +4664,11 @@
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="4" t="n"/>
-      <c r="F137" s="4" t="n"/>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="n"/>
       <c r="H137" s="4" t="n"/>
       <c r="I137" s="5" t="inlineStr">
@@ -4690,7 +4697,11 @@
       <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="4" t="n"/>
-      <c r="F138" s="4" t="n"/>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="n"/>
       <c r="H138" s="4" t="n"/>
       <c r="I138" s="5" t="inlineStr">
@@ -4719,7 +4730,11 @@
       <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="4" t="n"/>
-      <c r="F139" s="4" t="n"/>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Delivery - Mabli a Ceff Ceff</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="n"/>
       <c r="H139" s="4" t="n"/>
       <c r="I139" s="5" t="inlineStr">
@@ -4794,7 +4809,11 @@
       <c r="G142" s="4" t="n"/>
       <c r="H142" s="4" t="n"/>
       <c r="I142" s="4" t="n"/>
-      <c r="J142" s="4" t="n"/>
+      <c r="J142" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
@@ -4815,7 +4834,11 @@
       <c r="G143" s="4" t="n"/>
       <c r="H143" s="4" t="n"/>
       <c r="I143" s="4" t="n"/>
-      <c r="J143" s="4" t="n"/>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
@@ -4941,7 +4964,11 @@
       <c r="G149" s="4" t="n"/>
       <c r="H149" s="4" t="n"/>
       <c r="I149" s="4" t="n"/>
-      <c r="J149" s="4" t="n"/>
+      <c r="J149" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
@@ -4962,7 +4989,11 @@
       <c r="G150" s="4" t="n"/>
       <c r="H150" s="4" t="n"/>
       <c r="I150" s="4" t="n"/>
-      <c r="J150" s="4" t="n"/>
+      <c r="J150" s="10" t="inlineStr">
+        <is>
+          <t>Film - LGBTQ+</t>
+        </is>
+      </c>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
@@ -5088,7 +5119,11 @@
       <c r="G156" s="4" t="n"/>
       <c r="H156" s="4" t="n"/>
       <c r="I156" s="4" t="n"/>
-      <c r="J156" s="4" t="n"/>
+      <c r="J156" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
@@ -5109,7 +5144,11 @@
       <c r="G157" s="4" t="n"/>
       <c r="H157" s="4" t="n"/>
       <c r="I157" s="4" t="n"/>
-      <c r="J157" s="4" t="n"/>
+      <c r="J157" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
@@ -5131,10 +5170,14 @@
       <c r="H158" s="4" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Delivery - Sioe Gerdd</t>
-        </is>
-      </c>
-      <c r="J158" s="4" t="n"/>
+          <t>Delivery - LGBTQ+</t>
+        </is>
+      </c>
+      <c r="J158" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
@@ -5155,7 +5198,11 @@
       <c r="G159" s="4" t="n"/>
       <c r="H159" s="4" t="n"/>
       <c r="I159" s="4" t="n"/>
-      <c r="J159" s="4" t="n"/>
+      <c r="J159" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
@@ -5176,7 +5223,11 @@
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
       <c r="I160" s="4" t="n"/>
-      <c r="J160" s="4" t="n"/>
+      <c r="J160" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
@@ -5239,7 +5290,11 @@
       <c r="G163" s="4" t="n"/>
       <c r="H163" s="4" t="n"/>
       <c r="I163" s="4" t="n"/>
-      <c r="J163" s="4" t="n"/>
+      <c r="J163" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
@@ -5260,7 +5315,11 @@
       <c r="G164" s="4" t="n"/>
       <c r="H164" s="4" t="n"/>
       <c r="I164" s="4" t="n"/>
-      <c r="J164" s="4" t="n"/>
+      <c r="J164" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
@@ -5281,7 +5340,11 @@
       <c r="G165" s="4" t="n"/>
       <c r="H165" s="4" t="n"/>
       <c r="I165" s="4" t="n"/>
-      <c r="J165" s="4" t="n"/>
+      <c r="J165" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
@@ -5302,7 +5365,11 @@
       <c r="G166" s="4" t="n"/>
       <c r="H166" s="4" t="n"/>
       <c r="I166" s="4" t="n"/>
-      <c r="J166" s="4" t="n"/>
+      <c r="J166" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
@@ -5323,7 +5390,11 @@
       <c r="G167" s="4" t="n"/>
       <c r="H167" s="4" t="n"/>
       <c r="I167" s="4" t="n"/>
-      <c r="J167" s="4" t="n"/>
+      <c r="J167" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
@@ -5386,7 +5457,11 @@
       <c r="G170" s="4" t="n"/>
       <c r="H170" s="4" t="n"/>
       <c r="I170" s="4" t="n"/>
-      <c r="J170" s="4" t="n"/>
+      <c r="J170" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
@@ -5407,7 +5482,11 @@
       <c r="G171" s="4" t="n"/>
       <c r="H171" s="4" t="n"/>
       <c r="I171" s="4" t="n"/>
-      <c r="J171" s="4" t="n"/>
+      <c r="J171" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
@@ -5428,7 +5507,11 @@
       <c r="G172" s="4" t="n"/>
       <c r="H172" s="4" t="n"/>
       <c r="I172" s="4" t="n"/>
-      <c r="J172" s="4" t="n"/>
+      <c r="J172" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
@@ -5449,7 +5532,11 @@
       <c r="G173" s="4" t="n"/>
       <c r="H173" s="4" t="n"/>
       <c r="I173" s="4" t="n"/>
-      <c r="J173" s="4" t="n"/>
+      <c r="J173" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
@@ -5470,7 +5557,11 @@
       <c r="G174" s="4" t="n"/>
       <c r="H174" s="4" t="n"/>
       <c r="I174" s="4" t="n"/>
-      <c r="J174" s="4" t="n"/>
+      <c r="J174" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
@@ -5533,7 +5624,11 @@
       <c r="G177" s="4" t="n"/>
       <c r="H177" s="4" t="n"/>
       <c r="I177" s="4" t="n"/>
-      <c r="J177" s="4" t="n"/>
+      <c r="J177" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
@@ -5554,7 +5649,11 @@
       <c r="G178" s="4" t="n"/>
       <c r="H178" s="4" t="n"/>
       <c r="I178" s="4" t="n"/>
-      <c r="J178" s="4" t="n"/>
+      <c r="J178" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
@@ -5575,7 +5674,11 @@
       <c r="G179" s="4" t="n"/>
       <c r="H179" s="4" t="n"/>
       <c r="I179" s="4" t="n"/>
-      <c r="J179" s="4" t="n"/>
+      <c r="J179" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
@@ -5596,7 +5699,11 @@
       <c r="G180" s="4" t="n"/>
       <c r="H180" s="4" t="n"/>
       <c r="I180" s="4" t="n"/>
-      <c r="J180" s="4" t="n"/>
+      <c r="J180" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
@@ -5617,7 +5724,11 @@
       <c r="G181" s="4" t="n"/>
       <c r="H181" s="4" t="n"/>
       <c r="I181" s="4" t="n"/>
-      <c r="J181" s="4" t="n"/>
+      <c r="J181" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
@@ -5680,7 +5791,11 @@
       <c r="G184" s="4" t="n"/>
       <c r="H184" s="4" t="n"/>
       <c r="I184" s="4" t="n"/>
-      <c r="J184" s="4" t="n"/>
+      <c r="J184" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
@@ -5701,7 +5816,11 @@
       <c r="G185" s="4" t="n"/>
       <c r="H185" s="4" t="n"/>
       <c r="I185" s="4" t="n"/>
-      <c r="J185" s="4" t="n"/>
+      <c r="J185" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
@@ -5722,7 +5841,11 @@
       <c r="G186" s="4" t="n"/>
       <c r="H186" s="4" t="n"/>
       <c r="I186" s="4" t="n"/>
-      <c r="J186" s="4" t="n"/>
+      <c r="J186" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
@@ -5743,7 +5866,11 @@
       <c r="G187" s="4" t="n"/>
       <c r="H187" s="4" t="n"/>
       <c r="I187" s="4" t="n"/>
-      <c r="J187" s="4" t="n"/>
+      <c r="J187" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
@@ -5764,7 +5891,11 @@
       <c r="G188" s="4" t="n"/>
       <c r="H188" s="4" t="n"/>
       <c r="I188" s="4" t="n"/>
-      <c r="J188" s="4" t="n"/>
+      <c r="J188" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
@@ -5827,7 +5958,11 @@
       <c r="G191" s="4" t="n"/>
       <c r="H191" s="4" t="n"/>
       <c r="I191" s="4" t="n"/>
-      <c r="J191" s="4" t="n"/>
+      <c r="J191" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
@@ -5848,7 +5983,11 @@
       <c r="G192" s="4" t="n"/>
       <c r="H192" s="4" t="n"/>
       <c r="I192" s="4" t="n"/>
-      <c r="J192" s="4" t="n"/>
+      <c r="J192" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
@@ -5869,7 +6008,11 @@
       <c r="G193" s="4" t="n"/>
       <c r="H193" s="4" t="n"/>
       <c r="I193" s="4" t="n"/>
-      <c r="J193" s="4" t="n"/>
+      <c r="J193" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
@@ -5890,7 +6033,11 @@
       <c r="G194" s="4" t="n"/>
       <c r="H194" s="4" t="n"/>
       <c r="I194" s="4" t="n"/>
-      <c r="J194" s="4" t="n"/>
+      <c r="J194" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
@@ -5911,7 +6058,11 @@
       <c r="G195" s="4" t="n"/>
       <c r="H195" s="4" t="n"/>
       <c r="I195" s="4" t="n"/>
-      <c r="J195" s="4" t="n"/>
+      <c r="J195" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
@@ -5974,7 +6125,11 @@
       <c r="G198" s="4" t="n"/>
       <c r="H198" s="4" t="n"/>
       <c r="I198" s="4" t="n"/>
-      <c r="J198" s="4" t="n"/>
+      <c r="J198" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
@@ -5995,7 +6150,11 @@
       <c r="G199" s="4" t="n"/>
       <c r="H199" s="4" t="n"/>
       <c r="I199" s="4" t="n"/>
-      <c r="J199" s="4" t="n"/>
+      <c r="J199" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
@@ -6016,7 +6175,11 @@
       <c r="G200" s="4" t="n"/>
       <c r="H200" s="4" t="n"/>
       <c r="I200" s="4" t="n"/>
-      <c r="J200" s="4" t="n"/>
+      <c r="J200" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
@@ -6037,7 +6200,11 @@
       <c r="G201" s="4" t="n"/>
       <c r="H201" s="4" t="n"/>
       <c r="I201" s="4" t="n"/>
-      <c r="J201" s="4" t="n"/>
+      <c r="J201" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
@@ -6058,7 +6225,11 @@
       <c r="G202" s="4" t="n"/>
       <c r="H202" s="4" t="n"/>
       <c r="I202" s="4" t="n"/>
-      <c r="J202" s="4" t="n"/>
+      <c r="J202" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
@@ -6121,7 +6292,11 @@
       <c r="G205" s="4" t="n"/>
       <c r="H205" s="4" t="n"/>
       <c r="I205" s="4" t="n"/>
-      <c r="J205" s="4" t="n"/>
+      <c r="J205" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
       <c r="M205" s="4" t="n"/>
@@ -6142,7 +6317,11 @@
       <c r="G206" s="4" t="n"/>
       <c r="H206" s="4" t="n"/>
       <c r="I206" s="4" t="n"/>
-      <c r="J206" s="4" t="n"/>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
@@ -6163,7 +6342,11 @@
       <c r="G207" s="4" t="n"/>
       <c r="H207" s="4" t="n"/>
       <c r="I207" s="4" t="n"/>
-      <c r="J207" s="4" t="n"/>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
@@ -6184,7 +6367,11 @@
       <c r="G208" s="4" t="n"/>
       <c r="H208" s="4" t="n"/>
       <c r="I208" s="4" t="n"/>
-      <c r="J208" s="4" t="n"/>
+      <c r="J208" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
@@ -6205,7 +6392,11 @@
       <c r="G209" s="4" t="n"/>
       <c r="H209" s="4" t="n"/>
       <c r="I209" s="4" t="n"/>
-      <c r="J209" s="4" t="n"/>
+      <c r="J209" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
@@ -6268,7 +6459,11 @@
       <c r="G212" s="4" t="n"/>
       <c r="H212" s="4" t="n"/>
       <c r="I212" s="4" t="n"/>
-      <c r="J212" s="4" t="n"/>
+      <c r="J212" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
@@ -6289,7 +6484,11 @@
       <c r="G213" s="4" t="n"/>
       <c r="H213" s="4" t="n"/>
       <c r="I213" s="4" t="n"/>
-      <c r="J213" s="4" t="n"/>
+      <c r="J213" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
@@ -6310,7 +6509,11 @@
       <c r="G214" s="4" t="n"/>
       <c r="H214" s="4" t="n"/>
       <c r="I214" s="4" t="n"/>
-      <c r="J214" s="4" t="n"/>
+      <c r="J214" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
@@ -6331,7 +6534,11 @@
       <c r="G215" s="4" t="n"/>
       <c r="H215" s="4" t="n"/>
       <c r="I215" s="4" t="n"/>
-      <c r="J215" s="4" t="n"/>
+      <c r="J215" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
       <c r="M215" s="4" t="n"/>
@@ -6352,7 +6559,12 @@
       <c r="G216" s="4" t="n"/>
       <c r="H216" s="4" t="n"/>
       <c r="I216" s="4" t="n"/>
-      <c r="J216" s="4" t="n"/>
+      <c r="J216" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni
+Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
       <c r="M216" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -6561,8 +6561,7 @@
       <c r="I216" s="4" t="n"/>
       <c r="J216" s="11" t="inlineStr">
         <is>
-          <t>Offline Edit - Sŵ Ni
-Offline Edit - Sŵ Ni</t>
+          <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
       <c r="K216" s="4" t="n"/>
@@ -6627,7 +6626,11 @@
       <c r="G219" s="4" t="n"/>
       <c r="H219" s="4" t="n"/>
       <c r="I219" s="4" t="n"/>
-      <c r="J219" s="4" t="n"/>
+      <c r="J219" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
       <c r="M219" s="4" t="n"/>
@@ -6648,7 +6651,11 @@
       <c r="G220" s="4" t="n"/>
       <c r="H220" s="4" t="n"/>
       <c r="I220" s="4" t="n"/>
-      <c r="J220" s="4" t="n"/>
+      <c r="J220" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
       <c r="M220" s="4" t="n"/>
@@ -6669,7 +6676,11 @@
       <c r="G221" s="4" t="n"/>
       <c r="H221" s="4" t="n"/>
       <c r="I221" s="4" t="n"/>
-      <c r="J221" s="4" t="n"/>
+      <c r="J221" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
       <c r="M221" s="4" t="n"/>
@@ -6690,7 +6701,11 @@
       <c r="G222" s="4" t="n"/>
       <c r="H222" s="4" t="n"/>
       <c r="I222" s="4" t="n"/>
-      <c r="J222" s="4" t="n"/>
+      <c r="J222" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
       <c r="M222" s="4" t="n"/>
@@ -6711,7 +6726,11 @@
       <c r="G223" s="4" t="n"/>
       <c r="H223" s="4" t="n"/>
       <c r="I223" s="4" t="n"/>
-      <c r="J223" s="4" t="n"/>
+      <c r="J223" s="11" t="inlineStr">
+        <is>
+          <t>Offline Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
       <c r="M223" s="4" t="n"/>
@@ -6774,7 +6793,11 @@
       <c r="G226" s="4" t="n"/>
       <c r="H226" s="4" t="n"/>
       <c r="I226" s="4" t="n"/>
-      <c r="J226" s="4" t="n"/>
+      <c r="J226" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
       <c r="M226" s="4" t="n"/>
@@ -6795,7 +6818,11 @@
       <c r="G227" s="4" t="n"/>
       <c r="H227" s="4" t="n"/>
       <c r="I227" s="4" t="n"/>
-      <c r="J227" s="4" t="n"/>
+      <c r="J227" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
       <c r="M227" s="4" t="n"/>
@@ -6816,7 +6843,11 @@
       <c r="G228" s="4" t="n"/>
       <c r="H228" s="4" t="n"/>
       <c r="I228" s="4" t="n"/>
-      <c r="J228" s="4" t="n"/>
+      <c r="J228" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
       <c r="M228" s="4" t="n"/>
@@ -6837,7 +6868,11 @@
       <c r="G229" s="4" t="n"/>
       <c r="H229" s="4" t="n"/>
       <c r="I229" s="4" t="n"/>
-      <c r="J229" s="4" t="n"/>
+      <c r="J229" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
       <c r="M229" s="4" t="n"/>
@@ -6858,7 +6893,11 @@
       <c r="G230" s="4" t="n"/>
       <c r="H230" s="4" t="n"/>
       <c r="I230" s="4" t="n"/>
-      <c r="J230" s="4" t="n"/>
+      <c r="J230" s="9" t="inlineStr">
+        <is>
+          <t>Notes / Changes - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
       <c r="M230" s="4" t="n"/>
@@ -6921,7 +6960,11 @@
       <c r="G233" s="4" t="n"/>
       <c r="H233" s="4" t="n"/>
       <c r="I233" s="4" t="n"/>
-      <c r="J233" s="4" t="n"/>
+      <c r="J233" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
       <c r="M233" s="4" t="n"/>
@@ -6942,7 +6985,11 @@
       <c r="G234" s="4" t="n"/>
       <c r="H234" s="4" t="n"/>
       <c r="I234" s="4" t="n"/>
-      <c r="J234" s="4" t="n"/>
+      <c r="J234" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
       <c r="M234" s="4" t="n"/>
@@ -6963,7 +7010,11 @@
       <c r="G235" s="4" t="n"/>
       <c r="H235" s="4" t="n"/>
       <c r="I235" s="4" t="n"/>
-      <c r="J235" s="4" t="n"/>
+      <c r="J235" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
       <c r="M235" s="4" t="n"/>
@@ -6984,7 +7035,11 @@
       <c r="G236" s="4" t="n"/>
       <c r="H236" s="4" t="n"/>
       <c r="I236" s="4" t="n"/>
-      <c r="J236" s="4" t="n"/>
+      <c r="J236" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
       <c r="M236" s="4" t="n"/>
@@ -7005,7 +7060,11 @@
       <c r="G237" s="4" t="n"/>
       <c r="H237" s="4" t="n"/>
       <c r="I237" s="4" t="n"/>
-      <c r="J237" s="4" t="n"/>
+      <c r="J237" s="10" t="inlineStr">
+        <is>
+          <t>Dub - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
       <c r="M237" s="4" t="n"/>
@@ -7068,7 +7127,11 @@
       <c r="G240" s="4" t="n"/>
       <c r="H240" s="4" t="n"/>
       <c r="I240" s="4" t="n"/>
-      <c r="J240" s="4" t="n"/>
+      <c r="J240" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
       <c r="M240" s="4" t="n"/>
@@ -7089,7 +7152,11 @@
       <c r="G241" s="4" t="n"/>
       <c r="H241" s="4" t="n"/>
       <c r="I241" s="4" t="n"/>
-      <c r="J241" s="4" t="n"/>
+      <c r="J241" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
       <c r="M241" s="4" t="n"/>
@@ -7114,7 +7181,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J242" s="4" t="n"/>
+      <c r="J242" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
       <c r="M242" s="4" t="n"/>
@@ -7139,7 +7210,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J243" s="4" t="n"/>
+      <c r="J243" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
@@ -7164,7 +7239,11 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J244" s="4" t="n"/>
+      <c r="J244" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1349,7 +1349,11 @@
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
       <c r="M28" s="8" t="n"/>
-      <c r="N28" s="8" t="n"/>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
       <c r="O28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
@@ -1374,7 +1378,11 @@
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
       <c r="O29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -4451,9 +4451,9 @@
       <c r="G128" s="4" t="n"/>
       <c r="H128" s="4" t="n"/>
       <c r="I128" s="4" t="n"/>
-      <c r="J128" s="10" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
+      <c r="J128" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - External</t>
         </is>
       </c>
       <c r="K128" s="4" t="n"/>
@@ -4476,9 +4476,9 @@
       <c r="G129" s="4" t="n"/>
       <c r="H129" s="4" t="n"/>
       <c r="I129" s="4" t="n"/>
-      <c r="J129" s="10" t="inlineStr">
-        <is>
-          <t>Film - LGBTQ+</t>
+      <c r="J129" s="11" t="inlineStr">
+        <is>
+          <t>Online Edit - External</t>
         </is>
       </c>
       <c r="K129" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1989,17 +1989,9 @@
         </is>
       </c>
       <c r="C46" s="4" t="n"/>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="5" t="inlineStr">
@@ -2007,11 +1999,7 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="10" t="inlineStr">
         <is>
@@ -2020,11 +2008,7 @@
       </c>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
-      <c r="O46" s="10" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="O46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1477,7 +1477,7 @@
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>Edit - Cardi Con</t>
+          <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="O31" s="10" t="inlineStr">
         <is>
-          <t>Fresh From Wales</t>
+          <t>Edit - Hansh Socials</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>Edit - Cardi Con</t>
+          <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>Fresh From Wales</t>
+          <t>Edit - Hansh Socials</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,11 @@
       </c>
       <c r="B72" s="4" t="n"/>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -2921,7 +2925,11 @@
       </c>
       <c r="B73" s="4" t="n"/>
       <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -2954,7 +2962,11 @@
       </c>
       <c r="B74" s="4" t="n"/>
       <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -2991,7 +3003,11 @@
       </c>
       <c r="B75" s="4" t="n"/>
       <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
           <t>OFF</t>
@@ -3704,7 +3720,11 @@
       </c>
       <c r="B100" s="4" t="n"/>
       <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="4" t="n"/>
@@ -3733,7 +3753,11 @@
       </c>
       <c r="B101" s="4" t="n"/>
       <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="n"/>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="4" t="n"/>
@@ -3762,7 +3786,11 @@
       </c>
       <c r="B102" s="4" t="n"/>
       <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
@@ -3791,7 +3819,11 @@
       </c>
       <c r="B103" s="4" t="n"/>
       <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="n"/>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="4" t="n"/>
@@ -3820,7 +3852,11 @@
       </c>
       <c r="B104" s="4" t="n"/>
       <c r="C104" s="4" t="n"/>
-      <c r="D104" s="4" t="n"/>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1577,7 +1577,7 @@
       </c>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>Hansh Socials</t>
+          <t>Edit - Fresh From Wales</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="O34" s="10" t="inlineStr">
         <is>
-          <t>Hansh Socials</t>
+          <t>Edit - Fresh From Wales</t>
         </is>
       </c>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1729,7 +1729,11 @@
         </is>
       </c>
       <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
@@ -1766,7 +1770,11 @@
         </is>
       </c>
       <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
@@ -1803,7 +1811,11 @@
         </is>
       </c>
       <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
@@ -1905,11 +1917,7 @@
           <t>Mon 14 Sep 2026</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>Development - Our Lives</t>
-        </is>
-      </c>
+      <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
@@ -1927,11 +1935,7 @@
         </is>
       </c>
       <c r="K44" s="4" t="n"/>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="6" t="inlineStr">
@@ -1946,11 +1950,7 @@
           <t>Tue 15 Sep 2026</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>Development - Our Lives</t>
-        </is>
-      </c>
+      <c r="B45" s="4" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
@@ -1968,11 +1968,7 @@
         </is>
       </c>
       <c r="K45" s="4" t="n"/>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
@@ -1983,11 +1979,7 @@
           <t>Wed 16 Sep 2026</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>Development - Our Lives</t>
-        </is>
-      </c>
+      <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
@@ -2001,11 +1993,7 @@
       </c>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
@@ -2016,11 +2004,7 @@
           <t>Thu 17 Sep 2026</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>Development - Our Lives</t>
-        </is>
-      </c>
+      <c r="B47" s="4" t="n"/>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="10" t="inlineStr">
         <is>
@@ -2042,11 +2026,7 @@
         </is>
       </c>
       <c r="K47" s="4" t="n"/>
-      <c r="L47" s="10" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="10" t="inlineStr">
@@ -2061,11 +2041,7 @@
           <t>Fri 18 Sep 2026</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Development - Our Lives</t>
-        </is>
-      </c>
+      <c r="B48" s="4" t="n"/>
       <c r="C48" s="4" t="n"/>
       <c r="D48" s="10" t="inlineStr">
         <is>
@@ -2087,11 +2063,7 @@
         </is>
       </c>
       <c r="K48" s="4" t="n"/>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="10" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O248"/>
+  <dimension ref="A1:N248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,6 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,40 +553,35 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Hannah Holton</t>
+          <t>Iestyn O'Leary</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Iestyn O'Leary</t>
+          <t>Jason Lye-Phillips</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Jason Lye-Phillips</t>
+          <t>Lara Hughes</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>Lara Hughes</t>
+          <t>Osian Lewis</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>Osian Lewis</t>
+          <t>Owain Jones</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>Owain Jones</t>
+          <t>Rhodri Lewis</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Rhodri Lewis</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wil Williams</t>
         </is>
@@ -605,18 +599,17 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -630,18 +623,17 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -662,7 +654,6 @@
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -683,7 +674,6 @@
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -697,18 +687,17 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -729,7 +718,6 @@
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -750,7 +738,6 @@
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -771,7 +758,6 @@
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -792,7 +778,6 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -813,7 +798,6 @@
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -834,7 +818,6 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -848,18 +831,17 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -880,7 +862,6 @@
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -901,7 +882,6 @@
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
-      <c r="O15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -922,7 +902,6 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -943,7 +922,6 @@
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -964,7 +942,6 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -985,7 +962,6 @@
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1006,7 +982,6 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1027,7 +1002,6 @@
       <c r="L21" s="8" t="n"/>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1048,7 +1022,6 @@
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1071,29 +1044,28 @@
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Mabli</t>
+        </is>
+      </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>Pre-Production - Mabli</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
           <t>Edit - Socials</t>
         </is>
       </c>
-      <c r="M23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
       <c r="N23" s="10" t="inlineStr">
-        <is>
-          <t>Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1124,29 +1096,28 @@
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
         <is>
           <t>TOIL - Hansh Socials</t>
         </is>
       </c>
-      <c r="M24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>Paperwork - PAC</t>
+        </is>
+      </c>
       <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -1177,33 +1148,32 @@
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Pre-Production - Black History 2026</t>
+          <t>Paperwork - PAC</t>
         </is>
       </c>
       <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="O25" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1238,33 +1208,32 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Production - Black History 2026</t>
+        </is>
+      </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>Pre-Production - Black History 2026</t>
+          <t>Paperwork - PAC</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
-        <is>
-          <t>Paperwork - PAC</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -1295,33 +1264,32 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
       </c>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="O27" s="10" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1348,13 +1316,12 @@
       <c r="J28" s="8" t="n"/>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
       <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>External - DARTS 6 G</t>
-        </is>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1377,13 +1344,12 @@
       <c r="J29" s="8" t="n"/>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8" t="n"/>
-      <c r="M29" s="8" t="n"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>External - DARTS 6 G</t>
+        </is>
+      </c>
       <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>External - DARTS 6 G</t>
-        </is>
-      </c>
-      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -1418,29 +1384,28 @@
         </is>
       </c>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
           <t>Film - Hansh Socials</t>
         </is>
       </c>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="O30" s="10" t="inlineStr">
+      <c r="N30" s="10" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -1463,29 +1428,28 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O31" s="10" t="inlineStr">
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -1504,29 +1468,28 @@
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O32" s="10" t="inlineStr">
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -1553,29 +1516,28 @@
         </is>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
-      <c r="K33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>Socials - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>Socials - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N33" s="9" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O33" s="10" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -1598,29 +1560,28 @@
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M34" s="10" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O34" s="10" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -1645,7 +1606,6 @@
       <c r="L35" s="8" t="n"/>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n"/>
-      <c r="O35" s="8" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -1666,7 +1626,6 @@
       <c r="L36" s="8" t="n"/>
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
-      <c r="O36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1681,29 +1640,28 @@
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="M37" s="10" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O37" s="10" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1722,29 +1680,28 @@
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L38" s="10" t="inlineStr">
         <is>
-          <t>Edit - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O38" s="10" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1763,29 +1720,28 @@
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Edit - Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L39" s="10" t="inlineStr">
         <is>
-          <t>Edit - Rookie Teachers</t>
-        </is>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O39" s="10" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1804,29 +1760,28 @@
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
-      <c r="K40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Hansh Socials</t>
+        </is>
+      </c>
       <c r="L40" s="10" t="inlineStr">
         <is>
-          <t>Hansh Socials</t>
-        </is>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O40" s="10" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1845,25 +1800,24 @@
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
+      <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="10" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O41" s="10" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -1888,7 +1842,6 @@
       <c r="L42" s="8" t="n"/>
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
-      <c r="O42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -1909,7 +1862,6 @@
       <c r="L43" s="8" t="n"/>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
-      <c r="O43" s="8" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1923,22 +1875,21 @@
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
       </c>
+      <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
-      <c r="O44" s="6" t="inlineStr">
+      <c r="N44" s="6" t="inlineStr">
         <is>
           <t>TOIL - Darts 6 G</t>
         </is>
@@ -1956,22 +1907,21 @@
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
       </c>
+      <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1985,18 +1935,17 @@
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
+      <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2019,17 +1968,16 @@
       </c>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J47" s="4" t="n"/>
       <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="10" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2056,17 +2004,16 @@
       </c>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
-      <c r="O48" s="10" t="inlineStr">
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2091,7 +2038,6 @@
       <c r="L49" s="8" t="n"/>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
-      <c r="O49" s="8" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -2112,7 +2058,6 @@
       <c r="L50" s="8" t="n"/>
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
-      <c r="O50" s="8" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2135,21 +2080,20 @@
       </c>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="10" t="inlineStr">
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
+      <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="10" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2176,25 +2120,24 @@
       </c>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="10" t="inlineStr">
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O52" s="10" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2221,25 +2164,24 @@
       </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M53" s="4" t="n"/>
-      <c r="N53" s="9" t="inlineStr">
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -2266,25 +2208,24 @@
       </c>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="10" t="inlineStr">
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M54" s="4" t="n"/>
-      <c r="N54" s="9" t="inlineStr">
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O54" s="10" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -2310,30 +2251,29 @@
         </is>
       </c>
       <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="10" t="inlineStr">
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="9" t="inlineStr">
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O55" s="10" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -2358,7 +2298,6 @@
       <c r="L56" s="8" t="n"/>
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
-      <c r="O56" s="8" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -2379,7 +2318,6 @@
       <c r="L57" s="8" t="n"/>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
-      <c r="O57" s="8" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2401,26 +2339,25 @@
         </is>
       </c>
       <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="J58" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="9" t="inlineStr">
+      <c r="M58" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O58" s="10" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2447,21 +2384,20 @@
       </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O59" s="10" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2488,21 +2424,20 @@
       </c>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="9" t="inlineStr">
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N60" s="4" t="n"/>
-      <c r="O60" s="10" t="inlineStr">
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2529,21 +2464,20 @@
       </c>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="9" t="inlineStr">
+      <c r="L61" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N61" s="4" t="n"/>
-      <c r="O61" s="10" t="inlineStr">
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -2594,37 +2528,32 @@
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathlu S4C Athrawon</t>
+        </is>
+      </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
-      <c r="M62" s="9" t="inlineStr">
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>Parti Dathlu S4C Athrawon</t>
+        </is>
+      </c>
       <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
-      <c r="O62" s="10" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
@@ -2650,7 +2579,6 @@
       <c r="L63" s="8" t="n"/>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n"/>
-      <c r="O63" s="8" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -2671,7 +2599,6 @@
       <c r="L64" s="8" t="n"/>
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
-      <c r="O64" s="8" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2689,14 +2616,13 @@
       <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="9" t="inlineStr">
+      <c r="L65" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
-      <c r="O65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2714,14 +2640,13 @@
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="9" t="inlineStr">
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
-      <c r="O66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2736,21 +2661,20 @@
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="9" t="inlineStr">
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
-      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -2765,17 +2689,16 @@
       <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="11" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2790,17 +2713,16 @@
       <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="11" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -2825,7 +2747,6 @@
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n"/>
-      <c r="O70" s="8" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -2850,7 +2771,6 @@
       <c r="L71" s="8" t="n"/>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
-      <c r="O71" s="8" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2873,21 +2793,20 @@
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="11" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2910,21 +2829,20 @@
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="11" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
+      <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2947,25 +2865,24 @@
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
-      <c r="J74" s="11" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L74" s="11" t="inlineStr">
+      <c r="K74" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2988,25 +2905,24 @@
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="11" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L75" s="11" t="inlineStr">
+      <c r="K75" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
-      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3025,25 +2941,24 @@
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
-      <c r="J76" s="11" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L76" s="11" t="inlineStr">
+      <c r="K76" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -3068,7 +2983,6 @@
       <c r="L77" s="8" t="n"/>
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n"/>
-      <c r="O77" s="8" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -3093,7 +3007,6 @@
       <c r="L78" s="8" t="n"/>
       <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n"/>
-      <c r="O78" s="8" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3112,25 +3025,24 @@
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
-      <c r="J79" s="11" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L79" s="11" t="inlineStr">
+      <c r="K79" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3145,25 +3057,24 @@
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L80" s="11" t="inlineStr">
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
-      <c r="O80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -3178,25 +3089,24 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L81" s="11" t="inlineStr">
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -3211,25 +3121,24 @@
       <c r="F82" s="4" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="4" t="n"/>
-      <c r="I82" s="4" t="n"/>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L82" s="11" t="inlineStr">
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
-      <c r="O82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -3244,25 +3153,24 @@
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="4" t="n"/>
-      <c r="I83" s="4" t="n"/>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L83" s="11" t="inlineStr">
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
-      <c r="O83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -3283,7 +3191,6 @@
       <c r="L84" s="8" t="n"/>
       <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
-      <c r="O84" s="8" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -3304,7 +3211,6 @@
       <c r="L85" s="8" t="n"/>
       <c r="M85" s="8" t="n"/>
       <c r="N85" s="8" t="n"/>
-      <c r="O85" s="8" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3319,21 +3225,20 @@
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
       <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="J86" s="11" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K86" s="4" t="n"/>
-      <c r="L86" s="11" t="inlineStr">
+      <c r="J86" s="4" t="n"/>
+      <c r="K86" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="n"/>
-      <c r="O86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -3348,21 +3253,20 @@
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="4" t="n"/>
       <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K87" s="4" t="n"/>
-      <c r="L87" s="11" t="inlineStr">
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
-      <c r="O87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -3377,21 +3281,20 @@
       <c r="F88" s="4" t="n"/>
       <c r="G88" s="4" t="n"/>
       <c r="H88" s="4" t="n"/>
-      <c r="I88" s="4" t="n"/>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="I88" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K88" s="4" t="n"/>
-      <c r="L88" s="11" t="inlineStr">
+      <c r="J88" s="4" t="n"/>
+      <c r="K88" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
-      <c r="O88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -3406,21 +3309,20 @@
       <c r="F89" s="4" t="n"/>
       <c r="G89" s="4" t="n"/>
       <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="11" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K89" s="4" t="n"/>
-      <c r="L89" s="11" t="inlineStr">
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
-      <c r="O89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -3435,21 +3337,20 @@
       <c r="F90" s="4" t="n"/>
       <c r="G90" s="4" t="n"/>
       <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="11" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K90" s="4" t="n"/>
-      <c r="L90" s="11" t="inlineStr">
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
       <c r="N90" s="4" t="n"/>
-      <c r="O90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -3470,7 +3371,6 @@
       <c r="L91" s="8" t="n"/>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
-      <c r="O91" s="8" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -3491,7 +3391,6 @@
       <c r="L92" s="8" t="n"/>
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n"/>
-      <c r="O92" s="8" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3506,21 +3405,20 @@
       <c r="F93" s="4" t="n"/>
       <c r="G93" s="4" t="n"/>
       <c r="H93" s="4" t="n"/>
-      <c r="I93" s="4" t="n"/>
-      <c r="J93" s="11" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K93" s="4" t="n"/>
-      <c r="L93" s="11" t="inlineStr">
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
-      <c r="O93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -3535,21 +3433,20 @@
       <c r="F94" s="4" t="n"/>
       <c r="G94" s="4" t="n"/>
       <c r="H94" s="4" t="n"/>
-      <c r="I94" s="4" t="n"/>
-      <c r="J94" s="11" t="inlineStr">
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K94" s="4" t="n"/>
-      <c r="L94" s="11" t="inlineStr">
+      <c r="J94" s="4" t="n"/>
+      <c r="K94" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
-      <c r="O94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3564,21 +3461,20 @@
       <c r="F95" s="4" t="n"/>
       <c r="G95" s="4" t="n"/>
       <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="9" t="inlineStr">
+      <c r="I95" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K95" s="4" t="n"/>
-      <c r="L95" s="11" t="inlineStr">
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
-      <c r="O95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -3593,21 +3489,20 @@
       <c r="F96" s="4" t="n"/>
       <c r="G96" s="4" t="n"/>
       <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
-      <c r="J96" s="9" t="inlineStr">
+      <c r="I96" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K96" s="4" t="n"/>
-      <c r="L96" s="11" t="inlineStr">
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
-      <c r="O96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3622,25 +3517,24 @@
       <c r="F97" s="4" t="n"/>
       <c r="G97" s="4" t="n"/>
       <c r="H97" s="4" t="n"/>
-      <c r="I97" s="4" t="n"/>
-      <c r="J97" s="10" t="inlineStr">
+      <c r="I97" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="11" t="inlineStr">
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="M97" s="4" t="n"/>
-      <c r="N97" s="9" t="inlineStr">
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="9" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="O97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -3661,7 +3555,6 @@
       <c r="L98" s="8" t="n"/>
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n"/>
-      <c r="O98" s="8" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -3682,7 +3575,6 @@
       <c r="L99" s="8" t="n"/>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
-      <c r="O99" s="8" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -3701,21 +3593,20 @@
       <c r="F100" s="4" t="n"/>
       <c r="G100" s="4" t="n"/>
       <c r="H100" s="4" t="n"/>
-      <c r="I100" s="4" t="n"/>
-      <c r="J100" s="10" t="inlineStr">
+      <c r="I100" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K100" s="4" t="n"/>
-      <c r="L100" s="11" t="inlineStr">
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
-      <c r="O100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3734,21 +3625,20 @@
       <c r="F101" s="4" t="n"/>
       <c r="G101" s="4" t="n"/>
       <c r="H101" s="4" t="n"/>
-      <c r="I101" s="4" t="n"/>
-      <c r="J101" s="11" t="inlineStr">
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K101" s="4" t="n"/>
-      <c r="L101" s="11" t="inlineStr">
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
-      <c r="O101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -3767,21 +3657,20 @@
       <c r="F102" s="4" t="n"/>
       <c r="G102" s="4" t="n"/>
       <c r="H102" s="4" t="n"/>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="11" t="inlineStr">
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
-      <c r="O102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3800,21 +3689,20 @@
       <c r="F103" s="4" t="n"/>
       <c r="G103" s="4" t="n"/>
       <c r="H103" s="4" t="n"/>
-      <c r="I103" s="4" t="n"/>
-      <c r="J103" s="10" t="inlineStr">
+      <c r="I103" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K103" s="4" t="n"/>
-      <c r="L103" s="11" t="inlineStr">
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
-      <c r="O103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -3833,21 +3721,20 @@
       <c r="F104" s="4" t="n"/>
       <c r="G104" s="4" t="n"/>
       <c r="H104" s="4" t="n"/>
-      <c r="I104" s="4" t="n"/>
-      <c r="J104" s="11" t="inlineStr">
+      <c r="I104" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="K104" s="4" t="n"/>
-      <c r="L104" s="11" t="inlineStr">
+      <c r="J104" s="4" t="n"/>
+      <c r="K104" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
-      <c r="O104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -3868,7 +3755,6 @@
       <c r="L105" s="8" t="n"/>
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="8" t="n"/>
-      <c r="O105" s="8" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -3889,7 +3775,6 @@
       <c r="L106" s="8" t="n"/>
       <c r="M106" s="8" t="n"/>
       <c r="N106" s="8" t="n"/>
-      <c r="O106" s="8" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3906,15 +3791,14 @@
       <c r="H107" s="4" t="n"/>
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
-      <c r="L107" s="11" t="inlineStr">
+      <c r="K107" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
-      <c r="O107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -3931,15 +3815,14 @@
       <c r="H108" s="4" t="n"/>
       <c r="I108" s="4" t="n"/>
       <c r="J108" s="4" t="n"/>
-      <c r="K108" s="4" t="n"/>
-      <c r="L108" s="11" t="inlineStr">
+      <c r="K108" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
-      <c r="O108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3954,22 +3837,21 @@
       <c r="F109" s="4" t="n"/>
       <c r="G109" s="4" t="n"/>
       <c r="H109" s="4" t="n"/>
-      <c r="I109" s="4" t="n"/>
-      <c r="J109" s="11" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K109" s="4" t="n"/>
-      <c r="L109" s="11" t="inlineStr">
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
-      <c r="O109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -3984,22 +3866,21 @@
       <c r="F110" s="4" t="n"/>
       <c r="G110" s="4" t="n"/>
       <c r="H110" s="4" t="n"/>
-      <c r="I110" s="4" t="n"/>
-      <c r="J110" s="11" t="inlineStr">
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K110" s="4" t="n"/>
-      <c r="L110" s="11" t="inlineStr">
+      <c r="J110" s="4" t="n"/>
+      <c r="K110" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
-      <c r="O110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4017,27 +3898,26 @@
         </is>
       </c>
       <c r="G111" s="4" t="n"/>
-      <c r="H111" s="4" t="n"/>
-      <c r="I111" s="5" t="inlineStr">
+      <c r="H111" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J111" s="11" t="inlineStr">
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K111" s="4" t="n"/>
-      <c r="L111" s="11" t="inlineStr">
+      <c r="J111" s="4" t="n"/>
+      <c r="K111" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
-      <c r="O111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -4058,7 +3938,6 @@
       <c r="L112" s="8" t="n"/>
       <c r="M112" s="8" t="n"/>
       <c r="N112" s="8" t="n"/>
-      <c r="O112" s="8" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -4079,7 +3958,6 @@
       <c r="L113" s="8" t="n"/>
       <c r="M113" s="8" t="n"/>
       <c r="N113" s="8" t="n"/>
-      <c r="O113" s="8" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -4094,22 +3972,21 @@
       <c r="F114" s="4" t="n"/>
       <c r="G114" s="4" t="n"/>
       <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="n"/>
-      <c r="J114" s="11" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Mabli a Ceff Ceff
 Dub - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="K114" s="4" t="n"/>
-      <c r="L114" s="11" t="inlineStr">
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
-      <c r="O114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -4124,18 +4001,17 @@
       <c r="F115" s="4" t="n"/>
       <c r="G115" s="4" t="n"/>
       <c r="H115" s="4" t="n"/>
-      <c r="I115" s="4" t="n"/>
-      <c r="J115" s="10" t="inlineStr">
+      <c r="I115" s="10" t="inlineStr">
         <is>
           <t>Dub - Mabli a Ceff Ceff
 Online Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
+      <c r="J115" s="4" t="n"/>
       <c r="K115" s="4" t="n"/>
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
-      <c r="O115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -4150,17 +4026,16 @@
       <c r="F116" s="4" t="n"/>
       <c r="G116" s="4" t="n"/>
       <c r="H116" s="4" t="n"/>
-      <c r="I116" s="4" t="n"/>
-      <c r="J116" s="10" t="inlineStr">
+      <c r="I116" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J116" s="4" t="n"/>
       <c r="K116" s="4" t="n"/>
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
-      <c r="O116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -4175,17 +4050,16 @@
       <c r="F117" s="4" t="n"/>
       <c r="G117" s="4" t="n"/>
       <c r="H117" s="4" t="n"/>
-      <c r="I117" s="4" t="n"/>
-      <c r="J117" s="10" t="inlineStr">
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J117" s="4" t="n"/>
       <c r="K117" s="4" t="n"/>
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
-      <c r="O117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -4203,22 +4077,21 @@
         </is>
       </c>
       <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J118" s="10" t="inlineStr">
+      <c r="I118" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J118" s="4" t="n"/>
       <c r="K118" s="4" t="n"/>
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
-      <c r="O118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -4239,7 +4112,6 @@
       <c r="L119" s="8" t="n"/>
       <c r="M119" s="8" t="n"/>
       <c r="N119" s="8" t="n"/>
-      <c r="O119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -4260,7 +4132,6 @@
       <c r="L120" s="8" t="n"/>
       <c r="M120" s="8" t="n"/>
       <c r="N120" s="8" t="n"/>
-      <c r="O120" s="8" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -4275,17 +4146,16 @@
       <c r="F121" s="4" t="n"/>
       <c r="G121" s="4" t="n"/>
       <c r="H121" s="4" t="n"/>
-      <c r="I121" s="4" t="n"/>
-      <c r="J121" s="10" t="inlineStr">
+      <c r="I121" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J121" s="4" t="n"/>
       <c r="K121" s="4" t="n"/>
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
-      <c r="O121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -4300,17 +4170,16 @@
       <c r="F122" s="4" t="n"/>
       <c r="G122" s="4" t="n"/>
       <c r="H122" s="4" t="n"/>
-      <c r="I122" s="4" t="n"/>
-      <c r="J122" s="10" t="inlineStr">
+      <c r="I122" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J122" s="4" t="n"/>
       <c r="K122" s="4" t="n"/>
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
-      <c r="O122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -4325,17 +4194,16 @@
       <c r="F123" s="4" t="n"/>
       <c r="G123" s="4" t="n"/>
       <c r="H123" s="4" t="n"/>
-      <c r="I123" s="4" t="n"/>
-      <c r="J123" s="11" t="inlineStr">
+      <c r="I123" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
+      <c r="J123" s="4" t="n"/>
       <c r="K123" s="4" t="n"/>
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
-      <c r="O123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -4350,17 +4218,16 @@
       <c r="F124" s="4" t="n"/>
       <c r="G124" s="4" t="n"/>
       <c r="H124" s="4" t="n"/>
-      <c r="I124" s="4" t="n"/>
-      <c r="J124" s="11" t="inlineStr">
+      <c r="I124" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
+      <c r="J124" s="4" t="n"/>
       <c r="K124" s="4" t="n"/>
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
-      <c r="O124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -4375,17 +4242,16 @@
       <c r="F125" s="4" t="n"/>
       <c r="G125" s="4" t="n"/>
       <c r="H125" s="4" t="n"/>
-      <c r="I125" s="4" t="n"/>
-      <c r="J125" s="11" t="inlineStr">
+      <c r="I125" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
+      <c r="J125" s="4" t="n"/>
       <c r="K125" s="4" t="n"/>
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
-      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -4406,7 +4272,6 @@
       <c r="L126" s="8" t="n"/>
       <c r="M126" s="8" t="n"/>
       <c r="N126" s="8" t="n"/>
-      <c r="O126" s="8" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -4427,7 +4292,6 @@
       <c r="L127" s="8" t="n"/>
       <c r="M127" s="8" t="n"/>
       <c r="N127" s="8" t="n"/>
-      <c r="O127" s="8" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -4442,17 +4306,16 @@
       <c r="F128" s="4" t="n"/>
       <c r="G128" s="4" t="n"/>
       <c r="H128" s="4" t="n"/>
-      <c r="I128" s="4" t="n"/>
-      <c r="J128" s="11" t="inlineStr">
+      <c r="I128" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
+      <c r="J128" s="4" t="n"/>
       <c r="K128" s="4" t="n"/>
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
-      <c r="O128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -4467,17 +4330,16 @@
       <c r="F129" s="4" t="n"/>
       <c r="G129" s="4" t="n"/>
       <c r="H129" s="4" t="n"/>
-      <c r="I129" s="4" t="n"/>
-      <c r="J129" s="11" t="inlineStr">
+      <c r="I129" s="11" t="inlineStr">
         <is>
           <t>Online Edit - External</t>
         </is>
       </c>
+      <c r="J129" s="4" t="n"/>
       <c r="K129" s="4" t="n"/>
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
-      <c r="O129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -4492,17 +4354,16 @@
       <c r="F130" s="4" t="n"/>
       <c r="G130" s="4" t="n"/>
       <c r="H130" s="4" t="n"/>
-      <c r="I130" s="4" t="n"/>
-      <c r="J130" s="10" t="inlineStr">
+      <c r="I130" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J130" s="4" t="n"/>
       <c r="K130" s="4" t="n"/>
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
-      <c r="O130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -4517,17 +4378,16 @@
       <c r="F131" s="4" t="n"/>
       <c r="G131" s="4" t="n"/>
       <c r="H131" s="4" t="n"/>
-      <c r="I131" s="4" t="n"/>
-      <c r="J131" s="10" t="inlineStr">
+      <c r="I131" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J131" s="4" t="n"/>
       <c r="K131" s="4" t="n"/>
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
-      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -4542,17 +4402,16 @@
       <c r="F132" s="4" t="n"/>
       <c r="G132" s="4" t="n"/>
       <c r="H132" s="4" t="n"/>
-      <c r="I132" s="4" t="n"/>
-      <c r="J132" s="10" t="inlineStr">
+      <c r="I132" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J132" s="4" t="n"/>
       <c r="K132" s="4" t="n"/>
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
-      <c r="O132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
@@ -4573,7 +4432,6 @@
       <c r="L133" s="8" t="n"/>
       <c r="M133" s="8" t="n"/>
       <c r="N133" s="8" t="n"/>
-      <c r="O133" s="8" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -4594,7 +4452,6 @@
       <c r="L134" s="8" t="n"/>
       <c r="M134" s="8" t="n"/>
       <c r="N134" s="8" t="n"/>
-      <c r="O134" s="8" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -4609,17 +4466,16 @@
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
       <c r="H135" s="4" t="n"/>
-      <c r="I135" s="4" t="n"/>
-      <c r="J135" s="10" t="inlineStr">
+      <c r="I135" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J135" s="4" t="n"/>
       <c r="K135" s="4" t="n"/>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
-      <c r="O135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -4637,22 +4493,21 @@
         </is>
       </c>
       <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J136" s="10" t="inlineStr">
+      <c r="I136" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J136" s="4" t="n"/>
       <c r="K136" s="4" t="n"/>
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
-      <c r="O136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -4670,22 +4525,21 @@
         </is>
       </c>
       <c r="G137" s="4" t="n"/>
-      <c r="H137" s="4" t="n"/>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J137" s="10" t="inlineStr">
+      <c r="I137" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J137" s="4" t="n"/>
       <c r="K137" s="4" t="n"/>
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
-      <c r="O137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -4703,22 +4557,21 @@
         </is>
       </c>
       <c r="G138" s="4" t="n"/>
-      <c r="H138" s="4" t="n"/>
-      <c r="I138" s="5" t="inlineStr">
+      <c r="H138" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J138" s="10" t="inlineStr">
+      <c r="I138" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J138" s="4" t="n"/>
       <c r="K138" s="4" t="n"/>
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
       <c r="N138" s="4" t="n"/>
-      <c r="O138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -4736,22 +4589,21 @@
         </is>
       </c>
       <c r="G139" s="4" t="n"/>
-      <c r="H139" s="4" t="n"/>
-      <c r="I139" s="5" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="J139" s="10" t="inlineStr">
+      <c r="I139" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J139" s="4" t="n"/>
       <c r="K139" s="4" t="n"/>
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="n"/>
-      <c r="O139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="inlineStr">
@@ -4772,7 +4624,6 @@
       <c r="L140" s="8" t="n"/>
       <c r="M140" s="8" t="n"/>
       <c r="N140" s="8" t="n"/>
-      <c r="O140" s="8" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
@@ -4793,7 +4644,6 @@
       <c r="L141" s="8" t="n"/>
       <c r="M141" s="8" t="n"/>
       <c r="N141" s="8" t="n"/>
-      <c r="O141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -4808,17 +4658,16 @@
       <c r="F142" s="4" t="n"/>
       <c r="G142" s="4" t="n"/>
       <c r="H142" s="4" t="n"/>
-      <c r="I142" s="4" t="n"/>
-      <c r="J142" s="10" t="inlineStr">
+      <c r="I142" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J142" s="4" t="n"/>
       <c r="K142" s="4" t="n"/>
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="n"/>
-      <c r="O142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -4833,17 +4682,16 @@
       <c r="F143" s="4" t="n"/>
       <c r="G143" s="4" t="n"/>
       <c r="H143" s="4" t="n"/>
-      <c r="I143" s="4" t="n"/>
-      <c r="J143" s="10" t="inlineStr">
+      <c r="I143" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J143" s="4" t="n"/>
       <c r="K143" s="4" t="n"/>
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
-      <c r="O143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -4864,7 +4712,6 @@
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
-      <c r="O144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -4885,7 +4732,6 @@
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
-      <c r="O145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -4906,7 +4752,6 @@
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
-      <c r="O146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="inlineStr">
@@ -4927,7 +4772,6 @@
       <c r="L147" s="8" t="n"/>
       <c r="M147" s="8" t="n"/>
       <c r="N147" s="8" t="n"/>
-      <c r="O147" s="8" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="inlineStr">
@@ -4948,7 +4792,6 @@
       <c r="L148" s="8" t="n"/>
       <c r="M148" s="8" t="n"/>
       <c r="N148" s="8" t="n"/>
-      <c r="O148" s="8" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -4963,17 +4806,16 @@
       <c r="F149" s="4" t="n"/>
       <c r="G149" s="4" t="n"/>
       <c r="H149" s="4" t="n"/>
-      <c r="I149" s="4" t="n"/>
-      <c r="J149" s="10" t="inlineStr">
+      <c r="I149" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J149" s="4" t="n"/>
       <c r="K149" s="4" t="n"/>
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
-      <c r="O149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -4988,17 +4830,16 @@
       <c r="F150" s="4" t="n"/>
       <c r="G150" s="4" t="n"/>
       <c r="H150" s="4" t="n"/>
-      <c r="I150" s="4" t="n"/>
-      <c r="J150" s="10" t="inlineStr">
+      <c r="I150" s="10" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
       </c>
+      <c r="J150" s="4" t="n"/>
       <c r="K150" s="4" t="n"/>
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
-      <c r="O150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -5019,7 +4860,6 @@
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
-      <c r="O151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -5040,7 +4880,6 @@
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
-      <c r="O152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -5061,7 +4900,6 @@
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
-      <c r="O153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="inlineStr">
@@ -5082,7 +4920,6 @@
       <c r="L154" s="8" t="n"/>
       <c r="M154" s="8" t="n"/>
       <c r="N154" s="8" t="n"/>
-      <c r="O154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="inlineStr">
@@ -5103,7 +4940,6 @@
       <c r="L155" s="8" t="n"/>
       <c r="M155" s="8" t="n"/>
       <c r="N155" s="8" t="n"/>
-      <c r="O155" s="8" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -5118,17 +4954,16 @@
       <c r="F156" s="4" t="n"/>
       <c r="G156" s="4" t="n"/>
       <c r="H156" s="4" t="n"/>
-      <c r="I156" s="4" t="n"/>
-      <c r="J156" s="11" t="inlineStr">
+      <c r="I156" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
-      <c r="O156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -5143,17 +4978,16 @@
       <c r="F157" s="4" t="n"/>
       <c r="G157" s="4" t="n"/>
       <c r="H157" s="4" t="n"/>
-      <c r="I157" s="4" t="n"/>
-      <c r="J157" s="11" t="inlineStr">
+      <c r="I157" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
-      <c r="O157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -5167,22 +5001,21 @@
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
       <c r="G158" s="4" t="n"/>
-      <c r="H158" s="4" t="n"/>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="H158" s="5" t="inlineStr">
         <is>
           <t>Delivery - LGBTQ+</t>
         </is>
       </c>
-      <c r="J158" s="11" t="inlineStr">
+      <c r="I158" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
-      <c r="O158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -5197,17 +5030,16 @@
       <c r="F159" s="4" t="n"/>
       <c r="G159" s="4" t="n"/>
       <c r="H159" s="4" t="n"/>
-      <c r="I159" s="4" t="n"/>
-      <c r="J159" s="11" t="inlineStr">
+      <c r="I159" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
-      <c r="O159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -5222,17 +5054,16 @@
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
-      <c r="I160" s="4" t="n"/>
-      <c r="J160" s="11" t="inlineStr">
+      <c r="I160" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
-      <c r="O160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="inlineStr">
@@ -5253,7 +5084,6 @@
       <c r="L161" s="8" t="n"/>
       <c r="M161" s="8" t="n"/>
       <c r="N161" s="8" t="n"/>
-      <c r="O161" s="8" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="inlineStr">
@@ -5274,7 +5104,6 @@
       <c r="L162" s="8" t="n"/>
       <c r="M162" s="8" t="n"/>
       <c r="N162" s="8" t="n"/>
-      <c r="O162" s="8" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -5289,17 +5118,16 @@
       <c r="F163" s="4" t="n"/>
       <c r="G163" s="4" t="n"/>
       <c r="H163" s="4" t="n"/>
-      <c r="I163" s="4" t="n"/>
-      <c r="J163" s="11" t="inlineStr">
+      <c r="I163" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J163" s="4" t="n"/>
       <c r="K163" s="4" t="n"/>
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
-      <c r="O163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -5314,17 +5142,16 @@
       <c r="F164" s="4" t="n"/>
       <c r="G164" s="4" t="n"/>
       <c r="H164" s="4" t="n"/>
-      <c r="I164" s="4" t="n"/>
-      <c r="J164" s="11" t="inlineStr">
+      <c r="I164" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J164" s="4" t="n"/>
       <c r="K164" s="4" t="n"/>
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
-      <c r="O164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -5339,17 +5166,16 @@
       <c r="F165" s="4" t="n"/>
       <c r="G165" s="4" t="n"/>
       <c r="H165" s="4" t="n"/>
-      <c r="I165" s="4" t="n"/>
-      <c r="J165" s="11" t="inlineStr">
+      <c r="I165" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
-      <c r="O165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -5364,17 +5190,16 @@
       <c r="F166" s="4" t="n"/>
       <c r="G166" s="4" t="n"/>
       <c r="H166" s="4" t="n"/>
-      <c r="I166" s="4" t="n"/>
-      <c r="J166" s="11" t="inlineStr">
+      <c r="I166" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
-      <c r="O166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -5389,17 +5214,16 @@
       <c r="F167" s="4" t="n"/>
       <c r="G167" s="4" t="n"/>
       <c r="H167" s="4" t="n"/>
-      <c r="I167" s="4" t="n"/>
-      <c r="J167" s="11" t="inlineStr">
+      <c r="I167" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="n"/>
-      <c r="O167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="inlineStr">
@@ -5420,7 +5244,6 @@
       <c r="L168" s="8" t="n"/>
       <c r="M168" s="8" t="n"/>
       <c r="N168" s="8" t="n"/>
-      <c r="O168" s="8" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="inlineStr">
@@ -5441,7 +5264,6 @@
       <c r="L169" s="8" t="n"/>
       <c r="M169" s="8" t="n"/>
       <c r="N169" s="8" t="n"/>
-      <c r="O169" s="8" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -5456,17 +5278,16 @@
       <c r="F170" s="4" t="n"/>
       <c r="G170" s="4" t="n"/>
       <c r="H170" s="4" t="n"/>
-      <c r="I170" s="4" t="n"/>
-      <c r="J170" s="11" t="inlineStr">
+      <c r="I170" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
       <c r="N170" s="4" t="n"/>
-      <c r="O170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -5481,17 +5302,16 @@
       <c r="F171" s="4" t="n"/>
       <c r="G171" s="4" t="n"/>
       <c r="H171" s="4" t="n"/>
-      <c r="I171" s="4" t="n"/>
-      <c r="J171" s="11" t="inlineStr">
+      <c r="I171" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
-      <c r="O171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -5506,17 +5326,16 @@
       <c r="F172" s="4" t="n"/>
       <c r="G172" s="4" t="n"/>
       <c r="H172" s="4" t="n"/>
-      <c r="I172" s="4" t="n"/>
-      <c r="J172" s="11" t="inlineStr">
+      <c r="I172" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
-      <c r="O172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -5531,17 +5350,16 @@
       <c r="F173" s="4" t="n"/>
       <c r="G173" s="4" t="n"/>
       <c r="H173" s="4" t="n"/>
-      <c r="I173" s="4" t="n"/>
-      <c r="J173" s="11" t="inlineStr">
+      <c r="I173" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J173" s="4" t="n"/>
       <c r="K173" s="4" t="n"/>
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
-      <c r="O173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -5556,17 +5374,16 @@
       <c r="F174" s="4" t="n"/>
       <c r="G174" s="4" t="n"/>
       <c r="H174" s="4" t="n"/>
-      <c r="I174" s="4" t="n"/>
-      <c r="J174" s="11" t="inlineStr">
+      <c r="I174" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J174" s="4" t="n"/>
       <c r="K174" s="4" t="n"/>
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
-      <c r="O174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
@@ -5587,7 +5404,6 @@
       <c r="L175" s="8" t="n"/>
       <c r="M175" s="8" t="n"/>
       <c r="N175" s="8" t="n"/>
-      <c r="O175" s="8" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="inlineStr">
@@ -5608,7 +5424,6 @@
       <c r="L176" s="8" t="n"/>
       <c r="M176" s="8" t="n"/>
       <c r="N176" s="8" t="n"/>
-      <c r="O176" s="8" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -5623,17 +5438,16 @@
       <c r="F177" s="4" t="n"/>
       <c r="G177" s="4" t="n"/>
       <c r="H177" s="4" t="n"/>
-      <c r="I177" s="4" t="n"/>
-      <c r="J177" s="11" t="inlineStr">
+      <c r="I177" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J177" s="4" t="n"/>
       <c r="K177" s="4" t="n"/>
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
-      <c r="O177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -5648,17 +5462,16 @@
       <c r="F178" s="4" t="n"/>
       <c r="G178" s="4" t="n"/>
       <c r="H178" s="4" t="n"/>
-      <c r="I178" s="4" t="n"/>
-      <c r="J178" s="11" t="inlineStr">
+      <c r="I178" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
-      <c r="O178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -5673,17 +5486,16 @@
       <c r="F179" s="4" t="n"/>
       <c r="G179" s="4" t="n"/>
       <c r="H179" s="4" t="n"/>
-      <c r="I179" s="4" t="n"/>
-      <c r="J179" s="11" t="inlineStr">
+      <c r="I179" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
-      <c r="O179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -5698,17 +5510,16 @@
       <c r="F180" s="4" t="n"/>
       <c r="G180" s="4" t="n"/>
       <c r="H180" s="4" t="n"/>
-      <c r="I180" s="4" t="n"/>
-      <c r="J180" s="11" t="inlineStr">
+      <c r="I180" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
-      <c r="O180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -5723,17 +5534,16 @@
       <c r="F181" s="4" t="n"/>
       <c r="G181" s="4" t="n"/>
       <c r="H181" s="4" t="n"/>
-      <c r="I181" s="4" t="n"/>
-      <c r="J181" s="11" t="inlineStr">
+      <c r="I181" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
-      <c r="O181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="inlineStr">
@@ -5754,7 +5564,6 @@
       <c r="L182" s="8" t="n"/>
       <c r="M182" s="8" t="n"/>
       <c r="N182" s="8" t="n"/>
-      <c r="O182" s="8" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
@@ -5775,7 +5584,6 @@
       <c r="L183" s="8" t="n"/>
       <c r="M183" s="8" t="n"/>
       <c r="N183" s="8" t="n"/>
-      <c r="O183" s="8" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -5790,17 +5598,16 @@
       <c r="F184" s="4" t="n"/>
       <c r="G184" s="4" t="n"/>
       <c r="H184" s="4" t="n"/>
-      <c r="I184" s="4" t="n"/>
-      <c r="J184" s="11" t="inlineStr">
+      <c r="I184" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
-      <c r="O184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -5815,17 +5622,16 @@
       <c r="F185" s="4" t="n"/>
       <c r="G185" s="4" t="n"/>
       <c r="H185" s="4" t="n"/>
-      <c r="I185" s="4" t="n"/>
-      <c r="J185" s="11" t="inlineStr">
+      <c r="I185" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
-      <c r="O185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -5840,17 +5646,16 @@
       <c r="F186" s="4" t="n"/>
       <c r="G186" s="4" t="n"/>
       <c r="H186" s="4" t="n"/>
-      <c r="I186" s="4" t="n"/>
-      <c r="J186" s="11" t="inlineStr">
+      <c r="I186" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J186" s="4" t="n"/>
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
-      <c r="O186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -5865,17 +5670,16 @@
       <c r="F187" s="4" t="n"/>
       <c r="G187" s="4" t="n"/>
       <c r="H187" s="4" t="n"/>
-      <c r="I187" s="4" t="n"/>
-      <c r="J187" s="11" t="inlineStr">
+      <c r="I187" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J187" s="4" t="n"/>
       <c r="K187" s="4" t="n"/>
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
-      <c r="O187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -5890,17 +5694,16 @@
       <c r="F188" s="4" t="n"/>
       <c r="G188" s="4" t="n"/>
       <c r="H188" s="4" t="n"/>
-      <c r="I188" s="4" t="n"/>
-      <c r="J188" s="11" t="inlineStr">
+      <c r="I188" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J188" s="4" t="n"/>
       <c r="K188" s="4" t="n"/>
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
-      <c r="O188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
@@ -5921,7 +5724,6 @@
       <c r="L189" s="8" t="n"/>
       <c r="M189" s="8" t="n"/>
       <c r="N189" s="8" t="n"/>
-      <c r="O189" s="8" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="inlineStr">
@@ -5942,7 +5744,6 @@
       <c r="L190" s="8" t="n"/>
       <c r="M190" s="8" t="n"/>
       <c r="N190" s="8" t="n"/>
-      <c r="O190" s="8" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -5957,17 +5758,16 @@
       <c r="F191" s="4" t="n"/>
       <c r="G191" s="4" t="n"/>
       <c r="H191" s="4" t="n"/>
-      <c r="I191" s="4" t="n"/>
-      <c r="J191" s="11" t="inlineStr">
+      <c r="I191" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J191" s="4" t="n"/>
       <c r="K191" s="4" t="n"/>
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
-      <c r="O191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -5982,17 +5782,16 @@
       <c r="F192" s="4" t="n"/>
       <c r="G192" s="4" t="n"/>
       <c r="H192" s="4" t="n"/>
-      <c r="I192" s="4" t="n"/>
-      <c r="J192" s="11" t="inlineStr">
+      <c r="I192" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J192" s="4" t="n"/>
       <c r="K192" s="4" t="n"/>
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
-      <c r="O192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -6007,17 +5806,16 @@
       <c r="F193" s="4" t="n"/>
       <c r="G193" s="4" t="n"/>
       <c r="H193" s="4" t="n"/>
-      <c r="I193" s="4" t="n"/>
-      <c r="J193" s="11" t="inlineStr">
+      <c r="I193" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J193" s="4" t="n"/>
       <c r="K193" s="4" t="n"/>
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
-      <c r="O193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -6032,17 +5830,16 @@
       <c r="F194" s="4" t="n"/>
       <c r="G194" s="4" t="n"/>
       <c r="H194" s="4" t="n"/>
-      <c r="I194" s="4" t="n"/>
-      <c r="J194" s="11" t="inlineStr">
+      <c r="I194" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J194" s="4" t="n"/>
       <c r="K194" s="4" t="n"/>
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
-      <c r="O194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -6057,17 +5854,16 @@
       <c r="F195" s="4" t="n"/>
       <c r="G195" s="4" t="n"/>
       <c r="H195" s="4" t="n"/>
-      <c r="I195" s="4" t="n"/>
-      <c r="J195" s="11" t="inlineStr">
+      <c r="I195" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
-      <c r="O195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="inlineStr">
@@ -6088,7 +5884,6 @@
       <c r="L196" s="8" t="n"/>
       <c r="M196" s="8" t="n"/>
       <c r="N196" s="8" t="n"/>
-      <c r="O196" s="8" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
@@ -6109,7 +5904,6 @@
       <c r="L197" s="8" t="n"/>
       <c r="M197" s="8" t="n"/>
       <c r="N197" s="8" t="n"/>
-      <c r="O197" s="8" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -6124,17 +5918,16 @@
       <c r="F198" s="4" t="n"/>
       <c r="G198" s="4" t="n"/>
       <c r="H198" s="4" t="n"/>
-      <c r="I198" s="4" t="n"/>
-      <c r="J198" s="11" t="inlineStr">
+      <c r="I198" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
-      <c r="O198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -6149,17 +5942,16 @@
       <c r="F199" s="4" t="n"/>
       <c r="G199" s="4" t="n"/>
       <c r="H199" s="4" t="n"/>
-      <c r="I199" s="4" t="n"/>
-      <c r="J199" s="11" t="inlineStr">
+      <c r="I199" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J199" s="4" t="n"/>
       <c r="K199" s="4" t="n"/>
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
-      <c r="O199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -6174,17 +5966,16 @@
       <c r="F200" s="4" t="n"/>
       <c r="G200" s="4" t="n"/>
       <c r="H200" s="4" t="n"/>
-      <c r="I200" s="4" t="n"/>
-      <c r="J200" s="11" t="inlineStr">
+      <c r="I200" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J200" s="4" t="n"/>
       <c r="K200" s="4" t="n"/>
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
-      <c r="O200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -6199,17 +5990,16 @@
       <c r="F201" s="4" t="n"/>
       <c r="G201" s="4" t="n"/>
       <c r="H201" s="4" t="n"/>
-      <c r="I201" s="4" t="n"/>
-      <c r="J201" s="11" t="inlineStr">
+      <c r="I201" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J201" s="4" t="n"/>
       <c r="K201" s="4" t="n"/>
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
-      <c r="O201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -6224,17 +6014,16 @@
       <c r="F202" s="4" t="n"/>
       <c r="G202" s="4" t="n"/>
       <c r="H202" s="4" t="n"/>
-      <c r="I202" s="4" t="n"/>
-      <c r="J202" s="11" t="inlineStr">
+      <c r="I202" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J202" s="4" t="n"/>
       <c r="K202" s="4" t="n"/>
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
-      <c r="O202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
@@ -6255,7 +6044,6 @@
       <c r="L203" s="8" t="n"/>
       <c r="M203" s="8" t="n"/>
       <c r="N203" s="8" t="n"/>
-      <c r="O203" s="8" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="inlineStr">
@@ -6276,7 +6064,6 @@
       <c r="L204" s="8" t="n"/>
       <c r="M204" s="8" t="n"/>
       <c r="N204" s="8" t="n"/>
-      <c r="O204" s="8" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -6291,17 +6078,16 @@
       <c r="F205" s="4" t="n"/>
       <c r="G205" s="4" t="n"/>
       <c r="H205" s="4" t="n"/>
-      <c r="I205" s="4" t="n"/>
-      <c r="J205" s="11" t="inlineStr">
+      <c r="I205" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J205" s="4" t="n"/>
       <c r="K205" s="4" t="n"/>
       <c r="L205" s="4" t="n"/>
       <c r="M205" s="4" t="n"/>
       <c r="N205" s="4" t="n"/>
-      <c r="O205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -6316,17 +6102,16 @@
       <c r="F206" s="4" t="n"/>
       <c r="G206" s="4" t="n"/>
       <c r="H206" s="4" t="n"/>
-      <c r="I206" s="4" t="n"/>
-      <c r="J206" s="11" t="inlineStr">
+      <c r="I206" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J206" s="4" t="n"/>
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
       <c r="N206" s="4" t="n"/>
-      <c r="O206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -6341,17 +6126,16 @@
       <c r="F207" s="4" t="n"/>
       <c r="G207" s="4" t="n"/>
       <c r="H207" s="4" t="n"/>
-      <c r="I207" s="4" t="n"/>
-      <c r="J207" s="11" t="inlineStr">
+      <c r="I207" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J207" s="4" t="n"/>
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
       <c r="N207" s="4" t="n"/>
-      <c r="O207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -6366,17 +6150,16 @@
       <c r="F208" s="4" t="n"/>
       <c r="G208" s="4" t="n"/>
       <c r="H208" s="4" t="n"/>
-      <c r="I208" s="4" t="n"/>
-      <c r="J208" s="11" t="inlineStr">
+      <c r="I208" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J208" s="4" t="n"/>
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
       <c r="N208" s="4" t="n"/>
-      <c r="O208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -6391,17 +6174,16 @@
       <c r="F209" s="4" t="n"/>
       <c r="G209" s="4" t="n"/>
       <c r="H209" s="4" t="n"/>
-      <c r="I209" s="4" t="n"/>
-      <c r="J209" s="11" t="inlineStr">
+      <c r="I209" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J209" s="4" t="n"/>
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="n"/>
-      <c r="O209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="inlineStr">
@@ -6422,7 +6204,6 @@
       <c r="L210" s="8" t="n"/>
       <c r="M210" s="8" t="n"/>
       <c r="N210" s="8" t="n"/>
-      <c r="O210" s="8" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
@@ -6443,7 +6224,6 @@
       <c r="L211" s="8" t="n"/>
       <c r="M211" s="8" t="n"/>
       <c r="N211" s="8" t="n"/>
-      <c r="O211" s="8" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -6458,17 +6238,16 @@
       <c r="F212" s="4" t="n"/>
       <c r="G212" s="4" t="n"/>
       <c r="H212" s="4" t="n"/>
-      <c r="I212" s="4" t="n"/>
-      <c r="J212" s="11" t="inlineStr">
+      <c r="I212" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J212" s="4" t="n"/>
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="n"/>
-      <c r="O212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -6483,17 +6262,16 @@
       <c r="F213" s="4" t="n"/>
       <c r="G213" s="4" t="n"/>
       <c r="H213" s="4" t="n"/>
-      <c r="I213" s="4" t="n"/>
-      <c r="J213" s="11" t="inlineStr">
+      <c r="I213" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J213" s="4" t="n"/>
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="n"/>
-      <c r="O213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -6508,17 +6286,16 @@
       <c r="F214" s="4" t="n"/>
       <c r="G214" s="4" t="n"/>
       <c r="H214" s="4" t="n"/>
-      <c r="I214" s="4" t="n"/>
-      <c r="J214" s="11" t="inlineStr">
+      <c r="I214" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J214" s="4" t="n"/>
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="n"/>
-      <c r="O214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -6533,17 +6310,16 @@
       <c r="F215" s="4" t="n"/>
       <c r="G215" s="4" t="n"/>
       <c r="H215" s="4" t="n"/>
-      <c r="I215" s="4" t="n"/>
-      <c r="J215" s="11" t="inlineStr">
+      <c r="I215" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J215" s="4" t="n"/>
       <c r="K215" s="4" t="n"/>
       <c r="L215" s="4" t="n"/>
       <c r="M215" s="4" t="n"/>
       <c r="N215" s="4" t="n"/>
-      <c r="O215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -6558,17 +6334,16 @@
       <c r="F216" s="4" t="n"/>
       <c r="G216" s="4" t="n"/>
       <c r="H216" s="4" t="n"/>
-      <c r="I216" s="4" t="n"/>
-      <c r="J216" s="11" t="inlineStr">
+      <c r="I216" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J216" s="4" t="n"/>
       <c r="K216" s="4" t="n"/>
       <c r="L216" s="4" t="n"/>
       <c r="M216" s="4" t="n"/>
       <c r="N216" s="4" t="n"/>
-      <c r="O216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
@@ -6589,7 +6364,6 @@
       <c r="L217" s="8" t="n"/>
       <c r="M217" s="8" t="n"/>
       <c r="N217" s="8" t="n"/>
-      <c r="O217" s="8" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="inlineStr">
@@ -6610,7 +6384,6 @@
       <c r="L218" s="8" t="n"/>
       <c r="M218" s="8" t="n"/>
       <c r="N218" s="8" t="n"/>
-      <c r="O218" s="8" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -6625,17 +6398,16 @@
       <c r="F219" s="4" t="n"/>
       <c r="G219" s="4" t="n"/>
       <c r="H219" s="4" t="n"/>
-      <c r="I219" s="4" t="n"/>
-      <c r="J219" s="11" t="inlineStr">
+      <c r="I219" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J219" s="4" t="n"/>
       <c r="K219" s="4" t="n"/>
       <c r="L219" s="4" t="n"/>
       <c r="M219" s="4" t="n"/>
       <c r="N219" s="4" t="n"/>
-      <c r="O219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -6650,17 +6422,16 @@
       <c r="F220" s="4" t="n"/>
       <c r="G220" s="4" t="n"/>
       <c r="H220" s="4" t="n"/>
-      <c r="I220" s="4" t="n"/>
-      <c r="J220" s="11" t="inlineStr">
+      <c r="I220" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J220" s="4" t="n"/>
       <c r="K220" s="4" t="n"/>
       <c r="L220" s="4" t="n"/>
       <c r="M220" s="4" t="n"/>
       <c r="N220" s="4" t="n"/>
-      <c r="O220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -6675,17 +6446,16 @@
       <c r="F221" s="4" t="n"/>
       <c r="G221" s="4" t="n"/>
       <c r="H221" s="4" t="n"/>
-      <c r="I221" s="4" t="n"/>
-      <c r="J221" s="11" t="inlineStr">
+      <c r="I221" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J221" s="4" t="n"/>
       <c r="K221" s="4" t="n"/>
       <c r="L221" s="4" t="n"/>
       <c r="M221" s="4" t="n"/>
       <c r="N221" s="4" t="n"/>
-      <c r="O221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -6700,17 +6470,16 @@
       <c r="F222" s="4" t="n"/>
       <c r="G222" s="4" t="n"/>
       <c r="H222" s="4" t="n"/>
-      <c r="I222" s="4" t="n"/>
-      <c r="J222" s="11" t="inlineStr">
+      <c r="I222" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J222" s="4" t="n"/>
       <c r="K222" s="4" t="n"/>
       <c r="L222" s="4" t="n"/>
       <c r="M222" s="4" t="n"/>
       <c r="N222" s="4" t="n"/>
-      <c r="O222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -6725,17 +6494,16 @@
       <c r="F223" s="4" t="n"/>
       <c r="G223" s="4" t="n"/>
       <c r="H223" s="4" t="n"/>
-      <c r="I223" s="4" t="n"/>
-      <c r="J223" s="11" t="inlineStr">
+      <c r="I223" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J223" s="4" t="n"/>
       <c r="K223" s="4" t="n"/>
       <c r="L223" s="4" t="n"/>
       <c r="M223" s="4" t="n"/>
       <c r="N223" s="4" t="n"/>
-      <c r="O223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="inlineStr">
@@ -6756,7 +6524,6 @@
       <c r="L224" s="8" t="n"/>
       <c r="M224" s="8" t="n"/>
       <c r="N224" s="8" t="n"/>
-      <c r="O224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
@@ -6777,7 +6544,6 @@
       <c r="L225" s="8" t="n"/>
       <c r="M225" s="8" t="n"/>
       <c r="N225" s="8" t="n"/>
-      <c r="O225" s="8" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -6792,17 +6558,16 @@
       <c r="F226" s="4" t="n"/>
       <c r="G226" s="4" t="n"/>
       <c r="H226" s="4" t="n"/>
-      <c r="I226" s="4" t="n"/>
-      <c r="J226" s="9" t="inlineStr">
+      <c r="I226" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
       <c r="M226" s="4" t="n"/>
       <c r="N226" s="4" t="n"/>
-      <c r="O226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -6817,17 +6582,16 @@
       <c r="F227" s="4" t="n"/>
       <c r="G227" s="4" t="n"/>
       <c r="H227" s="4" t="n"/>
-      <c r="I227" s="4" t="n"/>
-      <c r="J227" s="9" t="inlineStr">
+      <c r="I227" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
       <c r="M227" s="4" t="n"/>
       <c r="N227" s="4" t="n"/>
-      <c r="O227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -6842,17 +6606,16 @@
       <c r="F228" s="4" t="n"/>
       <c r="G228" s="4" t="n"/>
       <c r="H228" s="4" t="n"/>
-      <c r="I228" s="4" t="n"/>
-      <c r="J228" s="9" t="inlineStr">
+      <c r="I228" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
       <c r="M228" s="4" t="n"/>
       <c r="N228" s="4" t="n"/>
-      <c r="O228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -6867,17 +6630,16 @@
       <c r="F229" s="4" t="n"/>
       <c r="G229" s="4" t="n"/>
       <c r="H229" s="4" t="n"/>
-      <c r="I229" s="4" t="n"/>
-      <c r="J229" s="9" t="inlineStr">
+      <c r="I229" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
       <c r="M229" s="4" t="n"/>
       <c r="N229" s="4" t="n"/>
-      <c r="O229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -6892,17 +6654,16 @@
       <c r="F230" s="4" t="n"/>
       <c r="G230" s="4" t="n"/>
       <c r="H230" s="4" t="n"/>
-      <c r="I230" s="4" t="n"/>
-      <c r="J230" s="9" t="inlineStr">
+      <c r="I230" s="9" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
       <c r="M230" s="4" t="n"/>
       <c r="N230" s="4" t="n"/>
-      <c r="O230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
@@ -6923,7 +6684,6 @@
       <c r="L231" s="8" t="n"/>
       <c r="M231" s="8" t="n"/>
       <c r="N231" s="8" t="n"/>
-      <c r="O231" s="8" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="inlineStr">
@@ -6944,7 +6704,6 @@
       <c r="L232" s="8" t="n"/>
       <c r="M232" s="8" t="n"/>
       <c r="N232" s="8" t="n"/>
-      <c r="O232" s="8" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -6959,17 +6718,16 @@
       <c r="F233" s="4" t="n"/>
       <c r="G233" s="4" t="n"/>
       <c r="H233" s="4" t="n"/>
-      <c r="I233" s="4" t="n"/>
-      <c r="J233" s="10" t="inlineStr">
+      <c r="I233" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
       <c r="M233" s="4" t="n"/>
       <c r="N233" s="4" t="n"/>
-      <c r="O233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -6984,17 +6742,16 @@
       <c r="F234" s="4" t="n"/>
       <c r="G234" s="4" t="n"/>
       <c r="H234" s="4" t="n"/>
-      <c r="I234" s="4" t="n"/>
-      <c r="J234" s="10" t="inlineStr">
+      <c r="I234" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
       <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="n"/>
-      <c r="O234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -7009,17 +6766,16 @@
       <c r="F235" s="4" t="n"/>
       <c r="G235" s="4" t="n"/>
       <c r="H235" s="4" t="n"/>
-      <c r="I235" s="4" t="n"/>
-      <c r="J235" s="10" t="inlineStr">
+      <c r="I235" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
       <c r="M235" s="4" t="n"/>
       <c r="N235" s="4" t="n"/>
-      <c r="O235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -7034,17 +6790,16 @@
       <c r="F236" s="4" t="n"/>
       <c r="G236" s="4" t="n"/>
       <c r="H236" s="4" t="n"/>
-      <c r="I236" s="4" t="n"/>
-      <c r="J236" s="10" t="inlineStr">
+      <c r="I236" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
       <c r="M236" s="4" t="n"/>
       <c r="N236" s="4" t="n"/>
-      <c r="O236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -7059,17 +6814,16 @@
       <c r="F237" s="4" t="n"/>
       <c r="G237" s="4" t="n"/>
       <c r="H237" s="4" t="n"/>
-      <c r="I237" s="4" t="n"/>
-      <c r="J237" s="10" t="inlineStr">
+      <c r="I237" s="10" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
       <c r="M237" s="4" t="n"/>
       <c r="N237" s="4" t="n"/>
-      <c r="O237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="inlineStr">
@@ -7090,7 +6844,6 @@
       <c r="L238" s="8" t="n"/>
       <c r="M238" s="8" t="n"/>
       <c r="N238" s="8" t="n"/>
-      <c r="O238" s="8" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
@@ -7111,7 +6864,6 @@
       <c r="L239" s="8" t="n"/>
       <c r="M239" s="8" t="n"/>
       <c r="N239" s="8" t="n"/>
-      <c r="O239" s="8" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -7126,17 +6878,16 @@
       <c r="F240" s="4" t="n"/>
       <c r="G240" s="4" t="n"/>
       <c r="H240" s="4" t="n"/>
-      <c r="I240" s="4" t="n"/>
-      <c r="J240" s="11" t="inlineStr">
+      <c r="I240" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J240" s="4" t="n"/>
       <c r="K240" s="4" t="n"/>
       <c r="L240" s="4" t="n"/>
       <c r="M240" s="4" t="n"/>
       <c r="N240" s="4" t="n"/>
-      <c r="O240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -7151,17 +6902,16 @@
       <c r="F241" s="4" t="n"/>
       <c r="G241" s="4" t="n"/>
       <c r="H241" s="4" t="n"/>
-      <c r="I241" s="4" t="n"/>
-      <c r="J241" s="11" t="inlineStr">
+      <c r="I241" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J241" s="4" t="n"/>
       <c r="K241" s="4" t="n"/>
       <c r="L241" s="4" t="n"/>
       <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="n"/>
-      <c r="O241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -7175,22 +6925,21 @@
       <c r="E242" s="4" t="n"/>
       <c r="F242" s="4" t="n"/>
       <c r="G242" s="4" t="n"/>
-      <c r="H242" s="4" t="n"/>
-      <c r="I242" s="5" t="inlineStr">
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J242" s="11" t="inlineStr">
+      <c r="I242" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J242" s="4" t="n"/>
       <c r="K242" s="4" t="n"/>
       <c r="L242" s="4" t="n"/>
       <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="n"/>
-      <c r="O242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -7204,22 +6953,21 @@
       <c r="E243" s="4" t="n"/>
       <c r="F243" s="4" t="n"/>
       <c r="G243" s="4" t="n"/>
-      <c r="H243" s="4" t="n"/>
-      <c r="I243" s="5" t="inlineStr">
+      <c r="H243" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J243" s="11" t="inlineStr">
+      <c r="I243" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J243" s="4" t="n"/>
       <c r="K243" s="4" t="n"/>
       <c r="L243" s="4" t="n"/>
       <c r="M243" s="4" t="n"/>
       <c r="N243" s="4" t="n"/>
-      <c r="O243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -7233,22 +6981,21 @@
       <c r="E244" s="4" t="n"/>
       <c r="F244" s="4" t="n"/>
       <c r="G244" s="4" t="n"/>
-      <c r="H244" s="4" t="n"/>
-      <c r="I244" s="5" t="inlineStr">
+      <c r="H244" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J244" s="11" t="inlineStr">
+      <c r="I244" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>
         </is>
       </c>
+      <c r="J244" s="4" t="n"/>
       <c r="K244" s="4" t="n"/>
       <c r="L244" s="4" t="n"/>
       <c r="M244" s="4" t="n"/>
       <c r="N244" s="4" t="n"/>
-      <c r="O244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
@@ -7269,7 +7016,6 @@
       <c r="L245" s="8" t="n"/>
       <c r="M245" s="8" t="n"/>
       <c r="N245" s="8" t="n"/>
-      <c r="O245" s="8" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="inlineStr">
@@ -7290,7 +7036,6 @@
       <c r="L246" s="8" t="n"/>
       <c r="M246" s="8" t="n"/>
       <c r="N246" s="8" t="n"/>
-      <c r="O246" s="8" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -7304,18 +7049,17 @@
       <c r="E247" s="4" t="n"/>
       <c r="F247" s="4" t="n"/>
       <c r="G247" s="4" t="n"/>
-      <c r="H247" s="4" t="n"/>
-      <c r="I247" s="5" t="inlineStr">
+      <c r="H247" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="I247" s="4" t="n"/>
       <c r="J247" s="4" t="n"/>
       <c r="K247" s="4" t="n"/>
       <c r="L247" s="4" t="n"/>
       <c r="M247" s="4" t="n"/>
       <c r="N247" s="4" t="n"/>
-      <c r="O247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -7329,18 +7073,17 @@
       <c r="E248" s="4" t="n"/>
       <c r="F248" s="4" t="n"/>
       <c r="G248" s="4" t="n"/>
-      <c r="H248" s="4" t="n"/>
-      <c r="I248" s="5" t="inlineStr">
+      <c r="H248" s="5" t="inlineStr">
         <is>
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
+      <c r="I248" s="4" t="n"/>
       <c r="J248" s="4" t="n"/>
       <c r="K248" s="4" t="n"/>
       <c r="L248" s="4" t="n"/>
       <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="n"/>
-      <c r="O248" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -624,7 +624,11 @@
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
@@ -644,7 +648,11 @@
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
@@ -684,7 +692,11 @@
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -744,7 +756,11 @@
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
@@ -764,7 +780,11 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
@@ -784,7 +804,11 @@
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -804,7 +828,11 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
@@ -824,7 +852,11 @@
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
@@ -1744,7 +1776,11 @@
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
@@ -1764,7 +1800,11 @@
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J60" s="4" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4" t="n"/>
@@ -3728,7 +3768,11 @@
       </c>
       <c r="G156" s="4" t="n"/>
       <c r="H156" s="4" t="n"/>
-      <c r="I156" s="4" t="n"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J156" s="4" t="n"/>
       <c r="K156" s="4" t="n"/>
       <c r="L156" s="4" t="n"/>
@@ -3752,7 +3796,11 @@
       </c>
       <c r="G157" s="4" t="n"/>
       <c r="H157" s="4" t="n"/>
-      <c r="I157" s="4" t="n"/>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J157" s="4" t="n"/>
       <c r="K157" s="4" t="n"/>
       <c r="L157" s="4" t="n"/>
@@ -3776,7 +3824,11 @@
       </c>
       <c r="G158" s="4" t="n"/>
       <c r="H158" s="4" t="n"/>
-      <c r="I158" s="4" t="n"/>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J158" s="4" t="n"/>
       <c r="K158" s="4" t="n"/>
       <c r="L158" s="4" t="n"/>
@@ -3796,7 +3848,11 @@
       <c r="F159" s="4" t="n"/>
       <c r="G159" s="4" t="n"/>
       <c r="H159" s="4" t="n"/>
-      <c r="I159" s="4" t="n"/>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J159" s="4" t="n"/>
       <c r="K159" s="4" t="n"/>
       <c r="L159" s="4" t="n"/>
@@ -3816,7 +3872,11 @@
       <c r="F160" s="4" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="4" t="n"/>
-      <c r="I160" s="4" t="n"/>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J160" s="4" t="n"/>
       <c r="K160" s="4" t="n"/>
       <c r="L160" s="4" t="n"/>
@@ -5144,7 +5204,11 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I226" s="4" t="n"/>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J226" s="4" t="n"/>
       <c r="K226" s="4" t="n"/>
       <c r="L226" s="4" t="n"/>
@@ -5172,7 +5236,11 @@
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I227" s="4" t="n"/>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J227" s="4" t="n"/>
       <c r="K227" s="4" t="n"/>
       <c r="L227" s="4" t="n"/>
@@ -5196,7 +5264,11 @@
       </c>
       <c r="G228" s="4" t="n"/>
       <c r="H228" s="4" t="n"/>
-      <c r="I228" s="4" t="n"/>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J228" s="4" t="n"/>
       <c r="K228" s="4" t="n"/>
       <c r="L228" s="4" t="n"/>
@@ -5220,7 +5292,11 @@
       </c>
       <c r="G229" s="4" t="n"/>
       <c r="H229" s="4" t="n"/>
-      <c r="I229" s="4" t="n"/>
+      <c r="I229" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J229" s="4" t="n"/>
       <c r="K229" s="4" t="n"/>
       <c r="L229" s="4" t="n"/>
@@ -5248,7 +5324,11 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I230" s="4" t="n"/>
+      <c r="I230" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J230" s="4" t="n"/>
       <c r="K230" s="4" t="n"/>
       <c r="L230" s="4" t="n"/>
@@ -5308,7 +5388,11 @@
       <c r="F233" s="4" t="n"/>
       <c r="G233" s="4" t="n"/>
       <c r="H233" s="4" t="n"/>
-      <c r="I233" s="4" t="n"/>
+      <c r="I233" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J233" s="4" t="n"/>
       <c r="K233" s="4" t="n"/>
       <c r="L233" s="4" t="n"/>
@@ -5332,7 +5416,11 @@
       </c>
       <c r="G234" s="4" t="n"/>
       <c r="H234" s="4" t="n"/>
-      <c r="I234" s="4" t="n"/>
+      <c r="I234" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J234" s="4" t="n"/>
       <c r="K234" s="4" t="n"/>
       <c r="L234" s="4" t="n"/>
@@ -5352,7 +5440,11 @@
       <c r="F235" s="4" t="n"/>
       <c r="G235" s="4" t="n"/>
       <c r="H235" s="4" t="n"/>
-      <c r="I235" s="4" t="n"/>
+      <c r="I235" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J235" s="4" t="n"/>
       <c r="K235" s="4" t="n"/>
       <c r="L235" s="4" t="n"/>
@@ -5372,7 +5464,11 @@
       <c r="F236" s="4" t="n"/>
       <c r="G236" s="4" t="n"/>
       <c r="H236" s="4" t="n"/>
-      <c r="I236" s="4" t="n"/>
+      <c r="I236" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J236" s="4" t="n"/>
       <c r="K236" s="4" t="n"/>
       <c r="L236" s="4" t="n"/>
@@ -5396,7 +5492,11 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I237" s="4" t="n"/>
+      <c r="I237" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="J237" s="4" t="n"/>
       <c r="K237" s="4" t="n"/>
       <c r="L237" s="4" t="n"/>
@@ -5606,7 +5706,8 @@
       <c r="H247" s="4" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J247" s="8" t="inlineStr">
@@ -5658,7 +5759,8 @@
       <c r="H248" s="4" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J248" s="8" t="inlineStr">
@@ -5710,7 +5812,8 @@
       <c r="H249" s="4" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J249" s="8" t="inlineStr">
@@ -5771,7 +5874,8 @@
       <c r="H250" s="4" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J250" s="8" t="inlineStr">
@@ -5828,7 +5932,8 @@
       <c r="H251" s="4" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave (5)
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J251" s="8" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -4281,7 +4281,11 @@
       <c r="K180" s="4" t="n"/>
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
-      <c r="N180" s="4" t="n"/>
+      <c r="N180" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -2701,7 +2701,11 @@
       <c r="K104" s="4" t="n"/>
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
-      <c r="N104" s="4" t="n"/>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -2765,7 +2769,11 @@
       <c r="K107" s="4" t="n"/>
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
-      <c r="N107" s="4" t="n"/>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -4305,7 +4313,11 @@
       <c r="K181" s="4" t="n"/>
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
-      <c r="N181" s="4" t="n"/>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -4365,7 +4377,11 @@
       <c r="K184" s="4" t="n"/>
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
-      <c r="N184" s="4" t="n"/>
+      <c r="N184" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4385,7 +4401,11 @@
       <c r="K185" s="4" t="n"/>
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
-      <c r="N185" s="4" t="n"/>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4405,7 +4425,11 @@
       <c r="K186" s="4" t="n"/>
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
-      <c r="N186" s="4" t="n"/>
+      <c r="N186" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4805,7 +4829,11 @@
       <c r="K206" s="4" t="n"/>
       <c r="L206" s="4" t="n"/>
       <c r="M206" s="4" t="n"/>
-      <c r="N206" s="4" t="n"/>
+      <c r="N206" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -4825,7 +4853,11 @@
       <c r="K207" s="4" t="n"/>
       <c r="L207" s="4" t="n"/>
       <c r="M207" s="4" t="n"/>
-      <c r="N207" s="4" t="n"/>
+      <c r="N207" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -4845,7 +4877,11 @@
       <c r="K208" s="4" t="n"/>
       <c r="L208" s="4" t="n"/>
       <c r="M208" s="4" t="n"/>
-      <c r="N208" s="4" t="n"/>
+      <c r="N208" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -4865,7 +4901,11 @@
       <c r="K209" s="4" t="n"/>
       <c r="L209" s="4" t="n"/>
       <c r="M209" s="4" t="n"/>
-      <c r="N209" s="4" t="n"/>
+      <c r="N209" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -4925,7 +4965,11 @@
       <c r="K212" s="4" t="n"/>
       <c r="L212" s="4" t="n"/>
       <c r="M212" s="4" t="n"/>
-      <c r="N212" s="4" t="n"/>
+      <c r="N212" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave (1)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -599,7 +599,11 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -623,7 +627,11 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -647,7 +655,11 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -691,7 +703,11 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -2263,7 +2279,11 @@
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
       <c r="G83" s="4" t="n"/>
-      <c r="H83" s="4" t="n"/>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I83" s="4" t="n"/>
       <c r="J83" s="4" t="n"/>
       <c r="K83" s="4" t="n"/>
@@ -2323,7 +2343,11 @@
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
       <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="n"/>
       <c r="J86" s="4" t="n"/>
       <c r="K86" s="4" t="n"/>
@@ -2343,7 +2367,11 @@
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
       <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I87" s="4" t="n"/>
       <c r="J87" s="4" t="n"/>
       <c r="K87" s="4" t="n"/>
@@ -3983,7 +4011,11 @@
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="4" t="n"/>
       <c r="G165" s="4" t="n"/>
-      <c r="H165" s="4" t="n"/>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I165" s="4" t="n"/>
       <c r="J165" s="4" t="n"/>
       <c r="K165" s="4" t="n"/>
@@ -4003,7 +4035,11 @@
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="n"/>
       <c r="G166" s="4" t="n"/>
-      <c r="H166" s="4" t="n"/>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="n"/>
       <c r="J166" s="4" t="n"/>
       <c r="K166" s="4" t="n"/>
@@ -4023,7 +4059,11 @@
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
       <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n"/>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I167" s="4" t="n"/>
       <c r="J167" s="4" t="n"/>
       <c r="K167" s="4" t="n"/>
@@ -4083,7 +4123,11 @@
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="4" t="n"/>
       <c r="G170" s="4" t="n"/>
-      <c r="H170" s="4" t="n"/>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="n"/>
       <c r="J170" s="4" t="n"/>
       <c r="K170" s="4" t="n"/>
@@ -4103,7 +4147,11 @@
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="n"/>
       <c r="G171" s="4" t="n"/>
-      <c r="H171" s="4" t="n"/>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I171" s="4" t="n"/>
       <c r="J171" s="4" t="n"/>
       <c r="K171" s="4" t="n"/>
@@ -4123,7 +4171,11 @@
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
       <c r="G172" s="4" t="n"/>
-      <c r="H172" s="4" t="n"/>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I172" s="4" t="n"/>
       <c r="J172" s="4" t="n"/>
       <c r="K172" s="4" t="n"/>
@@ -4243,7 +4295,11 @@
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="4" t="n"/>
       <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="n"/>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I178" s="4" t="n"/>
       <c r="J178" s="4" t="n"/>
       <c r="K178" s="4" t="n"/>
@@ -4263,7 +4319,11 @@
       <c r="E179" s="4" t="n"/>
       <c r="F179" s="4" t="n"/>
       <c r="G179" s="4" t="n"/>
-      <c r="H179" s="4" t="n"/>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I179" s="4" t="n"/>
       <c r="J179" s="4" t="n"/>
       <c r="K179" s="4" t="n"/>
@@ -4283,7 +4343,11 @@
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="n"/>
       <c r="G180" s="4" t="n"/>
-      <c r="H180" s="4" t="n"/>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I180" s="4" t="n"/>
       <c r="J180" s="4" t="n"/>
       <c r="K180" s="4" t="n"/>
@@ -4307,7 +4371,11 @@
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="n"/>
       <c r="G181" s="4" t="n"/>
-      <c r="H181" s="4" t="n"/>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I181" s="4" t="n"/>
       <c r="J181" s="4" t="n"/>
       <c r="K181" s="4" t="n"/>
@@ -4371,7 +4439,11 @@
       <c r="E184" s="4" t="n"/>
       <c r="F184" s="4" t="n"/>
       <c r="G184" s="4" t="n"/>
-      <c r="H184" s="4" t="n"/>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I184" s="4" t="n"/>
       <c r="J184" s="4" t="n"/>
       <c r="K184" s="4" t="n"/>
@@ -4395,7 +4467,11 @@
       <c r="E185" s="4" t="n"/>
       <c r="F185" s="4" t="n"/>
       <c r="G185" s="4" t="n"/>
-      <c r="H185" s="4" t="n"/>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I185" s="4" t="n"/>
       <c r="J185" s="4" t="n"/>
       <c r="K185" s="4" t="n"/>
@@ -4603,7 +4679,11 @@
       <c r="E195" s="4" t="n"/>
       <c r="F195" s="4" t="n"/>
       <c r="G195" s="4" t="n"/>
-      <c r="H195" s="4" t="n"/>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I195" s="4" t="n"/>
       <c r="J195" s="4" t="n"/>
       <c r="K195" s="4" t="n"/>
@@ -4663,7 +4743,11 @@
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="4" t="n"/>
       <c r="G198" s="4" t="n"/>
-      <c r="H198" s="4" t="n"/>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="n"/>
       <c r="J198" s="4" t="n"/>
       <c r="K198" s="4" t="n"/>
@@ -4967,7 +5051,7 @@
       <c r="M212" s="4" t="n"/>
       <c r="N212" s="5" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5073,11 @@
       <c r="K213" s="4" t="n"/>
       <c r="L213" s="4" t="n"/>
       <c r="M213" s="4" t="n"/>
-      <c r="N213" s="4" t="n"/>
+      <c r="N213" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -5009,7 +5097,11 @@
       <c r="K214" s="4" t="n"/>
       <c r="L214" s="4" t="n"/>
       <c r="M214" s="4" t="n"/>
-      <c r="N214" s="4" t="n"/>
+      <c r="N214" s="5" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -52,12 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +617,11 @@
           <t>Thu 20 Nov 2025</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave (1)</t>
+        </is>
+      </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
@@ -637,7 +641,11 @@
           <t>Fri 21 Nov 2025</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>A/L (Half Day) - Annual Leave (2)</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
@@ -652,44 +660,44 @@
       <c r="N4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Sat 22 Nov 2025</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Sun 23 Nov 2025</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -792,44 +800,44 @@
       <c r="N11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Sat 29 Nov 2025</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="8" t="n"/>
+      <c r="N12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Sun 30 Nov 2025</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -932,44 +940,44 @@
       <c r="N18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Sat 06 Dec 2025</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Sun 07 Dec 2025</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1072,44 +1080,44 @@
       <c r="N25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Sat 13 Dec 2025</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sun 14 Dec 2025</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1212,44 +1220,44 @@
       <c r="N32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Sat 20 Dec 2025</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="7" t="n"/>
-      <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
-      <c r="N33" s="7" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="8" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Sun 21 Dec 2025</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1384,44 +1392,44 @@
       <c r="N39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Sat 27 Dec 2025</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
-      <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
-      <c r="N40" s="7" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Sun 28 Dec 2025</t>
         </is>
       </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="7" t="n"/>
-      <c r="J41" s="7" t="n"/>
-      <c r="K41" s="7" t="n"/>
-      <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
-      <c r="N41" s="7" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1544,44 +1552,44 @@
       <c r="N46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Sat 03 Jan 2026</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
-      <c r="J47" s="7" t="n"/>
-      <c r="K47" s="7" t="n"/>
-      <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
-      <c r="N47" s="7" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="8" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="8" t="n"/>
+      <c r="N47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>Sun 04 Jan 2026</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
-      <c r="L48" s="7" t="n"/>
-      <c r="M48" s="7" t="n"/>
-      <c r="N48" s="7" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="8" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="8" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n"/>
+      <c r="N48" s="8" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1684,44 +1692,44 @@
       <c r="N53" s="5" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Sat 10 Jan 2026</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
-      <c r="J54" s="7" t="n"/>
-      <c r="K54" s="7" t="n"/>
-      <c r="L54" s="7" t="n"/>
-      <c r="M54" s="7" t="n"/>
-      <c r="N54" s="7" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="8" t="n"/>
+      <c r="N54" s="8" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>Sun 11 Jan 2026</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-      <c r="J55" s="7" t="n"/>
-      <c r="K55" s="7" t="n"/>
-      <c r="L55" s="7" t="n"/>
-      <c r="M55" s="7" t="n"/>
-      <c r="N55" s="7" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="8" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -1824,44 +1832,44 @@
       <c r="N60" s="5" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Sat 17 Jan 2026</t>
         </is>
       </c>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
-      <c r="N61" s="7" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
+      <c r="N61" s="8" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>Sun 18 Jan 2026</t>
         </is>
       </c>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
-      <c r="L62" s="7" t="n"/>
-      <c r="M62" s="7" t="n"/>
-      <c r="N62" s="7" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
+      <c r="N62" s="8" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -1964,44 +1972,44 @@
       <c r="N67" s="5" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>Sat 24 Jan 2026</t>
         </is>
       </c>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n"/>
-      <c r="I68" s="7" t="n"/>
-      <c r="J68" s="7" t="n"/>
-      <c r="K68" s="7" t="n"/>
-      <c r="L68" s="7" t="n"/>
-      <c r="M68" s="7" t="n"/>
-      <c r="N68" s="7" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>Sun 25 Jan 2026</t>
         </is>
       </c>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
-      <c r="L69" s="7" t="n"/>
-      <c r="M69" s="7" t="n"/>
-      <c r="N69" s="7" t="n"/>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2104,44 +2112,44 @@
       <c r="N74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>Sat 31 Jan 2026</t>
         </is>
       </c>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="n"/>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n"/>
-      <c r="I75" s="7" t="n"/>
-      <c r="J75" s="7" t="n"/>
-      <c r="K75" s="7" t="n"/>
-      <c r="L75" s="7" t="n"/>
-      <c r="M75" s="7" t="n"/>
-      <c r="N75" s="7" t="n"/>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="8" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="8" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>Sun 01 Feb 2026</t>
         </is>
       </c>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
-      <c r="F76" s="7" t="n"/>
-      <c r="G76" s="7" t="n"/>
-      <c r="H76" s="7" t="n"/>
-      <c r="I76" s="7" t="n"/>
-      <c r="J76" s="7" t="n"/>
-      <c r="K76" s="7" t="n"/>
-      <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
-      <c r="N76" s="7" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="8" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2244,44 +2252,44 @@
       <c r="N81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>Sat 07 Feb 2026</t>
         </is>
       </c>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="n"/>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
-      <c r="J82" s="7" t="n"/>
-      <c r="K82" s="7" t="n"/>
-      <c r="L82" s="7" t="n"/>
-      <c r="M82" s="7" t="n"/>
-      <c r="N82" s="7" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
+      <c r="N82" s="8" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>Sun 08 Feb 2026</t>
         </is>
       </c>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="7" t="n"/>
-      <c r="G83" s="7" t="n"/>
-      <c r="H83" s="7" t="n"/>
-      <c r="I83" s="7" t="n"/>
-      <c r="J83" s="7" t="n"/>
-      <c r="K83" s="7" t="n"/>
-      <c r="L83" s="7" t="n"/>
-      <c r="M83" s="7" t="n"/>
-      <c r="N83" s="7" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="8" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2384,44 +2392,44 @@
       <c r="N88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="inlineStr">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>Sat 14 Feb 2026</t>
         </is>
       </c>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="7" t="n"/>
-      <c r="I89" s="7" t="n"/>
-      <c r="J89" s="7" t="n"/>
-      <c r="K89" s="7" t="n"/>
-      <c r="L89" s="7" t="n"/>
-      <c r="M89" s="7" t="n"/>
-      <c r="N89" s="7" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>Sun 15 Feb 2026</t>
         </is>
       </c>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="7" t="n"/>
-      <c r="I90" s="7" t="n"/>
-      <c r="J90" s="7" t="n"/>
-      <c r="K90" s="7" t="n"/>
-      <c r="L90" s="7" t="n"/>
-      <c r="M90" s="7" t="n"/>
-      <c r="N90" s="7" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="8" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2532,44 +2540,44 @@
       <c r="N95" s="5" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>Sat 21 Feb 2026</t>
         </is>
       </c>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="7" t="n"/>
-      <c r="I96" s="7" t="n"/>
-      <c r="J96" s="7" t="n"/>
-      <c r="K96" s="7" t="n"/>
-      <c r="L96" s="7" t="n"/>
-      <c r="M96" s="7" t="n"/>
-      <c r="N96" s="7" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+      <c r="N96" s="8" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>Sun 22 Feb 2026</t>
         </is>
       </c>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="n"/>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
-      <c r="J97" s="7" t="n"/>
-      <c r="K97" s="7" t="n"/>
-      <c r="L97" s="7" t="n"/>
-      <c r="M97" s="7" t="n"/>
-      <c r="N97" s="7" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="8" t="n"/>
+      <c r="F97" s="8" t="n"/>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="8" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -2672,44 +2680,44 @@
       <c r="N102" s="5" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>Sat 28 Feb 2026</t>
         </is>
       </c>
-      <c r="B103" s="7" t="n"/>
-      <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="7" t="n"/>
-      <c r="I103" s="7" t="n"/>
-      <c r="J103" s="7" t="n"/>
-      <c r="K103" s="7" t="n"/>
-      <c r="L103" s="7" t="n"/>
-      <c r="M103" s="7" t="n"/>
-      <c r="N103" s="7" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="8" t="n"/>
+      <c r="N103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>Sun 01 Mar 2026</t>
         </is>
       </c>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="7" t="n"/>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="7" t="n"/>
-      <c r="I104" s="7" t="n"/>
-      <c r="J104" s="7" t="n"/>
-      <c r="K104" s="7" t="n"/>
-      <c r="L104" s="7" t="n"/>
-      <c r="M104" s="7" t="n"/>
-      <c r="N104" s="7" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+      <c r="G104" s="8" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="8" t="n"/>
+      <c r="M104" s="8" t="n"/>
+      <c r="N104" s="8" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -2812,44 +2820,44 @@
       <c r="N109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>Sat 07 Mar 2026</t>
         </is>
       </c>
-      <c r="B110" s="7" t="n"/>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
-      <c r="K110" s="7" t="n"/>
-      <c r="L110" s="7" t="n"/>
-      <c r="M110" s="7" t="n"/>
-      <c r="N110" s="7" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
+      <c r="G110" s="8" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="8" t="n"/>
+      <c r="M110" s="8" t="n"/>
+      <c r="N110" s="8" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>Sun 08 Mar 2026</t>
         </is>
       </c>
-      <c r="B111" s="7" t="n"/>
-      <c r="C111" s="7" t="n"/>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="7" t="n"/>
-      <c r="I111" s="7" t="n"/>
-      <c r="J111" s="7" t="n"/>
-      <c r="K111" s="7" t="n"/>
-      <c r="L111" s="7" t="n"/>
-      <c r="M111" s="7" t="n"/>
-      <c r="N111" s="7" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="8" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="8" t="n"/>
+      <c r="N111" s="8" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -2956,44 +2964,44 @@
       <c r="N116" s="5" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>Sat 14 Mar 2026</t>
         </is>
       </c>
-      <c r="B117" s="7" t="n"/>
-      <c r="C117" s="7" t="n"/>
-      <c r="D117" s="7" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
-      <c r="K117" s="7" t="n"/>
-      <c r="L117" s="7" t="n"/>
-      <c r="M117" s="7" t="n"/>
-      <c r="N117" s="7" t="n"/>
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+      <c r="G117" s="8" t="n"/>
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="8" t="n"/>
+      <c r="J117" s="8" t="n"/>
+      <c r="K117" s="8" t="n"/>
+      <c r="L117" s="8" t="n"/>
+      <c r="M117" s="8" t="n"/>
+      <c r="N117" s="8" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>Sun 15 Mar 2026</t>
         </is>
       </c>
-      <c r="B118" s="7" t="n"/>
-      <c r="C118" s="7" t="n"/>
-      <c r="D118" s="7" t="n"/>
-      <c r="E118" s="7" t="n"/>
-      <c r="F118" s="7" t="n"/>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="7" t="n"/>
-      <c r="I118" s="7" t="n"/>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="7" t="n"/>
-      <c r="L118" s="7" t="n"/>
-      <c r="M118" s="7" t="n"/>
-      <c r="N118" s="7" t="n"/>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="8" t="n"/>
+      <c r="F118" s="8" t="n"/>
+      <c r="G118" s="8" t="n"/>
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="8" t="n"/>
+      <c r="J118" s="8" t="n"/>
+      <c r="K118" s="8" t="n"/>
+      <c r="L118" s="8" t="n"/>
+      <c r="M118" s="8" t="n"/>
+      <c r="N118" s="8" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3104,44 +3112,44 @@
       <c r="N123" s="5" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>Sat 21 Mar 2026</t>
         </is>
       </c>
-      <c r="B124" s="7" t="n"/>
-      <c r="C124" s="7" t="n"/>
-      <c r="D124" s="7" t="n"/>
-      <c r="E124" s="7" t="n"/>
-      <c r="F124" s="7" t="n"/>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-      <c r="J124" s="7" t="n"/>
-      <c r="K124" s="7" t="n"/>
-      <c r="L124" s="7" t="n"/>
-      <c r="M124" s="7" t="n"/>
-      <c r="N124" s="7" t="n"/>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="8" t="n"/>
+      <c r="G124" s="8" t="n"/>
+      <c r="H124" s="8" t="n"/>
+      <c r="I124" s="8" t="n"/>
+      <c r="J124" s="8" t="n"/>
+      <c r="K124" s="8" t="n"/>
+      <c r="L124" s="8" t="n"/>
+      <c r="M124" s="8" t="n"/>
+      <c r="N124" s="8" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>Sun 22 Mar 2026</t>
         </is>
       </c>
-      <c r="B125" s="7" t="n"/>
-      <c r="C125" s="7" t="n"/>
-      <c r="D125" s="7" t="n"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-      <c r="J125" s="7" t="n"/>
-      <c r="K125" s="7" t="n"/>
-      <c r="L125" s="7" t="n"/>
-      <c r="M125" s="7" t="n"/>
-      <c r="N125" s="7" t="n"/>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="8" t="n"/>
+      <c r="J125" s="8" t="n"/>
+      <c r="K125" s="8" t="n"/>
+      <c r="L125" s="8" t="n"/>
+      <c r="M125" s="8" t="n"/>
+      <c r="N125" s="8" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -3244,44 +3252,44 @@
       <c r="N130" s="5" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>Sat 28 Mar 2026</t>
         </is>
       </c>
-      <c r="B131" s="7" t="n"/>
-      <c r="C131" s="7" t="n"/>
-      <c r="D131" s="7" t="n"/>
-      <c r="E131" s="7" t="n"/>
-      <c r="F131" s="7" t="n"/>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="7" t="n"/>
-      <c r="I131" s="7" t="n"/>
-      <c r="J131" s="7" t="n"/>
-      <c r="K131" s="7" t="n"/>
-      <c r="L131" s="7" t="n"/>
-      <c r="M131" s="7" t="n"/>
-      <c r="N131" s="7" t="n"/>
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+      <c r="G131" s="8" t="n"/>
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="8" t="n"/>
+      <c r="J131" s="8" t="n"/>
+      <c r="K131" s="8" t="n"/>
+      <c r="L131" s="8" t="n"/>
+      <c r="M131" s="8" t="n"/>
+      <c r="N131" s="8" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>Sun 29 Mar 2026</t>
         </is>
       </c>
-      <c r="B132" s="7" t="n"/>
-      <c r="C132" s="7" t="n"/>
-      <c r="D132" s="7" t="n"/>
-      <c r="E132" s="7" t="n"/>
-      <c r="F132" s="7" t="n"/>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="7" t="n"/>
-      <c r="I132" s="7" t="n"/>
-      <c r="J132" s="7" t="n"/>
-      <c r="K132" s="7" t="n"/>
-      <c r="L132" s="7" t="n"/>
-      <c r="M132" s="7" t="n"/>
-      <c r="N132" s="7" t="n"/>
+      <c r="B132" s="8" t="n"/>
+      <c r="C132" s="8" t="n"/>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="8" t="n"/>
+      <c r="F132" s="8" t="n"/>
+      <c r="G132" s="8" t="n"/>
+      <c r="H132" s="8" t="n"/>
+      <c r="I132" s="8" t="n"/>
+      <c r="J132" s="8" t="n"/>
+      <c r="K132" s="8" t="n"/>
+      <c r="L132" s="8" t="n"/>
+      <c r="M132" s="8" t="n"/>
+      <c r="N132" s="8" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -3400,44 +3408,44 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>Sat 04 Apr 2026</t>
         </is>
       </c>
-      <c r="B138" s="7" t="n"/>
-      <c r="C138" s="7" t="n"/>
-      <c r="D138" s="7" t="n"/>
-      <c r="E138" s="7" t="n"/>
-      <c r="F138" s="7" t="n"/>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="7" t="n"/>
-      <c r="I138" s="7" t="n"/>
-      <c r="J138" s="7" t="n"/>
-      <c r="K138" s="7" t="n"/>
-      <c r="L138" s="7" t="n"/>
-      <c r="M138" s="7" t="n"/>
-      <c r="N138" s="7" t="n"/>
+      <c r="B138" s="8" t="n"/>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="8" t="n"/>
+      <c r="E138" s="8" t="n"/>
+      <c r="F138" s="8" t="n"/>
+      <c r="G138" s="8" t="n"/>
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="8" t="n"/>
+      <c r="J138" s="8" t="n"/>
+      <c r="K138" s="8" t="n"/>
+      <c r="L138" s="8" t="n"/>
+      <c r="M138" s="8" t="n"/>
+      <c r="N138" s="8" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>Sun 05 Apr 2026</t>
         </is>
       </c>
-      <c r="B139" s="7" t="n"/>
-      <c r="C139" s="7" t="n"/>
-      <c r="D139" s="7" t="n"/>
-      <c r="E139" s="7" t="n"/>
-      <c r="F139" s="7" t="n"/>
-      <c r="G139" s="7" t="n"/>
-      <c r="H139" s="7" t="n"/>
-      <c r="I139" s="7" t="n"/>
-      <c r="J139" s="7" t="n"/>
-      <c r="K139" s="7" t="n"/>
-      <c r="L139" s="7" t="n"/>
-      <c r="M139" s="7" t="n"/>
-      <c r="N139" s="7" t="n"/>
+      <c r="B139" s="8" t="n"/>
+      <c r="C139" s="8" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="8" t="n"/>
+      <c r="F139" s="8" t="n"/>
+      <c r="G139" s="8" t="n"/>
+      <c r="H139" s="8" t="n"/>
+      <c r="I139" s="8" t="n"/>
+      <c r="J139" s="8" t="n"/>
+      <c r="K139" s="8" t="n"/>
+      <c r="L139" s="8" t="n"/>
+      <c r="M139" s="8" t="n"/>
+      <c r="N139" s="8" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -3564,44 +3572,44 @@
       <c r="N144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>Sat 11 Apr 2026</t>
         </is>
       </c>
-      <c r="B145" s="7" t="n"/>
-      <c r="C145" s="7" t="n"/>
-      <c r="D145" s="7" t="n"/>
-      <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="n"/>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="7" t="n"/>
-      <c r="I145" s="7" t="n"/>
-      <c r="J145" s="7" t="n"/>
-      <c r="K145" s="7" t="n"/>
-      <c r="L145" s="7" t="n"/>
-      <c r="M145" s="7" t="n"/>
-      <c r="N145" s="7" t="n"/>
+      <c r="B145" s="8" t="n"/>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="8" t="n"/>
+      <c r="G145" s="8" t="n"/>
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="8" t="n"/>
+      <c r="J145" s="8" t="n"/>
+      <c r="K145" s="8" t="n"/>
+      <c r="L145" s="8" t="n"/>
+      <c r="M145" s="8" t="n"/>
+      <c r="N145" s="8" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>Sun 12 Apr 2026</t>
         </is>
       </c>
-      <c r="B146" s="7" t="n"/>
-      <c r="C146" s="7" t="n"/>
-      <c r="D146" s="7" t="n"/>
-      <c r="E146" s="7" t="n"/>
-      <c r="F146" s="7" t="n"/>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="7" t="n"/>
-      <c r="I146" s="7" t="n"/>
-      <c r="J146" s="7" t="n"/>
-      <c r="K146" s="7" t="n"/>
-      <c r="L146" s="7" t="n"/>
-      <c r="M146" s="7" t="n"/>
-      <c r="N146" s="7" t="n"/>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="8" t="n"/>
+      <c r="G146" s="8" t="n"/>
+      <c r="H146" s="8" t="n"/>
+      <c r="I146" s="8" t="n"/>
+      <c r="J146" s="8" t="n"/>
+      <c r="K146" s="8" t="n"/>
+      <c r="L146" s="8" t="n"/>
+      <c r="M146" s="8" t="n"/>
+      <c r="N146" s="8" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -3704,44 +3712,44 @@
       <c r="N151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>Sat 18 Apr 2026</t>
         </is>
       </c>
-      <c r="B152" s="7" t="n"/>
-      <c r="C152" s="7" t="n"/>
-      <c r="D152" s="7" t="n"/>
-      <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" s="7" t="n"/>
-      <c r="K152" s="7" t="n"/>
-      <c r="L152" s="7" t="n"/>
-      <c r="M152" s="7" t="n"/>
-      <c r="N152" s="7" t="n"/>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="8" t="n"/>
+      <c r="D152" s="8" t="n"/>
+      <c r="E152" s="8" t="n"/>
+      <c r="F152" s="8" t="n"/>
+      <c r="G152" s="8" t="n"/>
+      <c r="H152" s="8" t="n"/>
+      <c r="I152" s="8" t="n"/>
+      <c r="J152" s="8" t="n"/>
+      <c r="K152" s="8" t="n"/>
+      <c r="L152" s="8" t="n"/>
+      <c r="M152" s="8" t="n"/>
+      <c r="N152" s="8" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="inlineStr">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>Sun 19 Apr 2026</t>
         </is>
       </c>
-      <c r="B153" s="7" t="n"/>
-      <c r="C153" s="7" t="n"/>
-      <c r="D153" s="7" t="n"/>
-      <c r="E153" s="7" t="n"/>
-      <c r="F153" s="7" t="n"/>
-      <c r="G153" s="7" t="n"/>
-      <c r="H153" s="7" t="n"/>
-      <c r="I153" s="7" t="n"/>
-      <c r="J153" s="7" t="n"/>
-      <c r="K153" s="7" t="n"/>
-      <c r="L153" s="7" t="n"/>
-      <c r="M153" s="7" t="n"/>
-      <c r="N153" s="7" t="n"/>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="8" t="n"/>
+      <c r="G153" s="8" t="n"/>
+      <c r="H153" s="8" t="n"/>
+      <c r="I153" s="8" t="n"/>
+      <c r="J153" s="8" t="n"/>
+      <c r="K153" s="8" t="n"/>
+      <c r="L153" s="8" t="n"/>
+      <c r="M153" s="8" t="n"/>
+      <c r="N153" s="8" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -3844,44 +3852,44 @@
       <c r="N158" s="5" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="6" t="inlineStr">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t>Sat 25 Apr 2026</t>
         </is>
       </c>
-      <c r="B159" s="7" t="n"/>
-      <c r="C159" s="7" t="n"/>
-      <c r="D159" s="7" t="n"/>
-      <c r="E159" s="7" t="n"/>
-      <c r="F159" s="7" t="n"/>
-      <c r="G159" s="7" t="n"/>
-      <c r="H159" s="7" t="n"/>
-      <c r="I159" s="7" t="n"/>
-      <c r="J159" s="7" t="n"/>
-      <c r="K159" s="7" t="n"/>
-      <c r="L159" s="7" t="n"/>
-      <c r="M159" s="7" t="n"/>
-      <c r="N159" s="7" t="n"/>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="8" t="n"/>
+      <c r="F159" s="8" t="n"/>
+      <c r="G159" s="8" t="n"/>
+      <c r="H159" s="8" t="n"/>
+      <c r="I159" s="8" t="n"/>
+      <c r="J159" s="8" t="n"/>
+      <c r="K159" s="8" t="n"/>
+      <c r="L159" s="8" t="n"/>
+      <c r="M159" s="8" t="n"/>
+      <c r="N159" s="8" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>Sun 26 Apr 2026</t>
         </is>
       </c>
-      <c r="B160" s="7" t="n"/>
-      <c r="C160" s="7" t="n"/>
-      <c r="D160" s="7" t="n"/>
-      <c r="E160" s="7" t="n"/>
-      <c r="F160" s="7" t="n"/>
-      <c r="G160" s="7" t="n"/>
-      <c r="H160" s="7" t="n"/>
-      <c r="I160" s="7" t="n"/>
-      <c r="J160" s="7" t="n"/>
-      <c r="K160" s="7" t="n"/>
-      <c r="L160" s="7" t="n"/>
-      <c r="M160" s="7" t="n"/>
-      <c r="N160" s="7" t="n"/>
+      <c r="B160" s="8" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="8" t="n"/>
+      <c r="G160" s="8" t="n"/>
+      <c r="H160" s="8" t="n"/>
+      <c r="I160" s="8" t="n"/>
+      <c r="J160" s="8" t="n"/>
+      <c r="K160" s="8" t="n"/>
+      <c r="L160" s="8" t="n"/>
+      <c r="M160" s="8" t="n"/>
+      <c r="N160" s="8" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -3973,7 +3981,7 @@
       <c r="C165" s="5" t="n"/>
       <c r="D165" s="5" t="n"/>
       <c r="E165" s="5" t="n"/>
-      <c r="F165" s="8" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -3988,44 +3996,44 @@
       <c r="N165" s="5" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t>Sat 02 May 2026</t>
         </is>
       </c>
-      <c r="B166" s="7" t="n"/>
-      <c r="C166" s="7" t="n"/>
-      <c r="D166" s="7" t="n"/>
-      <c r="E166" s="7" t="n"/>
-      <c r="F166" s="7" t="n"/>
-      <c r="G166" s="7" t="n"/>
-      <c r="H166" s="7" t="n"/>
-      <c r="I166" s="7" t="n"/>
-      <c r="J166" s="7" t="n"/>
-      <c r="K166" s="7" t="n"/>
-      <c r="L166" s="7" t="n"/>
-      <c r="M166" s="7" t="n"/>
-      <c r="N166" s="7" t="n"/>
+      <c r="B166" s="8" t="n"/>
+      <c r="C166" s="8" t="n"/>
+      <c r="D166" s="8" t="n"/>
+      <c r="E166" s="8" t="n"/>
+      <c r="F166" s="8" t="n"/>
+      <c r="G166" s="8" t="n"/>
+      <c r="H166" s="8" t="n"/>
+      <c r="I166" s="8" t="n"/>
+      <c r="J166" s="8" t="n"/>
+      <c r="K166" s="8" t="n"/>
+      <c r="L166" s="8" t="n"/>
+      <c r="M166" s="8" t="n"/>
+      <c r="N166" s="8" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="inlineStr">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>Sun 03 May 2026</t>
         </is>
       </c>
-      <c r="B167" s="7" t="n"/>
-      <c r="C167" s="7" t="n"/>
-      <c r="D167" s="7" t="n"/>
-      <c r="E167" s="7" t="n"/>
-      <c r="F167" s="7" t="n"/>
-      <c r="G167" s="7" t="n"/>
-      <c r="H167" s="7" t="n"/>
-      <c r="I167" s="7" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="7" t="n"/>
-      <c r="L167" s="7" t="n"/>
-      <c r="M167" s="7" t="n"/>
-      <c r="N167" s="7" t="n"/>
+      <c r="B167" s="8" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+      <c r="G167" s="8" t="n"/>
+      <c r="H167" s="8" t="n"/>
+      <c r="I167" s="8" t="n"/>
+      <c r="J167" s="8" t="n"/>
+      <c r="K167" s="8" t="n"/>
+      <c r="L167" s="8" t="n"/>
+      <c r="M167" s="8" t="n"/>
+      <c r="N167" s="8" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -4132,44 +4140,44 @@
       <c r="N172" s="5" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>Sat 09 May 2026</t>
         </is>
       </c>
-      <c r="B173" s="7" t="n"/>
-      <c r="C173" s="7" t="n"/>
-      <c r="D173" s="7" t="n"/>
-      <c r="E173" s="7" t="n"/>
-      <c r="F173" s="7" t="n"/>
-      <c r="G173" s="7" t="n"/>
-      <c r="H173" s="7" t="n"/>
-      <c r="I173" s="7" t="n"/>
-      <c r="J173" s="7" t="n"/>
-      <c r="K173" s="7" t="n"/>
-      <c r="L173" s="7" t="n"/>
-      <c r="M173" s="7" t="n"/>
-      <c r="N173" s="7" t="n"/>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
+      <c r="G173" s="8" t="n"/>
+      <c r="H173" s="8" t="n"/>
+      <c r="I173" s="8" t="n"/>
+      <c r="J173" s="8" t="n"/>
+      <c r="K173" s="8" t="n"/>
+      <c r="L173" s="8" t="n"/>
+      <c r="M173" s="8" t="n"/>
+      <c r="N173" s="8" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="inlineStr">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>Sun 10 May 2026</t>
         </is>
       </c>
-      <c r="B174" s="7" t="n"/>
-      <c r="C174" s="7" t="n"/>
-      <c r="D174" s="7" t="n"/>
-      <c r="E174" s="7" t="n"/>
-      <c r="F174" s="7" t="n"/>
-      <c r="G174" s="7" t="n"/>
-      <c r="H174" s="7" t="n"/>
-      <c r="I174" s="7" t="n"/>
-      <c r="J174" s="7" t="n"/>
-      <c r="K174" s="7" t="n"/>
-      <c r="L174" s="7" t="n"/>
-      <c r="M174" s="7" t="n"/>
-      <c r="N174" s="7" t="n"/>
+      <c r="B174" s="8" t="n"/>
+      <c r="C174" s="8" t="n"/>
+      <c r="D174" s="8" t="n"/>
+      <c r="E174" s="8" t="n"/>
+      <c r="F174" s="8" t="n"/>
+      <c r="G174" s="8" t="n"/>
+      <c r="H174" s="8" t="n"/>
+      <c r="I174" s="8" t="n"/>
+      <c r="J174" s="8" t="n"/>
+      <c r="K174" s="8" t="n"/>
+      <c r="L174" s="8" t="n"/>
+      <c r="M174" s="8" t="n"/>
+      <c r="N174" s="8" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -4272,44 +4280,44 @@
       <c r="N179" s="5" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>Sat 16 May 2026</t>
         </is>
       </c>
-      <c r="B180" s="7" t="n"/>
-      <c r="C180" s="7" t="n"/>
-      <c r="D180" s="7" t="n"/>
-      <c r="E180" s="7" t="n"/>
-      <c r="F180" s="7" t="n"/>
-      <c r="G180" s="7" t="n"/>
-      <c r="H180" s="7" t="n"/>
-      <c r="I180" s="7" t="n"/>
-      <c r="J180" s="7" t="n"/>
-      <c r="K180" s="7" t="n"/>
-      <c r="L180" s="7" t="n"/>
-      <c r="M180" s="7" t="n"/>
-      <c r="N180" s="7" t="n"/>
+      <c r="B180" s="8" t="n"/>
+      <c r="C180" s="8" t="n"/>
+      <c r="D180" s="8" t="n"/>
+      <c r="E180" s="8" t="n"/>
+      <c r="F180" s="8" t="n"/>
+      <c r="G180" s="8" t="n"/>
+      <c r="H180" s="8" t="n"/>
+      <c r="I180" s="8" t="n"/>
+      <c r="J180" s="8" t="n"/>
+      <c r="K180" s="8" t="n"/>
+      <c r="L180" s="8" t="n"/>
+      <c r="M180" s="8" t="n"/>
+      <c r="N180" s="8" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t>Sun 17 May 2026</t>
         </is>
       </c>
-      <c r="B181" s="7" t="n"/>
-      <c r="C181" s="7" t="n"/>
-      <c r="D181" s="7" t="n"/>
-      <c r="E181" s="7" t="n"/>
-      <c r="F181" s="7" t="n"/>
-      <c r="G181" s="7" t="n"/>
-      <c r="H181" s="7" t="n"/>
-      <c r="I181" s="7" t="n"/>
-      <c r="J181" s="7" t="n"/>
-      <c r="K181" s="7" t="n"/>
-      <c r="L181" s="7" t="n"/>
-      <c r="M181" s="7" t="n"/>
-      <c r="N181" s="7" t="n"/>
+      <c r="B181" s="8" t="n"/>
+      <c r="C181" s="8" t="n"/>
+      <c r="D181" s="8" t="n"/>
+      <c r="E181" s="8" t="n"/>
+      <c r="F181" s="8" t="n"/>
+      <c r="G181" s="8" t="n"/>
+      <c r="H181" s="8" t="n"/>
+      <c r="I181" s="8" t="n"/>
+      <c r="J181" s="8" t="n"/>
+      <c r="K181" s="8" t="n"/>
+      <c r="L181" s="8" t="n"/>
+      <c r="M181" s="8" t="n"/>
+      <c r="N181" s="8" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -4412,44 +4420,44 @@
       <c r="N186" s="5" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="6" t="inlineStr">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t>Sat 23 May 2026</t>
         </is>
       </c>
-      <c r="B187" s="7" t="n"/>
-      <c r="C187" s="7" t="n"/>
-      <c r="D187" s="7" t="n"/>
-      <c r="E187" s="7" t="n"/>
-      <c r="F187" s="7" t="n"/>
-      <c r="G187" s="7" t="n"/>
-      <c r="H187" s="7" t="n"/>
-      <c r="I187" s="7" t="n"/>
-      <c r="J187" s="7" t="n"/>
-      <c r="K187" s="7" t="n"/>
-      <c r="L187" s="7" t="n"/>
-      <c r="M187" s="7" t="n"/>
-      <c r="N187" s="7" t="n"/>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
+      <c r="G187" s="8" t="n"/>
+      <c r="H187" s="8" t="n"/>
+      <c r="I187" s="8" t="n"/>
+      <c r="J187" s="8" t="n"/>
+      <c r="K187" s="8" t="n"/>
+      <c r="L187" s="8" t="n"/>
+      <c r="M187" s="8" t="n"/>
+      <c r="N187" s="8" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t>Sun 24 May 2026</t>
         </is>
       </c>
-      <c r="B188" s="7" t="n"/>
-      <c r="C188" s="7" t="n"/>
-      <c r="D188" s="7" t="n"/>
-      <c r="E188" s="7" t="n"/>
-      <c r="F188" s="7" t="n"/>
-      <c r="G188" s="7" t="n"/>
-      <c r="H188" s="7" t="n"/>
-      <c r="I188" s="7" t="n"/>
-      <c r="J188" s="7" t="n"/>
-      <c r="K188" s="7" t="n"/>
-      <c r="L188" s="7" t="n"/>
-      <c r="M188" s="7" t="n"/>
-      <c r="N188" s="7" t="n"/>
+      <c r="B188" s="8" t="n"/>
+      <c r="C188" s="8" t="n"/>
+      <c r="D188" s="8" t="n"/>
+      <c r="E188" s="8" t="n"/>
+      <c r="F188" s="8" t="n"/>
+      <c r="G188" s="8" t="n"/>
+      <c r="H188" s="8" t="n"/>
+      <c r="I188" s="8" t="n"/>
+      <c r="J188" s="8" t="n"/>
+      <c r="K188" s="8" t="n"/>
+      <c r="L188" s="8" t="n"/>
+      <c r="M188" s="8" t="n"/>
+      <c r="N188" s="8" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -4584,44 +4592,44 @@
       <c r="N193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="inlineStr">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>Sat 30 May 2026</t>
         </is>
       </c>
-      <c r="B194" s="7" t="n"/>
-      <c r="C194" s="7" t="n"/>
-      <c r="D194" s="7" t="n"/>
-      <c r="E194" s="7" t="n"/>
-      <c r="F194" s="7" t="n"/>
-      <c r="G194" s="7" t="n"/>
-      <c r="H194" s="7" t="n"/>
-      <c r="I194" s="7" t="n"/>
-      <c r="J194" s="7" t="n"/>
-      <c r="K194" s="7" t="n"/>
-      <c r="L194" s="7" t="n"/>
-      <c r="M194" s="7" t="n"/>
-      <c r="N194" s="7" t="n"/>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
+      <c r="G194" s="8" t="n"/>
+      <c r="H194" s="8" t="n"/>
+      <c r="I194" s="8" t="n"/>
+      <c r="J194" s="8" t="n"/>
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="8" t="n"/>
+      <c r="M194" s="8" t="n"/>
+      <c r="N194" s="8" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="6" t="inlineStr">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>Sun 31 May 2026</t>
         </is>
       </c>
-      <c r="B195" s="7" t="n"/>
-      <c r="C195" s="7" t="n"/>
-      <c r="D195" s="7" t="n"/>
-      <c r="E195" s="7" t="n"/>
-      <c r="F195" s="7" t="n"/>
-      <c r="G195" s="7" t="n"/>
-      <c r="H195" s="7" t="n"/>
-      <c r="I195" s="7" t="n"/>
-      <c r="J195" s="7" t="n"/>
-      <c r="K195" s="7" t="n"/>
-      <c r="L195" s="7" t="n"/>
-      <c r="M195" s="7" t="n"/>
-      <c r="N195" s="7" t="n"/>
+      <c r="B195" s="8" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="8" t="n"/>
+      <c r="F195" s="8" t="n"/>
+      <c r="G195" s="8" t="n"/>
+      <c r="H195" s="8" t="n"/>
+      <c r="I195" s="8" t="n"/>
+      <c r="J195" s="8" t="n"/>
+      <c r="K195" s="8" t="n"/>
+      <c r="L195" s="8" t="n"/>
+      <c r="M195" s="8" t="n"/>
+      <c r="N195" s="8" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -4736,44 +4744,44 @@
       <c r="N200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="6" t="inlineStr">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>Sat 06 Jun 2026</t>
         </is>
       </c>
-      <c r="B201" s="7" t="n"/>
-      <c r="C201" s="7" t="n"/>
-      <c r="D201" s="7" t="n"/>
-      <c r="E201" s="7" t="n"/>
-      <c r="F201" s="7" t="n"/>
-      <c r="G201" s="7" t="n"/>
-      <c r="H201" s="7" t="n"/>
-      <c r="I201" s="7" t="n"/>
-      <c r="J201" s="7" t="n"/>
-      <c r="K201" s="7" t="n"/>
-      <c r="L201" s="7" t="n"/>
-      <c r="M201" s="7" t="n"/>
-      <c r="N201" s="7" t="n"/>
+      <c r="B201" s="8" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="8" t="n"/>
+      <c r="F201" s="8" t="n"/>
+      <c r="G201" s="8" t="n"/>
+      <c r="H201" s="8" t="n"/>
+      <c r="I201" s="8" t="n"/>
+      <c r="J201" s="8" t="n"/>
+      <c r="K201" s="8" t="n"/>
+      <c r="L201" s="8" t="n"/>
+      <c r="M201" s="8" t="n"/>
+      <c r="N201" s="8" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="6" t="inlineStr">
+      <c r="A202" s="7" t="inlineStr">
         <is>
           <t>Sun 07 Jun 2026</t>
         </is>
       </c>
-      <c r="B202" s="7" t="n"/>
-      <c r="C202" s="7" t="n"/>
-      <c r="D202" s="7" t="n"/>
-      <c r="E202" s="7" t="n"/>
-      <c r="F202" s="7" t="n"/>
-      <c r="G202" s="7" t="n"/>
-      <c r="H202" s="7" t="n"/>
-      <c r="I202" s="7" t="n"/>
-      <c r="J202" s="7" t="n"/>
-      <c r="K202" s="7" t="n"/>
-      <c r="L202" s="7" t="n"/>
-      <c r="M202" s="7" t="n"/>
-      <c r="N202" s="7" t="n"/>
+      <c r="B202" s="8" t="n"/>
+      <c r="C202" s="8" t="n"/>
+      <c r="D202" s="8" t="n"/>
+      <c r="E202" s="8" t="n"/>
+      <c r="F202" s="8" t="n"/>
+      <c r="G202" s="8" t="n"/>
+      <c r="H202" s="8" t="n"/>
+      <c r="I202" s="8" t="n"/>
+      <c r="J202" s="8" t="n"/>
+      <c r="K202" s="8" t="n"/>
+      <c r="L202" s="8" t="n"/>
+      <c r="M202" s="8" t="n"/>
+      <c r="N202" s="8" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -4888,44 +4896,44 @@
       <c r="N207" s="5" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="6" t="inlineStr">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t>Sat 13 Jun 2026</t>
         </is>
       </c>
-      <c r="B208" s="7" t="n"/>
-      <c r="C208" s="7" t="n"/>
-      <c r="D208" s="7" t="n"/>
-      <c r="E208" s="7" t="n"/>
-      <c r="F208" s="7" t="n"/>
-      <c r="G208" s="7" t="n"/>
-      <c r="H208" s="7" t="n"/>
-      <c r="I208" s="7" t="n"/>
-      <c r="J208" s="7" t="n"/>
-      <c r="K208" s="7" t="n"/>
-      <c r="L208" s="7" t="n"/>
-      <c r="M208" s="7" t="n"/>
-      <c r="N208" s="7" t="n"/>
+      <c r="B208" s="8" t="n"/>
+      <c r="C208" s="8" t="n"/>
+      <c r="D208" s="8" t="n"/>
+      <c r="E208" s="8" t="n"/>
+      <c r="F208" s="8" t="n"/>
+      <c r="G208" s="8" t="n"/>
+      <c r="H208" s="8" t="n"/>
+      <c r="I208" s="8" t="n"/>
+      <c r="J208" s="8" t="n"/>
+      <c r="K208" s="8" t="n"/>
+      <c r="L208" s="8" t="n"/>
+      <c r="M208" s="8" t="n"/>
+      <c r="N208" s="8" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="6" t="inlineStr">
+      <c r="A209" s="7" t="inlineStr">
         <is>
           <t>Sun 14 Jun 2026</t>
         </is>
       </c>
-      <c r="B209" s="7" t="n"/>
-      <c r="C209" s="7" t="n"/>
-      <c r="D209" s="7" t="n"/>
-      <c r="E209" s="7" t="n"/>
-      <c r="F209" s="7" t="n"/>
-      <c r="G209" s="7" t="n"/>
-      <c r="H209" s="7" t="n"/>
-      <c r="I209" s="7" t="n"/>
-      <c r="J209" s="7" t="n"/>
-      <c r="K209" s="7" t="n"/>
-      <c r="L209" s="7" t="n"/>
-      <c r="M209" s="7" t="n"/>
-      <c r="N209" s="7" t="n"/>
+      <c r="B209" s="8" t="n"/>
+      <c r="C209" s="8" t="n"/>
+      <c r="D209" s="8" t="n"/>
+      <c r="E209" s="8" t="n"/>
+      <c r="F209" s="8" t="n"/>
+      <c r="G209" s="8" t="n"/>
+      <c r="H209" s="8" t="n"/>
+      <c r="I209" s="8" t="n"/>
+      <c r="J209" s="8" t="n"/>
+      <c r="K209" s="8" t="n"/>
+      <c r="L209" s="8" t="n"/>
+      <c r="M209" s="8" t="n"/>
+      <c r="N209" s="8" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -5052,44 +5060,44 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+      <c r="A215" s="7" t="inlineStr">
         <is>
           <t>Sat 20 Jun 2026</t>
         </is>
       </c>
-      <c r="B215" s="7" t="n"/>
-      <c r="C215" s="7" t="n"/>
-      <c r="D215" s="7" t="n"/>
-      <c r="E215" s="7" t="n"/>
-      <c r="F215" s="7" t="n"/>
-      <c r="G215" s="7" t="n"/>
-      <c r="H215" s="7" t="n"/>
-      <c r="I215" s="7" t="n"/>
-      <c r="J215" s="7" t="n"/>
-      <c r="K215" s="7" t="n"/>
-      <c r="L215" s="7" t="n"/>
-      <c r="M215" s="7" t="n"/>
-      <c r="N215" s="7" t="n"/>
+      <c r="B215" s="8" t="n"/>
+      <c r="C215" s="8" t="n"/>
+      <c r="D215" s="8" t="n"/>
+      <c r="E215" s="8" t="n"/>
+      <c r="F215" s="8" t="n"/>
+      <c r="G215" s="8" t="n"/>
+      <c r="H215" s="8" t="n"/>
+      <c r="I215" s="8" t="n"/>
+      <c r="J215" s="8" t="n"/>
+      <c r="K215" s="8" t="n"/>
+      <c r="L215" s="8" t="n"/>
+      <c r="M215" s="8" t="n"/>
+      <c r="N215" s="8" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="6" t="inlineStr">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t>Sun 21 Jun 2026</t>
         </is>
       </c>
-      <c r="B216" s="7" t="n"/>
-      <c r="C216" s="7" t="n"/>
-      <c r="D216" s="7" t="n"/>
-      <c r="E216" s="7" t="n"/>
-      <c r="F216" s="7" t="n"/>
-      <c r="G216" s="7" t="n"/>
-      <c r="H216" s="7" t="n"/>
-      <c r="I216" s="7" t="n"/>
-      <c r="J216" s="7" t="n"/>
-      <c r="K216" s="7" t="n"/>
-      <c r="L216" s="7" t="n"/>
-      <c r="M216" s="7" t="n"/>
-      <c r="N216" s="7" t="n"/>
+      <c r="B216" s="8" t="n"/>
+      <c r="C216" s="8" t="n"/>
+      <c r="D216" s="8" t="n"/>
+      <c r="E216" s="8" t="n"/>
+      <c r="F216" s="8" t="n"/>
+      <c r="G216" s="8" t="n"/>
+      <c r="H216" s="8" t="n"/>
+      <c r="I216" s="8" t="n"/>
+      <c r="J216" s="8" t="n"/>
+      <c r="K216" s="8" t="n"/>
+      <c r="L216" s="8" t="n"/>
+      <c r="M216" s="8" t="n"/>
+      <c r="N216" s="8" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -5212,44 +5220,44 @@
       <c r="N221" s="5" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="6" t="inlineStr">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t>Sat 27 Jun 2026</t>
         </is>
       </c>
-      <c r="B222" s="7" t="n"/>
-      <c r="C222" s="7" t="n"/>
-      <c r="D222" s="7" t="n"/>
-      <c r="E222" s="7" t="n"/>
-      <c r="F222" s="7" t="n"/>
-      <c r="G222" s="7" t="n"/>
-      <c r="H222" s="7" t="n"/>
-      <c r="I222" s="7" t="n"/>
-      <c r="J222" s="7" t="n"/>
-      <c r="K222" s="7" t="n"/>
-      <c r="L222" s="7" t="n"/>
-      <c r="M222" s="7" t="n"/>
-      <c r="N222" s="7" t="n"/>
+      <c r="B222" s="8" t="n"/>
+      <c r="C222" s="8" t="n"/>
+      <c r="D222" s="8" t="n"/>
+      <c r="E222" s="8" t="n"/>
+      <c r="F222" s="8" t="n"/>
+      <c r="G222" s="8" t="n"/>
+      <c r="H222" s="8" t="n"/>
+      <c r="I222" s="8" t="n"/>
+      <c r="J222" s="8" t="n"/>
+      <c r="K222" s="8" t="n"/>
+      <c r="L222" s="8" t="n"/>
+      <c r="M222" s="8" t="n"/>
+      <c r="N222" s="8" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
+      <c r="A223" s="7" t="inlineStr">
         <is>
           <t>Sun 28 Jun 2026</t>
         </is>
       </c>
-      <c r="B223" s="7" t="n"/>
-      <c r="C223" s="7" t="n"/>
-      <c r="D223" s="7" t="n"/>
-      <c r="E223" s="7" t="n"/>
-      <c r="F223" s="7" t="n"/>
-      <c r="G223" s="7" t="n"/>
-      <c r="H223" s="7" t="n"/>
-      <c r="I223" s="7" t="n"/>
-      <c r="J223" s="7" t="n"/>
-      <c r="K223" s="7" t="n"/>
-      <c r="L223" s="7" t="n"/>
-      <c r="M223" s="7" t="n"/>
-      <c r="N223" s="7" t="n"/>
+      <c r="B223" s="8" t="n"/>
+      <c r="C223" s="8" t="n"/>
+      <c r="D223" s="8" t="n"/>
+      <c r="E223" s="8" t="n"/>
+      <c r="F223" s="8" t="n"/>
+      <c r="G223" s="8" t="n"/>
+      <c r="H223" s="8" t="n"/>
+      <c r="I223" s="8" t="n"/>
+      <c r="J223" s="8" t="n"/>
+      <c r="K223" s="8" t="n"/>
+      <c r="L223" s="8" t="n"/>
+      <c r="M223" s="8" t="n"/>
+      <c r="N223" s="8" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -5356,44 +5364,44 @@
       <c r="N228" s="5" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="6" t="inlineStr">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t>Sat 04 Jul 2026</t>
         </is>
       </c>
-      <c r="B229" s="7" t="n"/>
-      <c r="C229" s="7" t="n"/>
-      <c r="D229" s="7" t="n"/>
-      <c r="E229" s="7" t="n"/>
-      <c r="F229" s="7" t="n"/>
-      <c r="G229" s="7" t="n"/>
-      <c r="H229" s="7" t="n"/>
-      <c r="I229" s="7" t="n"/>
-      <c r="J229" s="7" t="n"/>
-      <c r="K229" s="7" t="n"/>
-      <c r="L229" s="7" t="n"/>
-      <c r="M229" s="7" t="n"/>
-      <c r="N229" s="7" t="n"/>
+      <c r="B229" s="8" t="n"/>
+      <c r="C229" s="8" t="n"/>
+      <c r="D229" s="8" t="n"/>
+      <c r="E229" s="8" t="n"/>
+      <c r="F229" s="8" t="n"/>
+      <c r="G229" s="8" t="n"/>
+      <c r="H229" s="8" t="n"/>
+      <c r="I229" s="8" t="n"/>
+      <c r="J229" s="8" t="n"/>
+      <c r="K229" s="8" t="n"/>
+      <c r="L229" s="8" t="n"/>
+      <c r="M229" s="8" t="n"/>
+      <c r="N229" s="8" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="6" t="inlineStr">
+      <c r="A230" s="7" t="inlineStr">
         <is>
           <t>Sun 05 Jul 2026</t>
         </is>
       </c>
-      <c r="B230" s="7" t="n"/>
-      <c r="C230" s="7" t="n"/>
-      <c r="D230" s="7" t="n"/>
-      <c r="E230" s="7" t="n"/>
-      <c r="F230" s="7" t="n"/>
-      <c r="G230" s="7" t="n"/>
-      <c r="H230" s="7" t="n"/>
-      <c r="I230" s="7" t="n"/>
-      <c r="J230" s="7" t="n"/>
-      <c r="K230" s="7" t="n"/>
-      <c r="L230" s="7" t="n"/>
-      <c r="M230" s="7" t="n"/>
-      <c r="N230" s="7" t="n"/>
+      <c r="B230" s="8" t="n"/>
+      <c r="C230" s="8" t="n"/>
+      <c r="D230" s="8" t="n"/>
+      <c r="E230" s="8" t="n"/>
+      <c r="F230" s="8" t="n"/>
+      <c r="G230" s="8" t="n"/>
+      <c r="H230" s="8" t="n"/>
+      <c r="I230" s="8" t="n"/>
+      <c r="J230" s="8" t="n"/>
+      <c r="K230" s="8" t="n"/>
+      <c r="L230" s="8" t="n"/>
+      <c r="M230" s="8" t="n"/>
+      <c r="N230" s="8" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -5500,44 +5508,44 @@
       <c r="N235" s="5" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
+      <c r="A236" s="7" t="inlineStr">
         <is>
           <t>Sat 11 Jul 2026</t>
         </is>
       </c>
-      <c r="B236" s="7" t="n"/>
-      <c r="C236" s="7" t="n"/>
-      <c r="D236" s="7" t="n"/>
-      <c r="E236" s="7" t="n"/>
-      <c r="F236" s="7" t="n"/>
-      <c r="G236" s="7" t="n"/>
-      <c r="H236" s="7" t="n"/>
-      <c r="I236" s="7" t="n"/>
-      <c r="J236" s="7" t="n"/>
-      <c r="K236" s="7" t="n"/>
-      <c r="L236" s="7" t="n"/>
-      <c r="M236" s="7" t="n"/>
-      <c r="N236" s="7" t="n"/>
+      <c r="B236" s="8" t="n"/>
+      <c r="C236" s="8" t="n"/>
+      <c r="D236" s="8" t="n"/>
+      <c r="E236" s="8" t="n"/>
+      <c r="F236" s="8" t="n"/>
+      <c r="G236" s="8" t="n"/>
+      <c r="H236" s="8" t="n"/>
+      <c r="I236" s="8" t="n"/>
+      <c r="J236" s="8" t="n"/>
+      <c r="K236" s="8" t="n"/>
+      <c r="L236" s="8" t="n"/>
+      <c r="M236" s="8" t="n"/>
+      <c r="N236" s="8" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="inlineStr">
+      <c r="A237" s="7" t="inlineStr">
         <is>
           <t>Sun 12 Jul 2026</t>
         </is>
       </c>
-      <c r="B237" s="7" t="n"/>
-      <c r="C237" s="7" t="n"/>
-      <c r="D237" s="7" t="n"/>
-      <c r="E237" s="7" t="n"/>
-      <c r="F237" s="7" t="n"/>
-      <c r="G237" s="7" t="n"/>
-      <c r="H237" s="7" t="n"/>
-      <c r="I237" s="7" t="n"/>
-      <c r="J237" s="7" t="n"/>
-      <c r="K237" s="7" t="n"/>
-      <c r="L237" s="7" t="n"/>
-      <c r="M237" s="7" t="n"/>
-      <c r="N237" s="7" t="n"/>
+      <c r="B237" s="8" t="n"/>
+      <c r="C237" s="8" t="n"/>
+      <c r="D237" s="8" t="n"/>
+      <c r="E237" s="8" t="n"/>
+      <c r="F237" s="8" t="n"/>
+      <c r="G237" s="8" t="n"/>
+      <c r="H237" s="8" t="n"/>
+      <c r="I237" s="8" t="n"/>
+      <c r="J237" s="8" t="n"/>
+      <c r="K237" s="8" t="n"/>
+      <c r="L237" s="8" t="n"/>
+      <c r="M237" s="8" t="n"/>
+      <c r="N237" s="8" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -5656,44 +5664,44 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
+      <c r="A243" s="7" t="inlineStr">
         <is>
           <t>Sat 18 Jul 2026</t>
         </is>
       </c>
-      <c r="B243" s="7" t="n"/>
-      <c r="C243" s="7" t="n"/>
-      <c r="D243" s="7" t="n"/>
-      <c r="E243" s="7" t="n"/>
-      <c r="F243" s="7" t="n"/>
-      <c r="G243" s="7" t="n"/>
-      <c r="H243" s="7" t="n"/>
-      <c r="I243" s="7" t="n"/>
-      <c r="J243" s="7" t="n"/>
-      <c r="K243" s="7" t="n"/>
-      <c r="L243" s="7" t="n"/>
-      <c r="M243" s="7" t="n"/>
-      <c r="N243" s="7" t="n"/>
+      <c r="B243" s="8" t="n"/>
+      <c r="C243" s="8" t="n"/>
+      <c r="D243" s="8" t="n"/>
+      <c r="E243" s="8" t="n"/>
+      <c r="F243" s="8" t="n"/>
+      <c r="G243" s="8" t="n"/>
+      <c r="H243" s="8" t="n"/>
+      <c r="I243" s="8" t="n"/>
+      <c r="J243" s="8" t="n"/>
+      <c r="K243" s="8" t="n"/>
+      <c r="L243" s="8" t="n"/>
+      <c r="M243" s="8" t="n"/>
+      <c r="N243" s="8" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
+      <c r="A244" s="7" t="inlineStr">
         <is>
           <t>Sun 19 Jul 2026</t>
         </is>
       </c>
-      <c r="B244" s="7" t="n"/>
-      <c r="C244" s="7" t="n"/>
-      <c r="D244" s="7" t="n"/>
-      <c r="E244" s="7" t="n"/>
-      <c r="F244" s="7" t="n"/>
-      <c r="G244" s="7" t="n"/>
-      <c r="H244" s="7" t="n"/>
-      <c r="I244" s="7" t="n"/>
-      <c r="J244" s="7" t="n"/>
-      <c r="K244" s="7" t="n"/>
-      <c r="L244" s="7" t="n"/>
-      <c r="M244" s="7" t="n"/>
-      <c r="N244" s="7" t="n"/>
+      <c r="B244" s="8" t="n"/>
+      <c r="C244" s="8" t="n"/>
+      <c r="D244" s="8" t="n"/>
+      <c r="E244" s="8" t="n"/>
+      <c r="F244" s="8" t="n"/>
+      <c r="G244" s="8" t="n"/>
+      <c r="H244" s="8" t="n"/>
+      <c r="I244" s="8" t="n"/>
+      <c r="J244" s="8" t="n"/>
+      <c r="K244" s="8" t="n"/>
+      <c r="L244" s="8" t="n"/>
+      <c r="M244" s="8" t="n"/>
+      <c r="N244" s="8" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -5808,44 +5816,44 @@
       <c r="N249" s="5" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="6" t="inlineStr">
+      <c r="A250" s="7" t="inlineStr">
         <is>
           <t>Sat 25 Jul 2026</t>
         </is>
       </c>
-      <c r="B250" s="7" t="n"/>
-      <c r="C250" s="7" t="n"/>
-      <c r="D250" s="7" t="n"/>
-      <c r="E250" s="7" t="n"/>
-      <c r="F250" s="7" t="n"/>
-      <c r="G250" s="7" t="n"/>
-      <c r="H250" s="7" t="n"/>
-      <c r="I250" s="7" t="n"/>
-      <c r="J250" s="7" t="n"/>
-      <c r="K250" s="7" t="n"/>
-      <c r="L250" s="7" t="n"/>
-      <c r="M250" s="7" t="n"/>
-      <c r="N250" s="7" t="n"/>
+      <c r="B250" s="8" t="n"/>
+      <c r="C250" s="8" t="n"/>
+      <c r="D250" s="8" t="n"/>
+      <c r="E250" s="8" t="n"/>
+      <c r="F250" s="8" t="n"/>
+      <c r="G250" s="8" t="n"/>
+      <c r="H250" s="8" t="n"/>
+      <c r="I250" s="8" t="n"/>
+      <c r="J250" s="8" t="n"/>
+      <c r="K250" s="8" t="n"/>
+      <c r="L250" s="8" t="n"/>
+      <c r="M250" s="8" t="n"/>
+      <c r="N250" s="8" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr">
         <is>
           <t>Sun 26 Jul 2026</t>
         </is>
       </c>
-      <c r="B251" s="7" t="n"/>
-      <c r="C251" s="7" t="n"/>
-      <c r="D251" s="7" t="n"/>
-      <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="n"/>
-      <c r="G251" s="7" t="n"/>
-      <c r="H251" s="7" t="n"/>
-      <c r="I251" s="7" t="n"/>
-      <c r="J251" s="7" t="n"/>
-      <c r="K251" s="7" t="n"/>
-      <c r="L251" s="7" t="n"/>
-      <c r="M251" s="7" t="n"/>
-      <c r="N251" s="7" t="n"/>
+      <c r="B251" s="8" t="n"/>
+      <c r="C251" s="8" t="n"/>
+      <c r="D251" s="8" t="n"/>
+      <c r="E251" s="8" t="n"/>
+      <c r="F251" s="8" t="n"/>
+      <c r="G251" s="8" t="n"/>
+      <c r="H251" s="8" t="n"/>
+      <c r="I251" s="8" t="n"/>
+      <c r="J251" s="8" t="n"/>
+      <c r="K251" s="8" t="n"/>
+      <c r="L251" s="8" t="n"/>
+      <c r="M251" s="8" t="n"/>
+      <c r="N251" s="8" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -5948,44 +5956,44 @@
       <c r="N256" s="5" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="6" t="inlineStr">
+      <c r="A257" s="7" t="inlineStr">
         <is>
           <t>Sat 01 Aug 2026</t>
         </is>
       </c>
-      <c r="B257" s="7" t="n"/>
-      <c r="C257" s="7" t="n"/>
-      <c r="D257" s="7" t="n"/>
-      <c r="E257" s="7" t="n"/>
-      <c r="F257" s="7" t="n"/>
-      <c r="G257" s="7" t="n"/>
-      <c r="H257" s="7" t="n"/>
-      <c r="I257" s="7" t="n"/>
-      <c r="J257" s="7" t="n"/>
-      <c r="K257" s="7" t="n"/>
-      <c r="L257" s="7" t="n"/>
-      <c r="M257" s="7" t="n"/>
-      <c r="N257" s="7" t="n"/>
+      <c r="B257" s="8" t="n"/>
+      <c r="C257" s="8" t="n"/>
+      <c r="D257" s="8" t="n"/>
+      <c r="E257" s="8" t="n"/>
+      <c r="F257" s="8" t="n"/>
+      <c r="G257" s="8" t="n"/>
+      <c r="H257" s="8" t="n"/>
+      <c r="I257" s="8" t="n"/>
+      <c r="J257" s="8" t="n"/>
+      <c r="K257" s="8" t="n"/>
+      <c r="L257" s="8" t="n"/>
+      <c r="M257" s="8" t="n"/>
+      <c r="N257" s="8" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
+      <c r="A258" s="7" t="inlineStr">
         <is>
           <t>Sun 02 Aug 2026</t>
         </is>
       </c>
-      <c r="B258" s="7" t="n"/>
-      <c r="C258" s="7" t="n"/>
-      <c r="D258" s="7" t="n"/>
-      <c r="E258" s="7" t="n"/>
-      <c r="F258" s="7" t="n"/>
-      <c r="G258" s="7" t="n"/>
-      <c r="H258" s="7" t="n"/>
-      <c r="I258" s="7" t="n"/>
-      <c r="J258" s="7" t="n"/>
-      <c r="K258" s="7" t="n"/>
-      <c r="L258" s="7" t="n"/>
-      <c r="M258" s="7" t="n"/>
-      <c r="N258" s="7" t="n"/>
+      <c r="B258" s="8" t="n"/>
+      <c r="C258" s="8" t="n"/>
+      <c r="D258" s="8" t="n"/>
+      <c r="E258" s="8" t="n"/>
+      <c r="F258" s="8" t="n"/>
+      <c r="G258" s="8" t="n"/>
+      <c r="H258" s="8" t="n"/>
+      <c r="I258" s="8" t="n"/>
+      <c r="J258" s="8" t="n"/>
+      <c r="K258" s="8" t="n"/>
+      <c r="L258" s="8" t="n"/>
+      <c r="M258" s="8" t="n"/>
+      <c r="N258" s="8" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -6140,44 +6148,44 @@
       <c r="N263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr">
         <is>
           <t>Sat 08 Aug 2026</t>
         </is>
       </c>
-      <c r="B264" s="7" t="n"/>
-      <c r="C264" s="7" t="n"/>
-      <c r="D264" s="7" t="n"/>
-      <c r="E264" s="7" t="n"/>
-      <c r="F264" s="7" t="n"/>
-      <c r="G264" s="7" t="n"/>
-      <c r="H264" s="7" t="n"/>
-      <c r="I264" s="7" t="n"/>
-      <c r="J264" s="7" t="n"/>
-      <c r="K264" s="7" t="n"/>
-      <c r="L264" s="7" t="n"/>
-      <c r="M264" s="7" t="n"/>
-      <c r="N264" s="7" t="n"/>
+      <c r="B264" s="8" t="n"/>
+      <c r="C264" s="8" t="n"/>
+      <c r="D264" s="8" t="n"/>
+      <c r="E264" s="8" t="n"/>
+      <c r="F264" s="8" t="n"/>
+      <c r="G264" s="8" t="n"/>
+      <c r="H264" s="8" t="n"/>
+      <c r="I264" s="8" t="n"/>
+      <c r="J264" s="8" t="n"/>
+      <c r="K264" s="8" t="n"/>
+      <c r="L264" s="8" t="n"/>
+      <c r="M264" s="8" t="n"/>
+      <c r="N264" s="8" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
+      <c r="A265" s="7" t="inlineStr">
         <is>
           <t>Sun 09 Aug 2026</t>
         </is>
       </c>
-      <c r="B265" s="7" t="n"/>
-      <c r="C265" s="7" t="n"/>
-      <c r="D265" s="7" t="n"/>
-      <c r="E265" s="7" t="n"/>
-      <c r="F265" s="7" t="n"/>
-      <c r="G265" s="7" t="n"/>
-      <c r="H265" s="7" t="n"/>
-      <c r="I265" s="7" t="n"/>
-      <c r="J265" s="7" t="n"/>
-      <c r="K265" s="7" t="n"/>
-      <c r="L265" s="7" t="n"/>
-      <c r="M265" s="7" t="n"/>
-      <c r="N265" s="7" t="n"/>
+      <c r="B265" s="8" t="n"/>
+      <c r="C265" s="8" t="n"/>
+      <c r="D265" s="8" t="n"/>
+      <c r="E265" s="8" t="n"/>
+      <c r="F265" s="8" t="n"/>
+      <c r="G265" s="8" t="n"/>
+      <c r="H265" s="8" t="n"/>
+      <c r="I265" s="8" t="n"/>
+      <c r="J265" s="8" t="n"/>
+      <c r="K265" s="8" t="n"/>
+      <c r="L265" s="8" t="n"/>
+      <c r="M265" s="8" t="n"/>
+      <c r="N265" s="8" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -6213,7 +6221,7 @@
       <c r="C267" s="5" t="n"/>
       <c r="D267" s="5" t="n"/>
       <c r="E267" s="5" t="n"/>
-      <c r="F267" s="8" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -6308,44 +6316,44 @@
       <c r="N270" s="5" t="n"/>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
+      <c r="A271" s="7" t="inlineStr">
         <is>
           <t>Sat 15 Aug 2026</t>
         </is>
       </c>
-      <c r="B271" s="7" t="n"/>
-      <c r="C271" s="7" t="n"/>
-      <c r="D271" s="7" t="n"/>
-      <c r="E271" s="7" t="n"/>
-      <c r="F271" s="7" t="n"/>
-      <c r="G271" s="7" t="n"/>
-      <c r="H271" s="7" t="n"/>
-      <c r="I271" s="7" t="n"/>
-      <c r="J271" s="7" t="n"/>
-      <c r="K271" s="7" t="n"/>
-      <c r="L271" s="7" t="n"/>
-      <c r="M271" s="7" t="n"/>
-      <c r="N271" s="7" t="n"/>
+      <c r="B271" s="8" t="n"/>
+      <c r="C271" s="8" t="n"/>
+      <c r="D271" s="8" t="n"/>
+      <c r="E271" s="8" t="n"/>
+      <c r="F271" s="8" t="n"/>
+      <c r="G271" s="8" t="n"/>
+      <c r="H271" s="8" t="n"/>
+      <c r="I271" s="8" t="n"/>
+      <c r="J271" s="8" t="n"/>
+      <c r="K271" s="8" t="n"/>
+      <c r="L271" s="8" t="n"/>
+      <c r="M271" s="8" t="n"/>
+      <c r="N271" s="8" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="6" t="inlineStr">
+      <c r="A272" s="7" t="inlineStr">
         <is>
           <t>Sun 16 Aug 2026</t>
         </is>
       </c>
-      <c r="B272" s="7" t="n"/>
-      <c r="C272" s="7" t="n"/>
-      <c r="D272" s="7" t="n"/>
-      <c r="E272" s="7" t="n"/>
-      <c r="F272" s="7" t="n"/>
-      <c r="G272" s="7" t="n"/>
-      <c r="H272" s="7" t="n"/>
-      <c r="I272" s="7" t="n"/>
-      <c r="J272" s="7" t="n"/>
-      <c r="K272" s="7" t="n"/>
-      <c r="L272" s="7" t="n"/>
-      <c r="M272" s="7" t="n"/>
-      <c r="N272" s="7" t="n"/>
+      <c r="B272" s="8" t="n"/>
+      <c r="C272" s="8" t="n"/>
+      <c r="D272" s="8" t="n"/>
+      <c r="E272" s="8" t="n"/>
+      <c r="F272" s="8" t="n"/>
+      <c r="G272" s="8" t="n"/>
+      <c r="H272" s="8" t="n"/>
+      <c r="I272" s="8" t="n"/>
+      <c r="J272" s="8" t="n"/>
+      <c r="K272" s="8" t="n"/>
+      <c r="L272" s="8" t="n"/>
+      <c r="M272" s="8" t="n"/>
+      <c r="N272" s="8" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -6448,44 +6456,44 @@
       <c r="N277" s="5" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
+      <c r="A278" s="7" t="inlineStr">
         <is>
           <t>Sat 22 Aug 2026</t>
         </is>
       </c>
-      <c r="B278" s="7" t="n"/>
-      <c r="C278" s="7" t="n"/>
-      <c r="D278" s="7" t="n"/>
-      <c r="E278" s="7" t="n"/>
-      <c r="F278" s="7" t="n"/>
-      <c r="G278" s="7" t="n"/>
-      <c r="H278" s="7" t="n"/>
-      <c r="I278" s="7" t="n"/>
-      <c r="J278" s="7" t="n"/>
-      <c r="K278" s="7" t="n"/>
-      <c r="L278" s="7" t="n"/>
-      <c r="M278" s="7" t="n"/>
-      <c r="N278" s="7" t="n"/>
+      <c r="B278" s="8" t="n"/>
+      <c r="C278" s="8" t="n"/>
+      <c r="D278" s="8" t="n"/>
+      <c r="E278" s="8" t="n"/>
+      <c r="F278" s="8" t="n"/>
+      <c r="G278" s="8" t="n"/>
+      <c r="H278" s="8" t="n"/>
+      <c r="I278" s="8" t="n"/>
+      <c r="J278" s="8" t="n"/>
+      <c r="K278" s="8" t="n"/>
+      <c r="L278" s="8" t="n"/>
+      <c r="M278" s="8" t="n"/>
+      <c r="N278" s="8" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="6" t="inlineStr">
+      <c r="A279" s="7" t="inlineStr">
         <is>
           <t>Sun 23 Aug 2026</t>
         </is>
       </c>
-      <c r="B279" s="7" t="n"/>
-      <c r="C279" s="7" t="n"/>
-      <c r="D279" s="7" t="n"/>
-      <c r="E279" s="7" t="n"/>
-      <c r="F279" s="7" t="n"/>
-      <c r="G279" s="7" t="n"/>
-      <c r="H279" s="7" t="n"/>
-      <c r="I279" s="7" t="n"/>
-      <c r="J279" s="7" t="n"/>
-      <c r="K279" s="7" t="n"/>
-      <c r="L279" s="7" t="n"/>
-      <c r="M279" s="7" t="n"/>
-      <c r="N279" s="7" t="n"/>
+      <c r="B279" s="8" t="n"/>
+      <c r="C279" s="8" t="n"/>
+      <c r="D279" s="8" t="n"/>
+      <c r="E279" s="8" t="n"/>
+      <c r="F279" s="8" t="n"/>
+      <c r="G279" s="8" t="n"/>
+      <c r="H279" s="8" t="n"/>
+      <c r="I279" s="8" t="n"/>
+      <c r="J279" s="8" t="n"/>
+      <c r="K279" s="8" t="n"/>
+      <c r="L279" s="8" t="n"/>
+      <c r="M279" s="8" t="n"/>
+      <c r="N279" s="8" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -6499,7 +6507,7 @@
         </is>
       </c>
       <c r="C280" s="5" t="n"/>
-      <c r="D280" s="8" t="inlineStr">
+      <c r="D280" s="6" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6514,23 +6522,23 @@
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J280" s="8" t="inlineStr">
+      <c r="J280" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="K280" s="8" t="inlineStr">
+      <c r="K280" s="6" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
       <c r="L280" s="5" t="n"/>
-      <c r="M280" s="8" t="inlineStr">
+      <c r="M280" s="6" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N280" s="8" t="inlineStr">
+      <c r="N280" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -6547,12 +6555,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C281" s="8" t="inlineStr">
+      <c r="C281" s="6" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D281" s="8" t="inlineStr">
+      <c r="D281" s="6" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6567,7 +6575,7 @@
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J281" s="8" t="inlineStr">
+      <c r="J281" s="6" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
@@ -6578,12 +6586,12 @@
         </is>
       </c>
       <c r="L281" s="5" t="n"/>
-      <c r="M281" s="8" t="inlineStr">
+      <c r="M281" s="6" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N281" s="8" t="inlineStr">
+      <c r="N281" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -6600,12 +6608,12 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C282" s="8" t="inlineStr">
+      <c r="C282" s="6" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D282" s="8" t="inlineStr">
+      <c r="D282" s="6" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6620,7 +6628,7 @@
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J282" s="8" t="inlineStr">
+      <c r="J282" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
@@ -6630,17 +6638,17 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L282" s="8" t="inlineStr">
+      <c r="L282" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M282" s="8" t="inlineStr">
+      <c r="M282" s="6" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N282" s="8" t="inlineStr">
+      <c r="N282" s="6" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -6657,18 +6665,18 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C283" s="8" t="inlineStr">
+      <c r="C283" s="6" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D283" s="8" t="inlineStr">
+      <c r="D283" s="6" t="inlineStr">
         <is>
           <t>Anifail Perffaith</t>
         </is>
       </c>
       <c r="E283" s="5" t="n"/>
-      <c r="F283" s="8" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave
 A/L - 1/2 Day Annual Leave</t>
@@ -6682,7 +6690,7 @@
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J283" s="8" t="inlineStr">
+      <c r="J283" s="6" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
@@ -6692,17 +6700,17 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L283" s="8" t="inlineStr">
+      <c r="L283" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M283" s="8" t="inlineStr">
+      <c r="M283" s="6" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N283" s="8" t="inlineStr">
+      <c r="N283" s="6" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -6720,7 +6728,7 @@
         </is>
       </c>
       <c r="C284" s="5" t="n"/>
-      <c r="D284" s="8" t="inlineStr">
+      <c r="D284" s="6" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6740,7 +6748,7 @@
 A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="J284" s="8" t="inlineStr">
+      <c r="J284" s="6" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
@@ -6750,7 +6758,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L284" s="8" t="inlineStr">
+      <c r="L284" s="6" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
@@ -6760,67 +6768,67 @@
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="N284" s="8" t="inlineStr">
+      <c r="N284" s="6" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="6" t="inlineStr">
+      <c r="A285" s="7" t="inlineStr">
         <is>
           <t>Sat 29 Aug 2026</t>
         </is>
       </c>
-      <c r="B285" s="7" t="n"/>
-      <c r="C285" s="7" t="n"/>
-      <c r="D285" s="7" t="n"/>
-      <c r="E285" s="7" t="n"/>
-      <c r="F285" s="7" t="n"/>
-      <c r="G285" s="8" t="inlineStr">
+      <c r="B285" s="8" t="n"/>
+      <c r="C285" s="8" t="n"/>
+      <c r="D285" s="8" t="n"/>
+      <c r="E285" s="8" t="n"/>
+      <c r="F285" s="8" t="n"/>
+      <c r="G285" s="6" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H285" s="7" t="n"/>
-      <c r="I285" s="7" t="n"/>
-      <c r="J285" s="7" t="n"/>
-      <c r="K285" s="7" t="n"/>
-      <c r="L285" s="7" t="n"/>
-      <c r="M285" s="8" t="inlineStr">
+      <c r="H285" s="8" t="n"/>
+      <c r="I285" s="8" t="n"/>
+      <c r="J285" s="8" t="n"/>
+      <c r="K285" s="8" t="n"/>
+      <c r="L285" s="8" t="n"/>
+      <c r="M285" s="6" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N285" s="8" t="inlineStr">
+      <c r="N285" s="6" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="inlineStr">
+      <c r="A286" s="7" t="inlineStr">
         <is>
           <t>Sun 30 Aug 2026</t>
         </is>
       </c>
-      <c r="B286" s="7" t="n"/>
-      <c r="C286" s="7" t="n"/>
-      <c r="D286" s="7" t="n"/>
-      <c r="E286" s="7" t="n"/>
-      <c r="F286" s="7" t="n"/>
-      <c r="G286" s="7" t="n"/>
-      <c r="H286" s="7" t="n"/>
-      <c r="I286" s="7" t="n"/>
-      <c r="J286" s="7" t="n"/>
-      <c r="K286" s="7" t="n"/>
-      <c r="L286" s="7" t="n"/>
-      <c r="M286" s="8" t="inlineStr">
+      <c r="B286" s="8" t="n"/>
+      <c r="C286" s="8" t="n"/>
+      <c r="D286" s="8" t="n"/>
+      <c r="E286" s="8" t="n"/>
+      <c r="F286" s="8" t="n"/>
+      <c r="G286" s="8" t="n"/>
+      <c r="H286" s="8" t="n"/>
+      <c r="I286" s="8" t="n"/>
+      <c r="J286" s="8" t="n"/>
+      <c r="K286" s="8" t="n"/>
+      <c r="L286" s="8" t="n"/>
+      <c r="M286" s="6" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N286" s="8" t="inlineStr">
+      <c r="N286" s="6" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -6837,7 +6845,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="C287" s="8" t="inlineStr">
+      <c r="C287" s="6" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
@@ -6862,12 +6870,12 @@
         </is>
       </c>
       <c r="J287" s="5" t="n"/>
-      <c r="K287" s="8" t="inlineStr">
+      <c r="K287" s="6" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L287" s="8" t="inlineStr">
+      <c r="L287" s="6" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
@@ -6877,7 +6885,7 @@
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="N287" s="8" t="inlineStr">
+      <c r="N287" s="6" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -6906,12 +6914,12 @@
         </is>
       </c>
       <c r="J288" s="5" t="n"/>
-      <c r="K288" s="8" t="inlineStr">
+      <c r="K288" s="6" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L288" s="8" t="inlineStr">
+      <c r="L288" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
@@ -6921,7 +6929,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N288" s="8" t="inlineStr">
+      <c r="N288" s="6" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -6946,12 +6954,12 @@
         </is>
       </c>
       <c r="J289" s="5" t="n"/>
-      <c r="K289" s="8" t="inlineStr">
+      <c r="K289" s="6" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L289" s="8" t="inlineStr">
+      <c r="L289" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
@@ -6961,7 +6969,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N289" s="8" t="inlineStr">
+      <c r="N289" s="6" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -6973,7 +6981,7 @@
           <t>Thu 03 Sep 2026</t>
         </is>
       </c>
-      <c r="B290" s="8" t="inlineStr">
+      <c r="B290" s="6" t="inlineStr">
         <is>
           <t>Linda Wilson</t>
         </is>
@@ -6982,24 +6990,24 @@
       <c r="D290" s="5" t="n"/>
       <c r="E290" s="5" t="n"/>
       <c r="F290" s="5" t="n"/>
-      <c r="G290" s="8" t="inlineStr">
+      <c r="G290" s="6" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
       <c r="H290" s="5" t="n"/>
-      <c r="I290" s="8" t="inlineStr">
+      <c r="I290" s="6" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
       <c r="J290" s="5" t="n"/>
-      <c r="K290" s="8" t="inlineStr">
+      <c r="K290" s="6" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L290" s="8" t="inlineStr">
+      <c r="L290" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
@@ -7009,7 +7017,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N290" s="8" t="inlineStr">
+      <c r="N290" s="6" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -7021,7 +7029,7 @@
           <t>Fri 04 Sep 2026</t>
         </is>
       </c>
-      <c r="B291" s="8" t="inlineStr">
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>Linda Wilson</t>
         </is>
@@ -7043,7 +7051,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L291" s="8" t="inlineStr">
+      <c r="L291" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
@@ -7053,51 +7061,51 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N291" s="8" t="inlineStr">
+      <c r="N291" s="6" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="6" t="inlineStr">
+      <c r="A292" s="7" t="inlineStr">
         <is>
           <t>Sat 05 Sep 2026</t>
         </is>
       </c>
-      <c r="B292" s="7" t="n"/>
-      <c r="C292" s="7" t="n"/>
-      <c r="D292" s="7" t="n"/>
-      <c r="E292" s="7" t="n"/>
-      <c r="F292" s="7" t="n"/>
-      <c r="G292" s="7" t="n"/>
-      <c r="H292" s="7" t="n"/>
-      <c r="I292" s="7" t="n"/>
-      <c r="J292" s="7" t="n"/>
-      <c r="K292" s="7" t="n"/>
-      <c r="L292" s="7" t="n"/>
-      <c r="M292" s="7" t="n"/>
-      <c r="N292" s="7" t="n"/>
+      <c r="B292" s="8" t="n"/>
+      <c r="C292" s="8" t="n"/>
+      <c r="D292" s="8" t="n"/>
+      <c r="E292" s="8" t="n"/>
+      <c r="F292" s="8" t="n"/>
+      <c r="G292" s="8" t="n"/>
+      <c r="H292" s="8" t="n"/>
+      <c r="I292" s="8" t="n"/>
+      <c r="J292" s="8" t="n"/>
+      <c r="K292" s="8" t="n"/>
+      <c r="L292" s="8" t="n"/>
+      <c r="M292" s="8" t="n"/>
+      <c r="N292" s="8" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
+      <c r="A293" s="7" t="inlineStr">
         <is>
           <t>Sun 06 Sep 2026</t>
         </is>
       </c>
-      <c r="B293" s="7" t="n"/>
-      <c r="C293" s="7" t="n"/>
-      <c r="D293" s="7" t="n"/>
-      <c r="E293" s="7" t="n"/>
-      <c r="F293" s="7" t="n"/>
-      <c r="G293" s="7" t="n"/>
-      <c r="H293" s="7" t="n"/>
-      <c r="I293" s="7" t="n"/>
-      <c r="J293" s="7" t="n"/>
-      <c r="K293" s="7" t="n"/>
-      <c r="L293" s="7" t="n"/>
-      <c r="M293" s="7" t="n"/>
-      <c r="N293" s="7" t="n"/>
+      <c r="B293" s="8" t="n"/>
+      <c r="C293" s="8" t="n"/>
+      <c r="D293" s="8" t="n"/>
+      <c r="E293" s="8" t="n"/>
+      <c r="F293" s="8" t="n"/>
+      <c r="G293" s="8" t="n"/>
+      <c r="H293" s="8" t="n"/>
+      <c r="I293" s="8" t="n"/>
+      <c r="J293" s="8" t="n"/>
+      <c r="K293" s="8" t="n"/>
+      <c r="L293" s="8" t="n"/>
+      <c r="M293" s="8" t="n"/>
+      <c r="N293" s="8" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -7112,7 +7120,7 @@
       <c r="F294" s="5" t="n"/>
       <c r="G294" s="5" t="n"/>
       <c r="H294" s="5" t="n"/>
-      <c r="I294" s="8" t="inlineStr">
+      <c r="I294" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -7123,7 +7131,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L294" s="8" t="inlineStr">
+      <c r="L294" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7133,7 +7141,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N294" s="8" t="inlineStr">
+      <c r="N294" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7152,18 +7160,18 @@
       <c r="F295" s="5" t="n"/>
       <c r="G295" s="5" t="n"/>
       <c r="H295" s="5" t="n"/>
-      <c r="I295" s="8" t="inlineStr">
+      <c r="I295" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J295" s="5" t="n"/>
-      <c r="K295" s="8" t="inlineStr">
+      <c r="K295" s="6" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L295" s="8" t="inlineStr">
+      <c r="L295" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7173,7 +7181,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N295" s="8" t="inlineStr">
+      <c r="N295" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7192,18 +7200,18 @@
       <c r="F296" s="5" t="n"/>
       <c r="G296" s="5" t="n"/>
       <c r="H296" s="5" t="n"/>
-      <c r="I296" s="8" t="inlineStr">
+      <c r="I296" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J296" s="5" t="n"/>
-      <c r="K296" s="8" t="inlineStr">
+      <c r="K296" s="6" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L296" s="8" t="inlineStr">
+      <c r="L296" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7213,7 +7221,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N296" s="8" t="inlineStr">
+      <c r="N296" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7232,18 +7240,18 @@
       <c r="F297" s="5" t="n"/>
       <c r="G297" s="5" t="n"/>
       <c r="H297" s="5" t="n"/>
-      <c r="I297" s="8" t="inlineStr">
+      <c r="I297" s="6" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
       <c r="J297" s="5" t="n"/>
-      <c r="K297" s="8" t="inlineStr">
+      <c r="K297" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
       </c>
-      <c r="L297" s="8" t="inlineStr">
+      <c r="L297" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7253,7 +7261,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N297" s="8" t="inlineStr">
+      <c r="N297" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7272,14 +7280,14 @@
       <c r="F298" s="5" t="n"/>
       <c r="G298" s="5" t="n"/>
       <c r="H298" s="5" t="n"/>
-      <c r="I298" s="8" t="inlineStr">
+      <c r="I298" s="6" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
       <c r="J298" s="5" t="n"/>
       <c r="K298" s="5" t="n"/>
-      <c r="L298" s="8" t="inlineStr">
+      <c r="L298" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7289,51 +7297,51 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N298" s="8" t="inlineStr">
+      <c r="N298" s="6" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr">
+      <c r="A299" s="7" t="inlineStr">
         <is>
           <t>Sat 12 Sep 2026</t>
         </is>
       </c>
-      <c r="B299" s="7" t="n"/>
-      <c r="C299" s="7" t="n"/>
-      <c r="D299" s="7" t="n"/>
-      <c r="E299" s="7" t="n"/>
-      <c r="F299" s="7" t="n"/>
-      <c r="G299" s="7" t="n"/>
-      <c r="H299" s="7" t="n"/>
-      <c r="I299" s="7" t="n"/>
-      <c r="J299" s="7" t="n"/>
-      <c r="K299" s="7" t="n"/>
-      <c r="L299" s="7" t="n"/>
-      <c r="M299" s="7" t="n"/>
-      <c r="N299" s="7" t="n"/>
+      <c r="B299" s="8" t="n"/>
+      <c r="C299" s="8" t="n"/>
+      <c r="D299" s="8" t="n"/>
+      <c r="E299" s="8" t="n"/>
+      <c r="F299" s="8" t="n"/>
+      <c r="G299" s="8" t="n"/>
+      <c r="H299" s="8" t="n"/>
+      <c r="I299" s="8" t="n"/>
+      <c r="J299" s="8" t="n"/>
+      <c r="K299" s="8" t="n"/>
+      <c r="L299" s="8" t="n"/>
+      <c r="M299" s="8" t="n"/>
+      <c r="N299" s="8" t="n"/>
     </row>
     <row r="300">
-      <c r="A300" s="6" t="inlineStr">
+      <c r="A300" s="7" t="inlineStr">
         <is>
           <t>Sun 13 Sep 2026</t>
         </is>
       </c>
-      <c r="B300" s="7" t="n"/>
-      <c r="C300" s="7" t="n"/>
-      <c r="D300" s="7" t="n"/>
-      <c r="E300" s="7" t="n"/>
-      <c r="F300" s="7" t="n"/>
-      <c r="G300" s="7" t="n"/>
-      <c r="H300" s="7" t="n"/>
-      <c r="I300" s="7" t="n"/>
-      <c r="J300" s="7" t="n"/>
-      <c r="K300" s="7" t="n"/>
-      <c r="L300" s="7" t="n"/>
-      <c r="M300" s="7" t="n"/>
-      <c r="N300" s="7" t="n"/>
+      <c r="B300" s="8" t="n"/>
+      <c r="C300" s="8" t="n"/>
+      <c r="D300" s="8" t="n"/>
+      <c r="E300" s="8" t="n"/>
+      <c r="F300" s="8" t="n"/>
+      <c r="G300" s="8" t="n"/>
+      <c r="H300" s="8" t="n"/>
+      <c r="I300" s="8" t="n"/>
+      <c r="J300" s="8" t="n"/>
+      <c r="K300" s="8" t="n"/>
+      <c r="L300" s="8" t="n"/>
+      <c r="M300" s="8" t="n"/>
+      <c r="N300" s="8" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -7352,7 +7360,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I301" s="8" t="inlineStr">
+      <c r="I301" s="6" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
@@ -7384,7 +7392,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I302" s="8" t="inlineStr">
+      <c r="I302" s="6" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
@@ -7427,20 +7435,20 @@
       </c>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="5" t="n"/>
-      <c r="D304" s="8" t="inlineStr">
+      <c r="D304" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E304" s="5" t="n"/>
-      <c r="F304" s="8" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G304" s="5" t="n"/>
       <c r="H304" s="5" t="n"/>
-      <c r="I304" s="8" t="inlineStr">
+      <c r="I304" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7449,7 +7457,7 @@
       <c r="K304" s="5" t="n"/>
       <c r="L304" s="5" t="n"/>
       <c r="M304" s="5" t="n"/>
-      <c r="N304" s="8" t="inlineStr">
+      <c r="N304" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7463,20 +7471,20 @@
       </c>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="5" t="n"/>
-      <c r="D305" s="8" t="inlineStr">
+      <c r="D305" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E305" s="5" t="n"/>
-      <c r="F305" s="8" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G305" s="5" t="n"/>
       <c r="H305" s="5" t="n"/>
-      <c r="I305" s="8" t="inlineStr">
+      <c r="I305" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7485,51 +7493,51 @@
       <c r="K305" s="5" t="n"/>
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="5" t="n"/>
-      <c r="N305" s="8" t="inlineStr">
+      <c r="N305" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="6" t="inlineStr">
+      <c r="A306" s="7" t="inlineStr">
         <is>
           <t>Sat 19 Sep 2026</t>
         </is>
       </c>
-      <c r="B306" s="7" t="n"/>
-      <c r="C306" s="7" t="n"/>
-      <c r="D306" s="7" t="n"/>
-      <c r="E306" s="7" t="n"/>
-      <c r="F306" s="7" t="n"/>
-      <c r="G306" s="7" t="n"/>
-      <c r="H306" s="7" t="n"/>
-      <c r="I306" s="7" t="n"/>
-      <c r="J306" s="7" t="n"/>
-      <c r="K306" s="7" t="n"/>
-      <c r="L306" s="7" t="n"/>
-      <c r="M306" s="7" t="n"/>
-      <c r="N306" s="7" t="n"/>
+      <c r="B306" s="8" t="n"/>
+      <c r="C306" s="8" t="n"/>
+      <c r="D306" s="8" t="n"/>
+      <c r="E306" s="8" t="n"/>
+      <c r="F306" s="8" t="n"/>
+      <c r="G306" s="8" t="n"/>
+      <c r="H306" s="8" t="n"/>
+      <c r="I306" s="8" t="n"/>
+      <c r="J306" s="8" t="n"/>
+      <c r="K306" s="8" t="n"/>
+      <c r="L306" s="8" t="n"/>
+      <c r="M306" s="8" t="n"/>
+      <c r="N306" s="8" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="inlineStr">
+      <c r="A307" s="7" t="inlineStr">
         <is>
           <t>Sun 20 Sep 2026</t>
         </is>
       </c>
-      <c r="B307" s="7" t="n"/>
-      <c r="C307" s="7" t="n"/>
-      <c r="D307" s="7" t="n"/>
-      <c r="E307" s="7" t="n"/>
-      <c r="F307" s="7" t="n"/>
-      <c r="G307" s="7" t="n"/>
-      <c r="H307" s="7" t="n"/>
-      <c r="I307" s="7" t="n"/>
-      <c r="J307" s="7" t="n"/>
-      <c r="K307" s="7" t="n"/>
-      <c r="L307" s="7" t="n"/>
-      <c r="M307" s="7" t="n"/>
-      <c r="N307" s="7" t="n"/>
+      <c r="B307" s="8" t="n"/>
+      <c r="C307" s="8" t="n"/>
+      <c r="D307" s="8" t="n"/>
+      <c r="E307" s="8" t="n"/>
+      <c r="F307" s="8" t="n"/>
+      <c r="G307" s="8" t="n"/>
+      <c r="H307" s="8" t="n"/>
+      <c r="I307" s="8" t="n"/>
+      <c r="J307" s="8" t="n"/>
+      <c r="K307" s="8" t="n"/>
+      <c r="L307" s="8" t="n"/>
+      <c r="M307" s="8" t="n"/>
+      <c r="N307" s="8" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -7539,33 +7547,33 @@
       </c>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="5" t="n"/>
-      <c r="D308" s="8" t="inlineStr">
+      <c r="D308" s="6" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E308" s="5" t="n"/>
-      <c r="F308" s="8" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G308" s="5" t="n"/>
       <c r="H308" s="5" t="n"/>
-      <c r="I308" s="8" t="inlineStr">
+      <c r="I308" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J308" s="5" t="n"/>
-      <c r="K308" s="8" t="inlineStr">
+      <c r="K308" s="6" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L308" s="5" t="n"/>
       <c r="M308" s="5" t="n"/>
-      <c r="N308" s="8" t="inlineStr">
+      <c r="N308" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7579,26 +7587,26 @@
       </c>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="5" t="n"/>
-      <c r="D309" s="8" t="inlineStr">
+      <c r="D309" s="6" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E309" s="5" t="n"/>
-      <c r="F309" s="8" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G309" s="5" t="n"/>
       <c r="H309" s="5" t="n"/>
-      <c r="I309" s="8" t="inlineStr">
+      <c r="I309" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J309" s="5" t="n"/>
-      <c r="K309" s="8" t="inlineStr">
+      <c r="K309" s="6" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
@@ -7609,7 +7617,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N309" s="8" t="inlineStr">
+      <c r="N309" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7623,26 +7631,26 @@
       </c>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="5" t="n"/>
-      <c r="D310" s="8" t="inlineStr">
+      <c r="D310" s="6" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E310" s="5" t="n"/>
-      <c r="F310" s="8" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G310" s="5" t="n"/>
       <c r="H310" s="5" t="n"/>
-      <c r="I310" s="8" t="inlineStr">
+      <c r="I310" s="6" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J310" s="5" t="n"/>
-      <c r="K310" s="8" t="inlineStr">
+      <c r="K310" s="6" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
@@ -7653,7 +7661,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N310" s="8" t="inlineStr">
+      <c r="N310" s="6" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7667,26 +7675,26 @@
       </c>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="5" t="n"/>
-      <c r="D311" s="8" t="inlineStr">
+      <c r="D311" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E311" s="5" t="n"/>
-      <c r="F311" s="8" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G311" s="5" t="n"/>
       <c r="H311" s="5" t="n"/>
-      <c r="I311" s="8" t="inlineStr">
+      <c r="I311" s="6" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
       <c r="J311" s="5" t="n"/>
-      <c r="K311" s="8" t="inlineStr">
+      <c r="K311" s="6" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
@@ -7697,7 +7705,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N311" s="8" t="inlineStr">
+      <c r="N311" s="6" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -7711,13 +7719,13 @@
       </c>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="5" t="n"/>
-      <c r="D312" s="8" t="inlineStr">
+      <c r="D312" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E312" s="5" t="n"/>
-      <c r="F312" s="8" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7728,13 +7736,13 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I312" s="8" t="inlineStr">
+      <c r="I312" s="6" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
       <c r="J312" s="5" t="n"/>
-      <c r="K312" s="8" t="inlineStr">
+      <c r="K312" s="6" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
@@ -7745,51 +7753,51 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N312" s="8" t="inlineStr">
+      <c r="N312" s="6" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="6" t="inlineStr">
+      <c r="A313" s="7" t="inlineStr">
         <is>
           <t>Sat 26 Sep 2026</t>
         </is>
       </c>
-      <c r="B313" s="7" t="n"/>
-      <c r="C313" s="7" t="n"/>
-      <c r="D313" s="7" t="n"/>
-      <c r="E313" s="7" t="n"/>
-      <c r="F313" s="7" t="n"/>
-      <c r="G313" s="7" t="n"/>
-      <c r="H313" s="7" t="n"/>
-      <c r="I313" s="7" t="n"/>
-      <c r="J313" s="7" t="n"/>
-      <c r="K313" s="7" t="n"/>
-      <c r="L313" s="7" t="n"/>
-      <c r="M313" s="7" t="n"/>
-      <c r="N313" s="7" t="n"/>
+      <c r="B313" s="8" t="n"/>
+      <c r="C313" s="8" t="n"/>
+      <c r="D313" s="8" t="n"/>
+      <c r="E313" s="8" t="n"/>
+      <c r="F313" s="8" t="n"/>
+      <c r="G313" s="8" t="n"/>
+      <c r="H313" s="8" t="n"/>
+      <c r="I313" s="8" t="n"/>
+      <c r="J313" s="8" t="n"/>
+      <c r="K313" s="8" t="n"/>
+      <c r="L313" s="8" t="n"/>
+      <c r="M313" s="8" t="n"/>
+      <c r="N313" s="8" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="6" t="inlineStr">
+      <c r="A314" s="7" t="inlineStr">
         <is>
           <t>Sun 27 Sep 2026</t>
         </is>
       </c>
-      <c r="B314" s="7" t="n"/>
-      <c r="C314" s="7" t="n"/>
-      <c r="D314" s="7" t="n"/>
-      <c r="E314" s="7" t="n"/>
-      <c r="F314" s="7" t="n"/>
-      <c r="G314" s="7" t="n"/>
-      <c r="H314" s="7" t="n"/>
-      <c r="I314" s="7" t="n"/>
-      <c r="J314" s="7" t="n"/>
-      <c r="K314" s="7" t="n"/>
-      <c r="L314" s="7" t="n"/>
-      <c r="M314" s="7" t="n"/>
-      <c r="N314" s="7" t="n"/>
+      <c r="B314" s="8" t="n"/>
+      <c r="C314" s="8" t="n"/>
+      <c r="D314" s="8" t="n"/>
+      <c r="E314" s="8" t="n"/>
+      <c r="F314" s="8" t="n"/>
+      <c r="G314" s="8" t="n"/>
+      <c r="H314" s="8" t="n"/>
+      <c r="I314" s="8" t="n"/>
+      <c r="J314" s="8" t="n"/>
+      <c r="K314" s="8" t="n"/>
+      <c r="L314" s="8" t="n"/>
+      <c r="M314" s="8" t="n"/>
+      <c r="N314" s="8" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -7799,13 +7807,13 @@
       </c>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="5" t="n"/>
-      <c r="D315" s="8" t="inlineStr">
+      <c r="D315" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E315" s="5" t="n"/>
-      <c r="F315" s="8" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7816,7 +7824,7 @@
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="I315" s="8" t="inlineStr">
+      <c r="I315" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7829,7 +7837,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N315" s="8" t="inlineStr">
+      <c r="N315" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7843,20 +7851,20 @@
       </c>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="5" t="n"/>
-      <c r="D316" s="8" t="inlineStr">
+      <c r="D316" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E316" s="5" t="n"/>
-      <c r="F316" s="8" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G316" s="5" t="n"/>
       <c r="H316" s="5" t="n"/>
-      <c r="I316" s="8" t="inlineStr">
+      <c r="I316" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7869,7 +7877,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N316" s="8" t="inlineStr">
+      <c r="N316" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7883,20 +7891,20 @@
       </c>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="5" t="n"/>
-      <c r="D317" s="8" t="inlineStr">
+      <c r="D317" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E317" s="5" t="n"/>
-      <c r="F317" s="8" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G317" s="5" t="n"/>
       <c r="H317" s="5" t="n"/>
-      <c r="I317" s="8" t="inlineStr">
+      <c r="I317" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7909,7 +7917,7 @@
         </is>
       </c>
       <c r="M317" s="5" t="n"/>
-      <c r="N317" s="8" t="inlineStr">
+      <c r="N317" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7923,20 +7931,20 @@
       </c>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="5" t="n"/>
-      <c r="D318" s="8" t="inlineStr">
+      <c r="D318" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E318" s="5" t="n"/>
-      <c r="F318" s="8" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G318" s="5" t="n"/>
       <c r="H318" s="5" t="n"/>
-      <c r="I318" s="8" t="inlineStr">
+      <c r="I318" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7949,7 +7957,7 @@
         </is>
       </c>
       <c r="M318" s="5" t="n"/>
-      <c r="N318" s="8" t="inlineStr">
+      <c r="N318" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7961,55 +7969,55 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B319" s="8" t="inlineStr">
+      <c r="B319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="C319" s="8" t="inlineStr">
+      <c r="C319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="D319" s="8" t="inlineStr">
+      <c r="D319" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="E319" s="8" t="inlineStr">
+      <c r="E319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="F319" s="8" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="G319" s="8" t="inlineStr">
+      <c r="G319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="H319" s="8" t="inlineStr">
+      <c r="H319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="I319" s="8" t="inlineStr">
+      <c r="I319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J319" s="8" t="inlineStr">
+      <c r="J319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="K319" s="8" t="inlineStr">
+      <c r="K319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
@@ -8020,12 +8028,12 @@
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="M319" s="8" t="inlineStr">
+      <c r="M319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="N319" s="8" t="inlineStr">
+      <c r="N319" s="6" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
@@ -8033,44 +8041,44 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr">
+      <c r="A320" s="7" t="inlineStr">
         <is>
           <t>Sat 03 Oct 2026</t>
         </is>
       </c>
-      <c r="B320" s="7" t="n"/>
-      <c r="C320" s="7" t="n"/>
-      <c r="D320" s="7" t="n"/>
-      <c r="E320" s="7" t="n"/>
-      <c r="F320" s="7" t="n"/>
-      <c r="G320" s="7" t="n"/>
-      <c r="H320" s="7" t="n"/>
-      <c r="I320" s="7" t="n"/>
-      <c r="J320" s="7" t="n"/>
-      <c r="K320" s="7" t="n"/>
-      <c r="L320" s="7" t="n"/>
-      <c r="M320" s="7" t="n"/>
-      <c r="N320" s="7" t="n"/>
+      <c r="B320" s="8" t="n"/>
+      <c r="C320" s="8" t="n"/>
+      <c r="D320" s="8" t="n"/>
+      <c r="E320" s="8" t="n"/>
+      <c r="F320" s="8" t="n"/>
+      <c r="G320" s="8" t="n"/>
+      <c r="H320" s="8" t="n"/>
+      <c r="I320" s="8" t="n"/>
+      <c r="J320" s="8" t="n"/>
+      <c r="K320" s="8" t="n"/>
+      <c r="L320" s="8" t="n"/>
+      <c r="M320" s="8" t="n"/>
+      <c r="N320" s="8" t="n"/>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr">
+      <c r="A321" s="7" t="inlineStr">
         <is>
           <t>Sun 04 Oct 2026</t>
         </is>
       </c>
-      <c r="B321" s="7" t="n"/>
-      <c r="C321" s="7" t="n"/>
-      <c r="D321" s="7" t="n"/>
-      <c r="E321" s="7" t="n"/>
-      <c r="F321" s="7" t="n"/>
-      <c r="G321" s="7" t="n"/>
-      <c r="H321" s="7" t="n"/>
-      <c r="I321" s="7" t="n"/>
-      <c r="J321" s="7" t="n"/>
-      <c r="K321" s="7" t="n"/>
-      <c r="L321" s="7" t="n"/>
-      <c r="M321" s="7" t="n"/>
-      <c r="N321" s="7" t="n"/>
+      <c r="B321" s="8" t="n"/>
+      <c r="C321" s="8" t="n"/>
+      <c r="D321" s="8" t="n"/>
+      <c r="E321" s="8" t="n"/>
+      <c r="F321" s="8" t="n"/>
+      <c r="G321" s="8" t="n"/>
+      <c r="H321" s="8" t="n"/>
+      <c r="I321" s="8" t="n"/>
+      <c r="J321" s="8" t="n"/>
+      <c r="K321" s="8" t="n"/>
+      <c r="L321" s="8" t="n"/>
+      <c r="M321" s="8" t="n"/>
+      <c r="N321" s="8" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -8197,52 +8205,52 @@
       <c r="N326" s="5" t="n"/>
     </row>
     <row r="327">
-      <c r="A327" s="6" t="inlineStr">
+      <c r="A327" s="7" t="inlineStr">
         <is>
           <t>Sat 10 Oct 2026</t>
         </is>
       </c>
-      <c r="B327" s="7" t="n"/>
-      <c r="C327" s="7" t="n"/>
-      <c r="D327" s="7" t="n"/>
+      <c r="B327" s="8" t="n"/>
+      <c r="C327" s="8" t="n"/>
+      <c r="D327" s="8" t="n"/>
       <c r="E327" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F327" s="7" t="n"/>
-      <c r="G327" s="7" t="n"/>
-      <c r="H327" s="7" t="n"/>
-      <c r="I327" s="7" t="n"/>
-      <c r="J327" s="7" t="n"/>
-      <c r="K327" s="7" t="n"/>
-      <c r="L327" s="7" t="n"/>
-      <c r="M327" s="7" t="n"/>
-      <c r="N327" s="7" t="n"/>
+      <c r="F327" s="8" t="n"/>
+      <c r="G327" s="8" t="n"/>
+      <c r="H327" s="8" t="n"/>
+      <c r="I327" s="8" t="n"/>
+      <c r="J327" s="8" t="n"/>
+      <c r="K327" s="8" t="n"/>
+      <c r="L327" s="8" t="n"/>
+      <c r="M327" s="8" t="n"/>
+      <c r="N327" s="8" t="n"/>
     </row>
     <row r="328">
-      <c r="A328" s="6" t="inlineStr">
+      <c r="A328" s="7" t="inlineStr">
         <is>
           <t>Sun 11 Oct 2026</t>
         </is>
       </c>
-      <c r="B328" s="7" t="n"/>
-      <c r="C328" s="7" t="n"/>
-      <c r="D328" s="7" t="n"/>
+      <c r="B328" s="8" t="n"/>
+      <c r="C328" s="8" t="n"/>
+      <c r="D328" s="8" t="n"/>
       <c r="E328" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F328" s="7" t="n"/>
-      <c r="G328" s="7" t="n"/>
-      <c r="H328" s="7" t="n"/>
-      <c r="I328" s="7" t="n"/>
-      <c r="J328" s="7" t="n"/>
-      <c r="K328" s="7" t="n"/>
-      <c r="L328" s="7" t="n"/>
-      <c r="M328" s="7" t="n"/>
-      <c r="N328" s="7" t="n"/>
+      <c r="F328" s="8" t="n"/>
+      <c r="G328" s="8" t="n"/>
+      <c r="H328" s="8" t="n"/>
+      <c r="I328" s="8" t="n"/>
+      <c r="J328" s="8" t="n"/>
+      <c r="K328" s="8" t="n"/>
+      <c r="L328" s="8" t="n"/>
+      <c r="M328" s="8" t="n"/>
+      <c r="N328" s="8" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -8433,52 +8441,52 @@
       <c r="N333" s="5" t="n"/>
     </row>
     <row r="334">
-      <c r="A334" s="6" t="inlineStr">
+      <c r="A334" s="7" t="inlineStr">
         <is>
           <t>Sat 17 Oct 2026</t>
         </is>
       </c>
-      <c r="B334" s="7" t="n"/>
-      <c r="C334" s="7" t="n"/>
-      <c r="D334" s="7" t="n"/>
+      <c r="B334" s="8" t="n"/>
+      <c r="C334" s="8" t="n"/>
+      <c r="D334" s="8" t="n"/>
       <c r="E334" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F334" s="7" t="n"/>
-      <c r="G334" s="7" t="n"/>
-      <c r="H334" s="7" t="n"/>
-      <c r="I334" s="7" t="n"/>
-      <c r="J334" s="7" t="n"/>
-      <c r="K334" s="7" t="n"/>
-      <c r="L334" s="7" t="n"/>
-      <c r="M334" s="7" t="n"/>
-      <c r="N334" s="7" t="n"/>
+      <c r="F334" s="8" t="n"/>
+      <c r="G334" s="8" t="n"/>
+      <c r="H334" s="8" t="n"/>
+      <c r="I334" s="8" t="n"/>
+      <c r="J334" s="8" t="n"/>
+      <c r="K334" s="8" t="n"/>
+      <c r="L334" s="8" t="n"/>
+      <c r="M334" s="8" t="n"/>
+      <c r="N334" s="8" t="n"/>
     </row>
     <row r="335">
-      <c r="A335" s="6" t="inlineStr">
+      <c r="A335" s="7" t="inlineStr">
         <is>
           <t>Sun 18 Oct 2026</t>
         </is>
       </c>
-      <c r="B335" s="7" t="n"/>
-      <c r="C335" s="7" t="n"/>
-      <c r="D335" s="7" t="n"/>
+      <c r="B335" s="8" t="n"/>
+      <c r="C335" s="8" t="n"/>
+      <c r="D335" s="8" t="n"/>
       <c r="E335" s="10" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="F335" s="7" t="n"/>
-      <c r="G335" s="7" t="n"/>
-      <c r="H335" s="7" t="n"/>
-      <c r="I335" s="7" t="n"/>
-      <c r="J335" s="7" t="n"/>
-      <c r="K335" s="7" t="n"/>
-      <c r="L335" s="7" t="n"/>
-      <c r="M335" s="7" t="n"/>
-      <c r="N335" s="7" t="n"/>
+      <c r="F335" s="8" t="n"/>
+      <c r="G335" s="8" t="n"/>
+      <c r="H335" s="8" t="n"/>
+      <c r="I335" s="8" t="n"/>
+      <c r="J335" s="8" t="n"/>
+      <c r="K335" s="8" t="n"/>
+      <c r="L335" s="8" t="n"/>
+      <c r="M335" s="8" t="n"/>
+      <c r="N335" s="8" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
@@ -8645,44 +8653,44 @@
       <c r="N340" s="5" t="n"/>
     </row>
     <row r="341">
-      <c r="A341" s="6" t="inlineStr">
+      <c r="A341" s="7" t="inlineStr">
         <is>
           <t>Sat 24 Oct 2026</t>
         </is>
       </c>
-      <c r="B341" s="7" t="n"/>
-      <c r="C341" s="7" t="n"/>
-      <c r="D341" s="7" t="n"/>
-      <c r="E341" s="7" t="n"/>
-      <c r="F341" s="7" t="n"/>
-      <c r="G341" s="7" t="n"/>
-      <c r="H341" s="7" t="n"/>
-      <c r="I341" s="7" t="n"/>
-      <c r="J341" s="7" t="n"/>
-      <c r="K341" s="7" t="n"/>
-      <c r="L341" s="7" t="n"/>
-      <c r="M341" s="7" t="n"/>
-      <c r="N341" s="7" t="n"/>
+      <c r="B341" s="8" t="n"/>
+      <c r="C341" s="8" t="n"/>
+      <c r="D341" s="8" t="n"/>
+      <c r="E341" s="8" t="n"/>
+      <c r="F341" s="8" t="n"/>
+      <c r="G341" s="8" t="n"/>
+      <c r="H341" s="8" t="n"/>
+      <c r="I341" s="8" t="n"/>
+      <c r="J341" s="8" t="n"/>
+      <c r="K341" s="8" t="n"/>
+      <c r="L341" s="8" t="n"/>
+      <c r="M341" s="8" t="n"/>
+      <c r="N341" s="8" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="6" t="inlineStr">
+      <c r="A342" s="7" t="inlineStr">
         <is>
           <t>Sun 25 Oct 2026</t>
         </is>
       </c>
-      <c r="B342" s="7" t="n"/>
-      <c r="C342" s="7" t="n"/>
-      <c r="D342" s="7" t="n"/>
-      <c r="E342" s="7" t="n"/>
-      <c r="F342" s="7" t="n"/>
-      <c r="G342" s="7" t="n"/>
-      <c r="H342" s="7" t="n"/>
-      <c r="I342" s="7" t="n"/>
-      <c r="J342" s="7" t="n"/>
-      <c r="K342" s="7" t="n"/>
-      <c r="L342" s="7" t="n"/>
-      <c r="M342" s="7" t="n"/>
-      <c r="N342" s="7" t="n"/>
+      <c r="B342" s="8" t="n"/>
+      <c r="C342" s="8" t="n"/>
+      <c r="D342" s="8" t="n"/>
+      <c r="E342" s="8" t="n"/>
+      <c r="F342" s="8" t="n"/>
+      <c r="G342" s="8" t="n"/>
+      <c r="H342" s="8" t="n"/>
+      <c r="I342" s="8" t="n"/>
+      <c r="J342" s="8" t="n"/>
+      <c r="K342" s="8" t="n"/>
+      <c r="L342" s="8" t="n"/>
+      <c r="M342" s="8" t="n"/>
+      <c r="N342" s="8" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -8825,44 +8833,44 @@
       <c r="N347" s="5" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="6" t="inlineStr">
+      <c r="A348" s="7" t="inlineStr">
         <is>
           <t>Sat 31 Oct 2026</t>
         </is>
       </c>
-      <c r="B348" s="7" t="n"/>
-      <c r="C348" s="7" t="n"/>
-      <c r="D348" s="7" t="n"/>
-      <c r="E348" s="7" t="n"/>
-      <c r="F348" s="7" t="n"/>
-      <c r="G348" s="7" t="n"/>
-      <c r="H348" s="7" t="n"/>
-      <c r="I348" s="7" t="n"/>
-      <c r="J348" s="7" t="n"/>
-      <c r="K348" s="7" t="n"/>
-      <c r="L348" s="7" t="n"/>
-      <c r="M348" s="7" t="n"/>
-      <c r="N348" s="7" t="n"/>
+      <c r="B348" s="8" t="n"/>
+      <c r="C348" s="8" t="n"/>
+      <c r="D348" s="8" t="n"/>
+      <c r="E348" s="8" t="n"/>
+      <c r="F348" s="8" t="n"/>
+      <c r="G348" s="8" t="n"/>
+      <c r="H348" s="8" t="n"/>
+      <c r="I348" s="8" t="n"/>
+      <c r="J348" s="8" t="n"/>
+      <c r="K348" s="8" t="n"/>
+      <c r="L348" s="8" t="n"/>
+      <c r="M348" s="8" t="n"/>
+      <c r="N348" s="8" t="n"/>
     </row>
     <row r="349">
-      <c r="A349" s="6" t="inlineStr">
+      <c r="A349" s="7" t="inlineStr">
         <is>
           <t>Sun 01 Nov 2026</t>
         </is>
       </c>
-      <c r="B349" s="7" t="n"/>
-      <c r="C349" s="7" t="n"/>
-      <c r="D349" s="7" t="n"/>
-      <c r="E349" s="7" t="n"/>
-      <c r="F349" s="7" t="n"/>
-      <c r="G349" s="7" t="n"/>
-      <c r="H349" s="7" t="n"/>
-      <c r="I349" s="7" t="n"/>
-      <c r="J349" s="7" t="n"/>
-      <c r="K349" s="7" t="n"/>
-      <c r="L349" s="7" t="n"/>
-      <c r="M349" s="7" t="n"/>
-      <c r="N349" s="7" t="n"/>
+      <c r="B349" s="8" t="n"/>
+      <c r="C349" s="8" t="n"/>
+      <c r="D349" s="8" t="n"/>
+      <c r="E349" s="8" t="n"/>
+      <c r="F349" s="8" t="n"/>
+      <c r="G349" s="8" t="n"/>
+      <c r="H349" s="8" t="n"/>
+      <c r="I349" s="8" t="n"/>
+      <c r="J349" s="8" t="n"/>
+      <c r="K349" s="8" t="n"/>
+      <c r="L349" s="8" t="n"/>
+      <c r="M349" s="8" t="n"/>
+      <c r="N349" s="8" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
@@ -8989,7 +8997,7 @@
       <c r="F354" s="5" t="n"/>
       <c r="G354" s="5" t="n"/>
       <c r="H354" s="5" t="n"/>
-      <c r="I354" s="8" t="inlineStr">
+      <c r="I354" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9009,44 +9017,44 @@
       <c r="N354" s="5" t="n"/>
     </row>
     <row r="355">
-      <c r="A355" s="6" t="inlineStr">
+      <c r="A355" s="7" t="inlineStr">
         <is>
           <t>Sat 07 Nov 2026</t>
         </is>
       </c>
-      <c r="B355" s="7" t="n"/>
-      <c r="C355" s="7" t="n"/>
-      <c r="D355" s="7" t="n"/>
-      <c r="E355" s="7" t="n"/>
-      <c r="F355" s="7" t="n"/>
-      <c r="G355" s="7" t="n"/>
-      <c r="H355" s="7" t="n"/>
-      <c r="I355" s="7" t="n"/>
-      <c r="J355" s="7" t="n"/>
-      <c r="K355" s="7" t="n"/>
-      <c r="L355" s="7" t="n"/>
-      <c r="M355" s="7" t="n"/>
-      <c r="N355" s="7" t="n"/>
+      <c r="B355" s="8" t="n"/>
+      <c r="C355" s="8" t="n"/>
+      <c r="D355" s="8" t="n"/>
+      <c r="E355" s="8" t="n"/>
+      <c r="F355" s="8" t="n"/>
+      <c r="G355" s="8" t="n"/>
+      <c r="H355" s="8" t="n"/>
+      <c r="I355" s="8" t="n"/>
+      <c r="J355" s="8" t="n"/>
+      <c r="K355" s="8" t="n"/>
+      <c r="L355" s="8" t="n"/>
+      <c r="M355" s="8" t="n"/>
+      <c r="N355" s="8" t="n"/>
     </row>
     <row r="356">
-      <c r="A356" s="6" t="inlineStr">
+      <c r="A356" s="7" t="inlineStr">
         <is>
           <t>Sun 08 Nov 2026</t>
         </is>
       </c>
-      <c r="B356" s="7" t="n"/>
-      <c r="C356" s="7" t="n"/>
-      <c r="D356" s="7" t="n"/>
-      <c r="E356" s="7" t="n"/>
-      <c r="F356" s="7" t="n"/>
-      <c r="G356" s="7" t="n"/>
-      <c r="H356" s="7" t="n"/>
-      <c r="I356" s="7" t="n"/>
-      <c r="J356" s="7" t="n"/>
-      <c r="K356" s="7" t="n"/>
-      <c r="L356" s="7" t="n"/>
-      <c r="M356" s="7" t="n"/>
-      <c r="N356" s="7" t="n"/>
+      <c r="B356" s="8" t="n"/>
+      <c r="C356" s="8" t="n"/>
+      <c r="D356" s="8" t="n"/>
+      <c r="E356" s="8" t="n"/>
+      <c r="F356" s="8" t="n"/>
+      <c r="G356" s="8" t="n"/>
+      <c r="H356" s="8" t="n"/>
+      <c r="I356" s="8" t="n"/>
+      <c r="J356" s="8" t="n"/>
+      <c r="K356" s="8" t="n"/>
+      <c r="L356" s="8" t="n"/>
+      <c r="M356" s="8" t="n"/>
+      <c r="N356" s="8" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -9065,7 +9073,7 @@
       <c r="F357" s="5" t="n"/>
       <c r="G357" s="5" t="n"/>
       <c r="H357" s="5" t="n"/>
-      <c r="I357" s="8" t="inlineStr">
+      <c r="I357" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9161,7 +9169,7 @@
       <c r="F360" s="5" t="n"/>
       <c r="G360" s="5" t="n"/>
       <c r="H360" s="5" t="n"/>
-      <c r="I360" s="8" t="inlineStr">
+      <c r="I360" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9209,44 +9217,44 @@
       <c r="N361" s="5" t="n"/>
     </row>
     <row r="362">
-      <c r="A362" s="6" t="inlineStr">
+      <c r="A362" s="7" t="inlineStr">
         <is>
           <t>Sat 14 Nov 2026</t>
         </is>
       </c>
-      <c r="B362" s="7" t="n"/>
-      <c r="C362" s="7" t="n"/>
-      <c r="D362" s="7" t="n"/>
-      <c r="E362" s="7" t="n"/>
-      <c r="F362" s="7" t="n"/>
-      <c r="G362" s="7" t="n"/>
-      <c r="H362" s="7" t="n"/>
-      <c r="I362" s="7" t="n"/>
-      <c r="J362" s="7" t="n"/>
-      <c r="K362" s="7" t="n"/>
-      <c r="L362" s="7" t="n"/>
-      <c r="M362" s="7" t="n"/>
-      <c r="N362" s="7" t="n"/>
+      <c r="B362" s="8" t="n"/>
+      <c r="C362" s="8" t="n"/>
+      <c r="D362" s="8" t="n"/>
+      <c r="E362" s="8" t="n"/>
+      <c r="F362" s="8" t="n"/>
+      <c r="G362" s="8" t="n"/>
+      <c r="H362" s="8" t="n"/>
+      <c r="I362" s="8" t="n"/>
+      <c r="J362" s="8" t="n"/>
+      <c r="K362" s="8" t="n"/>
+      <c r="L362" s="8" t="n"/>
+      <c r="M362" s="8" t="n"/>
+      <c r="N362" s="8" t="n"/>
     </row>
     <row r="363">
-      <c r="A363" s="6" t="inlineStr">
+      <c r="A363" s="7" t="inlineStr">
         <is>
           <t>Sun 15 Nov 2026</t>
         </is>
       </c>
-      <c r="B363" s="7" t="n"/>
-      <c r="C363" s="7" t="n"/>
-      <c r="D363" s="7" t="n"/>
-      <c r="E363" s="7" t="n"/>
-      <c r="F363" s="7" t="n"/>
-      <c r="G363" s="7" t="n"/>
-      <c r="H363" s="7" t="n"/>
-      <c r="I363" s="7" t="n"/>
-      <c r="J363" s="7" t="n"/>
-      <c r="K363" s="7" t="n"/>
-      <c r="L363" s="7" t="n"/>
-      <c r="M363" s="7" t="n"/>
-      <c r="N363" s="7" t="n"/>
+      <c r="B363" s="8" t="n"/>
+      <c r="C363" s="8" t="n"/>
+      <c r="D363" s="8" t="n"/>
+      <c r="E363" s="8" t="n"/>
+      <c r="F363" s="8" t="n"/>
+      <c r="G363" s="8" t="n"/>
+      <c r="H363" s="8" t="n"/>
+      <c r="I363" s="8" t="n"/>
+      <c r="J363" s="8" t="n"/>
+      <c r="K363" s="8" t="n"/>
+      <c r="L363" s="8" t="n"/>
+      <c r="M363" s="8" t="n"/>
+      <c r="N363" s="8" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
@@ -9392,44 +9400,44 @@
       <c r="N368" s="5" t="n"/>
     </row>
     <row r="369">
-      <c r="A369" s="6" t="inlineStr">
+      <c r="A369" s="7" t="inlineStr">
         <is>
           <t>Sat 21 Nov 2026</t>
         </is>
       </c>
-      <c r="B369" s="7" t="n"/>
-      <c r="C369" s="7" t="n"/>
-      <c r="D369" s="7" t="n"/>
-      <c r="E369" s="7" t="n"/>
-      <c r="F369" s="7" t="n"/>
-      <c r="G369" s="7" t="n"/>
-      <c r="H369" s="7" t="n"/>
-      <c r="I369" s="7" t="n"/>
-      <c r="J369" s="7" t="n"/>
-      <c r="K369" s="7" t="n"/>
-      <c r="L369" s="7" t="n"/>
-      <c r="M369" s="7" t="n"/>
-      <c r="N369" s="7" t="n"/>
+      <c r="B369" s="8" t="n"/>
+      <c r="C369" s="8" t="n"/>
+      <c r="D369" s="8" t="n"/>
+      <c r="E369" s="8" t="n"/>
+      <c r="F369" s="8" t="n"/>
+      <c r="G369" s="8" t="n"/>
+      <c r="H369" s="8" t="n"/>
+      <c r="I369" s="8" t="n"/>
+      <c r="J369" s="8" t="n"/>
+      <c r="K369" s="8" t="n"/>
+      <c r="L369" s="8" t="n"/>
+      <c r="M369" s="8" t="n"/>
+      <c r="N369" s="8" t="n"/>
     </row>
     <row r="370">
-      <c r="A370" s="6" t="inlineStr">
+      <c r="A370" s="7" t="inlineStr">
         <is>
           <t>Sun 22 Nov 2026</t>
         </is>
       </c>
-      <c r="B370" s="7" t="n"/>
-      <c r="C370" s="7" t="n"/>
-      <c r="D370" s="7" t="n"/>
-      <c r="E370" s="7" t="n"/>
-      <c r="F370" s="7" t="n"/>
-      <c r="G370" s="7" t="n"/>
-      <c r="H370" s="7" t="n"/>
-      <c r="I370" s="7" t="n"/>
-      <c r="J370" s="7" t="n"/>
-      <c r="K370" s="7" t="n"/>
-      <c r="L370" s="7" t="n"/>
-      <c r="M370" s="7" t="n"/>
-      <c r="N370" s="7" t="n"/>
+      <c r="B370" s="8" t="n"/>
+      <c r="C370" s="8" t="n"/>
+      <c r="D370" s="8" t="n"/>
+      <c r="E370" s="8" t="n"/>
+      <c r="F370" s="8" t="n"/>
+      <c r="G370" s="8" t="n"/>
+      <c r="H370" s="8" t="n"/>
+      <c r="I370" s="8" t="n"/>
+      <c r="J370" s="8" t="n"/>
+      <c r="K370" s="8" t="n"/>
+      <c r="L370" s="8" t="n"/>
+      <c r="M370" s="8" t="n"/>
+      <c r="N370" s="8" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -9473,7 +9481,7 @@
       <c r="F372" s="5" t="n"/>
       <c r="G372" s="5" t="n"/>
       <c r="H372" s="5" t="n"/>
-      <c r="I372" s="8" t="inlineStr">
+      <c r="I372" s="6" t="inlineStr">
         <is>
           <t>Dub - Mabli a Ceff Ceff
 Online Edit - Mabli a Ceff Ceff</t>
@@ -9498,7 +9506,7 @@
       <c r="F373" s="5" t="n"/>
       <c r="G373" s="5" t="n"/>
       <c r="H373" s="5" t="n"/>
-      <c r="I373" s="8" t="inlineStr">
+      <c r="I373" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9522,7 +9530,7 @@
       <c r="F374" s="5" t="n"/>
       <c r="G374" s="5" t="n"/>
       <c r="H374" s="5" t="n"/>
-      <c r="I374" s="8" t="inlineStr">
+      <c r="I374" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9554,7 +9562,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I375" s="8" t="inlineStr">
+      <c r="I375" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9566,44 +9574,44 @@
       <c r="N375" s="5" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="6" t="inlineStr">
+      <c r="A376" s="7" t="inlineStr">
         <is>
           <t>Sat 28 Nov 2026</t>
         </is>
       </c>
-      <c r="B376" s="7" t="n"/>
-      <c r="C376" s="7" t="n"/>
-      <c r="D376" s="7" t="n"/>
-      <c r="E376" s="7" t="n"/>
-      <c r="F376" s="7" t="n"/>
-      <c r="G376" s="7" t="n"/>
-      <c r="H376" s="7" t="n"/>
-      <c r="I376" s="7" t="n"/>
-      <c r="J376" s="7" t="n"/>
-      <c r="K376" s="7" t="n"/>
-      <c r="L376" s="7" t="n"/>
-      <c r="M376" s="7" t="n"/>
-      <c r="N376" s="7" t="n"/>
+      <c r="B376" s="8" t="n"/>
+      <c r="C376" s="8" t="n"/>
+      <c r="D376" s="8" t="n"/>
+      <c r="E376" s="8" t="n"/>
+      <c r="F376" s="8" t="n"/>
+      <c r="G376" s="8" t="n"/>
+      <c r="H376" s="8" t="n"/>
+      <c r="I376" s="8" t="n"/>
+      <c r="J376" s="8" t="n"/>
+      <c r="K376" s="8" t="n"/>
+      <c r="L376" s="8" t="n"/>
+      <c r="M376" s="8" t="n"/>
+      <c r="N376" s="8" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="6" t="inlineStr">
+      <c r="A377" s="7" t="inlineStr">
         <is>
           <t>Sun 29 Nov 2026</t>
         </is>
       </c>
-      <c r="B377" s="7" t="n"/>
-      <c r="C377" s="7" t="n"/>
-      <c r="D377" s="7" t="n"/>
-      <c r="E377" s="7" t="n"/>
-      <c r="F377" s="7" t="n"/>
-      <c r="G377" s="7" t="n"/>
-      <c r="H377" s="7" t="n"/>
-      <c r="I377" s="7" t="n"/>
-      <c r="J377" s="7" t="n"/>
-      <c r="K377" s="7" t="n"/>
-      <c r="L377" s="7" t="n"/>
-      <c r="M377" s="7" t="n"/>
-      <c r="N377" s="7" t="n"/>
+      <c r="B377" s="8" t="n"/>
+      <c r="C377" s="8" t="n"/>
+      <c r="D377" s="8" t="n"/>
+      <c r="E377" s="8" t="n"/>
+      <c r="F377" s="8" t="n"/>
+      <c r="G377" s="8" t="n"/>
+      <c r="H377" s="8" t="n"/>
+      <c r="I377" s="8" t="n"/>
+      <c r="J377" s="8" t="n"/>
+      <c r="K377" s="8" t="n"/>
+      <c r="L377" s="8" t="n"/>
+      <c r="M377" s="8" t="n"/>
+      <c r="N377" s="8" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
@@ -9618,7 +9626,7 @@
       <c r="F378" s="5" t="n"/>
       <c r="G378" s="5" t="n"/>
       <c r="H378" s="5" t="n"/>
-      <c r="I378" s="8" t="inlineStr">
+      <c r="I378" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9642,7 +9650,7 @@
       <c r="F379" s="5" t="n"/>
       <c r="G379" s="5" t="n"/>
       <c r="H379" s="5" t="n"/>
-      <c r="I379" s="8" t="inlineStr">
+      <c r="I379" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9726,44 +9734,44 @@
       <c r="N382" s="5" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="6" t="inlineStr">
+      <c r="A383" s="7" t="inlineStr">
         <is>
           <t>Sat 05 Dec 2026</t>
         </is>
       </c>
-      <c r="B383" s="7" t="n"/>
-      <c r="C383" s="7" t="n"/>
-      <c r="D383" s="7" t="n"/>
-      <c r="E383" s="7" t="n"/>
-      <c r="F383" s="7" t="n"/>
-      <c r="G383" s="7" t="n"/>
-      <c r="H383" s="7" t="n"/>
-      <c r="I383" s="7" t="n"/>
-      <c r="J383" s="7" t="n"/>
-      <c r="K383" s="7" t="n"/>
-      <c r="L383" s="7" t="n"/>
-      <c r="M383" s="7" t="n"/>
-      <c r="N383" s="7" t="n"/>
+      <c r="B383" s="8" t="n"/>
+      <c r="C383" s="8" t="n"/>
+      <c r="D383" s="8" t="n"/>
+      <c r="E383" s="8" t="n"/>
+      <c r="F383" s="8" t="n"/>
+      <c r="G383" s="8" t="n"/>
+      <c r="H383" s="8" t="n"/>
+      <c r="I383" s="8" t="n"/>
+      <c r="J383" s="8" t="n"/>
+      <c r="K383" s="8" t="n"/>
+      <c r="L383" s="8" t="n"/>
+      <c r="M383" s="8" t="n"/>
+      <c r="N383" s="8" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="6" t="inlineStr">
+      <c r="A384" s="7" t="inlineStr">
         <is>
           <t>Sun 06 Dec 2026</t>
         </is>
       </c>
-      <c r="B384" s="7" t="n"/>
-      <c r="C384" s="7" t="n"/>
-      <c r="D384" s="7" t="n"/>
-      <c r="E384" s="7" t="n"/>
-      <c r="F384" s="7" t="n"/>
-      <c r="G384" s="7" t="n"/>
-      <c r="H384" s="7" t="n"/>
-      <c r="I384" s="7" t="n"/>
-      <c r="J384" s="7" t="n"/>
-      <c r="K384" s="7" t="n"/>
-      <c r="L384" s="7" t="n"/>
-      <c r="M384" s="7" t="n"/>
-      <c r="N384" s="7" t="n"/>
+      <c r="B384" s="8" t="n"/>
+      <c r="C384" s="8" t="n"/>
+      <c r="D384" s="8" t="n"/>
+      <c r="E384" s="8" t="n"/>
+      <c r="F384" s="8" t="n"/>
+      <c r="G384" s="8" t="n"/>
+      <c r="H384" s="8" t="n"/>
+      <c r="I384" s="8" t="n"/>
+      <c r="J384" s="8" t="n"/>
+      <c r="K384" s="8" t="n"/>
+      <c r="L384" s="8" t="n"/>
+      <c r="M384" s="8" t="n"/>
+      <c r="N384" s="8" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -9826,7 +9834,7 @@
       <c r="F387" s="5" t="n"/>
       <c r="G387" s="5" t="n"/>
       <c r="H387" s="5" t="n"/>
-      <c r="I387" s="8" t="inlineStr">
+      <c r="I387" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9850,7 +9858,7 @@
       <c r="F388" s="5" t="n"/>
       <c r="G388" s="5" t="n"/>
       <c r="H388" s="5" t="n"/>
-      <c r="I388" s="8" t="inlineStr">
+      <c r="I388" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9874,7 +9882,7 @@
       <c r="F389" s="5" t="n"/>
       <c r="G389" s="5" t="n"/>
       <c r="H389" s="5" t="n"/>
-      <c r="I389" s="8" t="inlineStr">
+      <c r="I389" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9886,44 +9894,44 @@
       <c r="N389" s="5" t="n"/>
     </row>
     <row r="390">
-      <c r="A390" s="6" t="inlineStr">
+      <c r="A390" s="7" t="inlineStr">
         <is>
           <t>Sat 12 Dec 2026</t>
         </is>
       </c>
-      <c r="B390" s="7" t="n"/>
-      <c r="C390" s="7" t="n"/>
-      <c r="D390" s="7" t="n"/>
-      <c r="E390" s="7" t="n"/>
-      <c r="F390" s="7" t="n"/>
-      <c r="G390" s="7" t="n"/>
-      <c r="H390" s="7" t="n"/>
-      <c r="I390" s="7" t="n"/>
-      <c r="J390" s="7" t="n"/>
-      <c r="K390" s="7" t="n"/>
-      <c r="L390" s="7" t="n"/>
-      <c r="M390" s="7" t="n"/>
-      <c r="N390" s="7" t="n"/>
+      <c r="B390" s="8" t="n"/>
+      <c r="C390" s="8" t="n"/>
+      <c r="D390" s="8" t="n"/>
+      <c r="E390" s="8" t="n"/>
+      <c r="F390" s="8" t="n"/>
+      <c r="G390" s="8" t="n"/>
+      <c r="H390" s="8" t="n"/>
+      <c r="I390" s="8" t="n"/>
+      <c r="J390" s="8" t="n"/>
+      <c r="K390" s="8" t="n"/>
+      <c r="L390" s="8" t="n"/>
+      <c r="M390" s="8" t="n"/>
+      <c r="N390" s="8" t="n"/>
     </row>
     <row r="391">
-      <c r="A391" s="6" t="inlineStr">
+      <c r="A391" s="7" t="inlineStr">
         <is>
           <t>Sun 13 Dec 2026</t>
         </is>
       </c>
-      <c r="B391" s="7" t="n"/>
-      <c r="C391" s="7" t="n"/>
-      <c r="D391" s="7" t="n"/>
-      <c r="E391" s="7" t="n"/>
-      <c r="F391" s="7" t="n"/>
-      <c r="G391" s="7" t="n"/>
-      <c r="H391" s="7" t="n"/>
-      <c r="I391" s="7" t="n"/>
-      <c r="J391" s="7" t="n"/>
-      <c r="K391" s="7" t="n"/>
-      <c r="L391" s="7" t="n"/>
-      <c r="M391" s="7" t="n"/>
-      <c r="N391" s="7" t="n"/>
+      <c r="B391" s="8" t="n"/>
+      <c r="C391" s="8" t="n"/>
+      <c r="D391" s="8" t="n"/>
+      <c r="E391" s="8" t="n"/>
+      <c r="F391" s="8" t="n"/>
+      <c r="G391" s="8" t="n"/>
+      <c r="H391" s="8" t="n"/>
+      <c r="I391" s="8" t="n"/>
+      <c r="J391" s="8" t="n"/>
+      <c r="K391" s="8" t="n"/>
+      <c r="L391" s="8" t="n"/>
+      <c r="M391" s="8" t="n"/>
+      <c r="N391" s="8" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -9938,7 +9946,7 @@
       <c r="F392" s="5" t="n"/>
       <c r="G392" s="5" t="n"/>
       <c r="H392" s="5" t="n"/>
-      <c r="I392" s="8" t="inlineStr">
+      <c r="I392" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9970,7 +9978,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I393" s="8" t="inlineStr">
+      <c r="I393" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10002,7 +10010,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I394" s="8" t="inlineStr">
+      <c r="I394" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10034,7 +10042,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I395" s="8" t="inlineStr">
+      <c r="I395" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10066,7 +10074,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I396" s="8" t="inlineStr">
+      <c r="I396" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10078,44 +10086,44 @@
       <c r="N396" s="5" t="n"/>
     </row>
     <row r="397">
-      <c r="A397" s="6" t="inlineStr">
+      <c r="A397" s="7" t="inlineStr">
         <is>
           <t>Sat 19 Dec 2026</t>
         </is>
       </c>
-      <c r="B397" s="7" t="n"/>
-      <c r="C397" s="7" t="n"/>
-      <c r="D397" s="7" t="n"/>
-      <c r="E397" s="7" t="n"/>
-      <c r="F397" s="7" t="n"/>
-      <c r="G397" s="7" t="n"/>
-      <c r="H397" s="7" t="n"/>
-      <c r="I397" s="7" t="n"/>
-      <c r="J397" s="7" t="n"/>
-      <c r="K397" s="7" t="n"/>
-      <c r="L397" s="7" t="n"/>
-      <c r="M397" s="7" t="n"/>
-      <c r="N397" s="7" t="n"/>
+      <c r="B397" s="8" t="n"/>
+      <c r="C397" s="8" t="n"/>
+      <c r="D397" s="8" t="n"/>
+      <c r="E397" s="8" t="n"/>
+      <c r="F397" s="8" t="n"/>
+      <c r="G397" s="8" t="n"/>
+      <c r="H397" s="8" t="n"/>
+      <c r="I397" s="8" t="n"/>
+      <c r="J397" s="8" t="n"/>
+      <c r="K397" s="8" t="n"/>
+      <c r="L397" s="8" t="n"/>
+      <c r="M397" s="8" t="n"/>
+      <c r="N397" s="8" t="n"/>
     </row>
     <row r="398">
-      <c r="A398" s="6" t="inlineStr">
+      <c r="A398" s="7" t="inlineStr">
         <is>
           <t>Sun 20 Dec 2026</t>
         </is>
       </c>
-      <c r="B398" s="7" t="n"/>
-      <c r="C398" s="7" t="n"/>
-      <c r="D398" s="7" t="n"/>
-      <c r="E398" s="7" t="n"/>
-      <c r="F398" s="7" t="n"/>
-      <c r="G398" s="7" t="n"/>
-      <c r="H398" s="7" t="n"/>
-      <c r="I398" s="7" t="n"/>
-      <c r="J398" s="7" t="n"/>
-      <c r="K398" s="7" t="n"/>
-      <c r="L398" s="7" t="n"/>
-      <c r="M398" s="7" t="n"/>
-      <c r="N398" s="7" t="n"/>
+      <c r="B398" s="8" t="n"/>
+      <c r="C398" s="8" t="n"/>
+      <c r="D398" s="8" t="n"/>
+      <c r="E398" s="8" t="n"/>
+      <c r="F398" s="8" t="n"/>
+      <c r="G398" s="8" t="n"/>
+      <c r="H398" s="8" t="n"/>
+      <c r="I398" s="8" t="n"/>
+      <c r="J398" s="8" t="n"/>
+      <c r="K398" s="8" t="n"/>
+      <c r="L398" s="8" t="n"/>
+      <c r="M398" s="8" t="n"/>
+      <c r="N398" s="8" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -10130,7 +10138,7 @@
       <c r="F399" s="5" t="n"/>
       <c r="G399" s="5" t="n"/>
       <c r="H399" s="5" t="n"/>
-      <c r="I399" s="8" t="inlineStr">
+      <c r="I399" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10154,7 +10162,7 @@
       <c r="F400" s="5" t="n"/>
       <c r="G400" s="5" t="n"/>
       <c r="H400" s="5" t="n"/>
-      <c r="I400" s="8" t="inlineStr">
+      <c r="I400" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10226,44 +10234,44 @@
       <c r="N403" s="5" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="6" t="inlineStr">
+      <c r="A404" s="7" t="inlineStr">
         <is>
           <t>Sat 26 Dec 2026</t>
         </is>
       </c>
-      <c r="B404" s="7" t="n"/>
-      <c r="C404" s="7" t="n"/>
-      <c r="D404" s="7" t="n"/>
-      <c r="E404" s="7" t="n"/>
-      <c r="F404" s="7" t="n"/>
-      <c r="G404" s="7" t="n"/>
-      <c r="H404" s="7" t="n"/>
-      <c r="I404" s="7" t="n"/>
-      <c r="J404" s="7" t="n"/>
-      <c r="K404" s="7" t="n"/>
-      <c r="L404" s="7" t="n"/>
-      <c r="M404" s="7" t="n"/>
-      <c r="N404" s="7" t="n"/>
+      <c r="B404" s="8" t="n"/>
+      <c r="C404" s="8" t="n"/>
+      <c r="D404" s="8" t="n"/>
+      <c r="E404" s="8" t="n"/>
+      <c r="F404" s="8" t="n"/>
+      <c r="G404" s="8" t="n"/>
+      <c r="H404" s="8" t="n"/>
+      <c r="I404" s="8" t="n"/>
+      <c r="J404" s="8" t="n"/>
+      <c r="K404" s="8" t="n"/>
+      <c r="L404" s="8" t="n"/>
+      <c r="M404" s="8" t="n"/>
+      <c r="N404" s="8" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="6" t="inlineStr">
+      <c r="A405" s="7" t="inlineStr">
         <is>
           <t>Sun 27 Dec 2026</t>
         </is>
       </c>
-      <c r="B405" s="7" t="n"/>
-      <c r="C405" s="7" t="n"/>
-      <c r="D405" s="7" t="n"/>
-      <c r="E405" s="7" t="n"/>
-      <c r="F405" s="7" t="n"/>
-      <c r="G405" s="7" t="n"/>
-      <c r="H405" s="7" t="n"/>
-      <c r="I405" s="7" t="n"/>
-      <c r="J405" s="7" t="n"/>
-      <c r="K405" s="7" t="n"/>
-      <c r="L405" s="7" t="n"/>
-      <c r="M405" s="7" t="n"/>
-      <c r="N405" s="7" t="n"/>
+      <c r="B405" s="8" t="n"/>
+      <c r="C405" s="8" t="n"/>
+      <c r="D405" s="8" t="n"/>
+      <c r="E405" s="8" t="n"/>
+      <c r="F405" s="8" t="n"/>
+      <c r="G405" s="8" t="n"/>
+      <c r="H405" s="8" t="n"/>
+      <c r="I405" s="8" t="n"/>
+      <c r="J405" s="8" t="n"/>
+      <c r="K405" s="8" t="n"/>
+      <c r="L405" s="8" t="n"/>
+      <c r="M405" s="8" t="n"/>
+      <c r="N405" s="8" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -10278,7 +10286,7 @@
       <c r="F406" s="5" t="n"/>
       <c r="G406" s="5" t="n"/>
       <c r="H406" s="5" t="n"/>
-      <c r="I406" s="8" t="inlineStr">
+      <c r="I406" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10302,7 +10310,7 @@
       <c r="F407" s="5" t="n"/>
       <c r="G407" s="5" t="n"/>
       <c r="H407" s="5" t="n"/>
-      <c r="I407" s="8" t="inlineStr">
+      <c r="I407" s="6" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10374,44 +10382,44 @@
       <c r="N410" s="5" t="n"/>
     </row>
     <row r="411">
-      <c r="A411" s="6" t="inlineStr">
+      <c r="A411" s="7" t="inlineStr">
         <is>
           <t>Sat 02 Jan 2027</t>
         </is>
       </c>
-      <c r="B411" s="7" t="n"/>
-      <c r="C411" s="7" t="n"/>
-      <c r="D411" s="7" t="n"/>
-      <c r="E411" s="7" t="n"/>
-      <c r="F411" s="7" t="n"/>
-      <c r="G411" s="7" t="n"/>
-      <c r="H411" s="7" t="n"/>
-      <c r="I411" s="7" t="n"/>
-      <c r="J411" s="7" t="n"/>
-      <c r="K411" s="7" t="n"/>
-      <c r="L411" s="7" t="n"/>
-      <c r="M411" s="7" t="n"/>
-      <c r="N411" s="7" t="n"/>
+      <c r="B411" s="8" t="n"/>
+      <c r="C411" s="8" t="n"/>
+      <c r="D411" s="8" t="n"/>
+      <c r="E411" s="8" t="n"/>
+      <c r="F411" s="8" t="n"/>
+      <c r="G411" s="8" t="n"/>
+      <c r="H411" s="8" t="n"/>
+      <c r="I411" s="8" t="n"/>
+      <c r="J411" s="8" t="n"/>
+      <c r="K411" s="8" t="n"/>
+      <c r="L411" s="8" t="n"/>
+      <c r="M411" s="8" t="n"/>
+      <c r="N411" s="8" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="6" t="inlineStr">
+      <c r="A412" s="7" t="inlineStr">
         <is>
           <t>Sun 03 Jan 2027</t>
         </is>
       </c>
-      <c r="B412" s="7" t="n"/>
-      <c r="C412" s="7" t="n"/>
-      <c r="D412" s="7" t="n"/>
-      <c r="E412" s="7" t="n"/>
-      <c r="F412" s="7" t="n"/>
-      <c r="G412" s="7" t="n"/>
-      <c r="H412" s="7" t="n"/>
-      <c r="I412" s="7" t="n"/>
-      <c r="J412" s="7" t="n"/>
-      <c r="K412" s="7" t="n"/>
-      <c r="L412" s="7" t="n"/>
-      <c r="M412" s="7" t="n"/>
-      <c r="N412" s="7" t="n"/>
+      <c r="B412" s="8" t="n"/>
+      <c r="C412" s="8" t="n"/>
+      <c r="D412" s="8" t="n"/>
+      <c r="E412" s="8" t="n"/>
+      <c r="F412" s="8" t="n"/>
+      <c r="G412" s="8" t="n"/>
+      <c r="H412" s="8" t="n"/>
+      <c r="I412" s="8" t="n"/>
+      <c r="J412" s="8" t="n"/>
+      <c r="K412" s="8" t="n"/>
+      <c r="L412" s="8" t="n"/>
+      <c r="M412" s="8" t="n"/>
+      <c r="N412" s="8" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -10538,44 +10546,44 @@
       <c r="N417" s="5" t="n"/>
     </row>
     <row r="418">
-      <c r="A418" s="6" t="inlineStr">
+      <c r="A418" s="7" t="inlineStr">
         <is>
           <t>Sat 09 Jan 2027</t>
         </is>
       </c>
-      <c r="B418" s="7" t="n"/>
-      <c r="C418" s="7" t="n"/>
-      <c r="D418" s="7" t="n"/>
-      <c r="E418" s="7" t="n"/>
-      <c r="F418" s="7" t="n"/>
-      <c r="G418" s="7" t="n"/>
-      <c r="H418" s="7" t="n"/>
-      <c r="I418" s="7" t="n"/>
-      <c r="J418" s="7" t="n"/>
-      <c r="K418" s="7" t="n"/>
-      <c r="L418" s="7" t="n"/>
-      <c r="M418" s="7" t="n"/>
-      <c r="N418" s="7" t="n"/>
+      <c r="B418" s="8" t="n"/>
+      <c r="C418" s="8" t="n"/>
+      <c r="D418" s="8" t="n"/>
+      <c r="E418" s="8" t="n"/>
+      <c r="F418" s="8" t="n"/>
+      <c r="G418" s="8" t="n"/>
+      <c r="H418" s="8" t="n"/>
+      <c r="I418" s="8" t="n"/>
+      <c r="J418" s="8" t="n"/>
+      <c r="K418" s="8" t="n"/>
+      <c r="L418" s="8" t="n"/>
+      <c r="M418" s="8" t="n"/>
+      <c r="N418" s="8" t="n"/>
     </row>
     <row r="419">
-      <c r="A419" s="6" t="inlineStr">
+      <c r="A419" s="7" t="inlineStr">
         <is>
           <t>Sun 10 Jan 2027</t>
         </is>
       </c>
-      <c r="B419" s="7" t="n"/>
-      <c r="C419" s="7" t="n"/>
-      <c r="D419" s="7" t="n"/>
-      <c r="E419" s="7" t="n"/>
-      <c r="F419" s="7" t="n"/>
-      <c r="G419" s="7" t="n"/>
-      <c r="H419" s="7" t="n"/>
-      <c r="I419" s="7" t="n"/>
-      <c r="J419" s="7" t="n"/>
-      <c r="K419" s="7" t="n"/>
-      <c r="L419" s="7" t="n"/>
-      <c r="M419" s="7" t="n"/>
-      <c r="N419" s="7" t="n"/>
+      <c r="B419" s="8" t="n"/>
+      <c r="C419" s="8" t="n"/>
+      <c r="D419" s="8" t="n"/>
+      <c r="E419" s="8" t="n"/>
+      <c r="F419" s="8" t="n"/>
+      <c r="G419" s="8" t="n"/>
+      <c r="H419" s="8" t="n"/>
+      <c r="I419" s="8" t="n"/>
+      <c r="J419" s="8" t="n"/>
+      <c r="K419" s="8" t="n"/>
+      <c r="L419" s="8" t="n"/>
+      <c r="M419" s="8" t="n"/>
+      <c r="N419" s="8" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
@@ -10698,44 +10706,44 @@
       <c r="N424" s="5" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="6" t="inlineStr">
+      <c r="A425" s="7" t="inlineStr">
         <is>
           <t>Sat 16 Jan 2027</t>
         </is>
       </c>
-      <c r="B425" s="7" t="n"/>
-      <c r="C425" s="7" t="n"/>
-      <c r="D425" s="7" t="n"/>
-      <c r="E425" s="7" t="n"/>
-      <c r="F425" s="7" t="n"/>
-      <c r="G425" s="7" t="n"/>
-      <c r="H425" s="7" t="n"/>
-      <c r="I425" s="7" t="n"/>
-      <c r="J425" s="7" t="n"/>
-      <c r="K425" s="7" t="n"/>
-      <c r="L425" s="7" t="n"/>
-      <c r="M425" s="7" t="n"/>
-      <c r="N425" s="7" t="n"/>
+      <c r="B425" s="8" t="n"/>
+      <c r="C425" s="8" t="n"/>
+      <c r="D425" s="8" t="n"/>
+      <c r="E425" s="8" t="n"/>
+      <c r="F425" s="8" t="n"/>
+      <c r="G425" s="8" t="n"/>
+      <c r="H425" s="8" t="n"/>
+      <c r="I425" s="8" t="n"/>
+      <c r="J425" s="8" t="n"/>
+      <c r="K425" s="8" t="n"/>
+      <c r="L425" s="8" t="n"/>
+      <c r="M425" s="8" t="n"/>
+      <c r="N425" s="8" t="n"/>
     </row>
     <row r="426">
-      <c r="A426" s="6" t="inlineStr">
+      <c r="A426" s="7" t="inlineStr">
         <is>
           <t>Sun 17 Jan 2027</t>
         </is>
       </c>
-      <c r="B426" s="7" t="n"/>
-      <c r="C426" s="7" t="n"/>
-      <c r="D426" s="7" t="n"/>
-      <c r="E426" s="7" t="n"/>
-      <c r="F426" s="7" t="n"/>
-      <c r="G426" s="7" t="n"/>
-      <c r="H426" s="7" t="n"/>
-      <c r="I426" s="7" t="n"/>
-      <c r="J426" s="7" t="n"/>
-      <c r="K426" s="7" t="n"/>
-      <c r="L426" s="7" t="n"/>
-      <c r="M426" s="7" t="n"/>
-      <c r="N426" s="7" t="n"/>
+      <c r="B426" s="8" t="n"/>
+      <c r="C426" s="8" t="n"/>
+      <c r="D426" s="8" t="n"/>
+      <c r="E426" s="8" t="n"/>
+      <c r="F426" s="8" t="n"/>
+      <c r="G426" s="8" t="n"/>
+      <c r="H426" s="8" t="n"/>
+      <c r="I426" s="8" t="n"/>
+      <c r="J426" s="8" t="n"/>
+      <c r="K426" s="8" t="n"/>
+      <c r="L426" s="8" t="n"/>
+      <c r="M426" s="8" t="n"/>
+      <c r="N426" s="8" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
@@ -10858,44 +10866,44 @@
       <c r="N431" s="5" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="6" t="inlineStr">
+      <c r="A432" s="7" t="inlineStr">
         <is>
           <t>Sat 23 Jan 2027</t>
         </is>
       </c>
-      <c r="B432" s="7" t="n"/>
-      <c r="C432" s="7" t="n"/>
-      <c r="D432" s="7" t="n"/>
-      <c r="E432" s="7" t="n"/>
-      <c r="F432" s="7" t="n"/>
-      <c r="G432" s="7" t="n"/>
-      <c r="H432" s="7" t="n"/>
-      <c r="I432" s="7" t="n"/>
-      <c r="J432" s="7" t="n"/>
-      <c r="K432" s="7" t="n"/>
-      <c r="L432" s="7" t="n"/>
-      <c r="M432" s="7" t="n"/>
-      <c r="N432" s="7" t="n"/>
+      <c r="B432" s="8" t="n"/>
+      <c r="C432" s="8" t="n"/>
+      <c r="D432" s="8" t="n"/>
+      <c r="E432" s="8" t="n"/>
+      <c r="F432" s="8" t="n"/>
+      <c r="G432" s="8" t="n"/>
+      <c r="H432" s="8" t="n"/>
+      <c r="I432" s="8" t="n"/>
+      <c r="J432" s="8" t="n"/>
+      <c r="K432" s="8" t="n"/>
+      <c r="L432" s="8" t="n"/>
+      <c r="M432" s="8" t="n"/>
+      <c r="N432" s="8" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="6" t="inlineStr">
+      <c r="A433" s="7" t="inlineStr">
         <is>
           <t>Sun 24 Jan 2027</t>
         </is>
       </c>
-      <c r="B433" s="7" t="n"/>
-      <c r="C433" s="7" t="n"/>
-      <c r="D433" s="7" t="n"/>
-      <c r="E433" s="7" t="n"/>
-      <c r="F433" s="7" t="n"/>
-      <c r="G433" s="7" t="n"/>
-      <c r="H433" s="7" t="n"/>
-      <c r="I433" s="7" t="n"/>
-      <c r="J433" s="7" t="n"/>
-      <c r="K433" s="7" t="n"/>
-      <c r="L433" s="7" t="n"/>
-      <c r="M433" s="7" t="n"/>
-      <c r="N433" s="7" t="n"/>
+      <c r="B433" s="8" t="n"/>
+      <c r="C433" s="8" t="n"/>
+      <c r="D433" s="8" t="n"/>
+      <c r="E433" s="8" t="n"/>
+      <c r="F433" s="8" t="n"/>
+      <c r="G433" s="8" t="n"/>
+      <c r="H433" s="8" t="n"/>
+      <c r="I433" s="8" t="n"/>
+      <c r="J433" s="8" t="n"/>
+      <c r="K433" s="8" t="n"/>
+      <c r="L433" s="8" t="n"/>
+      <c r="M433" s="8" t="n"/>
+      <c r="N433" s="8" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
@@ -11018,44 +11026,44 @@
       <c r="N438" s="5" t="n"/>
     </row>
     <row r="439">
-      <c r="A439" s="6" t="inlineStr">
+      <c r="A439" s="7" t="inlineStr">
         <is>
           <t>Sat 30 Jan 2027</t>
         </is>
       </c>
-      <c r="B439" s="7" t="n"/>
-      <c r="C439" s="7" t="n"/>
-      <c r="D439" s="7" t="n"/>
-      <c r="E439" s="7" t="n"/>
-      <c r="F439" s="7" t="n"/>
-      <c r="G439" s="7" t="n"/>
-      <c r="H439" s="7" t="n"/>
-      <c r="I439" s="7" t="n"/>
-      <c r="J439" s="7" t="n"/>
-      <c r="K439" s="7" t="n"/>
-      <c r="L439" s="7" t="n"/>
-      <c r="M439" s="7" t="n"/>
-      <c r="N439" s="7" t="n"/>
+      <c r="B439" s="8" t="n"/>
+      <c r="C439" s="8" t="n"/>
+      <c r="D439" s="8" t="n"/>
+      <c r="E439" s="8" t="n"/>
+      <c r="F439" s="8" t="n"/>
+      <c r="G439" s="8" t="n"/>
+      <c r="H439" s="8" t="n"/>
+      <c r="I439" s="8" t="n"/>
+      <c r="J439" s="8" t="n"/>
+      <c r="K439" s="8" t="n"/>
+      <c r="L439" s="8" t="n"/>
+      <c r="M439" s="8" t="n"/>
+      <c r="N439" s="8" t="n"/>
     </row>
     <row r="440">
-      <c r="A440" s="6" t="inlineStr">
+      <c r="A440" s="7" t="inlineStr">
         <is>
           <t>Sun 31 Jan 2027</t>
         </is>
       </c>
-      <c r="B440" s="7" t="n"/>
-      <c r="C440" s="7" t="n"/>
-      <c r="D440" s="7" t="n"/>
-      <c r="E440" s="7" t="n"/>
-      <c r="F440" s="7" t="n"/>
-      <c r="G440" s="7" t="n"/>
-      <c r="H440" s="7" t="n"/>
-      <c r="I440" s="7" t="n"/>
-      <c r="J440" s="7" t="n"/>
-      <c r="K440" s="7" t="n"/>
-      <c r="L440" s="7" t="n"/>
-      <c r="M440" s="7" t="n"/>
-      <c r="N440" s="7" t="n"/>
+      <c r="B440" s="8" t="n"/>
+      <c r="C440" s="8" t="n"/>
+      <c r="D440" s="8" t="n"/>
+      <c r="E440" s="8" t="n"/>
+      <c r="F440" s="8" t="n"/>
+      <c r="G440" s="8" t="n"/>
+      <c r="H440" s="8" t="n"/>
+      <c r="I440" s="8" t="n"/>
+      <c r="J440" s="8" t="n"/>
+      <c r="K440" s="8" t="n"/>
+      <c r="L440" s="8" t="n"/>
+      <c r="M440" s="8" t="n"/>
+      <c r="N440" s="8" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -11178,44 +11186,44 @@
       <c r="N445" s="5" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="6" t="inlineStr">
+      <c r="A446" s="7" t="inlineStr">
         <is>
           <t>Sat 06 Feb 2027</t>
         </is>
       </c>
-      <c r="B446" s="7" t="n"/>
-      <c r="C446" s="7" t="n"/>
-      <c r="D446" s="7" t="n"/>
-      <c r="E446" s="7" t="n"/>
-      <c r="F446" s="7" t="n"/>
-      <c r="G446" s="7" t="n"/>
-      <c r="H446" s="7" t="n"/>
-      <c r="I446" s="7" t="n"/>
-      <c r="J446" s="7" t="n"/>
-      <c r="K446" s="7" t="n"/>
-      <c r="L446" s="7" t="n"/>
-      <c r="M446" s="7" t="n"/>
-      <c r="N446" s="7" t="n"/>
+      <c r="B446" s="8" t="n"/>
+      <c r="C446" s="8" t="n"/>
+      <c r="D446" s="8" t="n"/>
+      <c r="E446" s="8" t="n"/>
+      <c r="F446" s="8" t="n"/>
+      <c r="G446" s="8" t="n"/>
+      <c r="H446" s="8" t="n"/>
+      <c r="I446" s="8" t="n"/>
+      <c r="J446" s="8" t="n"/>
+      <c r="K446" s="8" t="n"/>
+      <c r="L446" s="8" t="n"/>
+      <c r="M446" s="8" t="n"/>
+      <c r="N446" s="8" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="6" t="inlineStr">
+      <c r="A447" s="7" t="inlineStr">
         <is>
           <t>Sun 07 Feb 2027</t>
         </is>
       </c>
-      <c r="B447" s="7" t="n"/>
-      <c r="C447" s="7" t="n"/>
-      <c r="D447" s="7" t="n"/>
-      <c r="E447" s="7" t="n"/>
-      <c r="F447" s="7" t="n"/>
-      <c r="G447" s="7" t="n"/>
-      <c r="H447" s="7" t="n"/>
-      <c r="I447" s="7" t="n"/>
-      <c r="J447" s="7" t="n"/>
-      <c r="K447" s="7" t="n"/>
-      <c r="L447" s="7" t="n"/>
-      <c r="M447" s="7" t="n"/>
-      <c r="N447" s="7" t="n"/>
+      <c r="B447" s="8" t="n"/>
+      <c r="C447" s="8" t="n"/>
+      <c r="D447" s="8" t="n"/>
+      <c r="E447" s="8" t="n"/>
+      <c r="F447" s="8" t="n"/>
+      <c r="G447" s="8" t="n"/>
+      <c r="H447" s="8" t="n"/>
+      <c r="I447" s="8" t="n"/>
+      <c r="J447" s="8" t="n"/>
+      <c r="K447" s="8" t="n"/>
+      <c r="L447" s="8" t="n"/>
+      <c r="M447" s="8" t="n"/>
+      <c r="N447" s="8" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
@@ -11338,44 +11346,44 @@
       <c r="N452" s="5" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="6" t="inlineStr">
+      <c r="A453" s="7" t="inlineStr">
         <is>
           <t>Sat 13 Feb 2027</t>
         </is>
       </c>
-      <c r="B453" s="7" t="n"/>
-      <c r="C453" s="7" t="n"/>
-      <c r="D453" s="7" t="n"/>
-      <c r="E453" s="7" t="n"/>
-      <c r="F453" s="7" t="n"/>
-      <c r="G453" s="7" t="n"/>
-      <c r="H453" s="7" t="n"/>
-      <c r="I453" s="7" t="n"/>
-      <c r="J453" s="7" t="n"/>
-      <c r="K453" s="7" t="n"/>
-      <c r="L453" s="7" t="n"/>
-      <c r="M453" s="7" t="n"/>
-      <c r="N453" s="7" t="n"/>
+      <c r="B453" s="8" t="n"/>
+      <c r="C453" s="8" t="n"/>
+      <c r="D453" s="8" t="n"/>
+      <c r="E453" s="8" t="n"/>
+      <c r="F453" s="8" t="n"/>
+      <c r="G453" s="8" t="n"/>
+      <c r="H453" s="8" t="n"/>
+      <c r="I453" s="8" t="n"/>
+      <c r="J453" s="8" t="n"/>
+      <c r="K453" s="8" t="n"/>
+      <c r="L453" s="8" t="n"/>
+      <c r="M453" s="8" t="n"/>
+      <c r="N453" s="8" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="6" t="inlineStr">
+      <c r="A454" s="7" t="inlineStr">
         <is>
           <t>Sun 14 Feb 2027</t>
         </is>
       </c>
-      <c r="B454" s="7" t="n"/>
-      <c r="C454" s="7" t="n"/>
-      <c r="D454" s="7" t="n"/>
-      <c r="E454" s="7" t="n"/>
-      <c r="F454" s="7" t="n"/>
-      <c r="G454" s="7" t="n"/>
-      <c r="H454" s="7" t="n"/>
-      <c r="I454" s="7" t="n"/>
-      <c r="J454" s="7" t="n"/>
-      <c r="K454" s="7" t="n"/>
-      <c r="L454" s="7" t="n"/>
-      <c r="M454" s="7" t="n"/>
-      <c r="N454" s="7" t="n"/>
+      <c r="B454" s="8" t="n"/>
+      <c r="C454" s="8" t="n"/>
+      <c r="D454" s="8" t="n"/>
+      <c r="E454" s="8" t="n"/>
+      <c r="F454" s="8" t="n"/>
+      <c r="G454" s="8" t="n"/>
+      <c r="H454" s="8" t="n"/>
+      <c r="I454" s="8" t="n"/>
+      <c r="J454" s="8" t="n"/>
+      <c r="K454" s="8" t="n"/>
+      <c r="L454" s="8" t="n"/>
+      <c r="M454" s="8" t="n"/>
+      <c r="N454" s="8" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -11498,44 +11506,44 @@
       <c r="N459" s="5" t="n"/>
     </row>
     <row r="460">
-      <c r="A460" s="6" t="inlineStr">
+      <c r="A460" s="7" t="inlineStr">
         <is>
           <t>Sat 20 Feb 2027</t>
         </is>
       </c>
-      <c r="B460" s="7" t="n"/>
-      <c r="C460" s="7" t="n"/>
-      <c r="D460" s="7" t="n"/>
-      <c r="E460" s="7" t="n"/>
-      <c r="F460" s="7" t="n"/>
-      <c r="G460" s="7" t="n"/>
-      <c r="H460" s="7" t="n"/>
-      <c r="I460" s="7" t="n"/>
-      <c r="J460" s="7" t="n"/>
-      <c r="K460" s="7" t="n"/>
-      <c r="L460" s="7" t="n"/>
-      <c r="M460" s="7" t="n"/>
-      <c r="N460" s="7" t="n"/>
+      <c r="B460" s="8" t="n"/>
+      <c r="C460" s="8" t="n"/>
+      <c r="D460" s="8" t="n"/>
+      <c r="E460" s="8" t="n"/>
+      <c r="F460" s="8" t="n"/>
+      <c r="G460" s="8" t="n"/>
+      <c r="H460" s="8" t="n"/>
+      <c r="I460" s="8" t="n"/>
+      <c r="J460" s="8" t="n"/>
+      <c r="K460" s="8" t="n"/>
+      <c r="L460" s="8" t="n"/>
+      <c r="M460" s="8" t="n"/>
+      <c r="N460" s="8" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="6" t="inlineStr">
+      <c r="A461" s="7" t="inlineStr">
         <is>
           <t>Sun 21 Feb 2027</t>
         </is>
       </c>
-      <c r="B461" s="7" t="n"/>
-      <c r="C461" s="7" t="n"/>
-      <c r="D461" s="7" t="n"/>
-      <c r="E461" s="7" t="n"/>
-      <c r="F461" s="7" t="n"/>
-      <c r="G461" s="7" t="n"/>
-      <c r="H461" s="7" t="n"/>
-      <c r="I461" s="7" t="n"/>
-      <c r="J461" s="7" t="n"/>
-      <c r="K461" s="7" t="n"/>
-      <c r="L461" s="7" t="n"/>
-      <c r="M461" s="7" t="n"/>
-      <c r="N461" s="7" t="n"/>
+      <c r="B461" s="8" t="n"/>
+      <c r="C461" s="8" t="n"/>
+      <c r="D461" s="8" t="n"/>
+      <c r="E461" s="8" t="n"/>
+      <c r="F461" s="8" t="n"/>
+      <c r="G461" s="8" t="n"/>
+      <c r="H461" s="8" t="n"/>
+      <c r="I461" s="8" t="n"/>
+      <c r="J461" s="8" t="n"/>
+      <c r="K461" s="8" t="n"/>
+      <c r="L461" s="8" t="n"/>
+      <c r="M461" s="8" t="n"/>
+      <c r="N461" s="8" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -11658,44 +11666,44 @@
       <c r="N466" s="5" t="n"/>
     </row>
     <row r="467">
-      <c r="A467" s="6" t="inlineStr">
+      <c r="A467" s="7" t="inlineStr">
         <is>
           <t>Sat 27 Feb 2027</t>
         </is>
       </c>
-      <c r="B467" s="7" t="n"/>
-      <c r="C467" s="7" t="n"/>
-      <c r="D467" s="7" t="n"/>
-      <c r="E467" s="7" t="n"/>
-      <c r="F467" s="7" t="n"/>
-      <c r="G467" s="7" t="n"/>
-      <c r="H467" s="7" t="n"/>
-      <c r="I467" s="7" t="n"/>
-      <c r="J467" s="7" t="n"/>
-      <c r="K467" s="7" t="n"/>
-      <c r="L467" s="7" t="n"/>
-      <c r="M467" s="7" t="n"/>
-      <c r="N467" s="7" t="n"/>
+      <c r="B467" s="8" t="n"/>
+      <c r="C467" s="8" t="n"/>
+      <c r="D467" s="8" t="n"/>
+      <c r="E467" s="8" t="n"/>
+      <c r="F467" s="8" t="n"/>
+      <c r="G467" s="8" t="n"/>
+      <c r="H467" s="8" t="n"/>
+      <c r="I467" s="8" t="n"/>
+      <c r="J467" s="8" t="n"/>
+      <c r="K467" s="8" t="n"/>
+      <c r="L467" s="8" t="n"/>
+      <c r="M467" s="8" t="n"/>
+      <c r="N467" s="8" t="n"/>
     </row>
     <row r="468">
-      <c r="A468" s="6" t="inlineStr">
+      <c r="A468" s="7" t="inlineStr">
         <is>
           <t>Sun 28 Feb 2027</t>
         </is>
       </c>
-      <c r="B468" s="7" t="n"/>
-      <c r="C468" s="7" t="n"/>
-      <c r="D468" s="7" t="n"/>
-      <c r="E468" s="7" t="n"/>
-      <c r="F468" s="7" t="n"/>
-      <c r="G468" s="7" t="n"/>
-      <c r="H468" s="7" t="n"/>
-      <c r="I468" s="7" t="n"/>
-      <c r="J468" s="7" t="n"/>
-      <c r="K468" s="7" t="n"/>
-      <c r="L468" s="7" t="n"/>
-      <c r="M468" s="7" t="n"/>
-      <c r="N468" s="7" t="n"/>
+      <c r="B468" s="8" t="n"/>
+      <c r="C468" s="8" t="n"/>
+      <c r="D468" s="8" t="n"/>
+      <c r="E468" s="8" t="n"/>
+      <c r="F468" s="8" t="n"/>
+      <c r="G468" s="8" t="n"/>
+      <c r="H468" s="8" t="n"/>
+      <c r="I468" s="8" t="n"/>
+      <c r="J468" s="8" t="n"/>
+      <c r="K468" s="8" t="n"/>
+      <c r="L468" s="8" t="n"/>
+      <c r="M468" s="8" t="n"/>
+      <c r="N468" s="8" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -11818,44 +11826,44 @@
       <c r="N473" s="5" t="n"/>
     </row>
     <row r="474">
-      <c r="A474" s="6" t="inlineStr">
+      <c r="A474" s="7" t="inlineStr">
         <is>
           <t>Sat 06 Mar 2027</t>
         </is>
       </c>
-      <c r="B474" s="7" t="n"/>
-      <c r="C474" s="7" t="n"/>
-      <c r="D474" s="7" t="n"/>
-      <c r="E474" s="7" t="n"/>
-      <c r="F474" s="7" t="n"/>
-      <c r="G474" s="7" t="n"/>
-      <c r="H474" s="7" t="n"/>
-      <c r="I474" s="7" t="n"/>
-      <c r="J474" s="7" t="n"/>
-      <c r="K474" s="7" t="n"/>
-      <c r="L474" s="7" t="n"/>
-      <c r="M474" s="7" t="n"/>
-      <c r="N474" s="7" t="n"/>
+      <c r="B474" s="8" t="n"/>
+      <c r="C474" s="8" t="n"/>
+      <c r="D474" s="8" t="n"/>
+      <c r="E474" s="8" t="n"/>
+      <c r="F474" s="8" t="n"/>
+      <c r="G474" s="8" t="n"/>
+      <c r="H474" s="8" t="n"/>
+      <c r="I474" s="8" t="n"/>
+      <c r="J474" s="8" t="n"/>
+      <c r="K474" s="8" t="n"/>
+      <c r="L474" s="8" t="n"/>
+      <c r="M474" s="8" t="n"/>
+      <c r="N474" s="8" t="n"/>
     </row>
     <row r="475">
-      <c r="A475" s="6" t="inlineStr">
+      <c r="A475" s="7" t="inlineStr">
         <is>
           <t>Sun 07 Mar 2027</t>
         </is>
       </c>
-      <c r="B475" s="7" t="n"/>
-      <c r="C475" s="7" t="n"/>
-      <c r="D475" s="7" t="n"/>
-      <c r="E475" s="7" t="n"/>
-      <c r="F475" s="7" t="n"/>
-      <c r="G475" s="7" t="n"/>
-      <c r="H475" s="7" t="n"/>
-      <c r="I475" s="7" t="n"/>
-      <c r="J475" s="7" t="n"/>
-      <c r="K475" s="7" t="n"/>
-      <c r="L475" s="7" t="n"/>
-      <c r="M475" s="7" t="n"/>
-      <c r="N475" s="7" t="n"/>
+      <c r="B475" s="8" t="n"/>
+      <c r="C475" s="8" t="n"/>
+      <c r="D475" s="8" t="n"/>
+      <c r="E475" s="8" t="n"/>
+      <c r="F475" s="8" t="n"/>
+      <c r="G475" s="8" t="n"/>
+      <c r="H475" s="8" t="n"/>
+      <c r="I475" s="8" t="n"/>
+      <c r="J475" s="8" t="n"/>
+      <c r="K475" s="8" t="n"/>
+      <c r="L475" s="8" t="n"/>
+      <c r="M475" s="8" t="n"/>
+      <c r="N475" s="8" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -11978,44 +11986,44 @@
       <c r="N480" s="5" t="n"/>
     </row>
     <row r="481">
-      <c r="A481" s="6" t="inlineStr">
+      <c r="A481" s="7" t="inlineStr">
         <is>
           <t>Sat 13 Mar 2027</t>
         </is>
       </c>
-      <c r="B481" s="7" t="n"/>
-      <c r="C481" s="7" t="n"/>
-      <c r="D481" s="7" t="n"/>
-      <c r="E481" s="7" t="n"/>
-      <c r="F481" s="7" t="n"/>
-      <c r="G481" s="7" t="n"/>
-      <c r="H481" s="7" t="n"/>
-      <c r="I481" s="7" t="n"/>
-      <c r="J481" s="7" t="n"/>
-      <c r="K481" s="7" t="n"/>
-      <c r="L481" s="7" t="n"/>
-      <c r="M481" s="7" t="n"/>
-      <c r="N481" s="7" t="n"/>
+      <c r="B481" s="8" t="n"/>
+      <c r="C481" s="8" t="n"/>
+      <c r="D481" s="8" t="n"/>
+      <c r="E481" s="8" t="n"/>
+      <c r="F481" s="8" t="n"/>
+      <c r="G481" s="8" t="n"/>
+      <c r="H481" s="8" t="n"/>
+      <c r="I481" s="8" t="n"/>
+      <c r="J481" s="8" t="n"/>
+      <c r="K481" s="8" t="n"/>
+      <c r="L481" s="8" t="n"/>
+      <c r="M481" s="8" t="n"/>
+      <c r="N481" s="8" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="6" t="inlineStr">
+      <c r="A482" s="7" t="inlineStr">
         <is>
           <t>Sun 14 Mar 2027</t>
         </is>
       </c>
-      <c r="B482" s="7" t="n"/>
-      <c r="C482" s="7" t="n"/>
-      <c r="D482" s="7" t="n"/>
-      <c r="E482" s="7" t="n"/>
-      <c r="F482" s="7" t="n"/>
-      <c r="G482" s="7" t="n"/>
-      <c r="H482" s="7" t="n"/>
-      <c r="I482" s="7" t="n"/>
-      <c r="J482" s="7" t="n"/>
-      <c r="K482" s="7" t="n"/>
-      <c r="L482" s="7" t="n"/>
-      <c r="M482" s="7" t="n"/>
-      <c r="N482" s="7" t="n"/>
+      <c r="B482" s="8" t="n"/>
+      <c r="C482" s="8" t="n"/>
+      <c r="D482" s="8" t="n"/>
+      <c r="E482" s="8" t="n"/>
+      <c r="F482" s="8" t="n"/>
+      <c r="G482" s="8" t="n"/>
+      <c r="H482" s="8" t="n"/>
+      <c r="I482" s="8" t="n"/>
+      <c r="J482" s="8" t="n"/>
+      <c r="K482" s="8" t="n"/>
+      <c r="L482" s="8" t="n"/>
+      <c r="M482" s="8" t="n"/>
+      <c r="N482" s="8" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -12138,44 +12146,44 @@
       <c r="N487" s="5" t="n"/>
     </row>
     <row r="488">
-      <c r="A488" s="6" t="inlineStr">
+      <c r="A488" s="7" t="inlineStr">
         <is>
           <t>Sat 20 Mar 2027</t>
         </is>
       </c>
-      <c r="B488" s="7" t="n"/>
-      <c r="C488" s="7" t="n"/>
-      <c r="D488" s="7" t="n"/>
-      <c r="E488" s="7" t="n"/>
-      <c r="F488" s="7" t="n"/>
-      <c r="G488" s="7" t="n"/>
-      <c r="H488" s="7" t="n"/>
-      <c r="I488" s="7" t="n"/>
-      <c r="J488" s="7" t="n"/>
-      <c r="K488" s="7" t="n"/>
-      <c r="L488" s="7" t="n"/>
-      <c r="M488" s="7" t="n"/>
-      <c r="N488" s="7" t="n"/>
+      <c r="B488" s="8" t="n"/>
+      <c r="C488" s="8" t="n"/>
+      <c r="D488" s="8" t="n"/>
+      <c r="E488" s="8" t="n"/>
+      <c r="F488" s="8" t="n"/>
+      <c r="G488" s="8" t="n"/>
+      <c r="H488" s="8" t="n"/>
+      <c r="I488" s="8" t="n"/>
+      <c r="J488" s="8" t="n"/>
+      <c r="K488" s="8" t="n"/>
+      <c r="L488" s="8" t="n"/>
+      <c r="M488" s="8" t="n"/>
+      <c r="N488" s="8" t="n"/>
     </row>
     <row r="489">
-      <c r="A489" s="6" t="inlineStr">
+      <c r="A489" s="7" t="inlineStr">
         <is>
           <t>Sun 21 Mar 2027</t>
         </is>
       </c>
-      <c r="B489" s="7" t="n"/>
-      <c r="C489" s="7" t="n"/>
-      <c r="D489" s="7" t="n"/>
-      <c r="E489" s="7" t="n"/>
-      <c r="F489" s="7" t="n"/>
-      <c r="G489" s="7" t="n"/>
-      <c r="H489" s="7" t="n"/>
-      <c r="I489" s="7" t="n"/>
-      <c r="J489" s="7" t="n"/>
-      <c r="K489" s="7" t="n"/>
-      <c r="L489" s="7" t="n"/>
-      <c r="M489" s="7" t="n"/>
-      <c r="N489" s="7" t="n"/>
+      <c r="B489" s="8" t="n"/>
+      <c r="C489" s="8" t="n"/>
+      <c r="D489" s="8" t="n"/>
+      <c r="E489" s="8" t="n"/>
+      <c r="F489" s="8" t="n"/>
+      <c r="G489" s="8" t="n"/>
+      <c r="H489" s="8" t="n"/>
+      <c r="I489" s="8" t="n"/>
+      <c r="J489" s="8" t="n"/>
+      <c r="K489" s="8" t="n"/>
+      <c r="L489" s="8" t="n"/>
+      <c r="M489" s="8" t="n"/>
+      <c r="N489" s="8" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
@@ -12190,7 +12198,7 @@
       <c r="F490" s="5" t="n"/>
       <c r="G490" s="5" t="n"/>
       <c r="H490" s="5" t="n"/>
-      <c r="I490" s="8" t="inlineStr">
+      <c r="I490" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12214,7 +12222,7 @@
       <c r="F491" s="5" t="n"/>
       <c r="G491" s="5" t="n"/>
       <c r="H491" s="5" t="n"/>
-      <c r="I491" s="8" t="inlineStr">
+      <c r="I491" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12238,7 +12246,7 @@
       <c r="F492" s="5" t="n"/>
       <c r="G492" s="5" t="n"/>
       <c r="H492" s="5" t="n"/>
-      <c r="I492" s="8" t="inlineStr">
+      <c r="I492" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12262,7 +12270,7 @@
       <c r="F493" s="5" t="n"/>
       <c r="G493" s="5" t="n"/>
       <c r="H493" s="5" t="n"/>
-      <c r="I493" s="8" t="inlineStr">
+      <c r="I493" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12286,7 +12294,7 @@
       <c r="F494" s="5" t="n"/>
       <c r="G494" s="5" t="n"/>
       <c r="H494" s="5" t="n"/>
-      <c r="I494" s="8" t="inlineStr">
+      <c r="I494" s="6" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12298,44 +12306,44 @@
       <c r="N494" s="5" t="n"/>
     </row>
     <row r="495">
-      <c r="A495" s="6" t="inlineStr">
+      <c r="A495" s="7" t="inlineStr">
         <is>
           <t>Sat 27 Mar 2027</t>
         </is>
       </c>
-      <c r="B495" s="7" t="n"/>
-      <c r="C495" s="7" t="n"/>
-      <c r="D495" s="7" t="n"/>
-      <c r="E495" s="7" t="n"/>
-      <c r="F495" s="7" t="n"/>
-      <c r="G495" s="7" t="n"/>
-      <c r="H495" s="7" t="n"/>
-      <c r="I495" s="7" t="n"/>
-      <c r="J495" s="7" t="n"/>
-      <c r="K495" s="7" t="n"/>
-      <c r="L495" s="7" t="n"/>
-      <c r="M495" s="7" t="n"/>
-      <c r="N495" s="7" t="n"/>
+      <c r="B495" s="8" t="n"/>
+      <c r="C495" s="8" t="n"/>
+      <c r="D495" s="8" t="n"/>
+      <c r="E495" s="8" t="n"/>
+      <c r="F495" s="8" t="n"/>
+      <c r="G495" s="8" t="n"/>
+      <c r="H495" s="8" t="n"/>
+      <c r="I495" s="8" t="n"/>
+      <c r="J495" s="8" t="n"/>
+      <c r="K495" s="8" t="n"/>
+      <c r="L495" s="8" t="n"/>
+      <c r="M495" s="8" t="n"/>
+      <c r="N495" s="8" t="n"/>
     </row>
     <row r="496">
-      <c r="A496" s="6" t="inlineStr">
+      <c r="A496" s="7" t="inlineStr">
         <is>
           <t>Sun 28 Mar 2027</t>
         </is>
       </c>
-      <c r="B496" s="7" t="n"/>
-      <c r="C496" s="7" t="n"/>
-      <c r="D496" s="7" t="n"/>
-      <c r="E496" s="7" t="n"/>
-      <c r="F496" s="7" t="n"/>
-      <c r="G496" s="7" t="n"/>
-      <c r="H496" s="7" t="n"/>
-      <c r="I496" s="7" t="n"/>
-      <c r="J496" s="7" t="n"/>
-      <c r="K496" s="7" t="n"/>
-      <c r="L496" s="7" t="n"/>
-      <c r="M496" s="7" t="n"/>
-      <c r="N496" s="7" t="n"/>
+      <c r="B496" s="8" t="n"/>
+      <c r="C496" s="8" t="n"/>
+      <c r="D496" s="8" t="n"/>
+      <c r="E496" s="8" t="n"/>
+      <c r="F496" s="8" t="n"/>
+      <c r="G496" s="8" t="n"/>
+      <c r="H496" s="8" t="n"/>
+      <c r="I496" s="8" t="n"/>
+      <c r="J496" s="8" t="n"/>
+      <c r="K496" s="8" t="n"/>
+      <c r="L496" s="8" t="n"/>
+      <c r="M496" s="8" t="n"/>
+      <c r="N496" s="8" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -12470,44 +12478,44 @@
       <c r="N501" s="5" t="n"/>
     </row>
     <row r="502">
-      <c r="A502" s="6" t="inlineStr">
+      <c r="A502" s="7" t="inlineStr">
         <is>
           <t>Sat 03 Apr 2027</t>
         </is>
       </c>
-      <c r="B502" s="7" t="n"/>
-      <c r="C502" s="7" t="n"/>
-      <c r="D502" s="7" t="n"/>
-      <c r="E502" s="7" t="n"/>
-      <c r="F502" s="7" t="n"/>
-      <c r="G502" s="7" t="n"/>
-      <c r="H502" s="7" t="n"/>
-      <c r="I502" s="7" t="n"/>
-      <c r="J502" s="7" t="n"/>
-      <c r="K502" s="7" t="n"/>
-      <c r="L502" s="7" t="n"/>
-      <c r="M502" s="7" t="n"/>
-      <c r="N502" s="7" t="n"/>
+      <c r="B502" s="8" t="n"/>
+      <c r="C502" s="8" t="n"/>
+      <c r="D502" s="8" t="n"/>
+      <c r="E502" s="8" t="n"/>
+      <c r="F502" s="8" t="n"/>
+      <c r="G502" s="8" t="n"/>
+      <c r="H502" s="8" t="n"/>
+      <c r="I502" s="8" t="n"/>
+      <c r="J502" s="8" t="n"/>
+      <c r="K502" s="8" t="n"/>
+      <c r="L502" s="8" t="n"/>
+      <c r="M502" s="8" t="n"/>
+      <c r="N502" s="8" t="n"/>
     </row>
     <row r="503">
-      <c r="A503" s="6" t="inlineStr">
+      <c r="A503" s="7" t="inlineStr">
         <is>
           <t>Sun 04 Apr 2027</t>
         </is>
       </c>
-      <c r="B503" s="7" t="n"/>
-      <c r="C503" s="7" t="n"/>
-      <c r="D503" s="7" t="n"/>
-      <c r="E503" s="7" t="n"/>
-      <c r="F503" s="7" t="n"/>
-      <c r="G503" s="7" t="n"/>
-      <c r="H503" s="7" t="n"/>
-      <c r="I503" s="7" t="n"/>
-      <c r="J503" s="7" t="n"/>
-      <c r="K503" s="7" t="n"/>
-      <c r="L503" s="7" t="n"/>
-      <c r="M503" s="7" t="n"/>
-      <c r="N503" s="7" t="n"/>
+      <c r="B503" s="8" t="n"/>
+      <c r="C503" s="8" t="n"/>
+      <c r="D503" s="8" t="n"/>
+      <c r="E503" s="8" t="n"/>
+      <c r="F503" s="8" t="n"/>
+      <c r="G503" s="8" t="n"/>
+      <c r="H503" s="8" t="n"/>
+      <c r="I503" s="8" t="n"/>
+      <c r="J503" s="8" t="n"/>
+      <c r="K503" s="8" t="n"/>
+      <c r="L503" s="8" t="n"/>
+      <c r="M503" s="8" t="n"/>
+      <c r="N503" s="8" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>A/L (Half Day) - Annual Leave (2)</t>
+          <t>A/L (Half Day) - Annual Leave</t>
         </is>
       </c>
       <c r="C4" s="5" t="n"/>
@@ -705,7 +705,11 @@
           <t>Mon 24 Nov 2025</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -725,7 +729,11 @@
           <t>Tue 25 Nov 2025</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
@@ -745,7 +753,11 @@
           <t>Wed 26 Nov 2025</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>A/L (Half Day) - Annual Leave</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -1265,7 +1277,11 @@
           <t>Mon 22 Dec 2025</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
@@ -1293,7 +1309,11 @@
           <t>Tue 23 Dec 2025</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
@@ -1321,7 +1341,11 @@
           <t>Wed 24 Dec 2025</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>A/L (Half Day) - Annual Leave</t>
+        </is>
+      </c>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
@@ -1369,7 +1393,11 @@
           <t>Fri 26 Dec 2025</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
@@ -1437,7 +1465,11 @@
           <t>Mon 29 Dec 2025</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5" t="n"/>
       <c r="E42" s="5" t="n"/>
@@ -1461,7 +1493,11 @@
           <t>Tue 30 Dec 2025</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
       <c r="E43" s="5" t="n"/>
@@ -1485,7 +1521,11 @@
           <t>Wed 31 Dec 2025</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="5" t="n"/>
       <c r="E44" s="5" t="n"/>
@@ -1509,7 +1549,11 @@
           <t>Thu 01 Jan 2026</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
@@ -1533,7 +1577,11 @@
           <t>Fri 02 Jan 2026</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n"/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
       <c r="E46" s="5" t="n"/>
@@ -3297,7 +3345,11 @@
           <t>Mon 30 Mar 2026</t>
         </is>
       </c>
-      <c r="B133" s="5" t="n"/>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C133" s="5" t="n"/>
       <c r="D133" s="5" t="n"/>
       <c r="E133" s="5" t="n"/>
@@ -3337,7 +3389,11 @@
           <t>Wed 01 Apr 2026</t>
         </is>
       </c>
-      <c r="B135" s="5" t="n"/>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C135" s="5" t="n"/>
       <c r="D135" s="5" t="n"/>
       <c r="E135" s="5" t="n"/>
@@ -3361,7 +3417,11 @@
           <t>Thu 02 Apr 2026</t>
         </is>
       </c>
-      <c r="B136" s="5" t="n"/>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="n"/>
       <c r="E136" s="5" t="n"/>
@@ -3385,13 +3445,17 @@
           <t>Fri 03 Apr 2026</t>
         </is>
       </c>
-      <c r="B137" s="5" t="n"/>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5" t="n"/>
       <c r="E137" s="5" t="n"/>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>A/L (Half Day) - Annual Leave</t>
         </is>
       </c>
       <c r="G137" s="5" t="n"/>
@@ -4065,7 +4129,11 @@
           <t>Tue 05 May 2026</t>
         </is>
       </c>
-      <c r="B169" s="5" t="n"/>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>A/L (Half Day) - Annual Leave</t>
+        </is>
+      </c>
       <c r="C169" s="5" t="n"/>
       <c r="D169" s="5" t="n"/>
       <c r="E169" s="5" t="n"/>
@@ -5861,7 +5929,11 @@
           <t>Mon 27 Jul 2026</t>
         </is>
       </c>
-      <c r="B252" s="5" t="n"/>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C252" s="5" t="n"/>
       <c r="D252" s="5" t="n"/>
       <c r="E252" s="5" t="n"/>
@@ -5881,7 +5953,11 @@
           <t>Tue 28 Jul 2026</t>
         </is>
       </c>
-      <c r="B253" s="5" t="n"/>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C253" s="5" t="n"/>
       <c r="D253" s="5" t="n"/>
       <c r="E253" s="5" t="n"/>
@@ -5901,7 +5977,11 @@
           <t>Wed 29 Jul 2026</t>
         </is>
       </c>
-      <c r="B254" s="5" t="n"/>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C254" s="5" t="n"/>
       <c r="D254" s="5" t="n"/>
       <c r="E254" s="5" t="n"/>
@@ -5921,7 +6001,11 @@
           <t>Thu 30 Jul 2026</t>
         </is>
       </c>
-      <c r="B255" s="5" t="n"/>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C255" s="5" t="n"/>
       <c r="D255" s="5" t="n"/>
       <c r="E255" s="5" t="n"/>
@@ -5941,7 +6025,11 @@
           <t>Fri 31 Jul 2026</t>
         </is>
       </c>
-      <c r="B256" s="5" t="n"/>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C256" s="5" t="n"/>
       <c r="D256" s="5" t="n"/>
       <c r="E256" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -6281,7 +6281,11 @@
           <t>Mon 10 Aug 2026</t>
         </is>
       </c>
-      <c r="B266" s="5" t="n"/>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C266" s="5" t="n"/>
       <c r="D266" s="5" t="n"/>
       <c r="E266" s="5" t="n"/>
@@ -6305,7 +6309,11 @@
           <t>Tue 11 Aug 2026</t>
         </is>
       </c>
-      <c r="B267" s="5" t="n"/>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C267" s="5" t="n"/>
       <c r="D267" s="5" t="n"/>
       <c r="E267" s="5" t="n"/>
@@ -6333,7 +6341,11 @@
           <t>Wed 12 Aug 2026</t>
         </is>
       </c>
-      <c r="B268" s="5" t="n"/>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C268" s="5" t="n"/>
       <c r="D268" s="5" t="n"/>
       <c r="E268" s="5" t="n"/>
@@ -6357,7 +6369,11 @@
           <t>Thu 13 Aug 2026</t>
         </is>
       </c>
-      <c r="B269" s="5" t="n"/>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C269" s="5" t="n"/>
       <c r="D269" s="5" t="n"/>
       <c r="E269" s="5" t="n"/>
@@ -6381,7 +6397,12 @@
           <t>Fri 14 Aug 2026</t>
         </is>
       </c>
-      <c r="B270" s="5" t="n"/>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave (1)
+A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C270" s="5" t="n"/>
       <c r="D270" s="5" t="n"/>
       <c r="E270" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -6089,7 +6089,11 @@
           <t>Mon 03 Aug 2026</t>
         </is>
       </c>
-      <c r="B259" s="5" t="n"/>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C259" s="5" t="n"/>
       <c r="D259" s="5" t="n"/>
       <c r="E259" s="5" t="n"/>
@@ -6121,7 +6125,11 @@
           <t>Tue 04 Aug 2026</t>
         </is>
       </c>
-      <c r="B260" s="5" t="n"/>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="C260" s="5" t="n"/>
       <c r="D260" s="5" t="n"/>
       <c r="E260" s="5" t="n"/>
@@ -6287,7 +6295,11 @@
         </is>
       </c>
       <c r="C266" s="5" t="n"/>
-      <c r="D266" s="5" t="n"/>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E266" s="5" t="n"/>
       <c r="F266" s="5" t="n"/>
       <c r="G266" s="5" t="n"/>
@@ -6315,7 +6327,11 @@
         </is>
       </c>
       <c r="C267" s="5" t="n"/>
-      <c r="D267" s="5" t="n"/>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n"/>
       <c r="F267" s="6" t="inlineStr">
         <is>
@@ -6347,7 +6363,11 @@
         </is>
       </c>
       <c r="C268" s="5" t="n"/>
-      <c r="D268" s="5" t="n"/>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E268" s="5" t="n"/>
       <c r="F268" s="5" t="n"/>
       <c r="G268" s="5" t="n"/>
@@ -6375,7 +6395,11 @@
         </is>
       </c>
       <c r="C269" s="5" t="n"/>
-      <c r="D269" s="5" t="n"/>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E269" s="5" t="n"/>
       <c r="F269" s="5" t="n"/>
       <c r="G269" s="5" t="n"/>
@@ -6399,8 +6423,7 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C270" s="5" t="n"/>
@@ -6610,11 +6633,7 @@
           <t>Mon 24 Aug 2026</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="B280" s="5" t="n"/>
       <c r="C280" s="5" t="n"/>
       <c r="D280" s="6" t="inlineStr">
         <is>
@@ -6951,7 +6970,7 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave (1)</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
@@ -8367,7 +8386,11 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="B329" s="5" t="n"/>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave (1)</t>
+        </is>
+      </c>
       <c r="C329" s="5" t="n"/>
       <c r="D329" s="4" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1796,7 +1796,11 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N56" s="5" t="n"/>
     </row>
     <row r="57">
@@ -1816,7 +1820,11 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N57" s="5" t="n"/>
     </row>
     <row r="58">
@@ -1836,7 +1844,11 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N58" s="5" t="n"/>
     </row>
     <row r="59">
@@ -1856,7 +1868,11 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="n"/>
-      <c r="M59" s="5" t="n"/>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N59" s="5" t="n"/>
     </row>
     <row r="60">
@@ -1876,7 +1892,11 @@
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N60" s="5" t="n"/>
     </row>
     <row r="61">
@@ -2844,7 +2864,11 @@
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="5" t="n"/>
       <c r="L108" s="5" t="n"/>
-      <c r="M108" s="5" t="n"/>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N108" s="5" t="n"/>
     </row>
     <row r="109">
@@ -2864,7 +2888,11 @@
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="5" t="n"/>
-      <c r="M109" s="5" t="n"/>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N109" s="5" t="n"/>
     </row>
     <row r="110">
@@ -2924,7 +2952,11 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="5" t="n"/>
       <c r="L112" s="5" t="n"/>
-      <c r="M112" s="5" t="n"/>
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N112" s="5" t="n"/>
     </row>
     <row r="113">
@@ -5788,7 +5820,11 @@
       <c r="J245" s="5" t="n"/>
       <c r="K245" s="5" t="n"/>
       <c r="L245" s="5" t="n"/>
-      <c r="M245" s="5" t="n"/>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -5812,7 +5848,11 @@
       <c r="J246" s="5" t="n"/>
       <c r="K246" s="5" t="n"/>
       <c r="L246" s="5" t="n"/>
-      <c r="M246" s="5" t="n"/>
+      <c r="M246" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N246" s="4" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -6391,7 +6431,8 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave (1)
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C269" s="5" t="n"/>
@@ -8386,11 +8427,7 @@
           <t>Mon 12 Oct 2026</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave (1)</t>
-        </is>
-      </c>
+      <c r="B329" s="5" t="n"/>
       <c r="C329" s="5" t="n"/>
       <c r="D329" s="4" t="inlineStr">
         <is>
@@ -9396,7 +9433,11 @@
       </c>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="5" t="n"/>
-      <c r="D364" s="5" t="n"/>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E364" s="5" t="n"/>
       <c r="F364" s="5" t="n"/>
       <c r="G364" s="5" t="n"/>
@@ -9420,7 +9461,11 @@
       </c>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="5" t="n"/>
-      <c r="D365" s="5" t="n"/>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E365" s="5" t="n"/>
       <c r="F365" s="5" t="n"/>
       <c r="G365" s="5" t="n"/>
@@ -9444,7 +9489,11 @@
       </c>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="5" t="n"/>
-      <c r="D366" s="5" t="n"/>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E366" s="5" t="n"/>
       <c r="F366" s="5" t="n"/>
       <c r="G366" s="5" t="n"/>
@@ -9473,7 +9522,11 @@
       </c>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="5" t="n"/>
-      <c r="D367" s="5" t="n"/>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="E367" s="5" t="n"/>
       <c r="F367" s="5" t="n"/>
       <c r="G367" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -5460,7 +5460,11 @@
       <c r="J228" s="5" t="n"/>
       <c r="K228" s="5" t="n"/>
       <c r="L228" s="5" t="n"/>
-      <c r="M228" s="5" t="n"/>
+      <c r="M228" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N228" s="5" t="n"/>
     </row>
     <row r="229">
@@ -5524,7 +5528,11 @@
       <c r="J231" s="5" t="n"/>
       <c r="K231" s="5" t="n"/>
       <c r="L231" s="5" t="n"/>
-      <c r="M231" s="5" t="n"/>
+      <c r="M231" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N231" s="5" t="n"/>
     </row>
     <row r="232">
@@ -5876,7 +5884,11 @@
       <c r="J247" s="5" t="n"/>
       <c r="K247" s="5" t="n"/>
       <c r="L247" s="5" t="n"/>
-      <c r="M247" s="5" t="n"/>
+      <c r="M247" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N247" s="4" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -5900,7 +5912,11 @@
       <c r="J248" s="5" t="n"/>
       <c r="K248" s="5" t="n"/>
       <c r="L248" s="5" t="n"/>
-      <c r="M248" s="5" t="n"/>
+      <c r="M248" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N248" s="5" t="n"/>
     </row>
     <row r="249">
@@ -6625,7 +6641,11 @@
       <c r="J277" s="5" t="n"/>
       <c r="K277" s="5" t="n"/>
       <c r="L277" s="5" t="n"/>
-      <c r="M277" s="5" t="n"/>
+      <c r="M277" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N277" s="5" t="n"/>
     </row>
     <row r="278">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -3493,7 +3493,11 @@
       <c r="G137" s="5" t="n"/>
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="n"/>
-      <c r="J137" s="5" t="n"/>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K137" s="5" t="n"/>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n"/>
@@ -4901,7 +4905,11 @@
         </is>
       </c>
       <c r="I203" s="5" t="n"/>
-      <c r="J203" s="5" t="n"/>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K203" s="5" t="n"/>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="5" t="n"/>
@@ -5825,7 +5833,11 @@
       <c r="G245" s="5" t="n"/>
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="n"/>
-      <c r="J245" s="5" t="n"/>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K245" s="5" t="n"/>
       <c r="L245" s="5" t="n"/>
       <c r="M245" s="4" t="inlineStr">
@@ -11523,7 +11535,11 @@
       <c r="J451" s="5" t="n"/>
       <c r="K451" s="5" t="n"/>
       <c r="L451" s="5" t="n"/>
-      <c r="M451" s="5" t="n"/>
+      <c r="M451" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N451" s="5" t="n"/>
     </row>
     <row r="452">
@@ -11547,7 +11563,11 @@
       <c r="J452" s="5" t="n"/>
       <c r="K452" s="5" t="n"/>
       <c r="L452" s="5" t="n"/>
-      <c r="M452" s="5" t="n"/>
+      <c r="M452" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="N452" s="5" t="n"/>
     </row>
     <row r="453">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -5721,7 +5721,11 @@
       <c r="G240" s="5" t="n"/>
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="n"/>
-      <c r="J240" s="5" t="n"/>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K240" s="5" t="n"/>
       <c r="L240" s="5" t="n"/>
       <c r="M240" s="5" t="n"/>
@@ -8347,7 +8351,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J324" s="5" t="n"/>
+      <c r="J324" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K324" s="5" t="n"/>
       <c r="L324" s="4" t="inlineStr">
         <is>
@@ -8375,7 +8383,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J325" s="5" t="n"/>
+      <c r="J325" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K325" s="5" t="n"/>
       <c r="L325" s="5" t="n"/>
       <c r="M325" s="5" t="n"/>
@@ -8399,7 +8411,11 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J326" s="5" t="n"/>
+      <c r="J326" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="K326" s="5" t="n"/>
       <c r="L326" s="5" t="n"/>
       <c r="M326" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1146,7 +1146,11 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L28" s="5" t="n"/>
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
@@ -1166,7 +1170,11 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
       <c r="N29" s="5" t="n"/>
@@ -1298,7 +1306,11 @@
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
       <c r="N35" s="5" t="n"/>
@@ -1330,7 +1342,11 @@
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
       <c r="N36" s="5" t="n"/>
@@ -1362,7 +1378,11 @@
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
       <c r="N37" s="5" t="n"/>
@@ -1414,7 +1434,11 @@
         </is>
       </c>
       <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="5" t="n"/>
       <c r="N39" s="5" t="n"/>
@@ -1510,7 +1534,11 @@
         </is>
       </c>
       <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
@@ -1566,7 +1594,11 @@
         </is>
       </c>
       <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
@@ -1594,7 +1626,11 @@
         </is>
       </c>
       <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L46" s="5" t="n"/>
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
@@ -4794,7 +4830,11 @@
       </c>
       <c r="I198" s="5" t="n"/>
       <c r="J198" s="5" t="n"/>
-      <c r="K198" s="5" t="n"/>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L198" s="5" t="n"/>
       <c r="M198" s="5" t="n"/>
       <c r="N198" s="5" t="n"/>
@@ -4910,7 +4950,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="K203" s="5" t="n"/>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n"/>
@@ -4934,7 +4978,11 @@
       </c>
       <c r="I204" s="5" t="n"/>
       <c r="J204" s="5" t="n"/>
-      <c r="K204" s="5" t="n"/>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L204" s="5" t="n"/>
       <c r="M204" s="5" t="n"/>
       <c r="N204" s="5" t="n"/>
@@ -4958,7 +5006,11 @@
       </c>
       <c r="I205" s="5" t="n"/>
       <c r="J205" s="5" t="n"/>
-      <c r="K205" s="5" t="n"/>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n"/>
@@ -4978,7 +5030,11 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="n"/>
       <c r="J206" s="5" t="n"/>
-      <c r="K206" s="5" t="n"/>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L206" s="5" t="n"/>
       <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="n"/>
@@ -4998,7 +5054,11 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="n"/>
       <c r="J207" s="5" t="n"/>
-      <c r="K207" s="5" t="n"/>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L207" s="5" t="n"/>
       <c r="M207" s="5" t="n"/>
       <c r="N207" s="5" t="n"/>
@@ -5058,7 +5118,11 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="n"/>
       <c r="J210" s="5" t="n"/>
-      <c r="K210" s="5" t="n"/>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L210" s="5" t="n"/>
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n"/>
@@ -5082,7 +5146,11 @@
       </c>
       <c r="I211" s="5" t="n"/>
       <c r="J211" s="5" t="n"/>
-      <c r="K211" s="5" t="n"/>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L211" s="5" t="n"/>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
@@ -5442,7 +5510,11 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="n"/>
       <c r="J227" s="5" t="n"/>
-      <c r="K227" s="5" t="n"/>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n"/>
@@ -5466,7 +5538,11 @@
       </c>
       <c r="I228" s="5" t="n"/>
       <c r="J228" s="5" t="n"/>
-      <c r="K228" s="5" t="n"/>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L228" s="5" t="n"/>
       <c r="M228" s="4" t="inlineStr">
         <is>
@@ -5534,7 +5610,11 @@
       </c>
       <c r="I231" s="5" t="n"/>
       <c r="J231" s="5" t="n"/>
-      <c r="K231" s="5" t="n"/>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="4" t="inlineStr">
         <is>
@@ -5558,7 +5638,11 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="n"/>
       <c r="J232" s="5" t="n"/>
-      <c r="K232" s="5" t="n"/>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L232" s="5" t="n"/>
       <c r="M232" s="5" t="n"/>
       <c r="N232" s="5" t="n"/>
@@ -7253,7 +7337,8 @@
       <c r="J291" s="5" t="n"/>
       <c r="K291" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave (1)
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -5123,7 +5123,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L210" s="5" t="n"/>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M210" s="5" t="n"/>
       <c r="N210" s="5" t="n"/>
     </row>
@@ -6502,7 +6506,11 @@
         </is>
       </c>
       <c r="J267" s="5" t="n"/>
-      <c r="K267" s="5" t="n"/>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L267" s="5" t="n"/>
       <c r="M267" s="5" t="n"/>
       <c r="N267" s="5" t="n"/>
@@ -6534,7 +6542,11 @@
         </is>
       </c>
       <c r="J268" s="5" t="n"/>
-      <c r="K268" s="5" t="n"/>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L268" s="5" t="n"/>
       <c r="M268" s="5" t="n"/>
       <c r="N268" s="5" t="n"/>
@@ -7337,8 +7349,7 @@
       <c r="J291" s="5" t="n"/>
       <c r="K291" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr">
@@ -8120,7 +8131,11 @@
         </is>
       </c>
       <c r="J315" s="5" t="n"/>
-      <c r="K315" s="5" t="n"/>
+      <c r="K315" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L315" s="5" t="n"/>
       <c r="M315" s="4" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -5155,7 +5155,11 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="L211" s="5" t="n"/>
+      <c r="L211" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
     </row>
@@ -5179,7 +5183,11 @@
       <c r="I212" s="5" t="n"/>
       <c r="J212" s="5" t="n"/>
       <c r="K212" s="5" t="n"/>
-      <c r="L212" s="5" t="n"/>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M212" s="5" t="n"/>
       <c r="N212" s="5" t="n"/>
     </row>
@@ -5707,7 +5715,11 @@
       <c r="I235" s="5" t="n"/>
       <c r="J235" s="5" t="n"/>
       <c r="K235" s="5" t="n"/>
-      <c r="L235" s="5" t="n"/>
+      <c r="L235" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M235" s="5" t="n"/>
       <c r="N235" s="5" t="n"/>
     </row>
@@ -6559,7 +6571,7 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)
+          <t>A/L - Annual Leave
 A/L - Annual Leave</t>
         </is>
       </c>
@@ -6612,7 +6624,11 @@
       </c>
       <c r="J270" s="5" t="n"/>
       <c r="K270" s="5" t="n"/>
-      <c r="L270" s="5" t="n"/>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M270" s="5" t="n"/>
       <c r="N270" s="5" t="n"/>
     </row>
@@ -6672,7 +6688,11 @@
       <c r="I273" s="5" t="n"/>
       <c r="J273" s="5" t="n"/>
       <c r="K273" s="5" t="n"/>
-      <c r="L273" s="5" t="n"/>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M273" s="5" t="n"/>
       <c r="N273" s="5" t="n"/>
     </row>
@@ -6692,7 +6712,11 @@
       <c r="I274" s="5" t="n"/>
       <c r="J274" s="5" t="n"/>
       <c r="K274" s="5" t="n"/>
-      <c r="L274" s="5" t="n"/>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M274" s="5" t="n"/>
       <c r="N274" s="5" t="n"/>
     </row>
@@ -6712,7 +6736,11 @@
       <c r="I275" s="5" t="n"/>
       <c r="J275" s="5" t="n"/>
       <c r="K275" s="5" t="n"/>
-      <c r="L275" s="5" t="n"/>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M275" s="5" t="n"/>
       <c r="N275" s="5" t="n"/>
     </row>
@@ -6732,7 +6760,11 @@
       <c r="I276" s="5" t="n"/>
       <c r="J276" s="5" t="n"/>
       <c r="K276" s="5" t="n"/>
-      <c r="L276" s="5" t="n"/>
+      <c r="L276" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M276" s="5" t="n"/>
       <c r="N276" s="5" t="n"/>
     </row>
@@ -6752,7 +6784,11 @@
       <c r="I277" s="5" t="n"/>
       <c r="J277" s="5" t="n"/>
       <c r="K277" s="5" t="n"/>
-      <c r="L277" s="5" t="n"/>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="M277" s="4" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -8218,7 +8254,8 @@
       <c r="K317" s="5" t="n"/>
       <c r="L317" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>A/L - Annual Leave
+A/L - Annual Leave</t>
         </is>
       </c>
       <c r="M317" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7236,11 +7236,7 @@
       </c>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="5" t="n"/>
-      <c r="D288" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="D288" s="5" t="n"/>
       <c r="E288" s="5" t="n"/>
       <c r="F288" s="5" t="n"/>
       <c r="G288" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -3521,9 +3521,9 @@
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5" t="n"/>
       <c r="E137" s="5" t="n"/>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>A/L (Half Day) - Annual Leave</t>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G137" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7015,8 +7015,7 @@
       <c r="E283" s="5" t="n"/>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>A/L (Half Day) - Annual Leave
-A/L - 1/2 Day Annual Leave</t>
+          <t>A/L (Half Day) - 1/2 Day Annual Leave</t>
         </is>
       </c>
       <c r="G283" s="5" t="n"/>
@@ -7073,8 +7072,7 @@
       <c r="E284" s="5" t="n"/>
       <c r="F284" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G284" s="5" t="n"/>
@@ -7191,8 +7189,7 @@
       <c r="E287" s="5" t="n"/>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G287" s="4" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7079,7 +7079,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (5)
+          <t>A/L - Annual Leave
 A/L - Annual Leave</t>
         </is>
       </c>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -6855,8 +6855,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J280" s="6" t="inlineStr">
@@ -6908,8 +6907,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
@@ -6961,8 +6959,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J282" s="6" t="inlineStr">
@@ -7022,8 +7019,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
@@ -7079,8 +7075,7 @@
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8916,11 +8916,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J338" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="J338" s="5" t="n"/>
       <c r="K338" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
@@ -8948,11 +8944,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J339" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="J339" s="5" t="n"/>
       <c r="K339" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>
@@ -8980,11 +8972,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J340" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="J340" s="5" t="n"/>
       <c r="K340" s="11" t="inlineStr">
         <is>
           <t>Offline Edit - Mabli a Ceff Ceff</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -6967,11 +6967,7 @@
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="K282" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K282" s="5" t="n"/>
       <c r="L282" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
@@ -7027,11 +7023,7 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K283" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K283" s="5" t="n"/>
       <c r="L283" s="6" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
@@ -7083,11 +7075,7 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K284" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K284" s="5" t="n"/>
       <c r="L284" s="6" t="inlineStr">
         <is>
           <t>Black History 2026</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8230,8 +8230,7 @@
       <c r="K317" s="5" t="n"/>
       <c r="L317" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-A/L - Annual Leave</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="M317" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7160,7 +7160,7 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave (1)</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -47,12 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="C2" s="5" t="n"/>
@@ -617,7 +617,7 @@
           <t>Thu 20 Nov 2025</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -641,7 +641,7 @@
           <t>Fri 21 Nov 2025</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -705,7 +705,7 @@
           <t>Mon 24 Nov 2025</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -729,7 +729,7 @@
           <t>Tue 25 Nov 2025</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -753,7 +753,7 @@
           <t>Wed 26 Nov 2025</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -1146,7 +1146,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1170,7 +1170,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1285,7 +1285,7 @@
           <t>Mon 22 Dec 2025</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1295,18 +1295,18 @@
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J35" s="5" t="n"/>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1321,7 +1321,7 @@
           <t>Tue 23 Dec 2025</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1331,18 +1331,18 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J36" s="5" t="n"/>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1357,7 +1357,7 @@
           <t>Wed 24 Dec 2025</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -1367,18 +1367,18 @@
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J37" s="5" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K37" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1413,7 +1413,7 @@
           <t>Fri 26 Dec 2025</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1423,18 +1423,18 @@
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J39" s="5" t="n"/>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K39" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1489,7 +1489,7 @@
           <t>Mon 29 Dec 2025</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1500,7 +1500,7 @@
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1517,7 +1517,7 @@
           <t>Tue 30 Dec 2025</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1528,13 +1528,13 @@
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J43" s="5" t="n"/>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1549,7 +1549,7 @@
           <t>Wed 31 Dec 2025</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1560,7 +1560,7 @@
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1577,7 +1577,7 @@
           <t>Thu 01 Jan 2026</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1588,13 +1588,13 @@
       <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J45" s="5" t="n"/>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1609,7 +1609,7 @@
           <t>Fri 02 Jan 2026</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1620,13 +1620,13 @@
       <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
-      <c r="I46" s="4" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J46" s="5" t="n"/>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1832,7 +1832,7 @@
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="5" t="n"/>
       <c r="L56" s="5" t="n"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1856,7 +1856,7 @@
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="5" t="n"/>
       <c r="L57" s="5" t="n"/>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1880,7 +1880,7 @@
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="5" t="n"/>
       <c r="L58" s="5" t="n"/>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1904,7 +1904,7 @@
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="5" t="n"/>
       <c r="L59" s="5" t="n"/>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -1928,7 +1928,7 @@
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="5" t="n"/>
       <c r="L60" s="5" t="n"/>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -2568,7 +2568,7 @@
       <c r="F92" s="5" t="n"/>
       <c r="G92" s="5" t="n"/>
       <c r="H92" s="5" t="n"/>
-      <c r="I92" s="4" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -2592,7 +2592,7 @@
       <c r="F93" s="5" t="n"/>
       <c r="G93" s="5" t="n"/>
       <c r="H93" s="5" t="n"/>
-      <c r="I93" s="4" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -2900,7 +2900,7 @@
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="5" t="n"/>
       <c r="L108" s="5" t="n"/>
-      <c r="M108" s="4" t="inlineStr">
+      <c r="M108" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -2924,7 +2924,7 @@
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="5" t="n"/>
       <c r="L109" s="5" t="n"/>
-      <c r="M109" s="4" t="inlineStr">
+      <c r="M109" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -2988,7 +2988,7 @@
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="5" t="n"/>
       <c r="L112" s="5" t="n"/>
-      <c r="M112" s="4" t="inlineStr">
+      <c r="M112" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3067,7 +3067,7 @@
       <c r="E116" s="5" t="n"/>
       <c r="F116" s="5" t="n"/>
       <c r="G116" s="5" t="n"/>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="H116" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3131,7 +3131,7 @@
       <c r="E119" s="5" t="n"/>
       <c r="F119" s="5" t="n"/>
       <c r="G119" s="5" t="n"/>
-      <c r="H119" s="4" t="inlineStr">
+      <c r="H119" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3155,7 +3155,7 @@
       <c r="E120" s="5" t="n"/>
       <c r="F120" s="5" t="n"/>
       <c r="G120" s="5" t="n"/>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3413,7 +3413,7 @@
           <t>Mon 30 Mar 2026</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3457,7 +3457,7 @@
           <t>Wed 01 Apr 2026</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3465,7 +3465,7 @@
       <c r="C135" s="5" t="n"/>
       <c r="D135" s="5" t="n"/>
       <c r="E135" s="5" t="n"/>
-      <c r="F135" s="4" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3485,7 +3485,7 @@
           <t>Thu 02 Apr 2026</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3493,7 +3493,7 @@
       <c r="C136" s="5" t="n"/>
       <c r="D136" s="5" t="n"/>
       <c r="E136" s="5" t="n"/>
-      <c r="F136" s="4" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3513,7 +3513,7 @@
           <t>Fri 03 Apr 2026</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3521,7 +3521,7 @@
       <c r="C137" s="5" t="n"/>
       <c r="D137" s="5" t="n"/>
       <c r="E137" s="5" t="n"/>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3529,7 +3529,7 @@
       <c r="G137" s="5" t="n"/>
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="n"/>
-      <c r="J137" s="4" t="inlineStr">
+      <c r="J137" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3537,7 +3537,7 @@
       <c r="K137" s="5" t="n"/>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n"/>
-      <c r="N137" s="4" t="inlineStr">
+      <c r="N137" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3593,7 +3593,7 @@
       <c r="C140" s="5" t="n"/>
       <c r="D140" s="5" t="n"/>
       <c r="E140" s="5" t="n"/>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3605,7 +3605,7 @@
       <c r="K140" s="5" t="n"/>
       <c r="L140" s="5" t="n"/>
       <c r="M140" s="5" t="n"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="N140" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3621,7 +3621,7 @@
       <c r="C141" s="5" t="n"/>
       <c r="D141" s="5" t="n"/>
       <c r="E141" s="5" t="n"/>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3645,7 +3645,7 @@
       <c r="C142" s="5" t="n"/>
       <c r="D142" s="5" t="n"/>
       <c r="E142" s="5" t="n"/>
-      <c r="F142" s="4" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3669,7 +3669,7 @@
       <c r="C143" s="5" t="n"/>
       <c r="D143" s="5" t="n"/>
       <c r="E143" s="5" t="n"/>
-      <c r="F143" s="4" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -3693,7 +3693,7 @@
       <c r="C144" s="5" t="n"/>
       <c r="D144" s="5" t="n"/>
       <c r="E144" s="5" t="n"/>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4117,7 +4117,7 @@
       <c r="C165" s="5" t="n"/>
       <c r="D165" s="5" t="n"/>
       <c r="E165" s="5" t="n"/>
-      <c r="F165" s="6" t="inlineStr">
+      <c r="F165" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -4181,7 +4181,7 @@
       <c r="C168" s="5" t="n"/>
       <c r="D168" s="5" t="n"/>
       <c r="E168" s="5" t="n"/>
-      <c r="F168" s="4" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4201,7 +4201,7 @@
           <t>Tue 05 May 2026</t>
         </is>
       </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
@@ -4609,14 +4609,14 @@
       <c r="C189" s="5" t="n"/>
       <c r="D189" s="5" t="n"/>
       <c r="E189" s="5" t="n"/>
-      <c r="F189" s="4" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G189" s="5" t="n"/>
       <c r="H189" s="5" t="n"/>
-      <c r="I189" s="4" t="inlineStr">
+      <c r="I189" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4637,14 +4637,14 @@
       <c r="C190" s="5" t="n"/>
       <c r="D190" s="5" t="n"/>
       <c r="E190" s="5" t="n"/>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G190" s="5" t="n"/>
       <c r="H190" s="5" t="n"/>
-      <c r="I190" s="4" t="inlineStr">
+      <c r="I190" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4665,14 +4665,14 @@
       <c r="C191" s="5" t="n"/>
       <c r="D191" s="5" t="n"/>
       <c r="E191" s="5" t="n"/>
-      <c r="F191" s="4" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G191" s="5" t="n"/>
       <c r="H191" s="5" t="n"/>
-      <c r="I191" s="4" t="inlineStr">
+      <c r="I191" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4696,7 +4696,7 @@
       <c r="F192" s="5" t="n"/>
       <c r="G192" s="5" t="n"/>
       <c r="H192" s="5" t="n"/>
-      <c r="I192" s="4" t="inlineStr">
+      <c r="I192" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4720,7 +4720,7 @@
       <c r="F193" s="5" t="n"/>
       <c r="G193" s="5" t="n"/>
       <c r="H193" s="5" t="n"/>
-      <c r="I193" s="4" t="inlineStr">
+      <c r="I193" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4823,14 +4823,14 @@
       <c r="E198" s="5" t="n"/>
       <c r="F198" s="5" t="n"/>
       <c r="G198" s="5" t="n"/>
-      <c r="H198" s="4" t="inlineStr">
+      <c r="H198" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I198" s="5" t="n"/>
       <c r="J198" s="5" t="n"/>
-      <c r="K198" s="4" t="inlineStr">
+      <c r="K198" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4851,7 +4851,7 @@
       <c r="E199" s="5" t="n"/>
       <c r="F199" s="5" t="n"/>
       <c r="G199" s="5" t="n"/>
-      <c r="H199" s="4" t="inlineStr">
+      <c r="H199" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4875,7 +4875,7 @@
       <c r="E200" s="5" t="n"/>
       <c r="F200" s="5" t="n"/>
       <c r="G200" s="5" t="n"/>
-      <c r="H200" s="4" t="inlineStr">
+      <c r="H200" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4939,18 +4939,18 @@
       <c r="E203" s="5" t="n"/>
       <c r="F203" s="5" t="n"/>
       <c r="G203" s="5" t="n"/>
-      <c r="H203" s="4" t="inlineStr">
+      <c r="H203" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I203" s="5" t="n"/>
-      <c r="J203" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="K203" s="4" t="inlineStr">
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4971,14 +4971,14 @@
       <c r="E204" s="5" t="n"/>
       <c r="F204" s="5" t="n"/>
       <c r="G204" s="5" t="n"/>
-      <c r="H204" s="4" t="inlineStr">
+      <c r="H204" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I204" s="5" t="n"/>
       <c r="J204" s="5" t="n"/>
-      <c r="K204" s="4" t="inlineStr">
+      <c r="K204" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -4999,14 +4999,14 @@
       <c r="E205" s="5" t="n"/>
       <c r="F205" s="5" t="n"/>
       <c r="G205" s="5" t="n"/>
-      <c r="H205" s="4" t="inlineStr">
+      <c r="H205" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I205" s="5" t="n"/>
       <c r="J205" s="5" t="n"/>
-      <c r="K205" s="4" t="inlineStr">
+      <c r="K205" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5030,7 +5030,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="n"/>
       <c r="J206" s="5" t="n"/>
-      <c r="K206" s="4" t="inlineStr">
+      <c r="K206" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5054,7 +5054,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="n"/>
       <c r="J207" s="5" t="n"/>
-      <c r="K207" s="4" t="inlineStr">
+      <c r="K207" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5118,12 +5118,12 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="n"/>
       <c r="J210" s="5" t="n"/>
-      <c r="K210" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L210" s="4" t="inlineStr">
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L210" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5143,19 +5143,19 @@
       <c r="E211" s="5" t="n"/>
       <c r="F211" s="5" t="n"/>
       <c r="G211" s="5" t="n"/>
-      <c r="H211" s="4" t="inlineStr">
+      <c r="H211" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I211" s="5" t="n"/>
       <c r="J211" s="5" t="n"/>
-      <c r="K211" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L211" s="4" t="inlineStr">
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5175,7 +5175,7 @@
       <c r="E212" s="5" t="n"/>
       <c r="F212" s="5" t="n"/>
       <c r="G212" s="5" t="n"/>
-      <c r="H212" s="4" t="inlineStr">
+      <c r="H212" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5183,7 +5183,7 @@
       <c r="I212" s="5" t="n"/>
       <c r="J212" s="5" t="n"/>
       <c r="K212" s="5" t="n"/>
-      <c r="L212" s="4" t="inlineStr">
+      <c r="L212" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5203,7 +5203,7 @@
       <c r="E213" s="5" t="n"/>
       <c r="F213" s="5" t="n"/>
       <c r="G213" s="5" t="n"/>
-      <c r="H213" s="4" t="inlineStr">
+      <c r="H213" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5213,7 +5213,7 @@
       <c r="K213" s="5" t="n"/>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
-      <c r="N213" s="4" t="inlineStr">
+      <c r="N213" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5231,7 +5231,7 @@
       <c r="E214" s="5" t="n"/>
       <c r="F214" s="5" t="n"/>
       <c r="G214" s="5" t="n"/>
-      <c r="H214" s="4" t="inlineStr">
+      <c r="H214" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5241,7 +5241,7 @@
       <c r="K214" s="5" t="n"/>
       <c r="L214" s="5" t="n"/>
       <c r="M214" s="5" t="n"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="N214" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5299,7 +5299,7 @@
       <c r="E217" s="5" t="n"/>
       <c r="F217" s="5" t="n"/>
       <c r="G217" s="5" t="n"/>
-      <c r="H217" s="4" t="inlineStr">
+      <c r="H217" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5309,7 +5309,7 @@
       <c r="K217" s="5" t="n"/>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
-      <c r="N217" s="4" t="inlineStr">
+      <c r="N217" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5327,7 +5327,7 @@
       <c r="E218" s="5" t="n"/>
       <c r="F218" s="5" t="n"/>
       <c r="G218" s="5" t="n"/>
-      <c r="H218" s="4" t="inlineStr">
+      <c r="H218" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5337,7 +5337,7 @@
       <c r="K218" s="5" t="n"/>
       <c r="L218" s="5" t="n"/>
       <c r="M218" s="5" t="n"/>
-      <c r="N218" s="4" t="inlineStr">
+      <c r="N218" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5361,7 +5361,7 @@
       <c r="K219" s="5" t="n"/>
       <c r="L219" s="5" t="n"/>
       <c r="M219" s="5" t="n"/>
-      <c r="N219" s="4" t="inlineStr">
+      <c r="N219" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5522,7 +5522,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="n"/>
       <c r="J227" s="5" t="n"/>
-      <c r="K227" s="4" t="inlineStr">
+      <c r="K227" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5543,20 +5543,20 @@
       <c r="E228" s="5" t="n"/>
       <c r="F228" s="5" t="n"/>
       <c r="G228" s="5" t="n"/>
-      <c r="H228" s="4" t="inlineStr">
+      <c r="H228" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I228" s="5" t="n"/>
       <c r="J228" s="5" t="n"/>
-      <c r="K228" s="4" t="inlineStr">
+      <c r="K228" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="L228" s="5" t="n"/>
-      <c r="M228" s="4" t="inlineStr">
+      <c r="M228" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5615,20 +5615,20 @@
       <c r="E231" s="5" t="n"/>
       <c r="F231" s="5" t="n"/>
       <c r="G231" s="5" t="n"/>
-      <c r="H231" s="4" t="inlineStr">
+      <c r="H231" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="I231" s="5" t="n"/>
       <c r="J231" s="5" t="n"/>
-      <c r="K231" s="4" t="inlineStr">
+      <c r="K231" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="L231" s="5" t="n"/>
-      <c r="M231" s="4" t="inlineStr">
+      <c r="M231" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5650,7 +5650,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="n"/>
       <c r="J232" s="5" t="n"/>
-      <c r="K232" s="4" t="inlineStr">
+      <c r="K232" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5715,7 +5715,7 @@
       <c r="I235" s="5" t="n"/>
       <c r="J235" s="5" t="n"/>
       <c r="K235" s="5" t="n"/>
-      <c r="L235" s="4" t="inlineStr">
+      <c r="L235" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5801,7 +5801,7 @@
       <c r="K239" s="5" t="n"/>
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="5" t="n"/>
-      <c r="N239" s="4" t="inlineStr">
+      <c r="N239" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5821,7 +5821,7 @@
       <c r="G240" s="5" t="n"/>
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="n"/>
-      <c r="J240" s="4" t="inlineStr">
+      <c r="J240" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5829,7 +5829,7 @@
       <c r="K240" s="5" t="n"/>
       <c r="L240" s="5" t="n"/>
       <c r="M240" s="5" t="n"/>
-      <c r="N240" s="4" t="inlineStr">
+      <c r="N240" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5853,7 +5853,7 @@
       <c r="K241" s="5" t="n"/>
       <c r="L241" s="5" t="n"/>
       <c r="M241" s="5" t="n"/>
-      <c r="N241" s="4" t="inlineStr">
+      <c r="N241" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5877,7 +5877,7 @@
       <c r="K242" s="5" t="n"/>
       <c r="L242" s="5" t="n"/>
       <c r="M242" s="5" t="n"/>
-      <c r="N242" s="4" t="inlineStr">
+      <c r="N242" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5937,19 +5937,19 @@
       <c r="G245" s="5" t="n"/>
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="n"/>
-      <c r="J245" s="4" t="inlineStr">
+      <c r="J245" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="K245" s="5" t="n"/>
       <c r="L245" s="5" t="n"/>
-      <c r="M245" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N245" s="4" t="inlineStr">
+      <c r="M245" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N245" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -5972,12 +5972,12 @@
       <c r="J246" s="5" t="n"/>
       <c r="K246" s="5" t="n"/>
       <c r="L246" s="5" t="n"/>
-      <c r="M246" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N246" s="4" t="inlineStr">
+      <c r="M246" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N246" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6000,12 +6000,12 @@
       <c r="J247" s="5" t="n"/>
       <c r="K247" s="5" t="n"/>
       <c r="L247" s="5" t="n"/>
-      <c r="M247" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N247" s="4" t="inlineStr">
+      <c r="M247" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N247" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6028,7 +6028,7 @@
       <c r="J248" s="5" t="n"/>
       <c r="K248" s="5" t="n"/>
       <c r="L248" s="5" t="n"/>
-      <c r="M248" s="4" t="inlineStr">
+      <c r="M248" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6101,7 +6101,7 @@
           <t>Mon 27 Jul 2026</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B252" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6125,7 +6125,7 @@
           <t>Tue 28 Jul 2026</t>
         </is>
       </c>
-      <c r="B253" s="4" t="inlineStr">
+      <c r="B253" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6149,7 +6149,7 @@
           <t>Wed 29 Jul 2026</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B254" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6173,7 +6173,7 @@
           <t>Thu 30 Jul 2026</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="B255" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6197,7 +6197,7 @@
           <t>Fri 31 Jul 2026</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="B256" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6261,7 +6261,7 @@
           <t>Mon 03 Aug 2026</t>
         </is>
       </c>
-      <c r="B259" s="4" t="inlineStr">
+      <c r="B259" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6269,7 +6269,7 @@
       <c r="C259" s="5" t="n"/>
       <c r="D259" s="5" t="n"/>
       <c r="E259" s="5" t="n"/>
-      <c r="F259" s="4" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6280,7 +6280,7 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I259" s="4" t="inlineStr">
+      <c r="I259" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6297,7 +6297,7 @@
           <t>Tue 04 Aug 2026</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="B260" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6305,7 +6305,7 @@
       <c r="C260" s="5" t="n"/>
       <c r="D260" s="5" t="n"/>
       <c r="E260" s="5" t="n"/>
-      <c r="F260" s="4" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6316,7 +6316,7 @@
           <t>TOIL - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I260" s="4" t="inlineStr">
+      <c r="I260" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6337,14 +6337,14 @@
       <c r="C261" s="5" t="n"/>
       <c r="D261" s="5" t="n"/>
       <c r="E261" s="5" t="n"/>
-      <c r="F261" s="4" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G261" s="5" t="n"/>
       <c r="H261" s="5" t="n"/>
-      <c r="I261" s="4" t="inlineStr">
+      <c r="I261" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6365,14 +6365,14 @@
       <c r="C262" s="5" t="n"/>
       <c r="D262" s="5" t="n"/>
       <c r="E262" s="5" t="n"/>
-      <c r="F262" s="4" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G262" s="5" t="n"/>
       <c r="H262" s="5" t="n"/>
-      <c r="I262" s="4" t="inlineStr">
+      <c r="I262" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6393,7 +6393,7 @@
       <c r="C263" s="5" t="n"/>
       <c r="D263" s="5" t="n"/>
       <c r="E263" s="5" t="n"/>
-      <c r="F263" s="4" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6404,7 +6404,7 @@
           <t>Delivery - Rhwym Galon</t>
         </is>
       </c>
-      <c r="I263" s="4" t="inlineStr">
+      <c r="I263" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6461,13 +6461,13 @@
           <t>Mon 10 Aug 2026</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C266" s="5" t="n"/>
-      <c r="D266" s="4" t="inlineStr">
+      <c r="D266" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6476,7 +6476,7 @@
       <c r="F266" s="5" t="n"/>
       <c r="G266" s="5" t="n"/>
       <c r="H266" s="5" t="n"/>
-      <c r="I266" s="4" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6493,32 +6493,32 @@
           <t>Tue 11 Aug 2026</t>
         </is>
       </c>
-      <c r="B267" s="4" t="inlineStr">
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C267" s="5" t="n"/>
-      <c r="D267" s="4" t="inlineStr">
+      <c r="D267" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="E267" s="5" t="n"/>
-      <c r="F267" s="6" t="inlineStr">
+      <c r="F267" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - Annual Leave</t>
         </is>
       </c>
       <c r="G267" s="5" t="n"/>
       <c r="H267" s="5" t="n"/>
-      <c r="I267" s="4" t="inlineStr">
+      <c r="I267" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J267" s="5" t="n"/>
-      <c r="K267" s="4" t="inlineStr">
+      <c r="K267" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6533,13 +6533,13 @@
           <t>Wed 12 Aug 2026</t>
         </is>
       </c>
-      <c r="B268" s="4" t="inlineStr">
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C268" s="5" t="n"/>
-      <c r="D268" s="4" t="inlineStr">
+      <c r="D268" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6548,13 +6548,13 @@
       <c r="F268" s="5" t="n"/>
       <c r="G268" s="5" t="n"/>
       <c r="H268" s="5" t="n"/>
-      <c r="I268" s="4" t="inlineStr">
+      <c r="I268" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J268" s="5" t="n"/>
-      <c r="K268" s="4" t="inlineStr">
+      <c r="K268" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6569,14 +6569,14 @@
           <t>Thu 13 Aug 2026</t>
         </is>
       </c>
-      <c r="B269" s="4" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave
 A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C269" s="5" t="n"/>
-      <c r="D269" s="4" t="inlineStr">
+      <c r="D269" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6585,7 +6585,7 @@
       <c r="F269" s="5" t="n"/>
       <c r="G269" s="5" t="n"/>
       <c r="H269" s="5" t="n"/>
-      <c r="I269" s="4" t="inlineStr">
+      <c r="I269" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6602,7 +6602,7 @@
           <t>Fri 14 Aug 2026</t>
         </is>
       </c>
-      <c r="B270" s="4" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6617,14 +6617,14 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I270" s="4" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="J270" s="5" t="n"/>
       <c r="K270" s="5" t="n"/>
-      <c r="L270" s="4" t="inlineStr">
+      <c r="L270" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6688,7 +6688,7 @@
       <c r="I273" s="5" t="n"/>
       <c r="J273" s="5" t="n"/>
       <c r="K273" s="5" t="n"/>
-      <c r="L273" s="4" t="inlineStr">
+      <c r="L273" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6712,7 +6712,7 @@
       <c r="I274" s="5" t="n"/>
       <c r="J274" s="5" t="n"/>
       <c r="K274" s="5" t="n"/>
-      <c r="L274" s="4" t="inlineStr">
+      <c r="L274" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6736,7 +6736,7 @@
       <c r="I275" s="5" t="n"/>
       <c r="J275" s="5" t="n"/>
       <c r="K275" s="5" t="n"/>
-      <c r="L275" s="4" t="inlineStr">
+      <c r="L275" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6760,7 +6760,7 @@
       <c r="I276" s="5" t="n"/>
       <c r="J276" s="5" t="n"/>
       <c r="K276" s="5" t="n"/>
-      <c r="L276" s="4" t="inlineStr">
+      <c r="L276" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6784,12 +6784,12 @@
       <c r="I277" s="5" t="n"/>
       <c r="J277" s="5" t="n"/>
       <c r="K277" s="5" t="n"/>
-      <c r="L277" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="M277" s="4" t="inlineStr">
+      <c r="L277" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="M277" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="5" t="n"/>
-      <c r="D280" s="6" t="inlineStr">
+      <c r="D280" s="4" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6853,28 +6853,28 @@
       <c r="F280" s="5" t="n"/>
       <c r="G280" s="5" t="n"/>
       <c r="H280" s="5" t="n"/>
-      <c r="I280" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J280" s="6" t="inlineStr">
+      <c r="I280" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Mabli</t>
         </is>
       </c>
-      <c r="K280" s="6" t="inlineStr">
+      <c r="K280" s="4" t="inlineStr">
         <is>
           <t>Edit - Socials</t>
         </is>
       </c>
       <c r="L280" s="5" t="n"/>
-      <c r="M280" s="6" t="inlineStr">
+      <c r="M280" s="4" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N280" s="6" t="inlineStr">
+      <c r="N280" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -6886,17 +6886,17 @@
           <t>Tue 25 Aug 2026</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="C281" s="6" t="inlineStr">
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D281" s="6" t="inlineStr">
+      <c r="D281" s="4" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6905,12 +6905,12 @@
       <c r="F281" s="5" t="n"/>
       <c r="G281" s="5" t="n"/>
       <c r="H281" s="5" t="n"/>
-      <c r="I281" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J281" s="6" t="inlineStr">
+      <c r="I281" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
@@ -6921,12 +6921,12 @@
         </is>
       </c>
       <c r="L281" s="5" t="n"/>
-      <c r="M281" s="6" t="inlineStr">
+      <c r="M281" s="4" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N281" s="6" t="inlineStr">
+      <c r="N281" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -6938,17 +6938,17 @@
           <t>Wed 26 Aug 2026</t>
         </is>
       </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="C282" s="6" t="inlineStr">
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D282" s="6" t="inlineStr">
+      <c r="D282" s="4" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
@@ -6957,28 +6957,28 @@
       <c r="F282" s="5" t="n"/>
       <c r="G282" s="5" t="n"/>
       <c r="H282" s="5" t="n"/>
-      <c r="I282" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J282" s="6" t="inlineStr">
+      <c r="I282" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
       <c r="K282" s="5" t="n"/>
-      <c r="L282" s="6" t="inlineStr">
+      <c r="L282" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M282" s="6" t="inlineStr">
+      <c r="M282" s="4" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N282" s="6" t="inlineStr">
+      <c r="N282" s="4" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -6990,51 +6990,51 @@
           <t>Thu 27 Aug 2026</t>
         </is>
       </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="C283" s="6" t="inlineStr">
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
         <is>
           <t>Hansh Short</t>
         </is>
       </c>
-      <c r="D283" s="6" t="inlineStr">
+      <c r="D283" s="4" t="inlineStr">
         <is>
           <t>Anifail Perffaith</t>
         </is>
       </c>
       <c r="E283" s="5" t="n"/>
-      <c r="F283" s="6" t="inlineStr">
+      <c r="F283" s="4" t="inlineStr">
         <is>
           <t>A/L (Half Day) - 1/2 Day Annual Leave</t>
         </is>
       </c>
       <c r="G283" s="5" t="n"/>
       <c r="H283" s="5" t="n"/>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J283" s="6" t="inlineStr">
+      <c r="I283" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
       <c r="K283" s="5" t="n"/>
-      <c r="L283" s="6" t="inlineStr">
+      <c r="L283" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M283" s="6" t="inlineStr">
+      <c r="M283" s="4" t="inlineStr">
         <is>
           <t>Paperwork - PAC</t>
         </is>
       </c>
-      <c r="N283" s="6" t="inlineStr">
+      <c r="N283" s="4" t="inlineStr">
         <is>
           <t>Edit Annibynwyr</t>
         </is>
@@ -7046,37 +7046,37 @@
           <t>Fri 28 Aug 2026</t>
         </is>
       </c>
-      <c r="B284" s="4" t="inlineStr">
+      <c r="B284" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C284" s="5" t="n"/>
-      <c r="D284" s="6" t="inlineStr">
+      <c r="D284" s="4" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="E284" s="5" t="n"/>
-      <c r="F284" s="4" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="G284" s="5" t="n"/>
       <c r="H284" s="5" t="n"/>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="J284" s="6" t="inlineStr">
+      <c r="I284" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
         <is>
           <t>Datblygu</t>
         </is>
       </c>
       <c r="K284" s="5" t="n"/>
-      <c r="L284" s="6" t="inlineStr">
+      <c r="L284" s="4" t="inlineStr">
         <is>
           <t>Black History 2026</t>
         </is>
@@ -7086,7 +7086,7 @@
           <t>TOIL - Darts</t>
         </is>
       </c>
-      <c r="N284" s="6" t="inlineStr">
+      <c r="N284" s="4" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7103,7 +7103,7 @@
       <c r="D285" s="8" t="n"/>
       <c r="E285" s="8" t="n"/>
       <c r="F285" s="8" t="n"/>
-      <c r="G285" s="6" t="inlineStr">
+      <c r="G285" s="4" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
@@ -7113,12 +7113,12 @@
       <c r="J285" s="8" t="n"/>
       <c r="K285" s="8" t="n"/>
       <c r="L285" s="8" t="n"/>
-      <c r="M285" s="6" t="inlineStr">
+      <c r="M285" s="4" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N285" s="6" t="inlineStr">
+      <c r="N285" s="4" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7141,12 +7141,12 @@
       <c r="J286" s="8" t="n"/>
       <c r="K286" s="8" t="n"/>
       <c r="L286" s="8" t="n"/>
-      <c r="M286" s="6" t="inlineStr">
+      <c r="M286" s="4" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
       </c>
-      <c r="N286" s="6" t="inlineStr">
+      <c r="N286" s="4" t="inlineStr">
         <is>
           <t>External - DARTS 6 G</t>
         </is>
@@ -7158,24 +7158,24 @@
           <t>Mon 31 Aug 2026</t>
         </is>
       </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="C287" s="6" t="inlineStr">
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
       </c>
       <c r="D287" s="5" t="n"/>
       <c r="E287" s="5" t="n"/>
-      <c r="F287" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="G287" s="4" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="G287" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -7187,12 +7187,12 @@
         </is>
       </c>
       <c r="J287" s="5" t="n"/>
-      <c r="K287" s="6" t="inlineStr">
+      <c r="K287" s="4" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L287" s="6" t="inlineStr">
+      <c r="L287" s="4" t="inlineStr">
         <is>
           <t>Film - Hansh Socials</t>
         </is>
@@ -7202,7 +7202,7 @@
           <t>TOIL - Darts 6 G</t>
         </is>
       </c>
-      <c r="N287" s="6" t="inlineStr">
+      <c r="N287" s="4" t="inlineStr">
         <is>
           <t>External - Darts 6 G</t>
         </is>
@@ -7227,22 +7227,22 @@
         </is>
       </c>
       <c r="J288" s="5" t="n"/>
-      <c r="K288" s="6" t="inlineStr">
+      <c r="K288" s="4" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L288" s="6" t="inlineStr">
+      <c r="L288" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M288" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N288" s="6" t="inlineStr">
+      <c r="M288" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N288" s="4" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -7267,22 +7267,22 @@
         </is>
       </c>
       <c r="J289" s="5" t="n"/>
-      <c r="K289" s="6" t="inlineStr">
+      <c r="K289" s="4" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L289" s="6" t="inlineStr">
+      <c r="L289" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M289" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N289" s="6" t="inlineStr">
+      <c r="M289" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N289" s="4" t="inlineStr">
         <is>
           <t>Edit - Hansh Socials</t>
         </is>
@@ -7294,7 +7294,7 @@
           <t>Thu 03 Sep 2026</t>
         </is>
       </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="B290" s="4" t="inlineStr">
         <is>
           <t>Linda Wilson</t>
         </is>
@@ -7303,34 +7303,34 @@
       <c r="D290" s="5" t="n"/>
       <c r="E290" s="5" t="n"/>
       <c r="F290" s="5" t="n"/>
-      <c r="G290" s="6" t="inlineStr">
+      <c r="G290" s="4" t="inlineStr">
         <is>
           <t>Film - Linda Wilson</t>
         </is>
       </c>
       <c r="H290" s="5" t="n"/>
-      <c r="I290" s="6" t="inlineStr">
+      <c r="I290" s="4" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
         </is>
       </c>
       <c r="J290" s="5" t="n"/>
-      <c r="K290" s="6" t="inlineStr">
+      <c r="K290" s="4" t="inlineStr">
         <is>
           <t>Socials - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L290" s="6" t="inlineStr">
+      <c r="L290" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M290" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N290" s="6" t="inlineStr">
+      <c r="M290" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N290" s="4" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -7342,7 +7342,7 @@
           <t>Fri 04 Sep 2026</t>
         </is>
       </c>
-      <c r="B291" s="6" t="inlineStr">
+      <c r="B291" s="4" t="inlineStr">
         <is>
           <t>Linda Wilson</t>
         </is>
@@ -7359,22 +7359,22 @@
         </is>
       </c>
       <c r="J291" s="5" t="n"/>
-      <c r="K291" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L291" s="6" t="inlineStr">
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="M291" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N291" s="6" t="inlineStr">
+      <c r="M291" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N291" s="4" t="inlineStr">
         <is>
           <t>Edit - Fresh From Wales</t>
         </is>
@@ -7433,28 +7433,28 @@
       <c r="F294" s="5" t="n"/>
       <c r="G294" s="5" t="n"/>
       <c r="H294" s="5" t="n"/>
-      <c r="I294" s="6" t="inlineStr">
+      <c r="I294" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J294" s="5" t="n"/>
-      <c r="K294" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="L294" s="6" t="inlineStr">
+      <c r="K294" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M294" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N294" s="6" t="inlineStr">
+      <c r="M294" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N294" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7473,28 +7473,28 @@
       <c r="F295" s="5" t="n"/>
       <c r="G295" s="5" t="n"/>
       <c r="H295" s="5" t="n"/>
-      <c r="I295" s="6" t="inlineStr">
+      <c r="I295" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J295" s="5" t="n"/>
-      <c r="K295" s="6" t="inlineStr">
+      <c r="K295" s="4" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L295" s="6" t="inlineStr">
+      <c r="L295" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M295" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N295" s="6" t="inlineStr">
+      <c r="M295" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N295" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7513,28 +7513,28 @@
       <c r="F296" s="5" t="n"/>
       <c r="G296" s="5" t="n"/>
       <c r="H296" s="5" t="n"/>
-      <c r="I296" s="6" t="inlineStr">
+      <c r="I296" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J296" s="5" t="n"/>
-      <c r="K296" s="6" t="inlineStr">
+      <c r="K296" s="4" t="inlineStr">
         <is>
           <t>Edit - Rookie Teachers</t>
         </is>
       </c>
-      <c r="L296" s="6" t="inlineStr">
+      <c r="L296" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M296" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N296" s="6" t="inlineStr">
+      <c r="M296" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N296" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7553,28 +7553,28 @@
       <c r="F297" s="5" t="n"/>
       <c r="G297" s="5" t="n"/>
       <c r="H297" s="5" t="n"/>
-      <c r="I297" s="6" t="inlineStr">
+      <c r="I297" s="4" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
       <c r="J297" s="5" t="n"/>
-      <c r="K297" s="6" t="inlineStr">
+      <c r="K297" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
       </c>
-      <c r="L297" s="6" t="inlineStr">
+      <c r="L297" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M297" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N297" s="6" t="inlineStr">
+      <c r="M297" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N297" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7593,24 +7593,24 @@
       <c r="F298" s="5" t="n"/>
       <c r="G298" s="5" t="n"/>
       <c r="H298" s="5" t="n"/>
-      <c r="I298" s="6" t="inlineStr">
+      <c r="I298" s="4" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>
         </is>
       </c>
       <c r="J298" s="5" t="n"/>
       <c r="K298" s="5" t="n"/>
-      <c r="L298" s="6" t="inlineStr">
+      <c r="L298" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
       </c>
-      <c r="M298" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N298" s="6" t="inlineStr">
+      <c r="M298" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N298" s="4" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>
         </is>
@@ -7673,7 +7673,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I301" s="6" t="inlineStr">
+      <c r="I301" s="4" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
@@ -7705,7 +7705,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I302" s="6" t="inlineStr">
+      <c r="I302" s="4" t="inlineStr">
         <is>
           <t>Sw Ni - Prep</t>
         </is>
@@ -7748,20 +7748,20 @@
       </c>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="5" t="n"/>
-      <c r="D304" s="6" t="inlineStr">
+      <c r="D304" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E304" s="5" t="n"/>
-      <c r="F304" s="6" t="inlineStr">
+      <c r="F304" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G304" s="5" t="n"/>
       <c r="H304" s="5" t="n"/>
-      <c r="I304" s="6" t="inlineStr">
+      <c r="I304" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7770,7 +7770,7 @@
       <c r="K304" s="5" t="n"/>
       <c r="L304" s="5" t="n"/>
       <c r="M304" s="5" t="n"/>
-      <c r="N304" s="6" t="inlineStr">
+      <c r="N304" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7784,20 +7784,20 @@
       </c>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="5" t="n"/>
-      <c r="D305" s="6" t="inlineStr">
+      <c r="D305" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E305" s="5" t="n"/>
-      <c r="F305" s="6" t="inlineStr">
+      <c r="F305" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G305" s="5" t="n"/>
       <c r="H305" s="5" t="n"/>
-      <c r="I305" s="6" t="inlineStr">
+      <c r="I305" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7806,7 +7806,7 @@
       <c r="K305" s="5" t="n"/>
       <c r="L305" s="5" t="n"/>
       <c r="M305" s="5" t="n"/>
-      <c r="N305" s="6" t="inlineStr">
+      <c r="N305" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -7860,33 +7860,33 @@
       </c>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="5" t="n"/>
-      <c r="D308" s="6" t="inlineStr">
+      <c r="D308" s="4" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E308" s="5" t="n"/>
-      <c r="F308" s="6" t="inlineStr">
+      <c r="F308" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G308" s="5" t="n"/>
       <c r="H308" s="5" t="n"/>
-      <c r="I308" s="6" t="inlineStr">
+      <c r="I308" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J308" s="5" t="n"/>
-      <c r="K308" s="6" t="inlineStr">
+      <c r="K308" s="4" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L308" s="5" t="n"/>
       <c r="M308" s="5" t="n"/>
-      <c r="N308" s="6" t="inlineStr">
+      <c r="N308" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7900,37 +7900,37 @@
       </c>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="5" t="n"/>
-      <c r="D309" s="6" t="inlineStr">
+      <c r="D309" s="4" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E309" s="5" t="n"/>
-      <c r="F309" s="6" t="inlineStr">
+      <c r="F309" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G309" s="5" t="n"/>
       <c r="H309" s="5" t="n"/>
-      <c r="I309" s="6" t="inlineStr">
+      <c r="I309" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J309" s="5" t="n"/>
-      <c r="K309" s="6" t="inlineStr">
+      <c r="K309" s="4" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L309" s="5" t="n"/>
-      <c r="M309" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N309" s="6" t="inlineStr">
+      <c r="M309" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N309" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7944,37 +7944,37 @@
       </c>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="5" t="n"/>
-      <c r="D310" s="6" t="inlineStr">
+      <c r="D310" s="4" t="inlineStr">
         <is>
           <t>Edit - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="E310" s="5" t="n"/>
-      <c r="F310" s="6" t="inlineStr">
+      <c r="F310" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="G310" s="5" t="n"/>
       <c r="H310" s="5" t="n"/>
-      <c r="I310" s="6" t="inlineStr">
+      <c r="I310" s="4" t="inlineStr">
         <is>
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
       <c r="J310" s="5" t="n"/>
-      <c r="K310" s="6" t="inlineStr">
+      <c r="K310" s="4" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L310" s="5" t="n"/>
-      <c r="M310" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N310" s="6" t="inlineStr">
+      <c r="M310" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N310" s="4" t="inlineStr">
         <is>
           <t>Hansh Socials</t>
         </is>
@@ -7988,37 +7988,37 @@
       </c>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="5" t="n"/>
-      <c r="D311" s="6" t="inlineStr">
+      <c r="D311" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E311" s="5" t="n"/>
-      <c r="F311" s="6" t="inlineStr">
+      <c r="F311" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G311" s="5" t="n"/>
       <c r="H311" s="5" t="n"/>
-      <c r="I311" s="6" t="inlineStr">
+      <c r="I311" s="4" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
       <c r="J311" s="5" t="n"/>
-      <c r="K311" s="6" t="inlineStr">
+      <c r="K311" s="4" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L311" s="5" t="n"/>
-      <c r="M311" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N311" s="6" t="inlineStr">
+      <c r="M311" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N311" s="4" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -8032,13 +8032,13 @@
       </c>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="5" t="n"/>
-      <c r="D312" s="6" t="inlineStr">
+      <c r="D312" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E312" s="5" t="n"/>
-      <c r="F312" s="6" t="inlineStr">
+      <c r="F312" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8049,24 +8049,24 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I312" s="6" t="inlineStr">
+      <c r="I312" s="4" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
       </c>
       <c r="J312" s="5" t="n"/>
-      <c r="K312" s="6" t="inlineStr">
+      <c r="K312" s="4" t="inlineStr">
         <is>
           <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L312" s="5" t="n"/>
-      <c r="M312" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N312" s="6" t="inlineStr">
+      <c r="M312" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N312" s="4" t="inlineStr">
         <is>
           <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
         </is>
@@ -8120,13 +8120,13 @@
       </c>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="5" t="n"/>
-      <c r="D315" s="6" t="inlineStr">
+      <c r="D315" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E315" s="5" t="n"/>
-      <c r="F315" s="6" t="inlineStr">
+      <c r="F315" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8137,24 +8137,24 @@
           <t>Delivery - Black History 2026</t>
         </is>
       </c>
-      <c r="I315" s="6" t="inlineStr">
+      <c r="I315" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="J315" s="5" t="n"/>
-      <c r="K315" s="4" t="inlineStr">
+      <c r="K315" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="L315" s="5" t="n"/>
-      <c r="M315" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N315" s="6" t="inlineStr">
+      <c r="M315" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N315" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8168,20 +8168,20 @@
       </c>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="5" t="n"/>
-      <c r="D316" s="6" t="inlineStr">
+      <c r="D316" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E316" s="5" t="n"/>
-      <c r="F316" s="6" t="inlineStr">
+      <c r="F316" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G316" s="5" t="n"/>
       <c r="H316" s="5" t="n"/>
-      <c r="I316" s="6" t="inlineStr">
+      <c r="I316" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8189,12 +8189,12 @@
       <c r="J316" s="5" t="n"/>
       <c r="K316" s="5" t="n"/>
       <c r="L316" s="5" t="n"/>
-      <c r="M316" s="4" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
-      <c r="N316" s="6" t="inlineStr">
+      <c r="M316" s="6" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
+      <c r="N316" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8208,33 +8208,33 @@
       </c>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="5" t="n"/>
-      <c r="D317" s="6" t="inlineStr">
+      <c r="D317" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E317" s="5" t="n"/>
-      <c r="F317" s="6" t="inlineStr">
+      <c r="F317" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G317" s="5" t="n"/>
       <c r="H317" s="5" t="n"/>
-      <c r="I317" s="6" t="inlineStr">
+      <c r="I317" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="J317" s="5" t="n"/>
       <c r="K317" s="5" t="n"/>
-      <c r="L317" s="4" t="inlineStr">
+      <c r="L317" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="M317" s="5" t="n"/>
-      <c r="N317" s="6" t="inlineStr">
+      <c r="N317" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8248,33 +8248,33 @@
       </c>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="5" t="n"/>
-      <c r="D318" s="6" t="inlineStr">
+      <c r="D318" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="E318" s="5" t="n"/>
-      <c r="F318" s="6" t="inlineStr">
+      <c r="F318" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G318" s="5" t="n"/>
       <c r="H318" s="5" t="n"/>
-      <c r="I318" s="6" t="inlineStr">
+      <c r="I318" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="J318" s="5" t="n"/>
       <c r="K318" s="5" t="n"/>
-      <c r="L318" s="4" t="inlineStr">
+      <c r="L318" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="M318" s="5" t="n"/>
-      <c r="N318" s="6" t="inlineStr">
+      <c r="N318" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
         </is>
@@ -8286,71 +8286,71 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B319" s="6" t="inlineStr">
+      <c r="B319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="C319" s="6" t="inlineStr">
+      <c r="C319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="D319" s="6" t="inlineStr">
+      <c r="D319" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr">
+      <c r="F319" s="4" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="G319" s="6" t="inlineStr">
+      <c r="G319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="H319" s="6" t="inlineStr">
+      <c r="H319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="I319" s="6" t="inlineStr">
+      <c r="I319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J319" s="6" t="inlineStr">
+      <c r="J319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="K319" s="6" t="inlineStr">
+      <c r="K319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="L319" s="4" t="inlineStr">
+      <c r="L319" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave
 Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="M319" s="6" t="inlineStr">
+      <c r="M319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon</t>
         </is>
       </c>
-      <c r="N319" s="6" t="inlineStr">
+      <c r="N319" s="4" t="inlineStr">
         <is>
           <t>Parti Dathlu S4C Athrawon
 Film - Sŵ Ni</t>
@@ -8413,7 +8413,7 @@
       <c r="I322" s="5" t="n"/>
       <c r="J322" s="5" t="n"/>
       <c r="K322" s="5" t="n"/>
-      <c r="L322" s="4" t="inlineStr">
+      <c r="L322" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8437,7 +8437,7 @@
       <c r="I323" s="5" t="n"/>
       <c r="J323" s="5" t="n"/>
       <c r="K323" s="5" t="n"/>
-      <c r="L323" s="4" t="inlineStr">
+      <c r="L323" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8463,13 +8463,13 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J324" s="4" t="inlineStr">
+      <c r="J324" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="K324" s="5" t="n"/>
-      <c r="L324" s="4" t="inlineStr">
+      <c r="L324" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8495,7 +8495,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J325" s="4" t="inlineStr">
+      <c r="J325" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8523,7 +8523,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J326" s="4" t="inlineStr">
+      <c r="J326" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="5" t="n"/>
-      <c r="D329" s="4" t="inlineStr">
+      <c r="D329" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8607,7 +8607,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J329" s="4" t="inlineStr">
+      <c r="J329" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="5" t="n"/>
-      <c r="D330" s="4" t="inlineStr">
+      <c r="D330" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8643,7 +8643,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J330" s="4" t="inlineStr">
+      <c r="J330" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="5" t="n"/>
-      <c r="D331" s="4" t="inlineStr">
+      <c r="D331" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8679,7 +8679,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J331" s="4" t="inlineStr">
+      <c r="J331" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="5" t="n"/>
-      <c r="D332" s="4" t="inlineStr">
+      <c r="D332" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8719,7 +8719,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J332" s="4" t="inlineStr">
+      <c r="J332" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8755,7 +8755,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J333" s="4" t="inlineStr">
+      <c r="J333" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8839,7 +8839,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J336" s="4" t="inlineStr">
+      <c r="J336" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -8871,7 +8871,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J337" s="4" t="inlineStr">
+      <c r="J337" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9258,7 +9258,7 @@
       <c r="F352" s="5" t="n"/>
       <c r="G352" s="5" t="n"/>
       <c r="H352" s="5" t="n"/>
-      <c r="I352" s="4" t="inlineStr">
+      <c r="I352" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -9286,7 +9286,7 @@
       <c r="F353" s="5" t="n"/>
       <c r="G353" s="5" t="n"/>
       <c r="H353" s="5" t="n"/>
-      <c r="I353" s="4" t="inlineStr">
+      <c r="I353" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -9314,7 +9314,7 @@
       <c r="F354" s="5" t="n"/>
       <c r="G354" s="5" t="n"/>
       <c r="H354" s="5" t="n"/>
-      <c r="I354" s="6" t="inlineStr">
+      <c r="I354" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="L354" s="5" t="n"/>
-      <c r="M354" s="4" t="inlineStr">
+      <c r="M354" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="5" t="n"/>
-      <c r="D357" s="4" t="inlineStr">
+      <c r="D357" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9390,7 +9390,7 @@
       <c r="F357" s="5" t="n"/>
       <c r="G357" s="5" t="n"/>
       <c r="H357" s="5" t="n"/>
-      <c r="I357" s="6" t="inlineStr">
+      <c r="I357" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="5" t="n"/>
-      <c r="D358" s="4" t="inlineStr">
+      <c r="D358" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="5" t="n"/>
-      <c r="D359" s="4" t="inlineStr">
+      <c r="D359" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="5" t="n"/>
-      <c r="D360" s="4" t="inlineStr">
+      <c r="D360" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9486,7 +9486,7 @@
       <c r="F360" s="5" t="n"/>
       <c r="G360" s="5" t="n"/>
       <c r="H360" s="5" t="n"/>
-      <c r="I360" s="6" t="inlineStr">
+      <c r="I360" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="5" t="n"/>
-      <c r="D361" s="4" t="inlineStr">
+      <c r="D361" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="5" t="n"/>
-      <c r="D364" s="4" t="inlineStr">
+      <c r="D364" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="5" t="n"/>
-      <c r="D365" s="4" t="inlineStr">
+      <c r="D365" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="5" t="n"/>
-      <c r="D366" s="4" t="inlineStr">
+      <c r="D366" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="5" t="n"/>
-      <c r="D367" s="4" t="inlineStr">
+      <c r="D367" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -9814,7 +9814,7 @@
       <c r="F372" s="5" t="n"/>
       <c r="G372" s="5" t="n"/>
       <c r="H372" s="5" t="n"/>
-      <c r="I372" s="6" t="inlineStr">
+      <c r="I372" s="4" t="inlineStr">
         <is>
           <t>Dub - Mabli a Ceff Ceff
 Online Edit - Mabli a Ceff Ceff</t>
@@ -9839,7 +9839,7 @@
       <c r="F373" s="5" t="n"/>
       <c r="G373" s="5" t="n"/>
       <c r="H373" s="5" t="n"/>
-      <c r="I373" s="6" t="inlineStr">
+      <c r="I373" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9863,7 +9863,7 @@
       <c r="F374" s="5" t="n"/>
       <c r="G374" s="5" t="n"/>
       <c r="H374" s="5" t="n"/>
-      <c r="I374" s="6" t="inlineStr">
+      <c r="I374" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9895,7 +9895,7 @@
           <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
-      <c r="I375" s="6" t="inlineStr">
+      <c r="I375" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9959,7 +9959,7 @@
       <c r="F378" s="5" t="n"/>
       <c r="G378" s="5" t="n"/>
       <c r="H378" s="5" t="n"/>
-      <c r="I378" s="6" t="inlineStr">
+      <c r="I378" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -9983,7 +9983,7 @@
       <c r="F379" s="5" t="n"/>
       <c r="G379" s="5" t="n"/>
       <c r="H379" s="5" t="n"/>
-      <c r="I379" s="6" t="inlineStr">
+      <c r="I379" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10167,7 +10167,7 @@
       <c r="F387" s="5" t="n"/>
       <c r="G387" s="5" t="n"/>
       <c r="H387" s="5" t="n"/>
-      <c r="I387" s="6" t="inlineStr">
+      <c r="I387" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10191,7 +10191,7 @@
       <c r="F388" s="5" t="n"/>
       <c r="G388" s="5" t="n"/>
       <c r="H388" s="5" t="n"/>
-      <c r="I388" s="6" t="inlineStr">
+      <c r="I388" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10215,7 +10215,7 @@
       <c r="F389" s="5" t="n"/>
       <c r="G389" s="5" t="n"/>
       <c r="H389" s="5" t="n"/>
-      <c r="I389" s="6" t="inlineStr">
+      <c r="I389" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10279,7 +10279,7 @@
       <c r="F392" s="5" t="n"/>
       <c r="G392" s="5" t="n"/>
       <c r="H392" s="5" t="n"/>
-      <c r="I392" s="6" t="inlineStr">
+      <c r="I392" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10311,7 +10311,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I393" s="6" t="inlineStr">
+      <c r="I393" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10343,7 +10343,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I394" s="6" t="inlineStr">
+      <c r="I394" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10375,7 +10375,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I395" s="6" t="inlineStr">
+      <c r="I395" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10407,7 +10407,7 @@
           <t>Delivery - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="I396" s="6" t="inlineStr">
+      <c r="I396" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10471,7 +10471,7 @@
       <c r="F399" s="5" t="n"/>
       <c r="G399" s="5" t="n"/>
       <c r="H399" s="5" t="n"/>
-      <c r="I399" s="6" t="inlineStr">
+      <c r="I399" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10495,7 +10495,7 @@
       <c r="F400" s="5" t="n"/>
       <c r="G400" s="5" t="n"/>
       <c r="H400" s="5" t="n"/>
-      <c r="I400" s="6" t="inlineStr">
+      <c r="I400" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10619,7 +10619,7 @@
       <c r="F406" s="5" t="n"/>
       <c r="G406" s="5" t="n"/>
       <c r="H406" s="5" t="n"/>
-      <c r="I406" s="6" t="inlineStr">
+      <c r="I406" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -10643,7 +10643,7 @@
       <c r="F407" s="5" t="n"/>
       <c r="G407" s="5" t="n"/>
       <c r="H407" s="5" t="n"/>
-      <c r="I407" s="6" t="inlineStr">
+      <c r="I407" s="4" t="inlineStr">
         <is>
           <t>Film - LGBTQ+</t>
         </is>
@@ -11651,7 +11651,7 @@
       <c r="J451" s="5" t="n"/>
       <c r="K451" s="5" t="n"/>
       <c r="L451" s="5" t="n"/>
-      <c r="M451" s="4" t="inlineStr">
+      <c r="M451" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -11679,7 +11679,7 @@
       <c r="J452" s="5" t="n"/>
       <c r="K452" s="5" t="n"/>
       <c r="L452" s="5" t="n"/>
-      <c r="M452" s="4" t="inlineStr">
+      <c r="M452" s="6" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
         </is>
@@ -12379,7 +12379,7 @@
       <c r="F483" s="5" t="n"/>
       <c r="G483" s="5" t="n"/>
       <c r="H483" s="5" t="n"/>
-      <c r="I483" s="4" t="inlineStr">
+      <c r="I483" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -12403,7 +12403,7 @@
       <c r="F484" s="5" t="n"/>
       <c r="G484" s="5" t="n"/>
       <c r="H484" s="5" t="n"/>
-      <c r="I484" s="4" t="inlineStr">
+      <c r="I484" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -12427,7 +12427,7 @@
       <c r="F485" s="5" t="n"/>
       <c r="G485" s="5" t="n"/>
       <c r="H485" s="5" t="n"/>
-      <c r="I485" s="4" t="inlineStr">
+      <c r="I485" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -12451,7 +12451,7 @@
       <c r="F486" s="5" t="n"/>
       <c r="G486" s="5" t="n"/>
       <c r="H486" s="5" t="n"/>
-      <c r="I486" s="4" t="inlineStr">
+      <c r="I486" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -12475,7 +12475,7 @@
       <c r="F487" s="5" t="n"/>
       <c r="G487" s="5" t="n"/>
       <c r="H487" s="5" t="n"/>
-      <c r="I487" s="4" t="inlineStr">
+      <c r="I487" s="6" t="inlineStr">
         <is>
           <t>Notes / Changes - Sŵ Ni</t>
         </is>
@@ -12539,7 +12539,7 @@
       <c r="F490" s="5" t="n"/>
       <c r="G490" s="5" t="n"/>
       <c r="H490" s="5" t="n"/>
-      <c r="I490" s="6" t="inlineStr">
+      <c r="I490" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12563,7 +12563,7 @@
       <c r="F491" s="5" t="n"/>
       <c r="G491" s="5" t="n"/>
       <c r="H491" s="5" t="n"/>
-      <c r="I491" s="6" t="inlineStr">
+      <c r="I491" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12587,7 +12587,7 @@
       <c r="F492" s="5" t="n"/>
       <c r="G492" s="5" t="n"/>
       <c r="H492" s="5" t="n"/>
-      <c r="I492" s="6" t="inlineStr">
+      <c r="I492" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12611,7 +12611,7 @@
       <c r="F493" s="5" t="n"/>
       <c r="G493" s="5" t="n"/>
       <c r="H493" s="5" t="n"/>
-      <c r="I493" s="6" t="inlineStr">
+      <c r="I493" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>
@@ -12635,7 +12635,7 @@
       <c r="F494" s="5" t="n"/>
       <c r="G494" s="5" t="n"/>
       <c r="H494" s="5" t="n"/>
-      <c r="I494" s="6" t="inlineStr">
+      <c r="I494" s="4" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
         </is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -4847,7 +4847,11 @@
       </c>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="5" t="n"/>
-      <c r="D199" s="5" t="n"/>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>Sick - Sick</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n"/>
       <c r="F199" s="5" t="n"/>
       <c r="G199" s="5" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -1213,9 +1213,9 @@
           <t>Wed 19 Nov 2025</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Annual Leave</t>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="C32" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7944,7 +7944,11 @@
           <t>Film - Linda Wilson</t>
         </is>
       </c>
-      <c r="H320" s="4" t="n"/>
+      <c r="H320" s="5" t="inlineStr">
+        <is>
+          <t>Film - Rhedeg Rhacs - Aberteifi</t>
+        </is>
+      </c>
       <c r="I320" s="5" t="inlineStr">
         <is>
           <t>Record VO &amp; Title Song</t>
@@ -7968,7 +7972,7 @@
       </c>
       <c r="N320" s="5" t="inlineStr">
         <is>
-          <t>Edit - Fresh From Wales</t>
+          <t>Film - Rhedeg Rhacs - Aberteifi</t>
         </is>
       </c>
     </row>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8072,7 +8072,11 @@
       <c r="E324" s="4" t="n"/>
       <c r="F324" s="4" t="n"/>
       <c r="G324" s="4" t="n"/>
-      <c r="H324" s="4" t="n"/>
+      <c r="H324" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - HOYS</t>
+        </is>
+      </c>
       <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8072,11 +8072,7 @@
       <c r="E324" s="4" t="n"/>
       <c r="F324" s="4" t="n"/>
       <c r="G324" s="4" t="n"/>
-      <c r="H324" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - HOYS</t>
-        </is>
-      </c>
+      <c r="H324" s="4" t="n"/>
       <c r="I324" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8152,7 +8152,11 @@
       <c r="E326" s="4" t="n"/>
       <c r="F326" s="4" t="n"/>
       <c r="G326" s="4" t="n"/>
-      <c r="H326" s="4" t="n"/>
+      <c r="H326" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I326" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
@@ -8192,7 +8196,11 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="4" t="n"/>
+      <c r="H327" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="I327" s="5" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8152,11 +8152,7 @@
       <c r="E326" s="4" t="n"/>
       <c r="F326" s="4" t="n"/>
       <c r="G326" s="4" t="n"/>
-      <c r="H326" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H326" s="4" t="n"/>
       <c r="I326" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
@@ -8196,11 +8192,7 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="H327" s="4" t="n"/>
       <c r="I327" s="5" t="inlineStr">
         <is>
           <t>Sw Ni - Cont/ Prep</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8195,7 +8195,7 @@
       <c r="H327" s="4" t="n"/>
       <c r="I327" s="5" t="inlineStr">
         <is>
-          <t>Sw Ni - Cont/ Prep</t>
+          <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="J327" s="4" t="n"/>
@@ -8235,7 +8235,7 @@
       <c r="H328" s="4" t="n"/>
       <c r="I328" s="5" t="inlineStr">
         <is>
-          <t>Sw Ni - Cont/ Prep</t>
+          <t>Dub - Sŵ Ni</t>
         </is>
       </c>
       <c r="J328" s="4" t="n"/>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="I331" s="5" t="inlineStr">
         <is>
-          <t>Sw Ni - Prep</t>
+          <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="J331" s="4" t="n"/>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="I332" s="5" t="inlineStr">
         <is>
-          <t>Sw Ni - Prep</t>
+          <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="J332" s="4" t="n"/>
@@ -8373,7 +8373,11 @@
           <t>Delivery - Rookie Teachers</t>
         </is>
       </c>
-      <c r="I333" s="4" t="n"/>
+      <c r="I333" s="5" t="inlineStr">
+        <is>
+          <t>Sŵ Ni</t>
+        </is>
+      </c>
       <c r="J333" s="4" t="n"/>
       <c r="K333" s="4" t="n"/>
       <c r="L333" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -9014,7 +9014,11 @@
       <c r="F350" s="7" t="n"/>
       <c r="G350" s="7" t="n"/>
       <c r="H350" s="7" t="n"/>
-      <c r="I350" s="7" t="n"/>
+      <c r="I350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="J350" s="7" t="n"/>
       <c r="K350" s="7" t="n"/>
       <c r="L350" s="7" t="n"/>
@@ -9803,7 +9807,11 @@
       <c r="C378" s="7" t="n"/>
       <c r="D378" s="7" t="n"/>
       <c r="E378" s="7" t="n"/>
-      <c r="F378" s="7" t="n"/>
+      <c r="F378" s="5" t="inlineStr">
+        <is>
+          <t>NORTHERN STAR DEADLINE</t>
+        </is>
+      </c>
       <c r="G378" s="7" t="n"/>
       <c r="H378" s="7" t="n"/>
       <c r="I378" s="7" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8871,7 +8871,11 @@
         </is>
       </c>
       <c r="J347" s="4" t="n"/>
-      <c r="K347" s="4" t="n"/>
+      <c r="K347" s="5" t="inlineStr">
+        <is>
+          <t>Socials - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="L347" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -8930,74 +8934,57 @@
           <t>Fri 02 Oct 2026</t>
         </is>
       </c>
-      <c r="B349" s="5" t="inlineStr">
-        <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
-      <c r="C349" s="5" t="inlineStr">
-        <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
+      <c r="B349" s="4" t="n"/>
+      <c r="C349" s="4" t="n"/>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni
-Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
-      <c r="E349" s="5" t="inlineStr">
-        <is>
-          <t>Parti Dathlu S4C Athrawon</t>
-        </is>
-      </c>
+          <t>Film - Sŵ Ni</t>
+        </is>
+      </c>
+      <c r="E349" s="4" t="n"/>
       <c r="F349" s="5" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni
-Parti Dathlu S4C Athrawon</t>
+          <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
+          <t>Urban Cowboys</t>
         </is>
       </c>
       <c r="H349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
+          <t>Urban Cowboys</t>
         </is>
       </c>
       <c r="I349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon
-Film - Sŵ Ni</t>
+          <t>Film - Sŵ Ni</t>
         </is>
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
+          <t>Urban Cowboys</t>
         </is>
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
+          <t>Urban Cowboys</t>
         </is>
       </c>
       <c r="L349" s="8" t="inlineStr">
         <is>
-          <t>A/L - Annual Leave
-Parti Dathlu S4C Athrawon</t>
+          <t>A/L - Annual Leave</t>
         </is>
       </c>
       <c r="M349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon</t>
+          <t>Urban Cowboys</t>
         </is>
       </c>
       <c r="N349" s="5" t="inlineStr">
         <is>
-          <t>Parti Dathlu S4C Athrawon
-Film - Sŵ Ni</t>
+          <t>Film - Sŵ Ni</t>
         </is>
       </c>
     </row>
@@ -9007,23 +8994,55 @@
           <t>Sat 03 Oct 2026</t>
         </is>
       </c>
-      <c r="B350" s="7" t="n"/>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="C350" s="7" t="n"/>
-      <c r="D350" s="7" t="n"/>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="E350" s="7" t="n"/>
       <c r="F350" s="7" t="n"/>
-      <c r="G350" s="7" t="n"/>
-      <c r="H350" s="7" t="n"/>
+      <c r="G350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="H350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="I350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="J350" s="7" t="n"/>
-      <c r="K350" s="7" t="n"/>
+      <c r="J350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="K350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="L350" s="7" t="n"/>
-      <c r="M350" s="7" t="n"/>
-      <c r="N350" s="7" t="n"/>
+      <c r="M350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="N350" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="6" t="inlineStr">
@@ -9031,19 +9050,55 @@
           <t>Sun 04 Oct 2026</t>
         </is>
       </c>
-      <c r="B351" s="7" t="n"/>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="C351" s="7" t="n"/>
-      <c r="D351" s="7" t="n"/>
+      <c r="D351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="E351" s="7" t="n"/>
       <c r="F351" s="7" t="n"/>
-      <c r="G351" s="7" t="n"/>
-      <c r="H351" s="7" t="n"/>
-      <c r="I351" s="7" t="n"/>
-      <c r="J351" s="7" t="n"/>
-      <c r="K351" s="7" t="n"/>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="H351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="I351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="J351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="K351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
       <c r="L351" s="7" t="n"/>
-      <c r="M351" s="7" t="n"/>
-      <c r="N351" s="7" t="n"/>
+      <c r="M351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
+      <c r="N351" s="5" t="inlineStr">
+        <is>
+          <t>Urban Cowboys</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -12220,7 +12275,11 @@
       <c r="C478" s="4" t="n"/>
       <c r="D478" s="4" t="n"/>
       <c r="E478" s="4" t="n"/>
-      <c r="F478" s="4" t="n"/>
+      <c r="F478" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="G478" s="4" t="n"/>
       <c r="H478" s="4" t="n"/>
       <c r="I478" s="11" t="inlineStr">
@@ -12244,7 +12303,11 @@
       <c r="C479" s="4" t="n"/>
       <c r="D479" s="4" t="n"/>
       <c r="E479" s="4" t="n"/>
-      <c r="F479" s="4" t="n"/>
+      <c r="F479" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="G479" s="4" t="n"/>
       <c r="H479" s="4" t="n"/>
       <c r="I479" s="11" t="inlineStr">
@@ -12268,7 +12331,11 @@
       <c r="C480" s="4" t="n"/>
       <c r="D480" s="4" t="n"/>
       <c r="E480" s="4" t="n"/>
-      <c r="F480" s="4" t="n"/>
+      <c r="F480" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="G480" s="4" t="n"/>
       <c r="H480" s="4" t="n"/>
       <c r="I480" s="11" t="inlineStr">
@@ -12292,7 +12359,11 @@
       <c r="C481" s="4" t="n"/>
       <c r="D481" s="4" t="n"/>
       <c r="E481" s="4" t="n"/>
-      <c r="F481" s="4" t="n"/>
+      <c r="F481" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="G481" s="4" t="n"/>
       <c r="H481" s="4" t="n"/>
       <c r="I481" s="11" t="inlineStr">
@@ -12320,7 +12391,11 @@
       <c r="C482" s="4" t="n"/>
       <c r="D482" s="4" t="n"/>
       <c r="E482" s="4" t="n"/>
-      <c r="F482" s="4" t="n"/>
+      <c r="F482" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="G482" s="4" t="n"/>
       <c r="H482" s="4" t="n"/>
       <c r="I482" s="11" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8870,7 +8870,11 @@
           <t>Film - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J347" s="4" t="n"/>
+      <c r="J347" s="5" t="inlineStr">
+        <is>
+          <t>SOCIAL MEDIA CONFERENCE</t>
+        </is>
+      </c>
       <c r="K347" s="5" t="inlineStr">
         <is>
           <t>Socials - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8112,7 +8112,11 @@
       <c r="E325" s="4" t="n"/>
       <c r="F325" s="4" t="n"/>
       <c r="G325" s="4" t="n"/>
-      <c r="H325" s="4" t="n"/>
+      <c r="H325" s="5" t="inlineStr">
+        <is>
+          <t>Edit - GFX - EP 5</t>
+        </is>
+      </c>
       <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
@@ -8192,7 +8196,11 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="4" t="n"/>
+      <c r="H327" s="5" t="inlineStr">
+        <is>
+          <t>Edit - GFX - EP 5</t>
+        </is>
+      </c>
       <c r="I327" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8232,7 +8240,11 @@
       <c r="E328" s="4" t="n"/>
       <c r="F328" s="4" t="n"/>
       <c r="G328" s="4" t="n"/>
-      <c r="H328" s="4" t="n"/>
+      <c r="H328" s="5" t="inlineStr">
+        <is>
+          <t>Edit - GFX - EP 5</t>
+        </is>
+      </c>
       <c r="I328" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8196,9 +8196,10 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="5" t="inlineStr">
-        <is>
-          <t>Edit - GFX - EP 5</t>
+      <c r="H327" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave
+Edit - GFX - EP 5</t>
         </is>
       </c>
       <c r="I327" s="5" t="inlineStr">
@@ -8240,9 +8241,10 @@
       <c r="E328" s="4" t="n"/>
       <c r="F328" s="4" t="n"/>
       <c r="G328" s="4" t="n"/>
-      <c r="H328" s="5" t="inlineStr">
-        <is>
-          <t>Edit - GFX - EP 5</t>
+      <c r="H328" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave
+Edit - GFX - EP 5</t>
         </is>
       </c>
       <c r="I328" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8196,10 +8196,9 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave
-Edit - GFX - EP 5</t>
+      <c r="H327" s="5" t="inlineStr">
+        <is>
+          <t>Edit - GFX - EP 5</t>
         </is>
       </c>
       <c r="I327" s="5" t="inlineStr">
@@ -8241,10 +8240,9 @@
       <c r="E328" s="4" t="n"/>
       <c r="F328" s="4" t="n"/>
       <c r="G328" s="4" t="n"/>
-      <c r="H328" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave
-Edit - GFX - EP 5</t>
+      <c r="H328" s="5" t="inlineStr">
+        <is>
+          <t>Edit - GFX - EP 5</t>
         </is>
       </c>
       <c r="I328" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8238,7 +8238,11 @@
       <c r="C328" s="4" t="n"/>
       <c r="D328" s="4" t="n"/>
       <c r="E328" s="4" t="n"/>
-      <c r="F328" s="4" t="n"/>
+      <c r="F328" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lleisio Sw Ni </t>
+        </is>
+      </c>
       <c r="G328" s="4" t="n"/>
       <c r="H328" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8324,11 +8324,7 @@
       <c r="E331" s="4" t="n"/>
       <c r="F331" s="4" t="n"/>
       <c r="G331" s="4" t="n"/>
-      <c r="H331" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="H331" s="4" t="n"/>
       <c r="I331" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8358,7 +8354,8 @@
       <c r="G332" s="4" t="n"/>
       <c r="H332" s="9" t="inlineStr">
         <is>
-          <t>Delivery - Sŵ Ni</t>
+          <t>Delivery - Sŵ Ni
+Delivery - Sŵ Ni</t>
         </is>
       </c>
       <c r="I332" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8112,11 +8112,7 @@
       <c r="E325" s="4" t="n"/>
       <c r="F325" s="4" t="n"/>
       <c r="G325" s="4" t="n"/>
-      <c r="H325" s="5" t="inlineStr">
-        <is>
-          <t>Edit - GFX - EP 5</t>
-        </is>
-      </c>
+      <c r="H325" s="4" t="n"/>
       <c r="I325" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>
@@ -8196,11 +8192,7 @@
       <c r="E327" s="4" t="n"/>
       <c r="F327" s="4" t="n"/>
       <c r="G327" s="4" t="n"/>
-      <c r="H327" s="5" t="inlineStr">
-        <is>
-          <t>Edit - GFX - EP 5</t>
-        </is>
-      </c>
+      <c r="H327" s="4" t="n"/>
       <c r="I327" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
@@ -8244,11 +8236,7 @@
         </is>
       </c>
       <c r="G328" s="4" t="n"/>
-      <c r="H328" s="5" t="inlineStr">
-        <is>
-          <t>Edit - GFX - EP 5</t>
-        </is>
-      </c>
+      <c r="H328" s="4" t="n"/>
       <c r="I328" s="5" t="inlineStr">
         <is>
           <t>Dub - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8312,14 +8312,22 @@
       <c r="E331" s="4" t="n"/>
       <c r="F331" s="4" t="n"/>
       <c r="G331" s="4" t="n"/>
-      <c r="H331" s="4" t="n"/>
+      <c r="H331" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Sŵ Ni</t>
+        </is>
+      </c>
       <c r="I331" s="5" t="inlineStr">
         <is>
           <t>Sŵ Ni</t>
         </is>
       </c>
       <c r="J331" s="4" t="n"/>
-      <c r="K331" s="4" t="n"/>
+      <c r="K331" s="5" t="inlineStr">
+        <is>
+          <t>Rhwym Galon</t>
+        </is>
+      </c>
       <c r="L331" s="4" t="n"/>
       <c r="M331" s="4" t="n"/>
       <c r="N331" s="10" t="inlineStr">
@@ -8342,8 +8350,7 @@
       <c r="G332" s="4" t="n"/>
       <c r="H332" s="9" t="inlineStr">
         <is>
-          <t>Delivery - Sŵ Ni
-Delivery - Sŵ Ni</t>
+          <t>Delivery - Sŵ Ni</t>
         </is>
       </c>
       <c r="I332" s="5" t="inlineStr">
@@ -8352,7 +8359,11 @@
         </is>
       </c>
       <c r="J332" s="4" t="n"/>
-      <c r="K332" s="4" t="n"/>
+      <c r="K332" s="5" t="inlineStr">
+        <is>
+          <t>Rhwym Galon</t>
+        </is>
+      </c>
       <c r="L332" s="4" t="n"/>
       <c r="M332" s="4" t="n"/>
       <c r="N332" s="4" t="n"/>
@@ -8380,7 +8391,11 @@
         </is>
       </c>
       <c r="J333" s="4" t="n"/>
-      <c r="K333" s="4" t="n"/>
+      <c r="K333" s="5" t="inlineStr">
+        <is>
+          <t>Rhwym Galon</t>
+        </is>
+      </c>
       <c r="L333" s="4" t="n"/>
       <c r="M333" s="4" t="n"/>
       <c r="N333" s="4" t="n"/>
@@ -8412,7 +8427,11 @@
         </is>
       </c>
       <c r="J334" s="4" t="n"/>
-      <c r="K334" s="4" t="n"/>
+      <c r="K334" s="5" t="inlineStr">
+        <is>
+          <t>Rhwym Galon</t>
+        </is>
+      </c>
       <c r="L334" s="4" t="n"/>
       <c r="M334" s="4" t="n"/>
       <c r="N334" s="5" t="inlineStr">
@@ -8448,7 +8467,11 @@
         </is>
       </c>
       <c r="J335" s="4" t="n"/>
-      <c r="K335" s="4" t="n"/>
+      <c r="K335" s="5" t="inlineStr">
+        <is>
+          <t>Rhwym Galon</t>
+        </is>
+      </c>
       <c r="L335" s="4" t="n"/>
       <c r="M335" s="4" t="n"/>
       <c r="N335" s="5" t="inlineStr">
@@ -9037,7 +9060,11 @@
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="L350" s="7" t="n"/>
+      <c r="L350" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="M350" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>
@@ -9093,7 +9120,11 @@
           <t>Urban Cowboys</t>
         </is>
       </c>
-      <c r="L351" s="7" t="n"/>
+      <c r="L351" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
       <c r="M351" s="5" t="inlineStr">
         <is>
           <t>Urban Cowboys</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7992,7 +7992,11 @@
       <c r="E321" s="4" t="n"/>
       <c r="F321" s="4" t="n"/>
       <c r="G321" s="4" t="n"/>
-      <c r="H321" s="4" t="n"/>
+      <c r="H321" s="5" t="inlineStr">
+        <is>
+          <t>Sick</t>
+        </is>
+      </c>
       <c r="I321" s="11" t="inlineStr">
         <is>
           <t>Online Edit - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8230,7 +8230,11 @@
           <t>Fri 11 Sep 2026</t>
         </is>
       </c>
-      <c r="B328" s="4" t="n"/>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>Rookie Teachers</t>
+        </is>
+      </c>
       <c r="C328" s="4" t="n"/>
       <c r="D328" s="4" t="n"/>
       <c r="E328" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8205,7 +8205,7 @@
       <c r="J327" s="4" t="n"/>
       <c r="K327" s="5" t="inlineStr">
         <is>
-          <t>Hansh Socials</t>
+          <t>Rookie Teachers</t>
         </is>
       </c>
       <c r="L327" s="5" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8205,7 +8205,7 @@
       <c r="J327" s="4" t="n"/>
       <c r="K327" s="5" t="inlineStr">
         <is>
-          <t>Hansh Socials</t>
+          <t>Rookie Teachers</t>
         </is>
       </c>
       <c r="L327" s="5" t="inlineStr">
@@ -8251,7 +8251,11 @@
         </is>
       </c>
       <c r="J328" s="4" t="n"/>
-      <c r="K328" s="4" t="n"/>
+      <c r="K328" s="5" t="inlineStr">
+        <is>
+          <t>Rookie Teachers</t>
+        </is>
+      </c>
       <c r="L328" s="5" t="inlineStr">
         <is>
           <t>Film - Black History 2026</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -7603,7 +7603,11 @@
           <t>Pre-Production - Black History 2026</t>
         </is>
       </c>
-      <c r="K312" s="4" t="n"/>
+      <c r="K312" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L312" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
@@ -7659,7 +7663,11 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K313" s="4" t="n"/>
+      <c r="K313" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
           <t>Pre-Production - Black History 2026</t>
@@ -7711,7 +7719,11 @@
           <t>Datblygu</t>
         </is>
       </c>
-      <c r="K314" s="4" t="n"/>
+      <c r="K314" s="8" t="inlineStr">
+        <is>
+          <t>A/L - Annual Leave</t>
+        </is>
+      </c>
       <c r="L314" s="5" t="inlineStr">
         <is>
           <t>Black History 2026</t>
@@ -8823,11 +8835,7 @@
         </is>
       </c>
       <c r="J345" s="4" t="n"/>
-      <c r="K345" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="K345" s="4" t="n"/>
       <c r="L345" s="4" t="n"/>
       <c r="M345" s="8" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8647,7 +8647,11 @@
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G340" s="4" t="n"/>
+      <c r="G340" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ffilmio Mabli </t>
+        </is>
+      </c>
       <c r="H340" s="4" t="n"/>
       <c r="I340" s="5" t="inlineStr">
         <is>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8202,7 +8202,11 @@
           <t>Thu 10 Sep 2026</t>
         </is>
       </c>
-      <c r="B327" s="4" t="n"/>
+      <c r="B327" s="5" t="inlineStr">
+        <is>
+          <t>Beth Toil</t>
+        </is>
+      </c>
       <c r="C327" s="4" t="n"/>
       <c r="D327" s="4" t="n"/>
       <c r="E327" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8202,9 +8202,9 @@
           <t>Thu 10 Sep 2026</t>
         </is>
       </c>
-      <c r="B327" s="5" t="inlineStr">
-        <is>
-          <t>Beth Toil</t>
+      <c r="B327" s="10" t="inlineStr">
+        <is>
+          <t>TOIL - Beth Toil</t>
         </is>
       </c>
       <c r="C327" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8324,7 +8324,11 @@
       <c r="I330" s="7" t="n"/>
       <c r="J330" s="7" t="n"/>
       <c r="K330" s="7" t="n"/>
-      <c r="L330" s="7" t="n"/>
+      <c r="L330" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M330" s="7" t="n"/>
       <c r="N330" s="7" t="n"/>
     </row>
@@ -8461,7 +8465,11 @@
         </is>
       </c>
       <c r="L334" s="4" t="n"/>
-      <c r="M334" s="4" t="n"/>
+      <c r="M334" s="5" t="inlineStr">
+        <is>
+          <t>Rhodri p/up Cyfranwyr</t>
+        </is>
+      </c>
       <c r="N334" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8698,20 +8698,16 @@
       <c r="C341" s="4" t="n"/>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni</t>
+          <t>Prep Sw Ni</t>
         </is>
       </c>
       <c r="E341" s="4" t="n"/>
-      <c r="F341" s="5" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="F341" s="4" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="4" t="n"/>
       <c r="I341" s="5" t="inlineStr">
         <is>
-          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+          <t>Prep Sw Ni MP</t>
         </is>
       </c>
       <c r="J341" s="4" t="n"/>
@@ -8726,11 +8722,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N341" s="5" t="inlineStr">
-        <is>
-          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
-        </is>
-      </c>
+      <c r="N341" s="4" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -8742,15 +8734,11 @@
       <c r="C342" s="4" t="n"/>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Film - Sŵ Ni</t>
+          <t>Prep Sw Ni</t>
         </is>
       </c>
       <c r="E342" s="4" t="n"/>
-      <c r="F342" s="5" t="inlineStr">
-        <is>
-          <t>Film - Sŵ Ni</t>
-        </is>
-      </c>
+      <c r="F342" s="4" t="n"/>
       <c r="G342" s="4" t="n"/>
       <c r="H342" s="9" t="inlineStr">
         <is>
@@ -8759,7 +8747,7 @@
       </c>
       <c r="I342" s="5" t="inlineStr">
         <is>
-          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
+          <t>Film - Prep Sw Ni MP</t>
         </is>
       </c>
       <c r="J342" s="4" t="n"/>
@@ -8774,11 +8762,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N342" s="5" t="inlineStr">
-        <is>
-          <t>Film - Sw Ni / Mabli a Ceff Ceff Cont</t>
-        </is>
-      </c>
+      <c r="N342" s="4" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ffilmio Mabli </t>
+          <t>Ffilmio Mabli - AM</t>
         </is>
       </c>
       <c r="H340" s="4" t="n"/>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8615,7 +8615,11 @@
           <t>Film - Mabli a Ceff Ceff</t>
         </is>
       </c>
-      <c r="G339" s="4" t="n"/>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>Film - Linda Wilson</t>
+        </is>
+      </c>
       <c r="H339" s="4" t="n"/>
       <c r="I339" s="5" t="inlineStr">
         <is>
@@ -8739,7 +8743,11 @@
       </c>
       <c r="E342" s="4" t="n"/>
       <c r="F342" s="4" t="n"/>
-      <c r="G342" s="4" t="n"/>
+      <c r="G342" s="5" t="inlineStr">
+        <is>
+          <t>Film - Linda Wilson</t>
+        </is>
+      </c>
       <c r="H342" s="9" t="inlineStr">
         <is>
           <t>Delivery - Rookie Teachers</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8110,11 +8110,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N324" s="5" t="inlineStr">
-        <is>
-          <t>Film - Black History 2026</t>
-        </is>
-      </c>
+      <c r="N324" s="4" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -8150,11 +8146,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N325" s="5" t="inlineStr">
-        <is>
-          <t>Film - Black History 2026</t>
-        </is>
-      </c>
+      <c r="N325" s="4" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -8190,11 +8182,7 @@
           <t>A/L - Annual Leave</t>
         </is>
       </c>
-      <c r="N326" s="5" t="inlineStr">
-        <is>
-          <t>Film - Black History 2026</t>
-        </is>
-      </c>
+      <c r="N326" s="4" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8571,11 +8571,7 @@
         </is>
       </c>
       <c r="J338" s="4" t="n"/>
-      <c r="K338" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="K338" s="4" t="n"/>
       <c r="L338" s="4" t="n"/>
       <c r="M338" s="4" t="n"/>
       <c r="N338" s="5" t="inlineStr">
@@ -8615,11 +8611,7 @@
         </is>
       </c>
       <c r="J339" s="4" t="n"/>
-      <c r="K339" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="K339" s="4" t="n"/>
       <c r="L339" s="4" t="n"/>
       <c r="M339" s="8" t="inlineStr">
         <is>
@@ -8665,7 +8657,7 @@
       <c r="J340" s="4" t="n"/>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>Edit - Black History 2026</t>
+          <t>Socials - Sŵ Ni</t>
         </is>
       </c>
       <c r="L340" s="4" t="n"/>
@@ -8703,11 +8695,7 @@
         </is>
       </c>
       <c r="J341" s="4" t="n"/>
-      <c r="K341" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="K341" s="4" t="n"/>
       <c r="L341" s="4" t="n"/>
       <c r="M341" s="8" t="inlineStr">
         <is>
@@ -8747,11 +8735,7 @@
         </is>
       </c>
       <c r="J342" s="4" t="n"/>
-      <c r="K342" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="K342" s="4" t="n"/>
       <c r="L342" s="4" t="n"/>
       <c r="M342" s="8" t="inlineStr">
         <is>
@@ -8831,7 +8815,11 @@
         </is>
       </c>
       <c r="J345" s="4" t="n"/>
-      <c r="K345" s="4" t="n"/>
+      <c r="K345" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="L345" s="4" t="n"/>
       <c r="M345" s="8" t="inlineStr">
         <is>
@@ -8871,7 +8859,11 @@
         </is>
       </c>
       <c r="J346" s="4" t="n"/>
-      <c r="K346" s="4" t="n"/>
+      <c r="K346" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="L346" s="4" t="n"/>
       <c r="M346" s="8" t="inlineStr">
         <is>
@@ -8917,7 +8909,7 @@
       </c>
       <c r="K347" s="5" t="inlineStr">
         <is>
-          <t>Socials - Sŵ Ni</t>
+          <t>Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L347" s="8" t="inlineStr">
@@ -8959,7 +8951,11 @@
         </is>
       </c>
       <c r="J348" s="4" t="n"/>
-      <c r="K348" s="4" t="n"/>
+      <c r="K348" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="L348" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>
@@ -9013,7 +9009,8 @@
       </c>
       <c r="K349" s="5" t="inlineStr">
         <is>
-          <t>Urban Cowboys</t>
+          <t>Urban Cowboys
+Edit - Black History 2026</t>
         </is>
       </c>
       <c r="L349" s="8" t="inlineStr">
@@ -9167,7 +9164,11 @@
       <c r="H352" s="4" t="n"/>
       <c r="I352" s="4" t="n"/>
       <c r="J352" s="4" t="n"/>
-      <c r="K352" s="4" t="n"/>
+      <c r="K352" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="L352" s="8" t="inlineStr">
         <is>
           <t>A/L - Annual Leave</t>

--- a/docs/schedule-grid-3bba0646.xlsx
+++ b/docs/schedule-grid-3bba0646.xlsx
@@ -8312,11 +8312,7 @@
       <c r="I330" s="7" t="n"/>
       <c r="J330" s="7" t="n"/>
       <c r="K330" s="7" t="n"/>
-      <c r="L330" s="5" t="inlineStr">
-        <is>
-          <t>Edit - Black History 2026</t>
-        </is>
-      </c>
+      <c r="L330" s="7" t="n"/>
       <c r="M330" s="7" t="n"/>
       <c r="N330" s="7" t="n"/>
     </row>
@@ -8348,7 +8344,11 @@
           <t>Rhwym Galon</t>
         </is>
       </c>
-      <c r="L331" s="4" t="n"/>
+      <c r="L331" s="5" t="inlineStr">
+        <is>
+          <t>Edit - Black History 2026</t>
+        </is>
+      </c>
       <c r="M331" s="4" t="n"/>
       <c r="N331" s="10" t="inlineStr">
         <is>
@@ -8804,11 +8804,7 @@
         </is>
       </c>
       <c r="G345" s="4" t="n"/>
-      <c r="H345" s="9" t="inlineStr">
-        <is>
-          <t>Delivery - Black History 2026</t>
-        </is>
-      </c>
+      <c r="H345" s="4" t="n"/>
       <c r="I345" s="5" t="inlineStr">
         <is>
           <t>Film - Sŵ Ni</t>
@@ -9161,7 +9157,11 @@
       <c r="E352" s="4" t="n"/>
       <c r="F352" s="4" t="n"/>
       <c r="G352" s="4" t="n"/>
-      <c r="H352" s="4" t="n"/>
+      <c r="H352" s="9" t="inlineStr">
+        <is>
+          <t>Delivery - Black History 2026</t>
+        </is>
+      </c>
       <c r="I352" s="4" t="n"/>
       <c r="J352" s="4" t="n"/>
       <c r="K352" s="5" t="inlineStr">
@@ -9219,11 +9219,7 @@
           <t>Offline Edit - Sŵ Ni</t>
         </is>
       </c>
-      <c r="J354" s="8" t="inlineStr">
-        <is>
-          <t>A/L - Annual Leave</t>
-        </is>
-      </c>
+      <c r="J354" s="4" t="n"/>
       <c r="K354" s="4" t="n"/>
       <c r="L354" s="8" t="inlineStr">
         <is>
